--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -416,13 +416,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="57" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -816,22 +816,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mota-Engil México (con Duro Felguera)</t>
+          <t>Mota-Engil México (EPC confirmado; plazo de construcción 33 meses)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ingeniería/desarrollo</t>
+          <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/oilandgas/news/pemex-advances-escolin-fertilizer-plant-semarnat-filing)</t>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -969,17 +969,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción (cerca de terminar; op. comercial H1 2027)</t>
+          <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/project-profile/topolobampo-ammonia-plant-proman-gpo)</t>
+          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sandpiper Chemicals, LLC (INEOS Acetyls, socio ancla)</t>
+          <t>Sandpiper Chemicals, LLC (INEOS Acetyls tomó participación accionaria)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1117,237 +1117,459 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED, Q2 2026) / FID prevista 2027</t>
+          <t>Ingeniería (FEED en curso, 2T2026) / FID prevista 2027</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[INEOS](https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
+          <t>[Alchempro](https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Iron Mesa (planta de gas)</t>
+          <t>OXEA Bay City Capacity Expansion + Air Liquide POX Syngas Unit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Goldsmith, Ector County, Texas, EE.UU.</t>
+          <t>Bay City, Matagorda County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>OXEA (oxo chemicals) / Air Liquide (unidad de syngas)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Air Liquide (unidad propia); OXEA no especificado</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Construcción (arranque previsto Q1 2027)</t>
+          <t>Construcción (FID confirmado 13-jul-2026; preparación de sitio 3T2026; finalización fines de 2028)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yeti II (planta de gas)</t>
+          <t>Targa Resources East Driver Gas Processing Plant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
+          <t>Condado de Midland, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
+          <t>Construcción (planta criogénica 275 MMcf/d; arranque previsto 3T2026)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Refinería Francisco I. Madero (rehabilitación)</t>
+          <t>Enterprise Products "Athena" Natural Gas Processing Plant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ciudad Madero, Tamaulipas, México</t>
+          <t>Cuenca Midland (cuatro condados), Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pemex</t>
+          <t>Enterprise Products Partners L.P.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
+          <t>Enterprise Products (propietario-constructor)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Licitación/bidding</t>
+          <t>Construcción (300 MMcf/d + hasta 40,000 bpd de NGLs; en servicio 4T2026)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fermachem Planta de Urea/Amoniaco</t>
+          <t>MPLX Secretariat II Gas Processing Plant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ejido Sapioris, Lerdo, Durango, México</t>
+          <t>Cuenca Pérmica (subcuenca Delaware), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fermaca Dreams (Fermachem)</t>
+          <t>MPLX LP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
+          <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Construcción (ejecución iniciada jun-2026)</t>
+          <t>Planeada/desarrollo (300 MMcf/d; en servicio 2S2028)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
+          <t>MPLX Titan Complex (Northwind) — Expansión de Tratamiento de Gas Amargo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
+          <t>Condado de Lea, Nuevo México / frontera TX-NM, EE.UU.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clean Hydrogen Works</t>
+          <t>MPLX LP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>McDermott (FEED)</t>
+          <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED) / Pre-FID</t>
+          <t>Construcción (expansión de capacidad &gt;400 MMcf/d; plenamente operativo 4T2026)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Northern Plains Nitrogen (urea/amoniaco)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Grand Forks, Dakota del Norte, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Northern Plains Nitrogen LLC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EPC no designado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pre-FEED completo / FID buscada 4T2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Iron Mesa (planta de gas)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Goldsmith, Ector County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Construcción (arranque previsto Q1 2027)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Yeti II (planta de gas)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Targa Resources</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Refinería Francisco I. Madero (rehabilitación)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ciudad Madero, Tamaulipas, México</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pemex</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Licitación/bidding</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fermachem Planta de Urea/Amoniaco</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ejido Sapioris, Lerdo, Durango, México</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fermaca Dreams (Fermachem)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Construcción (ejecución iniciada jun-2026)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Clean Hydrogen Works</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>McDermott (FEED)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ingeniería (FEED) / Pre-FID</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Zeus Gas Plant + 3ra Fraccionadora Coastal Bend</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, Texas / Robstown, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>No especificado</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Ingeniería (sancionado; en línea 2028)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
@@ -1364,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1806,17 +2028,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Construcción (NTP limitado; USD 500M de inversión de HPS Investment Partners/BlackRock asegurados, paso previo a FID)</t>
+          <t>Construcción (LNTP otorgado a Kiewit 4-jul-2026 para compra de equipo de entrega larga, ingeniería EPC y geotécnico; FID prevista fin de 2026)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/pipelines-transportation/lng/news/55390720/glenfarne-group-secures-500-million-for-texas-lng-development)</t>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/lng/news/55388908/texas-lng-advances-pre-fid-project-with-limited-notice-to-proceed)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -1860,17 +2082,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Energía Costa Azul (ECA LNG) Fase 2</t>
+          <t>Galveston LNG (Pelican Island)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ensenada, Baja California, México</t>
+          <t>Isla Pelican, Galveston, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sempra Infrastructure / TotalEnergies</t>
+          <t>Power LNG Ventures, LLC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1880,49 +2102,49 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ingeniería/Pre-FID (Fase 1 operando desde jul-2026)</t>
+          <t>Permitting temprano (arrendamiento preliminar de 30 acres con Galveston Wharves; solicitud federal de exportación presentada; producción prevista dic-2028)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
+          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gato Negro LNG</t>
+          <t>Energía Costa Azul (ECA LNG) Fase 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manzanillo, Colima, México</t>
+          <t>Ensenada, Baja California, México</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Big River Energy</t>
+          <t>Sempra Infrastructure / TotalEnergies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Samsung E&amp;A (ingeniería)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pre-FID (retrasado a fines de 2027)</t>
+          <t>Ingeniería/Pre-FID (Fase 1 operando desde jul-2026)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
+          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1934,106 +2156,106 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amigo LNG (FLNG)</t>
+          <t>Gato Negro LNG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guaymas, Sonora, México</t>
+          <t>Manzanillo, Colima, México</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amigo LNG (Epsilon LNG / LNG Alliance)</t>
+          <t>Big River Energy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Drydocks World (EPC de barcazas FLNG)</t>
+          <t>Samsung E&amp;A (ingeniería)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Construcción (conversión de FSU y fabricación de barcazas en Dubái; operación prevista 2a mitad 2028)</t>
+          <t>Pre-FID (retrasado a fines de 2027)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
+          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coastal Bend LNG</t>
+          <t>Amigo LNG (FLNG)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ingleside, Texas, EE.UU.</t>
+          <t>Guaymas, Sonora, México</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Coastal Bend LNG (Kyomera Ventures/Amirian Group)</t>
+          <t>Amigo LNG (Epsilon LNG / LNG Alliance)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KBR + Técnicas Reunidas (FEED)</t>
+          <t>Drydocks World (EPC de barcazas FLNG)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED)</t>
+          <t>Construcción (conversión de FSU y fabricación de barcazas en Dubái; operación prevista 2a mitad 2028)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gulfstream LNG</t>
+          <t>Coastal Bend LNG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Plaquemines Parish, Luisiana, EE.UU.</t>
+          <t>Ingleside, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gulfstream LNG Development LLC</t>
+          <t>Coastal Bend LNG (Kyomera Ventures/Amirian Group)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>KBR + Técnicas Reunidas (FEED)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pre-FID (trámite FERC, docket CP25-519)</t>
+          <t>Ingeniería (FEED)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
+          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2045,17 +2267,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaska LNG (Fase 1: gasoducto + terminal Nikiski)</t>
+          <t>Gulfstream LNG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>North Slope a Nikiski, Alaska, EE.UU.</t>
+          <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Glenfarne Group / Alaska Gasline Development Corp</t>
+          <t>Gulfstream LNG Development LLC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2065,12 +2287,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pre-FID (avanzando hacia cierre financiero)</t>
+          <t>Pre-FID (trámite FERC, docket CP25-519)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[Glenfarne](https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
+          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2082,17 +2304,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gasoducto Naco–Guaymas (alimenta Amigo LNG)</t>
+          <t>Alaska LNG (Fase 1: gasoducto + terminal Nikiski)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Naco (frontera Sonora/Arizona) a Guaymas, Sonora, México</t>
+          <t>North Slope a Nikiski, Alaska, EE.UU.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cenagas / LNG Alliance</t>
+          <t>Glenfarne Group / Alaska Gasline Development Corp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2102,12 +2324,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ingeniería/pre-construcción (inicio de obra previsto próximos meses)</t>
+          <t>Pre-FID (avanzando hacia cierre financiero)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/news/mexico-advances-us28bn-sonora-gas-pipeline)</t>
+          <t>[Glenfarne](https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2119,17 +2341,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gasoducto Mustang Express (alimenta Port Arthur LNG Fase 2)</t>
+          <t>Gasoducto Naco–Guaymas (alimenta Amigo LNG)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Katy a Port Arthur, Texas, EE.UU.</t>
+          <t>Naco (frontera Sonora/Arizona) a Guaymas, Sonora, México</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARM Energy Holdings / PIMCO</t>
+          <t>Cenagas / LNG Alliance / Freedom LNG LLC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2139,49 +2361,49 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Construcción (FID alcanzada)</t>
+          <t>Ingeniería/pre-construcción (ceremonia binacional México-EE.UU. 25-jun-2026 formaliza avance del "Sonora Energy Corridor", 500km/US$2.8bn; aún sin FID)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PODEBI Coatzacoalcos II (planta LNG)</t>
+          <t>Gasoducto Mustang Express (alimenta Port Arthur LNG Fase 2)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Villa Allende, Coatzacoalcos, Veracruz, México</t>
+          <t>Katy a Port Arthur, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ursus Energy</t>
+          <t>ARM Energy Holdings / PIMCO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Samsung E&amp;A (FEED+EPC); Honeywell (tecnología)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ingeniería (transición a obra civil, verano 2026)</t>
+          <t>Construcción (FID alcanzada)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Gobierno de Veracruz](https://www.veracruz.gob.mx/2026/07/13/confianza-en-veracruz-atrae-proyecto-energetico-de-mas-de-2-mil-millones-de-dolares/)</t>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2193,69 +2415,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Delfin FLNG2 (segundo buque FLNG)</t>
+          <t>PODEBI Coatzacoalcos II (planta LNG)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Golfo de México, costa afuera de Luisiana, EE.UU.</t>
+          <t>Villa Allende, Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Delfin Midstream / MidOcean Energy (EIG)</t>
+          <t>Ursus Energy</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Siemens Energy (LNTP para equipo de largo plazo)</t>
+          <t>Samsung E&amp;A (FEED+EPC); Honeywell (tecnología)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pre-FID (LNTP emitido; FID prevista para fines de 2026)</t>
+          <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; primer desembolso de US$100M previsto fines de jul-2026; transición a obra civil, verano 2026)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gasoducto Texas Gateway (alimenta terminales LNG del Golfo)</t>
+          <t>Delfin FLNG2 (segundo buque FLNG)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Carthage, Texas a Beauregard Parish, Luisiana, EE.UU.</t>
+          <t>Golfo de México, costa afuera de Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gulf South Pipeline Company (Boardwalk Pipelines)</t>
+          <t>Delfin Midstream / MidOcean Energy (EIG)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Siemens Energy (LNTP para equipo de largo plazo)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Open season vinculante (hasta 8-dic-2026) / FAST-41; en servicio previsto nov-2029</t>
+          <t>Pre-FID (LNTP emitido; FID prevista para fines de 2026)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2267,72 +2489,109 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argent LNG (Port Fourchon)</t>
+          <t>Gasoducto Texas Gateway (alimenta terminales LNG del Golfo)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Port Fourchon, Lafourche Parish, Luisiana, EE.UU.</t>
+          <t>Carthage, Texas a Beauregard Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argent LNG</t>
+          <t>Gulf South Pipeline Company (Boardwalk Pipelines)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Baker Hughes (tecnología modular NMBL); GIS Engineering (ingeniería de sitio)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ingeniería/Pre-FID (permitting FERC/DOE en curso; inicio de construcción previsto 2026)</t>
+          <t>Open season vinculante (hasta 8-dic-2026) / FAST-41; en servicio previsto nov-2029</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[World Oil](https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Argent LNG (Port Fourchon)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Port Fourchon, Lafourche Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Argent LNG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Baker Hughes (tecnología modular NMBL); GIS Engineering (ingeniería marina/ambiental/de sitio, contrato ampliado)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ingeniería/Pre-FID (permitting FERC/DOE en curso para terminal de 25 MMtpa; inicio de construcción previsto 2026)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[World Oil](https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>ST LNG Deepwater Port</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Costa afuera de Matagorda, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>ST LNG, LLC</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Permitting/Pre-FID (Draft EIS publicado abr-2026)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>[Federal Register](https://www.federalregister.gov/documents/2026/04/17/2026-07517/deepwater-port-license-application-st-lng-deepwater-port-development-project-draft-environmental)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
@@ -2349,11 +2608,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="56" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -3013,17 +3272,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ingeniería completa/listo para construcción</t>
+          <t>Ingeniería completa/permisado a nivel estatal; inicio de construcción retrasado de 2026 a 1T2027 (complicaciones de suministro de agua y derecho de vía)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[U.S. Gold Corp](https://www.usgoldcorp.com/properties/ck-gold-project/overview)</t>
+          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3161,17 +3420,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Permitting (aceptado en programa federal FAST-41; solicitud de permiso Clean Water Act Sección 404 presentada abr-2026)</t>
+          <t>Permitting (cronograma coordinado de permisos federales/estatales publicado 16-jul-2026; revisión ambiental integrada de 29 meses liderada por USACE; ROD objetivo sep-2028)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-acceptance-of-alaskas-high-grade-arctic-copper-zinc-lead-gold-silver-project-into-the-fast-41-federal-permitting-program-302773296.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3283,6 +3542,154 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Orisyvo Project</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sierra Madre (Rarámuri), Chihuahua, México</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fresnillo plc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pre-feasibility (transicionando a feasibility, resultados esperados medio 2026)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Planta de Separación de Tierras Raras (US Army)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tooele Army Depot, Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>REalloys Inc.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Planta de Purificación de Grafito (US Army)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pine Bluff Arsenal, Arkansas o Anniston Army Depot, Alabama (sin confirmar), EE.UU.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Titan Mining Corp.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Plantas de Litio y Boro (US Army)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Base militar de EE.UU. sin confirmar</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EnergyX (litio) / ioneer Ltd. (boro)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Acuerdo firmado/planeación (construcción prevista desde 2027; producción 2028)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3297,11 +3704,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="57" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -3475,22 +3882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chevron (suministro de gas 20 años); turbinas GE Vernova/Caterpillar</t>
+          <t>Chevron + Engine No. 1 (suministro de gas 20 años, sitio &gt;2,000 acres); turbinas GE Vernova/Caterpillar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ingeniería avanzada/Construcción temprana</t>
+          <t>Ingeniería avanzada/Construcción temprana (capacidad rampa a 2.67GW; planta operativa 2028; FID de la planta esperada fines de 2026)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[TechCrunch](https://techcrunch.com/2026/06/22/microsoft-and-chevron-plan-one-of-the-largest-gas-powered-data-center-projects-in-us/)</t>
+          <t>[CNBC](https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3517,17 +3924,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Permisos/preparación de sitio (fase final; 200MW iniciales asegurados; operación prevista Q2 2027)</t>
+          <t>Permisos/preparación de sitio (confirmado oficialmente por gobierno federal 7-jul-2026 bajo Plan México; inversión US$4,800M, 52 hectáreas, 900MW; subestación propia de 2GW prevista Q2 2027)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/trade-and-investment/news/cloudhq-invests-us48-billion-queretaros-data-center-campus)</t>
+          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3850,17 +4257,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción activa</t>
+          <t>Construcción activa (confirmado como sitio oficial Stargate; BLM aprobó derecho de vía del gasoducto "Green Chile" de Energy Transfer, 17.7 millas/US$60M)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Oracle](https://www.oracle.com/news/announcement/oracle-borderplex-and-bloom-energy-to-power-project-jupiter-with-fuel-cell-technology-2026-04-27/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/openai-announces-five-more-us-stargate-data-centers-with-oracle-and-softbank/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3919,22 +4326,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stream Data Centers (JV vía LOI)</t>
+          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ingeniería Fase Two (LOI para 203 acres adicionales, 438 en total; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
+          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/tcdc-signs-loi-to-acquire-an-additional-203-acres-for-offgrid-data-center-campus-in-ector-county-texas/)</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4496,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood)</t>
+          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4109,17 +4516,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ingeniería/procurement (NTP completo para generación de 1.2GW a gas)</t>
+          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Babcock &amp; Wilcox](https://www.babcock.com/home/about/corporate/news/babcock-and-wilcox-receives-full-notice-to-proceed-on-24-billion-power-generation-project-for-base-electron-to-supply-power-to-applied-digital-ai-factory-campuses)</t>
+          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -4368,17 +4775,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[East Daley](https://eastdaley.com/media-and-news/wmbs-project-socrates-offers-enlightening-energy-solution)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4977,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Crusoe/Tallgrass AI Data Center Campus</t>
+          <t>Crusoe/Tallgrass AI Data Center Campus (Project Jade)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4590,17 +4997,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Construcción (aprobado ene-2026; 1.8GW inicial escalable a 10GW; primeros edificios previstos mediados de 2027)</t>
+          <t>Desarrollo PAUSADO (Crusoe pausó actividades en jun-2026 a solicitud de su cliente; afecta también la generación de gas asociada BFC Power/Cheyenne Power Hub; aprobado ene-2026, 1.8GW inicial escalable a 10GW)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-gets-go-ahead-for-18gw-data-center-campus-and-power-plant-in-cheyenne-wyoming/)</t>
+          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -4755,7 +5162,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mon Power/FirstEnergy Gas Plant</t>
+          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4775,17 +5182,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Planeación/regulatorio (audiencia ante PSC; 1,200MW dimensionados para data center de ~1,000MW, sin contrato firmado)</t>
+          <t>Planeación/regulatorio (nombrado oficialmente "Maidsville Energy Center", USD 2.47 mil millones, 1,200MW; audiencia pública 15-jul y audiencia probatoria 16/17-jul-2026 ante PSC; demanda proyectada casi toda de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+          <t>[WV MetroNews](https://wvmetronews.com/2026/07/17/consultant-testifies-mon-power-gas-plant-planned-for-data-centers-not-cost-free-to-other-customers/)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -4823,6 +5230,154 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AWS "Project Eagle"</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Permisos (presentados ante TDLR; construcción de 4 edificios, USD 1.2 mil millones, inicia 1-ago-2026)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Crusoe/Lancium Childress Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Condado de Childress, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Williams "Neo" Power Innovation Project</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cliente de centro de datos no revelado</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Williams "Socrates the Younger" Power Innovation Project</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cliente de centro de datos no revelado</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo (340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -12,12 +12,7 @@
     <sheet name="Mining" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Data Centers" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Petroquímica'!$A$1:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LNG'!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mining'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Centers'!$A$1:$G$48</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -25,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,29 +28,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,14 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,1167 +416,1203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>America First Refining</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>America First Refining</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Fluor Corporation</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ingeniería/FEED</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Fluor newsroom (https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ExxonMobil Coastal Plain (cracker + PE)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Calhoun County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ingeniería/FEED</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>AllStream Insiders (https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Golden Triangle Polymers</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Orange, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Chevron Phillips Chemical (CPChem) / QatarEnergy</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>ZDJV (Zachry/DL USA); JKJV (JGC America/Kiewit)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Construcción (comisionamiento)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>BIC Magazine (https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>CF Industries Blue Point (amoniaco bajo carbono)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>CF Industries / JERA / Mitsui &amp; Co.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Technip Energies</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Construction Front (https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Plantas de gas — Cuenca Pérmica</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>West Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Enterprise Products / Targa Resources / Phillips 66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Audubon Companies (parcial); otros no especificados</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>East Daley (https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Refinería Dos Bocas (Olmeca)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Paraíso, Tabasco, México</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Techint (parcial)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Construcción/ajustes</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Techint (https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Refinería de Tula (modernización)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Tula, Hidalgo, México</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Construcción/modernización</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>OGJ (https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Rehab. Etano-Etileno (Cangrejera/Morelos)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>POLIOLES S.A. de C.V.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Forbes México (https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Rehab. Planta de Aromáticos (Cangrejera)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>ICA Fluor Daniel S. de R.L.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Forbes México (https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Proyecto Escolín (amoniaco/urea)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Poza Rica, Veracruz, México</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Mota-Engil México (EPC confirmado; plazo de construcción 33 meses)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Forbes México (https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Rehab. Fertinal-ProAgro (urea y fosfatos)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas, Michoacán, México</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Tribuna (https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Pacífico Mexinol (metanol ultra bajo carbono)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Transition Industries</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Siemens Energy / Techint E&amp;C (FEED electrolizador)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Construcción (iniciada abr-2026)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>PV Magazine México (https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>First Ammonia (amoniaco verde)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Victoria, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>First Ammonia / Cox Group USA</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Worley (FEED)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Ingeniería (FEED completo) / FID prevista 2026</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>H2 View (https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Planta de Amoniaco Topolobampo (GPO)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Gas y Petroquímica de Occidente (GPO) / Proman AG</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Debate (https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Lake Charles Methanol II</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Lake Charles, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Lake Charles Methanol II LLC</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Zachry Group (FEED)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Ingeniería (FEED) / FID prevista</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ICIS (https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Planta Coquizadora Salina Cruz</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Salina Cruz, Oaxaca, México</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>ICA Fluor</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Construcción (~74% avance)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Diario del Istmo (https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Shintech Louisiana — Expansión Plaquemine (2do craqueador de etileno + 4ta unidad cloro-álcali/VCM)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Plaquemine, Iberville Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Shintech Louisiana, LLC</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (construcción por fases, 1a fase prevista 2030)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Sandpiper Chemicals (metanol bajo carbono)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Texas City, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Sandpiper Chemicals, LLC (INEOS Acetyls tomó participación accionaria)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Ingeniería (FEED en curso, 2T2026) / FID prevista 2027</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Alchempro (https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[Alchempro](https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>OXEA Bay City Capacity Expansion + Air Liquide POX Syngas Unit</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Bay City, Matagorda County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>OXEA (oxo chemicals) / Air Liquide (unidad de syngas)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Air Liquide (unidad propia); OXEA no especificado</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Construcción (FID confirmado 13-jul-2026; preparación de sitio 3T2026; finalización fines de 2028)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Targa Resources East Driver Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Condado de Midland, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Targa Resources Corp.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Construcción (planta criogénica 275 MMcf/d; arranque previsto 3T2026)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>OGJ (https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Enterprise Products "Athena" Natural Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Cuenca Midland (cuatro condados), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Enterprise Products Partners L.P.</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Enterprise Products (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Construcción (300 MMcf/d + hasta 40,000 bpd de NGLs; en servicio 4T2026)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>MPLX Secretariat II Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Cuenca Pérmica (subcuenca Delaware), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Planeada/desarrollo (300 MMcf/d; en servicio 2S2028)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Natural Gas Intel (https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>MPLX Titan Complex (Northwind) — Expansión de Tratamiento de Gas Amargo</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Condado de Lea, Nuevo México / frontera TX-NM, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Construcción (expansión de capacidad &gt;400 MMcf/d; plenamente operativo 4T2026)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>East Daley (https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Northern Plains Nitrogen (urea/amoniaco)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Grand Forks, Dakota del Norte, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Northern Plains Nitrogen LLC</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>EPC no designado</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Pre-FEED completo / FID buscada 4T2026</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Grand Forks Herald (https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Iron Mesa (planta de gas)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Goldsmith, Ector County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Construcción (arranque previsto Q1 2027)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Phillips 66 (https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Yeti II (planta de gas)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Targa Resources</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Targa Resources (https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Refinería Francisco I. Madero (rehabilitación)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Ciudad Madero, Tamaulipas, México</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Licitación/bidding</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Elefante Blanco (https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Fermachem Planta de Urea/Amoniaco</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Ejido Sapioris, Lerdo, Durango, México</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Fermaca Dreams (Fermachem)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Construcción (ejecución iniciada jun-2026)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>La Jornada (https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Clean Hydrogen Works</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>McDermott (FEED)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Ingeniería (FEED) / Pre-FID</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Downstream Calendar (https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Zeus Gas Plant + 3ra Fraccionadora Coastal Bend</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, Texas / Robstown, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Ingeniería (sancionado; en línea 2028)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Project Meadowlark (complejo de amoniaco azul/UAN/ATS/DEF)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gothenburg, Nebraska, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>J. Westling &amp; Co. (JWC Gburg, LLC)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado (tecnología licenciada Topsoe SynCOR Ammonia); contrato EPC/fabricación asegurado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ingeniería/Permisos (permiso de aire emitido, sitio zonificado; obras civiles previstas 2027, operación comercial 2029)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1614,1093 +1623,1129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Rio Grande LNG (Trenes 1-5)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>NextDecade Corporation</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Bechtel (https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Port Arthur LNG Fase 2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Port Arthur, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sempra Infrastructure</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Bechtel Energy Inc.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Bechtel (https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Woodside Louisiana LNG (ex-Driftwood)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Calcasieu Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Woodside Energy Group</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Woodside (https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>CP2 LNG Fase 2</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Venture Global</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Worley</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción (FID alcanzada mar-2026, NTP completo a Worley)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>GEM.wiki (https://www.gem.wiki/CP2_LNG_Terminal)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Plaquemines LNG Fase 2</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Venture Global</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>KBR / Zachry Group (KZJV)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Offshore Energy (https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Golden Pass LNG (Trenes 1-3)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sabine Pass, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Golden Pass LNG (ExxonMobil/QatarEnergy)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Chiyoda / McDermott (CB&amp;I) / Zachry Group</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>LNG Prime (https://lngprime.com/contracts-and-tenders/golden-pass-lng-contractors-ink-revised-epc-deal-for-second-and-third-train/169104/)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[LNG Prime](https://lngprime.com/contracts-and-tenders/golden-pass-lng-contractors-ink-revised-epc-deal-for-second-and-third-train/169104/)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Corpus Christi Stage 3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Corpus Christi, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Cheniere Energy</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Construcción (98%)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>LNG Prime (https://lngprime.com/americas/chenieres-corpus-christi-stage-3-project-98-percent-complete/190871/)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-stage-3-project-98-percent-complete/190871/)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Delfin FLNG 1</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Golfo de México, costa afuera de Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Delfin Midstream</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Samsung Heavy Industries + Black &amp; Veatch</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Construcción (FID positiva jun-2026)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Saguaro Energía LNG + gasoducto Sierra Madre/Saguaro Connector</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Puerto Libertad, Sonora, México</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Mexico Pacific Limited</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Techint (obras tempranas); GDI Sicim Pipelines/Bonatti (gasoducto); EPC planta no especificado</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ingeniería/Pre-FID con retrasos</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>IEEFA (https://ieefa.org/resources/mexico-pacific-limited-delays-turmoil-and-permitting-errors-have-stymied-mexicos-largest)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[IEEFA](https://ieefa.org/resources/mexico-pacific-limited-delays-turmoil-and-permitting-errors-have-stymied-mexicos-largest)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Altamira FLNG Train 2</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Altamira, Tamaulipas, México</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>New Fortress Energy</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>GEM Wiki (https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Texas LNG Brownsville</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Glenfarne Group</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Kiewit Energy Group</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Construcción (LNTP otorgado a Kiewit 4-jul-2026 para compra de equipo de entrega larga, ingeniería EPC y geotécnico; FID prevista fin de 2026)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>OGJ (https://www.ogj.com/pipelines-transportation/lng/news/55388908/texas-lng-advances-pre-fid-project-with-limited-notice-to-proceed)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/lng/news/55388908/texas-lng-advances-pre-fid-project-with-limited-notice-to-proceed)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Commonwealth LNG</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Caturus (Kimmeridge/Mubadala Energy/CPP Investments)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Technip Energies</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Construcción (Full NTP a Technip Energies; contrato de automatización principal a Yokogawa jul-2026)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>PGJ (https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Galveston LNG (Pelican Island)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Isla Pelican, Galveston, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Power LNG Ventures, LLC</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Permitting temprano (arrendamiento preliminar de 30 acres con Galveston Wharves; solicitud federal de exportación presentada; producción prevista dic-2028)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Houston Public Media (https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Energía Costa Azul (ECA LNG) Fase 2</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Ensenada, Baja California, México</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sempra Infrastructure / TotalEnergies</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Ingeniería/Pre-FID (Fase 1 operando desde jul-2026)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Sempra (https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Gato Negro LNG</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Manzanillo, Colima, México</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Big River Energy</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Samsung E&amp;A (ingeniería)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Pre-FID (retrasado a fines de 2027)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>LNG Prime (https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Amigo LNG (FLNG)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Guaymas, Sonora, México</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Amigo LNG (Epsilon LNG / LNG Alliance)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Drydocks World (EPC de barcazas FLNG)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Construcción (conversión de FSU y fabricación de barcazas en Dubái; operación prevista 2a mitad 2028)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Coastal Bend LNG</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Ingleside, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Coastal Bend LNG (Kyomera Ventures/Amirian Group)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>KBR + Técnicas Reunidas (FEED)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ingeniería (FEED)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>KBR (https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Gulfstream LNG</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Gulfstream LNG Development LLC</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Pre-FID (trámite FERC, docket CP25-519)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>FERC (https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Alaska LNG (Fase 1: gasoducto + terminal Nikiski)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>North Slope a Nikiski, Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Glenfarne Group / Alaska Gasline Development Corp</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Pre-FID (avanzando hacia cierre financiero)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Glenfarne (https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[Glenfarne](https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Gasoducto Naco–Guaymas (alimenta Amigo LNG)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Naco (frontera Sonora/Arizona) a Guaymas, Sonora, México</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Cenagas / LNG Alliance / Freedom LNG LLC</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Ingeniería/pre-construcción (ceremonia binacional México-EE.UU. 25-jun-2026 formaliza avance del "Sonora Energy Corridor", 500km/US$2.8bn; aún sin FID)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>PGJ (https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Gasoducto Mustang Express (alimenta Port Arthur LNG Fase 2)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Katy a Port Arthur, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>ARM Energy Holdings / PIMCO</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Construcción (FID alcanzada)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>OGJ (https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>PODEBI Coatzacoalcos II (planta LNG)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Villa Allende, Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ursus Energy</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Samsung E&amp;A (FEED+EPC); Honeywell (tecnología)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; primer desembolso de US$100M previsto fines de jul-2026; transición a obra civil, verano 2026)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Mexico Business News (https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Delfin FLNG2 (segundo buque FLNG)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Golfo de México, costa afuera de Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Delfin Midstream / MidOcean Energy (EIG)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Siemens Energy (LNTP para equipo de largo plazo)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Pre-FID (LNTP emitido; FID prevista para fines de 2026)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Gasoducto Texas Gateway (alimenta terminales LNG del Golfo)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Carthage, Texas a Beauregard Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Gulf South Pipeline Company (Boardwalk Pipelines)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Open season vinculante (hasta 8-dic-2026) / FAST-41; en servicio previsto nov-2029</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Argent LNG (Port Fourchon)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Port Fourchon, Lafourche Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Argent LNG</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología modular NMBL); GIS Engineering (ingeniería marina/ambiental/de sitio, contrato ampliado)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Ingeniería/Pre-FID (permitting FERC/DOE en curso para terminal de 25 MMtpa; inicio de construcción previsto 2026)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>World Oil (https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[World Oil](https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>ST LNG Deepwater Port</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Costa afuera de Matagorda, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>ST LNG, LLC</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Permitting/Pre-FID (Draft EIS publicado abr-2026)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/04/17/2026-07517/deepwater-port-license-application-st-lng-deepwater-port-development-project-draft-environmental)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/04/17/2026-07517/deepwater-port-license-application-st-lng-deepwater-port-development-project-draft-environmental)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Gasoducto Mississippi Crossing (MSX)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Misisipi/Alabama, EE.UU.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Permitting (orden de certificado FERC esperada 31-jul-2026; USD 1.7 mil millones, 208 millas; alimenta demanda de LNG/generación en el sureste de EE.UU.)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Natural Gas Intel (https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Gasoducto South System Expansion 4 (SSE4)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Misisipi/Alabama/Georgia, EE.UU.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Permitting (orden de certificado FERC esperada 31-jul-2026; USD 3.5 mil millones, 291 millas; alimenta demanda de LNG/generación en el sureste de EE.UU.)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Natural Gas Intel (https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gulf LNG Liquefaction Project</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pascagoula, Misisipi, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kinder Morgan (50%) / Thunderbird LNG LLC (30%) / Arc Logistics-Lightfoot Capital (20%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pre-FID/Permitting (Kinder Morgan solicitó extensión de permiso DOE no-FTA a jul-2031 tras no cumplir fecha límite de exportación jul-2026; 11.5 MTPA, ~USD 8 mil millones, dos trenes de licuefacción en terminal de importación existente)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2711,1241 +2756,1314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Santa Cruz Copper Project</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ivanhoe Electric Inc.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Fluor Corporation</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ingeniería completada / construcción prevista H1 2026</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Copper World Complex</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Pima County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Hudbay Minerals (70%) / Mitsubishi Corporation (30%)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sundt, M3 Engineering, Ames, DRA Global, Knight Piésold, Mipac, Stantec</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ingeniería/Feasibility (DFS &gt;85% completo)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>SEC/Hudbay (https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Resolution Copper (Shaft No. 9)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Superior, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Rio Tinto (55%) / BHP (45%) JV</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hatch</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Ingeniería temprana post intercambio de tierras (marzo 2026)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>SEC (https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Thacker Pass Lithium Mine (Fase I)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Humboldt County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Lithium Americas Corp.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción (10-20% avance)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Nevada Appeal (https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[Nevada Appeal](https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>San Nicolás Copper-Zinc Project</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Zacatecas, México</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Teck Resources / Agnico Eagle Mines (JV 50/50)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Construcción, producción esperada 2026</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>El Arco Copper Project</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Baja California, México</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Ingeniería de detalle</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Energy Magazine MX (https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>El Pilar Copper Project</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Grupo México</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Ingeniería básica completada / trámite ambiental</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Mexico Mining Center (https://www.mexicominingcenter.com/grupo-mexico-compra-mina-el-pilar/)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[Mexico Mining Center](https://www.mexicominingcenter.com/grupo-mexico-compra-mina-el-pilar/)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Buenavista del Cobre — Concentradora No. 2</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cananea, Sonora, México</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corporation</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Ingeniería/ejecución de expansión</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>M3 Engineering (https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Media Luna Mine (North/EPO)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Guerrero, México</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Construcción (tubería de pasta pendiente)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Pumpkin Hollow Copper Mine (reinicio)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Yerington, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Nevada Copper Corp. (Kinterra Capital)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Planeación de reinicio/construcción</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Hermosa Critical Minerals Project (Taylor/Clark)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Santa Cruz County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>South32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>DMC Mining Services (parcial)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Construcción (Record of Decision final emitido por USFS 14-jul-2026; ~50% avance en porción privada; autorización operativa prevista sep-2026)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Chamber Business News (https://chamberbusinessnews.com/2026/07/14/hermosa-critical-minerals-mining-project-reaches-major-federal-permitting-milestone/)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[Chamber Business News](https://chamberbusinessnews.com/2026/07/14/hermosa-critical-minerals-mining-project-reaches-major-federal-permitting-milestone/)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Stibnite Gold Project</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Valley County, Idaho, EE.UU.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Perpetua Resources</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Hatch Ltd. (EPCM)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Construcción temprana</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>El Tigre Project</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Silver Tiger Metals</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Kappes, Cassiday &amp; Associates (EPCM)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Construcción (166 personas en sitio, 100,000 horas-hombre; primer vaciado previsto dic-2027)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Silver Tiger Metals (https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Panuco Silver-Gold Project</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Sinaloa, México</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Vizsla Silver Corp.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Ingeniería de detalle/planeación de construcción (post-Feasibility Study)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>South Railroad Project (South Carlin Complex)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Elko/Eureka County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Orla Mining Ltd.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Construcción (inicio previsto mediados 2026, pendiente ROD final de BLM)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Orla Mining (https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Copperstone Gold Project</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>La Paz County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Minera Alamos Inc.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Contratista de minería subterránea por definir</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Construcción (decisión de inversión may-2026)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>CK Gold Project</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Distrito Silver Crown, Laramie Range, Wyoming, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>U.S. Gold Corp</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Halyard-Micon International (feasibility); EPC por asignar</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ingeniería completa/permisado a nivel estatal; inicio de construcción retrasado de 2026 a 1T2027 (complicaciones de suministro de agua y derecho de vía)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Wyoming News (https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Distrito Santa Elena — Expansión (Santo Niño y Navidad)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>First Majestic Silver Corp.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Construcción (permisos recibidos jun-2026)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>First Majestic (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Galena Complex — Planta de Relleno en Pasta</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Wallace, Idaho, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Americas Gold and Silver Corporation</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Construcción (comisionamiento previsto Q4 2026)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>SEC/Americas Gold and Silver (https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Guanacevi Silver Project (Ocampo Mining)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Durango, México</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Minera Frisco (Grupo Carso)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Construcción (nueva planta de proceso; primera producción prevista fin de 2026)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Kitco (https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Arctic Project (Distrito Minero Ambler)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Distrito Minero Ambler, Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ambler Metals LLC (Trilogy Metals / South32, JV 50/50)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Permitting (cronograma coordinado de permisos federales/estatales publicado 16-jul-2026; revisión ambiental integrada de 29 meses liderada por USACE; ROD objetivo sep-2028)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Los Ricos South Mine</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Jalisco, México</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GoGold Resources</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Construcción aprobada (permisos SEMARNAT jun-2026)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Northern Miner (https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Cordero Project</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Chihuahua, México</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Discovery Silver</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Ausenco (ingeniería)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Feasibility completa / permitting (MIA pendiente ante SEMARNAT)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>BNamericas (https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Gran Pilar Gold-Silver Project</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Tocvan Ventures</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Construcción (piloto; primer doré previsto Q4 2026)</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Resource World (https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Orisyvo Project</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Sierra Madre (Rarámuri), Chihuahua, México</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Fresnillo plc</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Pre-feasibility (transicionando a feasibility, resultados esperados medio 2026)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Fresnillo plc (https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Planta de Separación de Tierras Raras (US Army)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Tooele Army Depot, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>REalloys Inc.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Planta de Purificación de Grafito (US Army)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Pine Bluff Arsenal, Arkansas o Anniston Army Depot, Alabama (sin confirmar), EE.UU.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Titan Mining Corp.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Plantas de Litio y Boro (US Army)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Base militar de EE.UU. sin confirmar</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>EnergyX (litio) / ioneer Ltd. (boro)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027; producción 2028)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Expansión Concentradora La Caridad</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Nacozari, Sonora, México</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Grupo México</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Metso (equipo de trituración)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Construcción/procura de equipo (pedido adicional &gt;EUR 20M de trituración secundaria a Metso, jun-2026, complementa equipos Nordberg MP800 instalados en 2025)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>IM Mining (https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Santo Tomás Copper Project</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Sinaloa, México</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Oroco Resource Corp.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Prefactibilidad (perforación fase 2 en curso; PFS objetivo 2T-3T 2027; capex estimado USD 2.84 mil millones; permisos federales pendientes)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Reapertura Fundición Hayden + Refinería Amarillo</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Hayden, Arizona / Amarillo, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Asarco (Grupo México)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Negociación/planeación (inversión ~USD 230 millones para reactivar fundición cerrada desde 2020; Grupo México evalúa hasta USD 6,000 millones adicionales para expansión de cobre en Arizona)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Cerro de Oro Gold Project</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Zacatecas, México</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Minera Alamos Inc.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Permitting (proyecto de oro a cielo abierto/heap leach; financiamiento de construcción ya asegurado)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Minera Alamos (https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Antler Copper Project</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Condado de Mohave, Arizona, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New World Resources Ltd. (respaldado por Kinterra Capital)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Permitting casi completo/inicio de construcción (BLM emitió Determinación de Adecuación NEPA; obras previstas 2do semestre 2026; embarque de concentrado previsto 2027)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lisbon Valley Copper Project</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Condado de San Juan, Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lisbon Valley Mining Company, LLC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Permitting federal completo (aprobación BLM + exención de acuífero EPA, oct-2025) / reapertura-construcción (agrega tajo abierto y pozos de recuperación in-situ)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3956,1796 +4074,1943 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Stargate Frontier Campus</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Shackelford County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Stargate Milam County (fast-build)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Milam County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>OpenAI / Oracle</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Epoch AI (https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Stargate Abilene Campus</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Abilene, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>OpenAI / Oracle</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Crusoe / DPR Construction</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Microsoft Pecos Data Center Campus (Project Kilby)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Pecos/Reeves County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Chevron + Engine No. 1 (suministro de gas 20 años, sitio &gt;2,000 acres); turbinas GE Vernova/Caterpillar</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Ingeniería avanzada/Construcción temprana (capacidad rampa a 2.67GW; planta operativa 2028; FID de la planta esperada fines de 2026)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>CNBC (https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[CNBC](https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>CloudHQ Querétaro (6 campus, incl. Campus Colón)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Colón y otras ubicaciones, Querétaro, México</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>CloudHQ</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Permisos/preparación de sitio (confirmado oficialmente por gobierno federal 7-jul-2026 bajo Plan México; inversión US$4,800M, 52 hectáreas, 900MW; subestación propia de 2GW prevista Q2 2027)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno de México (https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Meta Hyperion Data Center</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Richland Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Turner Construction / DPR Construction / Mortenson</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Construcción (escalado de ~2GW a 5GW de cómputo; inversión ampliada a USD 27-50 mil millones; Entergy busca aprobación regulatoria para 10 plantas de gas/7GW+ ante la Comisión de Servicio Público de Luisiana; juez ordenó a Meta divulgar información sobre 7 plantas adicionales, 14-jul-2026)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>UCS (https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[UCS](https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Vantage Data Centers NV1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Storey County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CloudBurst San Marcos Data Center I</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>San Marcos/New Braunfels, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>CloudBurst Data Centers</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Evolve (eVOLVE Data Center Solutions)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Prometheus Hyperscale Dallas Campus</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Kaufman County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Prometheus Hyperscale</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>No especificado (socio energía: Engie)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ingeniería/construcción temprana</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>GW Ranch Power Campus</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Pecos County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Pacifico Energy</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Permisos obtenidos/inicio construcción</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Amazon Mattermeade Data Center Campus</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Caroline/Spotsylvania County, Virginia, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Amazon (AWS)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fermaca Digital City (+ gasoducto + planta de ciclo combinado)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Durango, Durango, México</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Grupo Fermaca (inquilino AI hyperscaler sin confirmar)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Permisos/negociación avanzada (construcción inminente)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Mexico News Daily (https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Circe Energy West Texas AI Infrastructure Campus</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, West Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Circe Energy</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>No especificado (gen-sets Cummins)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Ingeniería/procurement</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Project Jupiter</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Santa Teresa, Doña Ana County, Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>BorderPlex Digital Assets/Stack (inquilino Oracle/OpenAI)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>No especificado (rediseño: hasta 2.45GW de celdas de combustible Bloom Energy, reemplazando turbinas de gas/diésel)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Construcción activa (confirmado como sitio oficial Stargate; BLM aprobó derecho de vía del gasoducto "Green Chile" de Energy Transfer, 17.7 millas/US$60M)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/openai-announces-five-more-us-stargate-data-centers-with-oracle-and-softbank/)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Construcción activa con riesgo regulatorio (Comisionado de Tierras de NM rechazó dos veces el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 15/16-jul-2026, tras la previa aprobación de BLM en tierra federal; meta de entrada en servicio ago-2026 en riesgo, posible retraso a 2027)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/new-mexico-regulators-reject-natural-gas-pipeline-for-oracles-25gw-project-jupiter-data-center/)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>New Era Energy &amp; Digital Hub</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lea County, Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New Era Energy &amp; Digital</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Planeación temprana (opción de terreno)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Texas Critical Data Centers (TCDC) Campus</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New Era Energy &amp; Digital</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>New Era Energy &amp; Digital Hub</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Lea County, Nuevo México, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>New Era Energy &amp; Digital</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Planeación temprana (opción de terreno)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PowerMag (https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Texas Critical Data Centers (TCDC) Campus</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>New Era Energy &amp; Digital</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Stargate Lordstown</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lordstown, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle / SoftBank</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SB Energy (SoftBank)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Construcción (rompimiento de tierra)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Stargate Wisconsin</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle / SoftBank</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers (en sociedad con Oracle)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo temprano</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AWS Región Digital Querétaro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Querétaro, México</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Stargate Michigan (Saline Barn Campus)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Saline Township, Michigan, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Walbridge</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>North Dakota, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Applied Digital / Base Electron</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Stargate Lordstown</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Lordstown, Ohio, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI / Oracle / SoftBank</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>SB Energy (SoftBank)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (rompimiento de tierra)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Stargate Wisconsin</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI / Oracle / SoftBank</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Vantage Data Centers (en sociedad con Oracle)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI-GDC / Cipre Holding "Green Data Center"</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>San Pedro Garza García, Nuevo León, México</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>AWS Región Digital Querétaro</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Querétaro, México</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Web Services (AWS)</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Mexico News Daily (https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Stargate Michigan (Saline Barn Campus)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Saline Township, Michigan, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Walbridge</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CleanArc Data Centers VA1 Campus</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Caroline County, Virginia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CleanArc Data Centers</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>North Dakota, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Applied Digital / Base Electron</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Valley News Live (https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Joule Energy and Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Millard County (Holden), Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Joule Capital Partners</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Amazon Montgomery County Campus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Anuncio/permisos</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Google Montgomery County Campus</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Anuncio/permisos</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hood County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Big Digital Energy + 10NetZero (JV)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Planeación/adquisición de sitio</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Williams "Project Socrates"</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>New Albany, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Meta (vía Sidecat, LLC)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Williams Companies / Will-Power</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>AI-GDC / Cipre Holding "Green Data Center"</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>San Pedro Garza García, Nuevo León, México</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Meta El Paso Campus (expansión)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>El Paso, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Permisos</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SB Energy/SoftBank PORTS Technology Campus</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pike County, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Energy Magazine MX (https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CleanArc Data Centers VA1 Campus</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Caroline County, Virginia, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>CleanArc Data Centers</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Construcción</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Construction Dive (https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Joule Energy and Data Center Campus</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Millard County (Holden), Utah, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Joule Capital Partners</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Construcción</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>KSL (https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Montgomery County Campus</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Anuncio/permisos</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Governor.mo.gov (https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Google Montgomery County Campus</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Anuncio/permisos</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>STLPR (https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Hood County, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Big Digital Energy + 10NetZero (JV)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Planeación/adquisición de sitio</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Williams "Project Socrates"</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>New Albany, Ohio, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Meta (vía Sidecat, LLC)</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Williams Companies / Will-Power</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Williams "Apollo" Power Generation Project</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Williams "Aquila" Power Project</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Utah, EE.UU. (condado no revelado)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>West Texas, EE.UU. (condado no revelado)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Crusoe/Tallgrass AI Data Center Campus (Project Jade)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Condado de Laramie, Wyoming, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Crusoe Energy / Tallgrass</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Desarrollo PAUSADO (Crusoe pausó actividades en jun-2026 a solicitud de su cliente; afecta también la generación de gas asociada BFC Power/Cheyenne Power Hub; aprobado ene-2026, 1.8GW inicial escalable a 10GW)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Meta El Paso Campus (expansión)</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>El Paso, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Permisos</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SB Energy/SoftBank PORTS Technology Campus</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Pike County, Ohio, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Planeación/desarrollo temprano</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/)</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Williams "Apollo" Power Generation Project</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Core Scientific Pecos Campus (expansión IA)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pecos, Reeves County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Core Scientific</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Stratos Project / Wonder Valley</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>O'Leary Digital (Kevin O'Leary)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Fermi America Project Matador</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Carson County (Amarillo), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fermi America</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Primoris Services Corporation (balance of plant, turbinas de gas)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Construcción (excavación de isla de turbinas completada; EPC firmado)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/fermi-selects-primoris-services-corporation-to-engineer-and-construct-balance-of-plant-for-first-six-sgt-800-gas-turbines-of-phase-one-power-buildout-302814505.html)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NextEra Texas Power Generation Hub</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Anderson County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NextEra Energy Resources</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Monongalia County, Virginia Occidental, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mon Power (FirstEnergy)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IEP Greene County Data Center &amp; Power Plant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Greene County, Pensilvania, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>International Electric Power</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AWS "Project Eagle"</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Permisos (presentados ante TDLR; construcción de 4 edificios, USD 1.2 mil millones, inicia 1-ago-2026)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Crusoe/Lancium Childress Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Condado de Childress, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Williams "Neo" Power Innovation Project</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cliente de centro de datos no revelado</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Williams "Aquila" Power Project</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Utah, EE.UU. (condado no revelado)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Williams "Socrates the Younger" Power Innovation Project</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Meta Platforms (vía Sidecat, LLC)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Williams Companies (https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>West Texas, EE.UU. (condado no revelado)</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Crusoe/Tallgrass AI Data Center Campus (Project Jade)</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Condado de Laramie, Wyoming, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Crusoe Energy / Tallgrass</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Desarrollo PAUSADO (Crusoe pausó actividades en jun-2026 a solicitud de su cliente; afecta también la generación de gas asociada BFC Power/Cheyenne Power Hub; aprobado ene-2026, 1.8GW inicial escalable a 10GW)</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Bloomberg (https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Core Scientific Pecos Campus (expansión IA)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Pecos, Reeves County, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Core Scientific</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>HPCwire (https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Stratos Project / Wonder Valley</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>O'Leary Digital (Kevin O'Leary)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Utah News Dispatch (https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Fermi America Project Matador</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Carson County (Amarillo), Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Fermi America</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Primoris Services Corporation (balance of plant, turbinas de gas)</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (excavación de isla de turbinas completada; EPC firmado)</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/fermi-selects-primoris-services-corporation-to-engineer-and-construct-balance-of-plant-for-first-six-sgt-800-gas-turbines-of-phase-one-power-buildout-302814505.html)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>NextEra Texas Power Generation Hub</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Anderson County, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>NextEra Energy Resources</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>KLTV (https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Monongalia County, Virginia Occidental, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Mon Power (FirstEnergy)</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>WV MetroNews (https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>IEP Greene County Data Center &amp; Power Plant</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Greene County, Pensilvania, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>International Electric Power</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Utility Dive (https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>AWS "Project Eagle"</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Web Services</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Permisos (presentados ante TDLR; construcción de 4 edificios, USD 1.2 mil millones, inicia 1-ago-2026)</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Crusoe/Lancium Childress Data Center Campus</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Condado de Childress, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Crusoe (https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Williams "Neo" Power Innovation Project</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Cliente de centro de datos no revelado</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Williams Companies</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Williams "Socrates the Younger" Power Innovation Project</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms (vía Sidecat, LLC)</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Williams Companies</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>PowerMag (https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Crusoe/Google "Goodnight Campus"</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Crusoe/Google "Goodnight Campus"</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Aterio (https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VoltaGrid/Serverfarm Covington</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Serverfarm</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>VoltaGrid/Serverfarm Covington</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Serverfarm</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>AJC (https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Homer City Energy Campus</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Condado de Indiana, Pensilvania, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Homer City Redevelopment (HCR)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Nebius Vineland AI Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Vineland, Nueva Jersey, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>No especificado (motores reciprocantes de gas Bergen, ~30 unidades)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; meta de entrega nov-2026 en riesgo)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>[Data Center Knowledge](https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TerraVolt Infrastructure AI Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CyrusOne SAT14A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Castroville, San Antonio, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CyrusOne (sin arrendatario asignado aún)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ingeniería/Permisos (6to campus en San Antonio, 11vo en Texas; USD 500 millones, 460,000 pies²; inicio de construcción previsto dic-2026)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,10 +20,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -49,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,47 +428,47 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -493,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
+          <t>https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
+          <t>https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -567,7 +576,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
+          <t>https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -604,7 +613,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/)</t>
+          <t>https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -641,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
+          <t>https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -678,7 +687,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
+          <t>https://www.techint.com/en/our-projects/dos-bocas-refinery</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -715,7 +724,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
+          <t>https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -752,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +798,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -826,7 +835,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
+          <t>https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -863,7 +872,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/)</t>
+          <t>https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -900,7 +909,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
+          <t>https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -937,7 +946,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
+          <t>https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -974,7 +983,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
+          <t>https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1011,7 +1020,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
+          <t>https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1048,7 +1057,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
+          <t>https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1085,7 +1094,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
+          <t>https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1122,7 +1131,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[Alchempro](https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
+          <t>https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1159,7 +1168,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
+          <t>https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1196,7 +1205,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
+          <t>https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1233,7 +1242,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
+          <t>https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1270,7 +1279,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+          <t>https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1307,7 +1316,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
+          <t>https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1344,7 +1353,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
+          <t>https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,7 +1390,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+          <t>https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1418,7 +1427,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+          <t>https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1455,7 +1464,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+          <t>https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1492,7 +1501,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+          <t>https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1529,7 +1538,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+          <t>https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1566,7 +1575,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
+          <t>https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1603,7 +1612,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
+          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1623,50 +1632,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -1700,7 +1709,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/)</t>
+          <t>https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1737,7 +1746,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
+          <t>https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1774,7 +1783,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
+          <t>https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1811,7 +1820,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal)</t>
+          <t>https://www.gem.wiki/CP2_LNG_Terminal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1848,7 +1857,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
+          <t>https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1885,7 +1894,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/contracts-and-tenders/golden-pass-lng-contractors-ink-revised-epc-deal-for-second-and-third-train/169104/)</t>
+          <t>https://lngprime.com/contracts-and-tenders/golden-pass-lng-contractors-ink-revised-epc-deal-for-second-and-third-train/169104/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1917,17 +1926,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Construcción (98%)</t>
+          <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026; primera producción de LNG esperada ago-2026, servicio comercial sep-2026)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-stage-3-project-98-percent-complete/190871/)</t>
+          <t>https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1968,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
+          <t>https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1991,17 +2000,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ingeniería/Pre-FID con retrasos</t>
+          <t>Pre-FID PAUSADO (suspensión judicial desde abr-2026 por demanda ambiental sobre ballenas en el Mar de Cortés; presión de activistas contra financiadores JPMorgan/Santander, 17-jul-2026; definición de autorización pendiente para 2026)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[IEEFA](https://ieefa.org/resources/mexico-pacific-limited-delays-turmoil-and-permitting-errors-have-stymied-mexicos-largest)</t>
+          <t>https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2042,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
+          <t>https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2065,17 +2074,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Construcción (LNTP otorgado a Kiewit 4-jul-2026 para compra de equipo de entrega larga, ingeniería EPC y geotécnico; FID prevista fin de 2026)</t>
+          <t>Construcción (LNTP otorgado a Kiewit 4-jul-2026; HPS Investment Partners/BlackRock invirtió US$500M para obras tempranas, visto como paso final previo a FID; FID prevista fin de 2026)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/pipelines-transportation/lng/news/55388908/texas-lng-advances-pre-fid-project-with-limited-notice-to-proceed)</t>
+          <t>https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2116,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
+          <t>https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2144,7 +2153,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
+          <t>https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2181,7 +2190,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
+          <t>https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2218,7 +2227,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
+          <t>https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2255,7 +2264,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
+          <t>https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2292,7 +2301,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
+          <t>https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2329,7 +2338,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
+          <t>https://www.ferc.gov/gulfstream-lng-terminal-project</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2366,7 +2375,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[Glenfarne](https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
+          <t>https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2403,7 +2412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
+          <t>https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2440,7 +2449,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
+          <t>https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2477,7 +2486,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
+          <t>https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2514,7 +2523,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
+          <t>https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2551,7 +2560,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
+          <t>https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2588,7 +2597,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[World Oil](https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
+          <t>https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2625,7 +2634,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/04/17/2026-07517/deepwater-port-license-application-st-lng-deepwater-port-development-project-draft-environmental)</t>
+          <t>https://www.federalregister.gov/documents/2026/04/17/2026-07517/deepwater-port-license-application-st-lng-deepwater-port-development-project-draft-environmental</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2662,7 +2671,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2699,7 +2708,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2736,12 +2745,49 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
+          <t>https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sabine Pass LNG Expansion (Train 7 + unidad de re-licuefacción de boil-off gas)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cameron Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Partners</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bechtel (EPC); Baker Hughes (equipo mayor)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Construcción/Procura de equipo mayor (EPC firmado 28-may-2026; Baker Hughes recibió pedido de 7 turbinas de gas PGT25+ G4 y 15 compresores centrífugos, ~6 MTPA adicionales; construcción plena prevista inicios de 2027)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -2756,50 +2802,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -2833,7 +2879,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25)</t>
+          <t>https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2870,7 +2916,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm)</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2907,7 +2953,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm)</t>
+          <t>https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2944,7 +2990,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[Nevada Appeal](https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/)</t>
+          <t>https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2981,7 +3027,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
+          <t>https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3018,7 +3064,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
+          <t>https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3040,7 +3086,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grupo México</t>
+          <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3050,17 +3096,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ingeniería básica completada / trámite ambiental</t>
+          <t>Permisos ambientales asegurados (proyecto revaluado en US$551 millones; preparación de sitio inicia sep-2026, construcción plena 2027, primer cobre ~2028)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[Mexico Mining Center](https://www.mexicominingcenter.com/grupo-mexico-compra-mina-el-pilar/)</t>
+          <t>https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3138,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
+          <t>https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3129,7 +3175,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
+          <t>https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3166,7 +3212,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
+          <t>https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3198,17 +3244,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Construcción (Record of Decision final emitido por USFS 14-jul-2026; ~50% avance en porción privada; autorización operativa prevista sep-2026)</t>
+          <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026, cerrando revisión NEPA de infraestructura en Coronado National Forest; primer proyecto minero aceptado en programa federal FAST-41; ~50% avance en porción privada; primer concentrado ahora proyectado H1-2028, antes H1-2027)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[Chamber Business News](https://chamberbusinessnews.com/2026/07/14/hermosa-critical-minerals-mining-project-reaches-major-federal-permitting-milestone/)</t>
+          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
+          <t>https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3277,7 +3323,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
+          <t>https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3314,7 +3360,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
+          <t>https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3351,7 +3397,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
+          <t>https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3388,7 +3434,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
+          <t>https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3425,7 +3471,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
+          <t>https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3462,7 +3508,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
+          <t>https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3499,7 +3545,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3536,7 +3582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
+          <t>https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3573,7 +3619,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
+          <t>https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3610,7 +3656,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/)</t>
+          <t>https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3647,7 +3693,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
+          <t>https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3684,7 +3730,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
+          <t>https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3721,7 +3767,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
+          <t>https://www.fresnilloplc.com/portfolio/exploration/orisyvo/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3758,7 +3804,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3795,7 +3841,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3832,7 +3878,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3869,7 +3915,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
+          <t>https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3906,7 +3952,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
+          <t>https://www.globenewswire.com/news-release/2026/05/21/3299182</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3943,7 +3989,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
+          <t>https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3980,7 +4026,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
+          <t>https://mineraalamos.com/our-assets/cerro-de-oro-project/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4017,7 +4063,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
+          <t>https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4054,12 +4100,86 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
+          <t>https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>South West Arkansas Lithium Project (Central Processing Facility)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sur de Arkansas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Smackover Lithium (JV Standard Lithium / Equinor)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>S&amp;B Engineers and Constructors (EPCC); Hatch Ltd. (ingeniería de diseño/comisionamiento)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ingeniería de detalle/procura temprana (contrato EPCC otorgado, NTP limitado activo; FID esperada en 2026; planta diseñada para 22,500 tpa de carbonato de litio grado batería)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bagdad Mine Concentrator Expansion</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Yavapai County, Arizona, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Freeport-McMoRan</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental estimado ~US$3,500 millones bajo revisión; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4074,50 +4194,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -4151,7 +4271,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4188,7 +4308,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
+          <t>https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4225,7 +4345,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4262,7 +4382,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[CNBC](https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
+          <t>https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4299,7 +4419,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
+          <t>https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4336,7 +4456,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[UCS](https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center)</t>
+          <t>https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4373,7 +4493,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
+          <t>https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4410,7 +4530,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4447,7 +4567,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4484,7 +4604,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
+          <t>https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4521,7 +4641,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4558,7 +4678,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/)</t>
+          <t>https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4595,7 +4715,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4612,7 +4732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Santa Teresa, Doña Ana County, Nuevo México, EE.UU.</t>
+          <t>Santa Teresa/Sunland Park, Doña Ana County, Nuevo México, EE.UU.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4627,197 +4747,197 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción activa con riesgo regulatorio (Comisionado de Tierras de NM rechazó dos veces el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 15/16-jul-2026, tras la previa aprobación de BLM en tierra federal; meta de entrada en servicio ago-2026 en riesgo, posible retraso a 2027)</t>
+          <t>Construcción activa con riesgo regulatorio (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 14-jul-2026; NMED pospuso la decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas y programó audiencia pública para 19-oct-2026; meta de entrada en servicio ago-2026 en riesgo)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/new-mexico-regulators-reject-natural-gas-pipeline-for-oracles-25gw-project-jupiter-data-center/)</t>
+          <t>https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>New Era Energy &amp; Digital Hub</t>
+          <t>PowerPlay AI "Greater Abilene" Data Center</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lea County, Nuevo México, EE.UU.</t>
+          <t>Área metropolitana de Abilene, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Era Energy &amp; Digital</t>
+          <t>PowerPlay AI (JV con socio Neocloud cotizado en Nasdaq, sin nombre público)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IPP en proceso de RFP (aún sin seleccionar)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Planeación temprana (opción de terreno)</t>
+          <t>Ejecución activa post-adquisición de terreno (400MW behind-the-meter iniciales; arranque objetivo 2028)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
+          <t>https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Texas Critical Data Centers (TCDC) Campus</t>
+          <t>Liberty Energy/PowerBridge "Alpha Digital Campus"</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
+          <t>Condado de Reeves, Texas, EE.UU. (cerca del hub de gas Waha)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Era Energy &amp; Digital</t>
+          <t>PowerBridge LLC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
+          <t>Liberty Power Innovations (subsidiaria de Liberty Energy, JV)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
+          <t>JV firmada/desarrollo temprano (~3,400 acres; primera fase &gt;300MW, primera entrega de energía prevista 4T2027; campus completo 2GW)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+          <t>https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stargate Lordstown</t>
+          <t>New Era Energy &amp; Digital Hub</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lordstown, Ohio, EE.UU.</t>
+          <t>Lea County, Nuevo México, EE.UU.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle / SoftBank</t>
+          <t>New Era Energy &amp; Digital</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SB Energy (SoftBank)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Construcción (rompimiento de tierra)</t>
+          <t>Planeación temprana (opción de terreno)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stargate Wisconsin</t>
+          <t>Texas Critical Data Centers (TCDC) Campus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
+          <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle / SoftBank</t>
+          <t>New Era Energy &amp; Digital</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers (en sociedad con Oracle)</t>
+          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo temprano</t>
+          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Región Digital Querétaro</t>
+          <t>Stargate Lordstown</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Querétaro, México</t>
+          <t>Lordstown, Ohio, EE.UU.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>SB Energy (SoftBank)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
+          <t>Construcción (rompimiento de tierra)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
+          <t>https://openai.com/index/five-new-stargate-sites/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4829,106 +4949,106 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stargate Michigan (Saline Barn Campus)</t>
+          <t>Stargate Wisconsin</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Saline Township, Michigan, EE.UU.</t>
+          <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
+          <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Walbridge</t>
+          <t>Vantage Data Centers (en sociedad con Oracle)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
+          <t>https://openai.com/index/five-new-stargate-sites/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
+          <t>AWS Región Digital Querétaro</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>North Dakota, EE.UU.</t>
+          <t>Querétaro, México</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Applied Digital / Base Electron</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
+          <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
+          <t>https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI-GDC / Cipre Holding "Green Data Center"</t>
+          <t>Stargate Michigan (Saline Barn Campus)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>San Pedro Garza García, Nuevo León, México</t>
+          <t>Saline Township, Michigan, EE.UU.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
+          <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Walbridge</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo temprano</t>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4940,54 +5060,54 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CleanArc Data Centers VA1 Campus</t>
+          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caroline County, Virginia, EE.UU.</t>
+          <t>North Dakota, EE.UU.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CleanArc Data Centers</t>
+          <t>Applied Digital / Base Electron</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
+          <t>https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Joule Energy and Data Center Campus</t>
+          <t>AI-GDC / Cipre Holding "Green Data Center"</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Millard County (Holden), Utah, EE.UU.</t>
+          <t>San Pedro Garza García, Nuevo León, México</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Joule Capital Partners</t>
+          <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4997,12 +5117,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
+          <t>https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5014,17 +5134,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amazon Montgomery County Campus</t>
+          <t>CleanArc Data Centers VA1 Campus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+          <t>Caroline County, Virginia, EE.UU.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>CleanArc Data Centers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5034,12 +5154,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Anuncio/permisos</t>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
+          <t>https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5051,17 +5171,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Google Montgomery County Campus</t>
+          <t>Joule Energy and Data Center Campus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+          <t>Millard County (Holden), Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Joule Capital Partners</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5071,12 +5191,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anuncio/permisos</t>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
+          <t>https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5088,17 +5208,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
+          <t>Amazon Montgomery County Campus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hood County, Texas, EE.UU.</t>
+          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Big Digital Energy + 10NetZero (JV)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5108,12 +5228,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Planeación/adquisición de sitio</t>
+          <t>Anuncio/permisos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
+          <t>https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5125,54 +5245,54 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Williams "Project Socrates"</t>
+          <t>Google Montgomery County Campus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Albany, Ohio, EE.UU.</t>
+          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Meta (vía Sidecat, LLC)</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Williams Companies / Will-Power</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
+          <t>Anuncio/permisos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Meta El Paso Campus (expansión)</t>
+          <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>El Paso, Texas, EE.UU.</t>
+          <t>Hood County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Big Digital Energy + 10NetZero (JV)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5182,12 +5302,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Permisos</t>
+          <t>Planeación/adquisición de sitio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
+          <t>https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5199,143 +5319,143 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SB Energy/SoftBank PORTS Technology Campus</t>
+          <t>Williams "Project Socrates"</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pike County, Ohio, EE.UU.</t>
+          <t>New Albany, Ohio, EE.UU.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
+          <t>Meta (vía Sidecat, LLC)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Williams Companies / Will-Power</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo temprano</t>
+          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Williams "Apollo" Power Generation Project</t>
+          <t>Meta El Paso Campus (expansión)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
+          <t>El Paso, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
+          <t>Permisos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Williams "Aquila" Power Project</t>
+          <t>SB Energy/SoftBank PORTS Technology Campus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Utah, EE.UU. (condado no revelado)</t>
+          <t>Pike County, Ohio, EE.UU.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
+          <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+          <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
+          <t>Williams "Apollo" Power Generation Project</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>West Texas, EE.UU. (condado no revelado)</t>
+          <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
+          <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
+          <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
+          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5347,54 +5467,54 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Crusoe/Tallgrass AI Data Center Campus (Project Jade)</t>
+          <t>Williams "Aquila" Power Project</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Condado de Laramie, Wyoming, EE.UU.</t>
+          <t>Utah, EE.UU. (condado no revelado)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Crusoe Energy / Tallgrass</t>
+          <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Desarrollo PAUSADO (Crusoe pausó actividades en jun-2026 a solicitud de su cliente; afecta también la generación de gas asociada BFC Power/Cheyenne Power Hub; aprobado ene-2026, 1.8GW inicial escalable a 10GW)</t>
+          <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
+          <t>https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Core Scientific Pecos Campus (expansión IA)</t>
+          <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pecos, Reeves County, Texas, EE.UU.</t>
+          <t>West Texas, EE.UU. (condado no revelado)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5404,12 +5524,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
+          <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
+          <t>https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5421,17 +5541,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stratos Project / Wonder Valley</t>
+          <t>Crusoe/Tallgrass AI Data Center Campus (Project Jade)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
+          <t>Condado de Laramie, Wyoming, EE.UU.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Leary Digital (Kevin O'Leary)</t>
+          <t>Crusoe Energy / Tallgrass</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5441,71 +5561,71 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
+          <t>Desarrollo PAUSADO (Crusoe pausó actividades en jun-2026 a solicitud de su cliente; afecta también la generación de gas asociada BFC Power/Cheyenne Power Hub; aprobado ene-2026, 1.8GW inicial escalable a 10GW)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
+          <t>https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fermi America Project Matador</t>
+          <t>Core Scientific Pecos Campus (expansión IA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Carson County (Amarillo), Texas, EE.UU.</t>
+          <t>Pecos, Reeves County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fermi America</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation (balance of plant, turbinas de gas)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Construcción (excavación de isla de turbinas completada; EPC firmado)</t>
+          <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/fermi-selects-primoris-services-corporation-to-engineer-and-construct-balance-of-plant-for-first-six-sgt-800-gas-turbines-of-phase-one-power-buildout-302814505.html)</t>
+          <t>https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NextEra Texas Power Generation Hub</t>
+          <t>Stratos Project / Wonder Valley</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anderson County, Texas, EE.UU.</t>
+          <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NextEra Energy Resources</t>
+          <t>O'Leary Digital (Kevin O'Leary)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5515,71 +5635,71 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
+          <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
+          <t>https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
+          <t>Fermi America Project Matador</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Monongalia County, Virginia Occidental, EE.UU.</t>
+          <t>Carson County (Amarillo), Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mon Power (FirstEnergy)</t>
+          <t>Fermi America</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Primoris Services Corporation (balance of plant, turbinas de gas)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
+          <t>Construcción (excavación de isla de turbinas completada; EPC firmado)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+          <t>https://www.prnewswire.com/news-releases/fermi-selects-primoris-services-corporation-to-engineer-and-construct-balance-of-plant-for-first-six-sgt-800-gas-turbines-of-phase-one-power-buildout-302814505.html</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IEP Greene County Data Center &amp; Power Plant</t>
+          <t>NextEra Texas Power Generation Hub</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Greene County, Pensilvania, EE.UU.</t>
+          <t>Anderson County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>International Electric Power</t>
+          <t>NextEra Energy Resources</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5589,12 +5709,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
+          <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
+          <t>https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5606,17 +5726,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS "Project Eagle"</t>
+          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
+          <t>Monongalia County, Virginia Occidental, EE.UU.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Amazon Web Services</t>
+          <t>Mon Power (FirstEnergy)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5626,34 +5746,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Permisos (presentados ante TDLR; construcción de 4 edificios, USD 1.2 mil millones, inicia 1-ago-2026)</t>
+          <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
+          <t>https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Crusoe/Lancium Childress Data Center Campus</t>
+          <t>IEP Greene County Data Center &amp; Power Plant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Condado de Childress, Texas, EE.UU.</t>
+          <t>Greene County, Pensilvania, EE.UU.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
+          <t>International Electric Power</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5663,49 +5783,49 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
+          <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+          <t>https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Williams "Neo" Power Innovation Project</t>
+          <t>AWS "Project Eagle"</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
+          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cliente de centro de datos no revelado</t>
+          <t>Amazon Web Services</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+          <t>Permisos (presentados ante TDLR; construcción de 4 edificios, USD 1.2 mil millones, inicia 1-ago-2026)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5717,106 +5837,106 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Williams "Socrates the Younger" Power Innovation Project</t>
+          <t>Crusoe/Lancium Childress Data Center Campus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
+          <t>Condado de Childress, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Meta Platforms (vía Sidecat, LLC)</t>
+          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
+          <t>https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Crusoe/Google "Goodnight Campus"</t>
+          <t>Williams "Neo" Power Innovation Project</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
+          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
+          <t>Cliente de centro de datos no revelado</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
+          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
+          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VoltaGrid/Serverfarm Covington</t>
+          <t>Williams "Socrates the Younger" Power Innovation Project</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
+          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serverfarm</t>
+          <t>Meta Platforms (vía Sidecat, LLC)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
+          <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
+          <t>https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5828,17 +5948,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
+          <t>Crusoe/Google "Goodnight Campus"</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
+          <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
+          <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5848,12 +5968,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
+          <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
+          <t>https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5865,106 +5985,106 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Homer City Energy Campus</t>
+          <t>VoltaGrid/Serverfarm Covington</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Condado de Indiana, Pensilvania, EE.UU.</t>
+          <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Homer City Redevelopment (HCR)</t>
+          <t>Serverfarm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
+          <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027)</t>
+          <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation)</t>
+          <t>https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nebius Vineland AI Data Center Campus</t>
+          <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vineland, Nueva Jersey, EE.UU.</t>
+          <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
+          <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>No especificado (motores reciprocantes de gas Bergen, ~30 unidades)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; meta de entrega nov-2026 en riesgo)</t>
+          <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[Data Center Knowledge](https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion)</t>
+          <t>https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TerraVolt Infrastructure AI Data Center Campus</t>
+          <t>Homer City Energy Campus</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
+          <t>Condado de Indiana, Pensilvania, EE.UU.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
+          <t>Homer City Redevelopment (HCR)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
+          <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
+          <t>https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5976,35 +6096,109 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Nebius Vineland AI Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Vineland, Nueva Jersey, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>No especificado (motores reciprocantes de gas Bergen, ~30 unidades)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; meta de entrega nov-2026 en riesgo)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TerraVolt Infrastructure AI Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>CyrusOne SAT14A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Castroville, San Antonio, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>CyrusOne (sin arrendatario asignado aún)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>Ingeniería/Permisos (6to campus en San Antonio, 11vo en Texas; USD 500 millones, 460,000 pies²; inicio de construcción previsto dic-2026)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -425,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx</t>
+          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/</t>
+          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/</t>
+          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/</t>
+          <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing</t>
+          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.techint.com/en/our-projects/dos-bocas-refinery</t>
+          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/</t>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/</t>
+          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/</t>
+          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/</t>
+          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html</t>
+          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/</t>
+          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321</t>
+          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm</t>
+          <t>[Alchempro](https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project</t>
+          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure</t>
+          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/</t>
+          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and</t>
+          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/</t>
+          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem</t>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/</t>
+          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1612,12 +1612,49 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Wabash Low-Carbon Ammonia Project</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>West Terre Haute, Indiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wabash Valley Resources</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Samsung E&amp;C (contrato EPF ~US$475 millones)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Construcción (groundbreaking 5-ene-2026; amoniaco bajo en carbono 500,000 ton/año con captura de 1.67 millones ton CO2/año; meta de finalización 2029)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -1632,16 +1669,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1709,7 +1746,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1746,7 +1783,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1783,7 +1820,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng</t>
+          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1820,7 +1857,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.gem.wiki/CP2_LNG_Terminal</t>
+          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1857,7 +1894,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/</t>
+          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1889,17 +1926,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción/Producción (Train 1: primer LNG mar-2026, primer cargamento exportado 22-abr-2026; Train 2 objetivo 2S2026; Train 3 objetivo 1S2027)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://lngprime.com/contracts-and-tenders/golden-pass-lng-contractors-ink-revised-epc-deal-for-second-and-third-train/169104/</t>
+          <t>[Port Arthur News](https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1968,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1968,7 +2005,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2005,7 +2042,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/</t>
+          <t>[Dossier Político](https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2042,7 +2079,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal</t>
+          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2079,7 +2116,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2116,7 +2153,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2153,7 +2190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/</t>
+          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2190,7 +2227,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos</t>
+          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2227,7 +2264,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/</t>
+          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2264,7 +2301,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2301,7 +2338,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project</t>
+          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2338,7 +2375,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ferc.gov/gulfstream-lng-terminal-project</t>
+          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2375,7 +2412,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/</t>
+          <t>[Glenfarne](https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2412,7 +2449,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2449,7 +2486,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline</t>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2486,7 +2523,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2523,7 +2560,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2560,7 +2597,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2597,7 +2634,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/</t>
+          <t>[World Oil](https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2629,17 +2666,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Permitting/Pre-FID (Draft EIS publicado abr-2026)</t>
+          <t>Permitting/Pre-FID (EIS Final publicado 24-jul-2026, avanzando desde Draft EIS de abr-2026; capacidad 8.4 Mtpa)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2026/04/17/2026-07517/deepwater-port-license-application-st-lng-deepwater-port-development-project-draft-environmental</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2708,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2708,7 +2745,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2745,7 +2782,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/</t>
+          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2782,12 +2819,123 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx</t>
+          <t>[Baker Hughes](https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Corpus Christi Stage 4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>San Patricio County / Corpus Christi, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cheniere Energy</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Permitting (solicitud FERC en proceso desde 17-feb-2026; DOE revisando solicitud de exportación; EIS borrador esperado sep-2026; incluye gasoducto de alimentación CCPL de 42"/26 millas)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Freeport LNG Train 4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Freeport, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Freeport LNG Development, L.P.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pre-FID (FERC extendió plazo de puesta en servicio a ago-2028; capacidad 5.1 Mtpa)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gasoducto Coatzacoalcos II (alimenta PODEBI Coatzacoalcos II)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Coatzacoalcos, Veracruz, México</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CFE / CENAGAS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Por definir (licitación pública, adjudicación 15-jul-2026)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bidding/Construcción inminente (9.69 km en dos etapas; inversión ~US$177 millones; plazo de ejecución 17 meses)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>[Proyectos México](https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -2802,16 +2950,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2879,7 +3027,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2916,7 +3064,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm</t>
+          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2953,7 +3101,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm</t>
+          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2990,7 +3138,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/</t>
+          <t>[Nevada Appeal](https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3027,7 +3175,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/</t>
+          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3064,7 +3212,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/</t>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3101,7 +3249,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico</t>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3138,7 +3286,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/</t>
+          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3175,7 +3323,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/</t>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3212,7 +3360,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/</t>
+          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3249,7 +3397,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3286,7 +3434,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3323,7 +3471,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update</t>
+          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3360,7 +3508,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3397,7 +3545,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/</t>
+          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3434,7 +3582,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3471,7 +3619,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html</t>
+          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3508,7 +3656,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html</t>
+          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3545,7 +3693,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm</t>
+          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3582,7 +3730,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit</t>
+          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3619,7 +3767,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3656,7 +3804,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/</t>
+          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3693,7 +3841,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico</t>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3730,7 +3878,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/</t>
+          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3767,7 +3915,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.fresnilloplc.com/portfolio/exploration/orisyvo/</t>
+          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3804,7 +3952,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3841,7 +3989,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3878,7 +4026,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3915,7 +4063,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/</t>
+          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3952,7 +4100,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/05/21/3299182</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3989,7 +4137,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4026,7 +4174,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://mineraalamos.com/our-assets/cerro-de-oro-project/</t>
+          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4063,7 +4211,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/</t>
+          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4100,7 +4248,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah</t>
+          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4137,7 +4285,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/</t>
+          <t>[InvestingNews](https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4174,12 +4322,197 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm</t>
+          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Elk Creek Critical Minerals Project</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Elk Creek, Nebraska, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NioCorp Developments Ltd.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; proyecto de niobio/escandio/titanio con planta de superficie que requerirá tubería de proceso)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Goldfield Project</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Goldfield, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Centerra Gold Inc.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ingeniería/Construcción temprana (ingeniería de detalle y procura de largo plazo en 2026; construcción mayor de pila de lixiviación y circuitos de trituración/procesamiento en 2027; primera producción fin de 2028)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[E&amp;MJ](https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cactus Mine (distrito Copper World/Arizona Sonoran)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Casa Grande, Arizona, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hudbay Minerals (adquisición de Arizona Sonoran Copper Co. anunciada 2-mar-2026)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Desarrollo/Feasibility (planta SX-EW de cátodos de cobre, ~103,000 t Cu/año proyectadas; Hudbay busca fusionarlo con el distrito Copper World adyacente ya rastreado)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Doby George Gold Project (Distrito Aura)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>~120 km al norte de Elko, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Western Exploration Inc.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No especificado (WSP realiza feasibility study; Stantec y Kappes Cassidy en estudios ambientales)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Feasibility/Permitting (PEA positiva 2025; Mine Plan of Operations en preparación; proyecto de lixiviación en pilas de óxidos)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[Western Exploration](https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Metates Project</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Durango, México</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chesapeake Gold Corp.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Feasibility (prefeasibility study objetivo 2026; pruebas metalúrgicas de lixiviación de sulfuros y estudios ambientales de línea base en curso; uno de los mayores depósitos de oro-plata no desarrollados de América)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[Chesapeake Gold Corp.](https://chesapeakegold.com/metates/)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -4194,16 +4527,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4271,7 +4604,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4308,7 +4641,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand</t>
+          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4345,7 +4678,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4382,7 +4715,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html</t>
+          <t>[CNBC](https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4419,7 +4752,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro</t>
+          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4456,7 +4789,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center</t>
+          <t>[UCS](https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4493,7 +4826,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4530,7 +4863,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4567,7 +4900,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4604,7 +4937,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4641,7 +4974,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4678,7 +5011,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/</t>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4715,7 +5048,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4752,7 +5085,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/</t>
+          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4789,7 +5122,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4826,7 +5159,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4863,7 +5196,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/</t>
+          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4900,7 +5233,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4937,7 +5270,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://openai.com/index/five-new-stargate-sites/</t>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4974,7 +5307,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://openai.com/index/five-new-stargate-sites/</t>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5011,7 +5344,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/</t>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5048,7 +5381,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5085,7 +5418,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/</t>
+          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -5122,7 +5455,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/</t>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5159,7 +5492,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/</t>
+          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5196,7 +5529,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center</t>
+          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5233,7 +5566,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county</t>
+          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5270,7 +5603,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county</t>
+          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5307,7 +5640,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5344,7 +5677,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5381,7 +5714,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5418,7 +5751,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5455,7 +5788,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5492,7 +5825,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/</t>
+          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5529,7 +5862,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5566,7 +5899,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site</t>
+          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5603,7 +5936,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/</t>
+          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5640,7 +5973,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/</t>
+          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5667,22 +6000,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation (balance of plant, turbinas de gas)</t>
+          <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Construcción (excavación de isla de turbinas completada; EPC firmado)</t>
+          <t>Construcción (excavación de isla de turbinas completada; EPC firmado; 3 turbinas de gas Siemens Energy SGT6-5000F, hasta 780MW ciclo simple, llegaron al Puerto de Houston 21-jul-2026 con destino al sitio; meta de 1GW en línea a fines de 2026)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/fermi-selects-primoris-services-corporation-to-engineer-and-construct-balance-of-plant-for-first-six-sgt-800-gas-turbines-of-phase-one-power-buildout-302814505.html</t>
+          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-announces-first-siemens-turbines-arrive-at-port-of-qg7ienp885jk.html)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -5714,7 +6047,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/</t>
+          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5751,7 +6084,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/</t>
+          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5788,7 +6121,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/</t>
+          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5825,7 +6158,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5862,7 +6195,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas</t>
+          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5899,7 +6232,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5936,7 +6269,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/</t>
+          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5973,7 +6306,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate</t>
+          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6010,7 +6343,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/</t>
+          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6047,7 +6380,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6084,7 +6417,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6121,7 +6454,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion</t>
+          <t>[Data Center Knowledge](https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6158,7 +6491,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6195,12 +6528,123 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EdgeConneX PowerConneX New Albany Energy Center (I y II)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>New Albany, Licking County, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EdgeConneX (propiedad de EQT Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>No especificado (desarrollado vía afiliada PowerConneX)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>xAI Colossus 2/Colossus 3 ("MACROHARDRR")</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Southaven, Misisipi / Memphis, Tennessee, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Operando parcialmente/en expansión con crisis regulatoria activa (59 turbinas de gas natural operando en Southaven, la mayoría sin permisos federales de Clean Air Act; demanda de NAACP/Southern Environmental Law Center/Earthjustice desde abr-2026; capacidad total del sitio creciendo hacia 2GW+ en tres edificios)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>[Technology.org](https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Applied Digital "Delta Forge 1" (planta de gas dedicada Cleco 756MW)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rapides Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cleco Power (planta de gas dedicada de 756MW)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Construcción (campus de USD 3.6 mil millones/430MW, la mayor carga individual jamás atendida por Cleco; rompimiento de tierra ene-2026; operaciones iniciales objetivo mediados de 2027)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,20 +29,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Arial"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,9 +63,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,13 +439,13 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,1184 +486,1184 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>America First Refining</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>America First Refining</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Fluor Corporation</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/FEED</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ExxonMobil Coastal Plain (cracker + PE)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Calhoun County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/FEED</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Golden Triangle Polymers</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Orange, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Chevron Phillips Chemical (CPChem) / QatarEnergy</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ZDJV (Zachry/DL USA); JKJV (JGC America/Kiewit)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Construcción (comisionamiento)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CF Industries Blue Point (amoniaco bajo carbono)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>CF Industries / JERA / Mitsui &amp; Co.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Technip Energies</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Plantas de gas — Cuenca Pérmica</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>West Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Enterprise Products / Targa Resources / Phillips 66</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Audubon Companies (parcial); otros no especificados</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Refinería Dos Bocas (Olmeca)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Paraíso, Tabasco, México</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Techint (parcial)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Construcción/ajustes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.techint.com/en/our-projects/dos-bocas-refinery</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Refinería de Tula (modernización)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Tula, Hidalgo, México</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Construcción/modernización</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Rehab. Etano-Etileno (Cangrejera/Morelos)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>POLIOLES S.A. de C.V.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rehab. Planta de Aromáticos (Cangrejera)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>ICA Fluor Daniel S. de R.L.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Proyecto Escolín (amoniaco/urea)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Poza Rica, Veracruz, México</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mota-Engil México (EPC confirmado; plazo de construcción 33 meses)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Rehab. Fertinal-ProAgro (urea y fosfatos)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas, Michoacán, México</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Pacífico Mexinol (metanol ultra bajo carbono)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Transition Industries</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Siemens Energy / Techint E&amp;C (FEED electrolizador)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Construcción (iniciada abr-2026)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>First Ammonia (amoniaco verde)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Victoria, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>First Ammonia / Cox Group USA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Worley (FEED)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Ingeniería (FEED completo) / FID prevista 2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Planta de Amoniaco Topolobampo (GPO)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Gas y Petroquímica de Occidente (GPO) / Proman AG</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Lake Charles Methanol II</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Lake Charles, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Lake Charles Methanol II LLC</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Zachry Group (FEED)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Ingeniería (FEED) / FID prevista</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Planta Coquizadora Salina Cruz</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Salina Cruz, Oaxaca, México</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>ICA Fluor</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Construcción (~74% avance)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Shintech Louisiana — Expansión Plaquemine (2do craqueador de etileno + 4ta unidad cloro-álcali/VCM)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Plaquemine, Iberville Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Shintech Louisiana, LLC</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (construcción por fases, 1a fase prevista 2030)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Sandpiper Chemicals (metanol bajo carbono)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Texas City, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Sandpiper Chemicals, LLC (INEOS Acetyls tomó participación accionaria)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Ingeniería (FEED en curso, 2T2026) / FID prevista 2027</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[Alchempro](https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>OXEA Bay City Capacity Expansion + Air Liquide POX Syngas Unit</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Bay City, Matagorda County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>OXEA (oxo chemicals) / Air Liquide (unidad de syngas)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Air Liquide (unidad propia); OXEA no especificado</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Construcción (FID confirmado 13-jul-2026; preparación de sitio 3T2026; finalización fines de 2028)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Targa Resources East Driver Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Condado de Midland, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Targa Resources Corp.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Construcción (planta criogénica 275 MMcf/d; arranque previsto 3T2026)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Enterprise Products "Athena" Natural Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Cuenca Midland (cuatro condados), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Enterprise Products Partners L.P.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Enterprise Products (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Construcción (300 MMcf/d + hasta 40,000 bpd de NGLs; en servicio 4T2026)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>MPLX Secretariat II Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Cuenca Pérmica (subcuenca Delaware), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Planeada/desarrollo (300 MMcf/d; en servicio 2S2028)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>MPLX Titan Complex (Northwind) — Expansión de Tratamiento de Gas Amargo</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Condado de Lea, Nuevo México / frontera TX-NM, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Construcción (expansión de capacidad &gt;400 MMcf/d; plenamente operativo 4T2026)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Northern Plains Nitrogen (urea/amoniaco)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Grand Forks, Dakota del Norte, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Northern Plains Nitrogen LLC</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>EPC no designado</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Pre-FEED completo / FID buscada 4T2026</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Iron Mesa (planta de gas)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Goldsmith, Ector County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Construcción (arranque previsto Q1 2027)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Yeti II (planta de gas)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Targa Resources</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Refinería Francisco I. Madero (rehabilitación)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Ciudad Madero, Tamaulipas, México</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Licitación/bidding</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Fermachem Planta de Urea/Amoniaco</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Ejido Sapioris, Lerdo, Durango, México</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Fermaca Dreams (Fermachem)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Construcción (ejecución iniciada jun-2026)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Clean Hydrogen Works</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>McDermott (FEED)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Ingeniería (FEED) / Pre-FID</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Zeus Gas Plant + 3ra Fraccionadora Coastal Bend</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, Texas / Robstown, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Ingeniería (sancionado; en línea 2028)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Project Meadowlark (complejo de amoniaco azul/UAN/ATS/DEF)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Gothenburg, Nebraska, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>J. Westling &amp; Co. (JWC Gburg, LLC)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>No especificado (tecnología licenciada Topsoe SynCOR Ammonia); contrato EPC/fabricación asegurado</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/Permisos (permiso de aire emitido, sitio zonificado; obras civiles previstas 2027, operación comercial 2029)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Wabash Low-Carbon Ammonia Project</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>West Terre Haute, Indiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Wabash Valley Resources</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Samsung E&amp;C (contrato EPF ~US$475 millones)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Construcción (groundbreaking 5-ene-2026; amoniaco bajo en carbono 500,000 ton/año con captura de 1.67 millones ton CO2/año; meta de finalización 2029)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
@@ -1669,16 +1680,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1719,1223 +1730,1260 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Rio Grande LNG (Trenes 1-5)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>NextDecade Corporation</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Port Arthur LNG Fase 2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Port Arthur, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Sempra Infrastructure</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Bechtel Energy Inc.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Woodside Louisiana LNG (ex-Driftwood)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Calcasieu Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Woodside Energy Group</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CP2 LNG Fase 2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Venture Global</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Worley</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Construcción (FID alcanzada mar-2026, NTP completo a Worley)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gem.wiki/CP2_LNG_Terminal</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Plaquemines LNG Fase 2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Venture Global</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>KBR / Zachry Group (KZJV)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Golden Pass LNG (Trenes 1-3)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Sabine Pass, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Golden Pass LNG (ExxonMobil/QatarEnergy)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Chiyoda / McDermott (CB&amp;I) / Zachry Group</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Construcción/Producción (Train 1: primer LNG mar-2026, primer cargamento exportado 22-abr-2026; Train 2 objetivo 2S2026; Train 3 objetivo 1S2027)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[Port Arthur News](https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Corpus Christi Stage 3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Corpus Christi, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Cheniere Energy</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026; primera producción de LNG esperada ago-2026, servicio comercial sep-2026)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Delfin FLNG 1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Golfo de México, costa afuera de Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Delfin Midstream</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Samsung Heavy Industries + Black &amp; Veatch</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Construcción (FID positiva jun-2026)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Saguaro Energía LNG + gasoducto Sierra Madre/Saguaro Connector</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Puerto Libertad, Sonora, México</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Mexico Pacific Limited</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Techint (obras tempranas); GDI Sicim Pipelines/Bonatti (gasoducto); EPC planta no especificado</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Pre-FID PAUSADO (suspensión judicial desde abr-2026 por demanda ambiental sobre ballenas en el Mar de Cortés; presión de activistas contra financiadores JPMorgan/Santander, 17-jul-2026; definición de autorización pendiente para 2026)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[Dossier Político](https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Altamira FLNG Train 2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Altamira, Tamaulipas, México</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>New Fortress Energy</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Texas LNG Brownsville</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Glenfarne Group</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Kiewit Energy Group</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Construcción (LNTP otorgado a Kiewit 4-jul-2026; HPS Investment Partners/BlackRock invirtió US$500M para obras tempranas, visto como paso final previo a FID; FID prevista fin de 2026)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Commonwealth LNG</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Caturus (Kimmeridge/Mubadala Energy/CPP Investments)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Technip Energies</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Construcción (Full NTP a Technip Energies; contrato de automatización principal a Yokogawa jul-2026)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Galveston LNG (Pelican Island)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Isla Pelican, Galveston, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Power LNG Ventures, LLC</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Permitting temprano (arrendamiento preliminar de 30 acres con Galveston Wharves; solicitud federal de exportación presentada; producción prevista dic-2028)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Energía Costa Azul (ECA LNG) Fase 2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Ensenada, Baja California, México</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Sempra Infrastructure / TotalEnergies</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/Pre-FID (Fase 1 operando desde jul-2026)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Gato Negro LNG</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Manzanillo, Colima, México</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Big River Energy</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Samsung E&amp;A (ingeniería)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Pre-FID (retrasado a fines de 2027)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Amigo LNG (FLNG)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Guaymas, Sonora, México</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Amigo LNG (Epsilon LNG / LNG Alliance)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Drydocks World (EPC de barcazas FLNG)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Construcción (conversión de FSU y fabricación de barcazas en Dubái; operación prevista 2a mitad 2028)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Coastal Bend LNG</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Ingleside, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Coastal Bend LNG (Kyomera Ventures/Amirian Group)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>KBR + Técnicas Reunidas (FEED)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Ingeniería (FEED)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Gulfstream LNG</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Gulfstream LNG Development LLC</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Pre-FID (trámite FERC, docket CP25-519)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ferc.gov/gulfstream-lng-terminal-project</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Alaska LNG (Fase 1: gasoducto + terminal Nikiski)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>North Slope a Nikiski, Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Glenfarne Group / Alaska Gasline Development Corp</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Pre-FID (avanzando hacia cierre financiero)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[Glenfarne](https://glenfarnegroup.com/glenfarne-announces-major-phase-one-alaska-lng-milestones-with-construction-line-pipe-supply-and-in-state-gas-agreements/)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Pre-FID (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381 necesario para el financiamiento de Glenfarne, 16-jul-2026; gobernador convocó sesión legislativa especial a partir del 27-jul-2026 para reintentar)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Gasoducto Naco–Guaymas (alimenta Amigo LNG)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Naco (frontera Sonora/Arizona) a Guaymas, Sonora, México</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Cenagas / LNG Alliance / Freedom LNG LLC</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ingeniería/pre-construcción (ceremonia binacional México-EE.UU. 25-jun-2026 formaliza avance del "Sonora Energy Corridor", 500km/US$2.8bn; aún sin FID)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Gasoducto Mustang Express (alimenta Port Arthur LNG Fase 2)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Katy a Port Arthur, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ARM Energy Holdings / PIMCO</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Construcción (FID alcanzada)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Gasoducto Naco–Guaymas (alimenta Amigo LNG)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Naco (frontera Sonora/Arizona) a Guaymas, Sonora, México</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Cenagas / LNG Alliance / Freedom LNG LLC</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Ingeniería/pre-construcción (ceremonia binacional México-EE.UU. 25-jun-2026 formaliza avance del "Sonora Energy Corridor", 500km/US$2.8bn; aún sin FID)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>PODEBI Coatzacoalcos II (planta LNG)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Villa Allende, Coatzacoalcos, Veracruz, México</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Ursus Energy</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Samsung E&amp;A (FEED+EPC); Honeywell (tecnología)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; primer desembolso de US$100M previsto fines de jul-2026; transición a obra civil, verano 2026)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Gasoducto Mustang Express (alimenta Port Arthur LNG Fase 2)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Katy a Port Arthur, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ARM Energy Holdings / PIMCO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Construcción (FID alcanzada)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PODEBI Coatzacoalcos II (planta LNG)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Villa Allende, Coatzacoalcos, Veracruz, México</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ursus Energy</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Samsung E&amp;A (FEED+EPC); Honeywell (tecnología)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; primer desembolso de US$100M previsto fines de jul-2026; transición a obra civil, verano 2026)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Delfin FLNG2 (segundo buque FLNG)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Golfo de México, costa afuera de Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Delfin Midstream / MidOcean Energy (EIG)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Siemens Energy (LNTP para equipo de largo plazo)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Pre-FID (LNTP emitido; FID prevista para fines de 2026)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Gasoducto Texas Gateway (alimenta terminales LNG del Golfo)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Carthage, Texas a Beauregard Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Gulf South Pipeline Company (Boardwalk Pipelines)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Open season vinculante (hasta 8-dic-2026) / FAST-41; en servicio previsto nov-2029</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Argent LNG (Port Fourchon)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Port Fourchon, Lafourche Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Argent LNG</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología modular NMBL); GIS Engineering (ingeniería marina/ambiental/de sitio, contrato ampliado)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ingeniería/Pre-FID (permitting FERC/DOE en curso para terminal de 25 MMtpa; inicio de construcción previsto 2026)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[World Oil](https://worldoil.com/news/2026/7/6/argent-lng-awards-engineering-contract-for-port-fourchon-lng-project/)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Permitting avanzado (DOE otorgó autorización de exportación FTA a 20 años para hasta 25 MMtpa, 24-jul-2026); ingeniería en curso; inicio de construcción previsto 2026</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>ST LNG Deepwater Port</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Costa afuera de Matagorda, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>ST LNG, LLC</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Permitting/Pre-FID (EIS Final publicado 24-jul-2026, avanzando desde Draft EIS de abr-2026; capacidad 8.4 Mtpa)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Gasoducto Mississippi Crossing (MSX)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Misisipi/Alabama, EE.UU.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Permitting (orden de certificado FERC esperada 31-jul-2026; USD 1.7 mil millones, 208 millas; alimenta demanda de LNG/generación en el sureste de EE.UU.)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Gasoducto South System Expansion 4 (SSE4)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Misisipi/Alabama/Georgia, EE.UU.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Permitting (orden de certificado FERC esperada 31-jul-2026; USD 3.5 mil millones, 291 millas; alimenta demanda de LNG/generación en el sureste de EE.UU.)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Gulf LNG Liquefaction Project</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Pascagoula, Misisipi, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Kinder Morgan (50%) / Thunderbird LNG LLC (30%) / Arc Logistics-Lightfoot Capital (20%)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Pre-FID/Permitting (Kinder Morgan solicitó extensión de permiso DOE no-FTA a jul-2031 tras no cumplir fecha límite de exportación jul-2026; 11.5 MTPA, ~USD 8 mil millones, dos trenes de licuefacción en terminal de importación existente)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sabine Pass LNG Expansion (Train 7 + unidad de re-licuefacción de boil-off gas)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Cheniere Energy Partners</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Bechtel (EPC); Baker Hughes (equipo mayor)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Construcción/Procura de equipo mayor (EPC firmado 28-may-2026; Baker Hughes recibió pedido de 7 turbinas de gas PGT25+ G4 y 15 compresores centrífugos, ~6 MTPA adicionales; construcción plena prevista inicios de 2027)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[Baker Hughes](https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Corpus Christi Stage 4</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>San Patricio County / Corpus Christi, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Cheniere Energy</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Permitting (solicitud FERC en proceso desde 17-feb-2026; DOE revisando solicitud de exportación; EIS borrador esperado sep-2026; incluye gasoducto de alimentación CCPL de 42"/26 millas)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Freeport LNG Train 4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Freeport, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Freeport LNG Development, L.P.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Pre-FID (FERC extendió plazo de puesta en servicio a ago-2028; capacidad 5.1 Mtpa)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Pre-FID/Regulatorio (FERC publicó aviso formal de solicitud para ampliar la tasa máxima horaria de producción de LNG del proyecto de licuefacción existente, Docket CP21-470-000, presentada 7-jul-2026; capacidad 5.1 Mtpa)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Gasoducto Coatzacoalcos II (alimenta PODEBI Coatzacoalcos II)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Coatzacoalcos, Veracruz, México</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CFE / CENAGAS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Por definir (licitación pública, adjudicación 15-jul-2026)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Bidding/Construcción inminente (9.69 km en dos etapas; inversión ~US$177 millones; plazo de ejecución 17 meses)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Gasoducto Coatzacoalcos II (alimenta PODEBI Coatzacoalcos II)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Coatzacoalcos, Veracruz, México</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CFE / CENAGAS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Por definir (licitación pública, adjudicación 15-jul-2026)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Bidding/Construcción inminente (9.69 km en dos etapas; inversión ~US$177 millones; plazo de ejecución 17 meses)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>[Proyectos México](https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Stabilis Galveston LNG (bunkering/carga a pequeña escala)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Puerto de Galveston, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Stabilis Solutions</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Permitting (Carta de Recomendación de la Guardia Costera de EE.UU. para instalación de carga/bunkering de LNG; nueva barcaza de bunkering Jones Act; producción prevista 3T2028)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2950,16 +2998,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3000,1519 +3048,1593 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Santa Cruz Copper Project</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Ivanhoe Electric Inc.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Fluor Corporation</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Ingeniería completada / construcción prevista H1 2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Copper World Complex</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Pima County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Hudbay Minerals (70%) / Mitsubishi Corporation (30%)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sundt, M3 Engineering, Ames, DRA Global, Knight Piésold, Mipac, Stantec</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/Feasibility (DFS &gt;85% completo)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Resolution Copper (Shaft No. 9)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Superior, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Rio Tinto (55%) / BHP (45%) JV</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Hatch</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Ingeniería temprana post intercambio de tierras (marzo 2026)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Thacker Pass Lithium Mine (Fase I)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Humboldt County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Lithium Americas Corp.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Construcción (10-20% avance)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[Nevada Appeal](https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>San Nicolás Copper-Zinc Project</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Zacatecas, México</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Teck Resources / Agnico Eagle Mines (JV 50/50)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Construcción, producción esperada 2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>El Arco Copper Project</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Baja California, México</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Ingeniería de detalle</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>El Pilar Copper Project</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Permisos ambientales asegurados (proyecto revaluado en US$551 millones; preparación de sitio inicia sep-2026, construcción plena 2027, primer cobre ~2028)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Buenavista del Cobre — Concentradora No. 2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Cananea, Sonora, México</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corporation</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/ejecución de expansión</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Media Luna Mine (North/EPO)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Guerrero, México</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Construcción (tubería de pasta pendiente)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Pumpkin Hollow Copper Mine (reinicio)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Yerington, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Nevada Copper Corp. (Kinterra Capital)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Planeación de reinicio/construcción</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Hermosa Critical Minerals Project (Taylor/Clark)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Santa Cruz County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>South32</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>DMC Mining Services (parcial)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026, cerrando revisión NEPA de infraestructura en Coronado National Forest; primer proyecto minero aceptado en programa federal FAST-41; ~50% avance en porción privada; primer concentrado ahora proyectado H1-2028, antes H1-2027)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Stibnite Gold Project</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Valley County, Idaho, EE.UU.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Perpetua Resources</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Hatch Ltd. (EPCM)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Construcción temprana</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>El Tigre Project</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Silver Tiger Metals</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Kappes, Cassiday &amp; Associates (EPCM)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Construcción (166 personas en sitio, 100,000 horas-hombre; primer vaciado previsto dic-2027)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Panuco Silver-Gold Project</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Sinaloa, México</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Vizsla Silver Corp.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Ingeniería de detalle/planeación de construcción (post-Feasibility Study)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>South Railroad Project (South Carlin Complex)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Elko/Eureka County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Orla Mining Ltd.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Construcción (inicio previsto mediados 2026, pendiente ROD final de BLM)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Copperstone Gold Project</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>La Paz County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Minera Alamos Inc.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Contratista de minería subterránea por definir</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Construcción (decisión de inversión may-2026)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>CK Gold Project</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Distrito Silver Crown, Laramie Range, Wyoming, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>U.S. Gold Corp</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Halyard-Micon International (feasibility); EPC por asignar</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Ingeniería completa/permisado a nivel estatal; inicio de construcción retrasado de 2026 a 1T2027 (complicaciones de suministro de agua y derecho de vía)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Distrito Santa Elena — Expansión (Santo Niño y Navidad)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>First Majestic Silver Corp.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Construcción (permisos recibidos jun-2026)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Galena Complex — Planta de Relleno en Pasta</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Wallace, Idaho, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Americas Gold and Silver Corporation</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Construcción (comisionamiento previsto Q4 2026)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Guanacevi Silver Project (Ocampo Mining)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Durango, México</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Minera Frisco (Grupo Carso)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Construcción (nueva planta de proceso; primera producción prevista fin de 2026)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Arctic Project (Distrito Minero Ambler)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Distrito Minero Ambler, Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Ambler Metals LLC (Trilogy Metals / South32, JV 50/50)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Permitting (cronograma coordinado de permisos federales/estatales publicado 16-jul-2026; revisión ambiental integrada de 29 meses liderada por USACE; ROD objetivo sep-2028)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Los Ricos South Mine</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Jalisco, México</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>GoGold Resources</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Construcción aprobada (permisos SEMARNAT jun-2026)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Cordero Project</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Chihuahua, México</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Discovery Silver</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Ausenco (ingeniería)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Feasibility completa / permitting (MIA pendiente ante SEMARNAT)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Gran Pilar Gold-Silver Project</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Tocvan Ventures</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Construcción (piloto; primer doré previsto Q4 2026)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Orisyvo Project</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Sierra Madre (Rarámuri), Chihuahua, México</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Fresnillo plc</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Pre-feasibility (transicionando a feasibility, resultados esperados medio 2026)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fresnilloplc.com/portfolio/exploration/orisyvo/</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Planta de Separación de Tierras Raras (US Army)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Tooele Army Depot, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>REalloys Inc.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Planta de Purificación de Grafito (US Army)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Pine Bluff Arsenal, Arkansas o Anniston Army Depot, Alabama (sin confirmar), EE.UU.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Titan Mining Corp.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Plantas de Litio y Boro (US Army)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Base militar de EE.UU. sin confirmar</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>EnergyX (litio) / ioneer Ltd. (boro)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027; producción 2028)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Expansión Concentradora La Caridad</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Nacozari, Sonora, México</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Grupo México</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Metso (equipo de trituración)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Construcción/procura de equipo (pedido adicional &gt;EUR 20M de trituración secundaria a Metso, jun-2026, complementa equipos Nordberg MP800 instalados en 2025)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Santo Tomás Copper Project</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Sinaloa, México</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Oroco Resource Corp.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Prefactibilidad (perforación fase 2 en curso; PFS objetivo 2T-3T 2027; capex estimado USD 2.84 mil millones; permisos federales pendientes)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/05/21/3299182</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Reapertura Fundición Hayden + Refinería Amarillo</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Hayden, Arizona / Amarillo, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Asarco (Grupo México)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Negociación/planeación (inversión ~USD 230 millones para reactivar fundición cerrada desde 2020; Grupo México evalúa hasta USD 6,000 millones adicionales para expansión de cobre en Arizona)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Cerro de Oro Gold Project</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Zacatecas, México</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Minera Alamos Inc.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Permitting (proyecto de oro a cielo abierto/heap leach; financiamiento de construcción ya asegurado)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://mineraalamos.com/our-assets/cerro-de-oro-project/</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Antler Copper Project</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Condado de Mohave, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>New World Resources Ltd. (respaldado por Kinterra Capital)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Permitting casi completo/inicio de construcción (BLM emitió Determinación de Adecuación NEPA; obras previstas 2do semestre 2026; embarque de concentrado previsto 2027)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Lisbon Valley Copper Project</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Condado de San Juan, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Lisbon Valley Mining Company, LLC</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Permitting federal completo (aprobación BLM + exención de acuífero EPA, oct-2025) / reapertura-construcción (agrega tajo abierto y pozos de recuperación in-situ)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>South West Arkansas Lithium Project (Central Processing Facility)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Sur de Arkansas, EE.UU.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Smackover Lithium (JV Standard Lithium / Equinor)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>S&amp;B Engineers and Constructors (EPCC); Hatch Ltd. (ingeniería de diseño/comisionamiento)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Ingeniería de detalle/procura temprana (contrato EPCC otorgado, NTP limitado activo; FID esperada en 2026; planta diseñada para 22,500 tpa de carbonato de litio grado batería)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>[InvestingNews](https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Bagdad Mine Concentrator Expansion</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Yavapai County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental estimado ~US$3,500 millones bajo revisión; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Elk Creek Critical Minerals Project</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Elk Creek, Nebraska, EE.UU.</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>NioCorp Developments Ltd.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; proyecto de niobio/escandio/titanio con planta de superficie que requerirá tubería de proceso)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Goldfield Project</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Goldfield, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Centerra Gold Inc.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/Construcción temprana (ingeniería de detalle y procura de largo plazo en 2026; construcción mayor de pila de lixiviación y circuitos de trituración/procesamiento en 2027; primera producción fin de 2028)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[E&amp;MJ](https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Cactus Mine (distrito Copper World/Arizona Sonoran)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Hudbay Minerals (adquisición de Arizona Sonoran Copper Co. anunciada 2-mar-2026)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Desarrollo/Feasibility (planta SX-EW de cátodos de cobre, ~103,000 t Cu/año proyectadas; Hudbay busca fusionarlo con el distrito Copper World adyacente ya rastreado)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Doby George Gold Project (Distrito Aura)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>~120 km al norte de Elko, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Western Exploration Inc.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>No especificado (WSP realiza feasibility study; Stantec y Kappes Cassidy en estudios ambientales)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Feasibility/Permitting (PEA positiva 2025; Mine Plan of Operations en preparación; proyecto de lixiviación en pilas de óxidos)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>[Western Exploration](https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Metates Project</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Durango, México</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Chesapeake Gold Corp.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Feasibility (prefeasibility study objetivo 2026; pruebas metalúrgicas de lixiviación de sulfuros y estudios ambientales de línea base en curso; uno de los mayores depósitos de oro-plata no desarrollados de América)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[Chesapeake Gold Corp.](https://chesapeakegold.com/metates/)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://chesapeakegold.com/metates/</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Libby Project (Cabinet Mountains)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Condado de Lincoln, Montana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Hecla Mining Company</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Permitting federal completado para exploración subterránea (extensión de ~1 milla del socavón Libby Adit; recurso potencial 1,500 millones lb de cobre y 183 millones oz de plata; pendiente permiso de descarga de agua de MT DEQ)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Donlin Gold</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Alaska, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>NovaGold Corporation (adquiriendo 100%, compra de participación del 40% de Paulson Advisers)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); aún sin decisión de construcción (FID)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4527,16 +4649,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4577,2074 +4699,2148 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Stargate Frontier Campus</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Shackelford County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Stargate Milam County (fast-build)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Milam County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Stargate Abilene Campus</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Abilene, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Crusoe / DPR Construction</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Microsoft Pecos Data Center Campus (Project Kilby)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Pecos/Reeves County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Chevron + Engine No. 1 (suministro de gas 20 años, sitio &gt;2,000 acres); turbinas GE Vernova/Caterpillar</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Ingeniería avanzada/Construcción temprana (capacidad rampa a 2.67GW; planta operativa 2028; FID de la planta esperada fines de 2026)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[CNBC](https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CloudHQ Querétaro (6 campus, incl. Campus Colón)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Colón y otras ubicaciones, Querétaro, México</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>CloudHQ</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Permisos/preparación de sitio (confirmado oficialmente por gobierno federal 7-jul-2026 bajo Plan México; inversión US$4,800M, 52 hectáreas, 900MW; subestación propia de 2GW prevista Q2 2027)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Meta Hyperion Data Center</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Richland Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Turner Construction / DPR Construction / Mortenson</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Construcción (escalado de ~2GW a 5GW de cómputo; inversión ampliada a USD 27-50 mil millones; Entergy busca aprobación regulatoria para 10 plantas de gas/7GW+ ante la Comisión de Servicio Público de Luisiana; juez ordenó a Meta divulgar información sobre 7 plantas adicionales, 14-jul-2026)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[UCS](https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Vantage Data Centers NV1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Storey County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CloudBurst San Marcos Data Center I</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>San Marcos/New Braunfels, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>CloudBurst Data Centers</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Evolve (eVOLVE Data Center Solutions)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Prometheus Hyperscale Dallas Campus</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Kaufman County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Prometheus Hyperscale</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>No especificado (socio energía: Engie)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/construcción temprana</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>GW Ranch Power Campus</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Pecos County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Pacifico Energy</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Permisos obtenidos/inicio construcción</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Amazon Mattermeade Data Center Campus</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Caroline/Spotsylvania County, Virginia, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Amazon (AWS)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Fermaca Digital City (+ gasoducto + planta de ciclo combinado)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Durango, Durango, México</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Grupo Fermaca (inquilino AI hyperscaler sin confirmar)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Permisos/negociación avanzada (construcción inminente)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Circe Energy West Texas AI Infrastructure Campus</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, West Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Circe Energy</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>No especificado (gen-sets Cummins)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/procurement</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Project Jupiter</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Santa Teresa/Sunland Park, Doña Ana County, Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BorderPlex Digital Assets/Stack (inquilino Oracle/OpenAI)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>No especificado (rediseño: hasta 2.45GW de celdas de combustible Bloom Energy, reemplazando turbinas de gas/diésel)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Construcción activa con riesgo regulatorio (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 14-jul-2026; NMED pospuso la decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas y programó audiencia pública para 19-oct-2026; meta de entrada en servicio ago-2026 en riesgo)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>PowerPlay AI "Greater Abilene" Data Center</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Área metropolitana de Abilene, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>PowerPlay AI (JV con socio Neocloud cotizado en Nasdaq, sin nombre público)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>IPP en proceso de RFP (aún sin seleccionar)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Ejecución activa post-adquisición de terreno (400MW behind-the-meter iniciales; arranque objetivo 2028)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Liberty Energy/PowerBridge "Alpha Digital Campus"</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Condado de Reeves, Texas, EE.UU. (cerca del hub de gas Waha)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>PowerBridge LLC</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Liberty Power Innovations (subsidiaria de Liberty Energy, JV)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>JV firmada/desarrollo temprano (~3,400 acres; primera fase &gt;300MW, primera entrega de energía prevista 4T2027; campus completo 2GW)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>New Era Energy &amp; Digital Hub</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Lea County, Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>New Era Energy &amp; Digital</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Planeación temprana (opción de terreno)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Texas Critical Data Centers (TCDC) Campus</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>New Era Energy &amp; Digital</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Stargate Lordstown</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Lordstown, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Construcción (rompimiento de tierra)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/five-new-stargate-sites/</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Stargate Wisconsin</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Vantage Data Centers (en sociedad con Oracle)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/five-new-stargate-sites/</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>AWS Región Digital Querétaro</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Querétaro, México</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Stargate Michigan (Saline Barn Campus)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Saline Township, Michigan, EE.UU.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Walbridge</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>North Dakota, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Applied Digital / Base Electron</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>AI-GDC / Cipre Holding "Green Data Center"</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>San Pedro Garza García, Nuevo León, México</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>CleanArc Data Centers VA1 Campus</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Caroline County, Virginia, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>CleanArc Data Centers</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Joule Energy and Data Center Campus</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Millard County (Holden), Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Joule Capital Partners</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Amazon Montgomery County Campus</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Anuncio/permisos</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Google Montgomery County Campus</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Anuncio/permisos</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Hood County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Big Digital Energy + 10NetZero (JV)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Planeación/adquisición de sitio</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Williams "Project Socrates"</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>New Albany, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Meta (vía Sidecat, LLC)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Williams Companies / Will-Power</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Meta El Paso Campus (expansión)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>El Paso, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Permisos</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>SB Energy/SoftBank PORTS Technology Campus</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Pike County, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Williams "Apollo" Power Generation Project</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Williams "Aquila" Power Project</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Utah, EE.UU. (condado no revelado)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>West Texas, EE.UU. (condado no revelado)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Crusoe/Tallgrass AI Data Center Campus (Project Jade)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Condado de Laramie, Wyoming, EE.UU.</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Crusoe Energy / Tallgrass</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Desarrollo PAUSADO (Crusoe pausó actividades en jun-2026 a solicitud de su cliente; afecta también la generación de gas asociada BFC Power/Cheyenne Power Hub; aprobado ene-2026, 1.8GW inicial escalable a 10GW)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Core Scientific Pecos Campus (expansión IA)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Pecos, Reeves County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Core Scientific</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Stratos Project / Wonder Valley</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>O'Leary Digital (Kevin O'Leary)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Fermi America Project Matador</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Carson County (Amarillo), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Fermi America</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas)</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Construcción (excavación de isla de turbinas completada; EPC firmado; 3 turbinas de gas Siemens Energy SGT6-5000F, hasta 780MW ciclo simple, llegaron al Puerto de Houston 21-jul-2026 con destino al sitio; meta de 1GW en línea a fines de 2026)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-announces-first-siemens-turbines-arrive-at-port-of-qg7ienp885jk.html)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stocktitan.net/news/FRMI/fermi-announces-first-siemens-turbines-arrive-at-port-of-qg7ienp885jk.html</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>NextEra Texas Power Generation Hub</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Anderson County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>NextEra Energy Resources</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Monongalia County, Virginia Occidental, EE.UU.</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Mon Power (FirstEnergy)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>IEP Greene County Data Center &amp; Power Plant</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Greene County, Pensilvania, EE.UU.</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>International Electric Power</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>AWS "Project Eagle"</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Permisos (presentados ante TDLR; construcción de 4 edificios, USD 1.2 mil millones, inicia 1-ago-2026)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Crusoe/Lancium Childress Data Center Campus</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Condado de Childress, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Williams "Neo" Power Innovation Project</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Cliente de centro de datos no revelado</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Williams "Socrates the Younger" Power Innovation Project</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Meta Platforms (vía Sidecat, LLC)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Crusoe/Google "Goodnight Campus"</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>VoltaGrid/Serverfarm Covington</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Serverfarm</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Homer City Energy Campus</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Condado de Indiana, Pensilvania, EE.UU.</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Homer City Redevelopment (HCR)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Nebius Vineland AI Data Center Campus</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Vineland, Nueva Jersey, EE.UU.</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>No especificado (motores reciprocantes de gas Bergen, ~30 unidades)</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; meta de entrega nov-2026 en riesgo)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[Data Center Knowledge](https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>TerraVolt Infrastructure AI Data Center Campus</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>CyrusOne SAT14A</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Castroville, San Antonio, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>CyrusOne (sin arrendatario asignado aún)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Ingeniería/Permisos (6to campus en San Antonio, 11vo en Texas; USD 500 millones, 460,000 pies²; inicio de construcción previsto dic-2026)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>EdgeConneX PowerConneX New Albany Energy Center (I y II)</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>New Albany, Licking County, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>EdgeConneX (propiedad de EQT Infrastructure)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>No especificado (desarrollado vía afiliada PowerConneX)</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>xAI Colossus 2/Colossus 3 ("MACROHARDRR")</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Southaven, Misisipi / Memphis, Tennessee, EE.UU.</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>xAI</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Operando parcialmente/en expansión con crisis regulatoria activa (59 turbinas de gas natural operando en Southaven, la mayoría sin permisos federales de Clean Air Act; demanda de NAACP/Southern Environmental Law Center/Earthjustice desde abr-2026; capacidad total del sitio creciendo hacia 2GW+ en tres edificios)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>[Technology.org](https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Applied Digital "Delta Forge 1" (planta de gas dedicada Cleco 756MW)</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Rapides Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Applied Digital</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Cleco Power (planta de gas dedicada de 756MW)</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Construcción (campus de USD 3.6 mil millones/430MW, la mayor carga individual jamás atendida por Cleco; rompimiento de tierra ene-2026; operaciones iniciales objetivo mediados de 2027)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Rubix Data Centers (Submer Group)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Russell, Kentucky, EE.UU. (antiguo sitio de acería AK Steel)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Rubix Data Centers / Submer Group</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta/planeación temprana (hasta 2GW, US$8-12 mil millones; moratoria municipal sobre solicitudes de data centers podría complicar el proyecto; fuente de energía aún no especificada)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>QTS/Lancium Hall County Campus</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Cerca de Turkey, Condado de Hall, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Lancium (dueño de sitio/energía) / QTS Data Centers (construcción/operación)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Lancium (autoabastecimiento solar+baterías; interconexión a red de 1GW; sin planta de gas confirmada)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Anuncio/desarrollo temprano (US$10 mil millones, hasta 11 edificios en 465 acres)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -35,6 +35,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -66,7 +67,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -436,16 +437,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,7 +514,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx</t>
+          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -550,7 +551,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/</t>
+          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -587,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/</t>
+          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,17 +620,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción (impulso federal de permisos anunciado may-2026 con finalización esperada en 45 días; CF Industries confirma inicio de construcción en 2026)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/</t>
+          <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/); [FuelCellsWorks](https://fuelcellsworks.com/2026/05/07/h2/cf-industries-targets-construction-start-this-year-on-blue-hydrogen-and-ammonia-complex)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -661,7 +662,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing</t>
+          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -698,7 +699,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.techint.com/en/our-projects/dos-bocas-refinery</t>
+          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -735,7 +736,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +773,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -809,7 +810,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/</t>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -846,7 +847,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/</t>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -878,17 +879,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ingeniería/rehabilitación</t>
+          <t>Ingeniería/rehabilitación (incorporado al plan de reactivación petroquímica de Pemex, jun-2026; 13,700 millones de pesos asignados para los complejos Lázaro Cárdenas y ProAgro; meta de 2.4 millones ton/año de urea y fertilizantes fosfatados)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/</t>
+          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); [Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -920,7 +921,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/</t>
+          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -957,7 +958,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/</t>
+          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -994,7 +995,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html</t>
+          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1031,7 +1032,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/</t>
+          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321</t>
+          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1105,7 +1106,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1142,7 +1143,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm</t>
+          <t>[Alchempro](https://www.alchempro.com/news/chemicals-news/ineos-backs-1-7-bn-low-carbon-methanol-project-in-texas-city-310108-newsdetails.htm)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1179,7 +1180,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1216,7 +1217,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1253,7 +1254,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1290,7 +1291,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1327,7 +1328,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project</t>
+          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1364,7 +1365,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure</t>
+          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1401,7 +1402,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/</t>
+          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1438,7 +1439,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and</t>
+          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1475,7 +1476,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/</t>
+          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1512,7 +1513,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem</t>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1549,7 +1550,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/</t>
+          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1586,7 +1587,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1623,7 +1624,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1660,12 +1661,49 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Green Fuels Operating — Refinería Duncan</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Duncan, Stephens County, Oklahoma, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Green Fuels Operating</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Construcción (groundbreaking 29-may-2026; inversión US$400 millones; capacidad inicial 30,000 bbl/d, expandible a 50,000 bbl/d, sobre sitio de refinería histórica de los años 1920)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1680,16 +1718,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1752,17 +1790,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción (FERC aprobó inicio de construcción de Trenes 4 y 5 en mar-2026; NextDecade evalúa un 6to tren para superar 36 mtpa; gasoducto de alimentación Rio Bravo Pipeline —138 millas, JV Whitewater/MPLX/Enbridge— en camino a entrar en servicio 2S2026)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); [Natural Gas Intel](https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1832,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1831,7 +1869,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng</t>
+          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1868,7 +1906,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.gem.wiki/CP2_LNG_Terminal</t>
+          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1905,7 +1943,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/</t>
+          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,7 +1980,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/</t>
+          <t>[Port Arthur News](https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1974,17 +2012,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026; primera producción de LNG esperada ago-2026, servicio comercial sep-2026)</t>
+          <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026; primera producción de LNG esperada ago-2026, servicio comercial sep-2026; Trenes 5 y 6 completados mar/jun-2026; expansión completa de 7 trenes 85.4% de avance, prevista para fin de 2026)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/corpus-christi-lng-train-7-cleared-to-introduce-fuel-gas-by-ferc); [LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2054,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2053,7 +2091,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/</t>
+          <t>[Dossier Político](https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2090,7 +2128,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal</t>
+          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2127,7 +2165,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2164,7 +2202,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2201,7 +2239,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/</t>
+          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2238,7 +2276,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos</t>
+          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2275,7 +2313,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/</t>
+          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2312,7 +2350,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2349,7 +2387,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project</t>
+          <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2386,7 +2424,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.ferc.gov/gulfstream-lng-terminal-project</t>
+          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2423,7 +2461,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/</t>
+          <t>[Alaska Beacon](https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2460,7 +2498,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2497,7 +2535,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline</t>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2534,7 +2572,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2571,7 +2609,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2608,7 +2646,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2645,7 +2683,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/</t>
+          <t>[World Oil](https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2682,7 +2720,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2719,7 +2757,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2756,7 +2794,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2793,7 +2831,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/</t>
+          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2830,7 +2868,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx</t>
+          <t>[Baker Hughes](https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2867,7 +2905,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2904,7 +2942,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2941,7 +2979,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/</t>
+          <t>[Proyectos México](https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2978,12 +3016,49 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/</t>
+          <t>[LNG Industry](https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CP2 LNG Fase 3</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Cameron Parish, Luisiana, EE.UU. (adyacente al complejo CP2 Fase 1/2)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Venture Global Inc.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>No especificado (pendiente FID)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Permitting (FERC exoneró proceso de pre-filing 16-abr-2026; solicitud formal presentada 26-may-2026; Notice of Application publicado 12-jun-2026; 6 bloques de licuefacción adicionales/12 trenes, planta de energía de 720MW, tercer atracadero marino; eleva capacidad pico del complejo de 28 a 35 mtpa)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2998,16 +3073,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3075,7 +3150,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3107,17 +3182,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ingeniería/Feasibility (DFS &gt;85% completo)</t>
+          <t>Ingeniería/Feasibility (DFS &gt;85% completo; colocación de bonos municipales por US$52 millones completada 24-jun-2026 para financiar el proyecto, ya totalmente permisado para iniciar construcción)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm</t>
+          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3144,17 +3219,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ingeniería temprana post intercambio de tierras (marzo 2026)</t>
+          <t>Ingeniería temprana post intercambio de tierras (marzo 2026); firmó Master Supply Agreement (1-jul-2026) con Johnson Controls Inc. y United Association Local 469 (sindicato de plomeros/pipefitters) para mantenimiento de instalaciones y soporte operativo en sitio</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm</t>
+          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); [Resolution Copper](https://resolutioncopper.com/resolution-copper-and-united-association-local-469-enter-into-master-supply-agreement-supporting-operations-in-arizona/)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3261,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/</t>
+          <t>[Nevada Appeal](https://www.nevadaappeal.com/news/2026/mar/26/lithium-americas-900-construction-workers-at-thacker-pass-mine/)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3223,7 +3298,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/</t>
+          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3260,7 +3335,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/</t>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3297,7 +3372,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico</t>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3334,7 +3409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/</t>
+          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,7 +3446,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/</t>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3408,7 +3483,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/</t>
+          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3445,7 +3520,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3482,7 +3557,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3519,7 +3594,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update</t>
+          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3556,7 +3631,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3593,7 +3668,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/</t>
+          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3630,7 +3705,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3667,7 +3742,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html</t>
+          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3704,7 +3779,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html</t>
+          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3741,7 +3816,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm</t>
+          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3778,7 +3853,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit</t>
+          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3815,7 +3890,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3847,17 +3922,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Construcción aprobada (permisos SEMARNAT jun-2026)</t>
+          <t>Construcción aprobada por el consejo (permisos SEMARNAT completos jun-2026; presupuesto ~US$227 millones; ventana de construcción de ~24 meses; primer vertido de metal previsto mediados de 2028)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/</t>
+          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); [Newsfile](https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3964,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico</t>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3926,7 +4001,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/</t>
+          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3963,7 +4038,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.fresnilloplc.com/portfolio/exploration/orisyvo/</t>
+          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4000,7 +4075,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4037,7 +4112,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4074,7 +4149,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4111,7 +4186,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/</t>
+          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4148,7 +4223,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/05/21/3299182</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4185,7 +4260,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4222,7 +4297,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://mineraalamos.com/our-assets/cerro-de-oro-project/</t>
+          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4259,7 +4334,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/</t>
+          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4296,7 +4371,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah</t>
+          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4333,7 +4408,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/</t>
+          <t>[InvestingNews](https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4370,7 +4445,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm</t>
+          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4407,7 +4482,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/</t>
+          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4444,7 +4519,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/</t>
+          <t>[E&amp;MJ](https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4481,7 +4556,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4518,7 +4593,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx</t>
+          <t>[Western Exploration](https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4555,7 +4630,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://chesapeakegold.com/metates/</t>
+          <t>[Chesapeake Gold Corp.](https://chesapeakegold.com/metates/)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4567,72 +4642,146 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Libby Project (Cabinet Mountains)</t>
+          <t>Pathfinder Tonopah (cobre-molibdeno-plata)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Condado de Lincoln, Montana, EE.UU.</t>
+          <t>Tonopah, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Hecla Mining Company</t>
+          <t>Pathfinder Minerals (Pathfinder Tonopah)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Bowman (permisos ambientales, FEED, planta piloto)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Permitting federal completado para exploración subterránea (extensión de ~1 milla del socavón Libby Adit; recurso potencial 1,500 millones lb de cobre y 183 millones oz de plata; pendiente permiso de descarga de agua de MT DEQ)</t>
+          <t>Permitting/FEED (avanzando hacia estudio de factibilidad definitivo; carta de interés no vinculante de EXIM Bank por US$896 millones para financiamiento, programa "Make More in America")</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/</t>
+          <t>[Mining Technology](https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>La Colorada Mine — Expansión Veta Madre/Veta Madre Plus</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Sonora, México</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Heliostar Metals</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Permisos completos obtenidos (2026); waste stripping programado 3T2026; producción de zona expandida esperada 1S2027</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Libby Project (Cabinet Mountains)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Condado de Lincoln, Montana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Hecla Mining Company</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Permitting federal completado para exploración subterránea (extensión de ~1 milla del socavón Libby Adit; recurso potencial 1,500 millones lb de cobre y 183 millones oz de plata; pendiente permiso de descarga de agua de MT DEQ)</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>[The Western News](https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>Donlin Gold</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>NovaGold Corporation (adquiriendo 100%, compra de participación del 40% de Paulson Advisers)</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); aún sin decisión de construcción (FID)</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
@@ -4649,16 +4798,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4721,17 +4870,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción (rompimiento de tierra formal completado; 1,200 acres/10 edificios/1.4GW; VoltaGrid aprobado para operar 210 generadores de gas industrial, 700MW combinados, permitiendo operación fuera de la red pública; primera instalación en servicio 2S2026)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); [Construction Owners](https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4912,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand</t>
+          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4800,7 +4949,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4837,7 +4986,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html</t>
+          <t>[CNBC](https://www.cnbc.com/2026/06/22/chevron-cvx-microsoft-msft-natural-gas-data-center.html)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4874,7 +5023,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro</t>
+          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4911,7 +5060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center</t>
+          <t>[UCS](https://www.ucs.org/about/news/judge-orders-meta-explain-new-gas-demand-hyperscale-louisiana-data-center)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4948,7 +5097,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4985,7 +5134,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5002,7 +5151,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kaufman County, Texas, EE.UU.</t>
+          <t>Entre Talty y Post Oak Bend City, Kaufman County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5017,17 +5166,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Ingeniería/construcción temprana</t>
+          <t>Ingeniería/construcción temprana (campus de 200MW/4 edificios; estrategia behind-the-meter con motores de gas Jenbacher J620 + almacenamiento en baterías de Engie; primera instalación 2026, fases hasta 2028)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5208,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5096,7 +5245,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5128,17 +5277,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Permisos/negociación avanzada (construcción inminente)</t>
+          <t>Permisos/negociación avanzada (inversión total US$3.7 mil millones: US$2.7B centro de datos + US$1B planta de fertilizantes Fermachem; gasoducto de 160km desde Texas; planta de ciclo combinado on-site de 350MW para alimentar data center de 250MW; Congreso de Durango aprobó donación de 50 hectáreas)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/</t>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); [DCD](https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5319,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5207,7 +5356,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/</t>
+          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5244,7 +5393,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5281,7 +5430,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5318,7 +5467,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/</t>
+          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5355,7 +5504,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5392,7 +5541,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/five-new-stargate-sites/</t>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5429,7 +5578,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/five-new-stargate-sites/</t>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5466,7 +5615,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/</t>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5503,7 +5652,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5540,7 +5689,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/</t>
+          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5577,7 +5726,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/</t>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5614,7 +5763,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/</t>
+          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5651,7 +5800,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center</t>
+          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5688,7 +5837,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county</t>
+          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -5725,7 +5874,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county</t>
+          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5762,7 +5911,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5799,7 +5948,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -5836,7 +5985,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5868,17 +6017,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo temprano</t>
+          <t>Planeación avanzada (SB Energy construirá 9.2GW de generación a gas natural, financiamiento de US$33.3 mil millones por SoftBank, más US$4.2 mil millones en transmisión; 26-jul-2026 trascendió que Nvidia negocia garantía financiera de hasta US$250 mil millones para que OpenAI arriende el sitio, primera fase de 800MW en 2028)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5910,7 +6059,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5947,7 +6096,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/</t>
+          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5984,7 +6133,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6021,7 +6170,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site</t>
+          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-06-09/crusoe-touts-5-gigawatts-worth-of-data-centers-deals-pauses-wyoming-site)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6058,7 +6207,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/</t>
+          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -6095,7 +6244,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/</t>
+          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -6132,7 +6281,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.stocktitan.net/news/FRMI/fermi-announces-first-siemens-turbines-arrive-at-port-of-qg7ienp885jk.html</t>
+          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-announces-first-siemens-turbines-arrive-at-port-of-qg7ienp885jk.html)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -6169,7 +6318,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/</t>
+          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -6206,7 +6355,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/</t>
+          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -6243,7 +6392,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/</t>
+          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -6280,7 +6429,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/aws-files-for-12bn-data-center-campus-outside-houston-texas/)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -6317,7 +6466,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas</t>
+          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -6354,7 +6503,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6391,7 +6540,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/</t>
+          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6428,7 +6577,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate</t>
+          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6465,7 +6614,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/</t>
+          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6502,7 +6651,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6539,7 +6688,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6576,7 +6725,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion</t>
+          <t>[Data Center Knowledge](https://www.datacenterknowledge.com/data-center-site-selection/nebius-plans-300-mw-data-center-in-new-jersey-amid-us-expansion)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6613,7 +6762,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6650,7 +6799,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6662,7 +6811,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>EdgeConneX PowerConneX New Albany Energy Center (I y II)</t>
+          <t>EdgeConneX PowerConneX New Albany Energy Center (I, II y III)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6682,17 +6831,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027)</t>
+          <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027; PowerConneX III, 430MW, notificación previa ante OPSB abr-2026, elevando capacidad total del sitio a ~766MW de gas)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/</t>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); [BeBeez](https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6873,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/</t>
+          <t>[Technology.org](https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6761,7 +6910,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/</t>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6798,7 +6947,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/</t>
+          <t>[Kentucky Lantern](https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6835,12 +6984,86 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic/Nexus Hubbard Campus</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Hubbard, Condado de Hill, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic (operado por Nexus Data Centers; respaldo financiero de Google)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Construcción iniciada (primera fase 500-612MW prevista 2026, ampliable a ~7.2-7.7GW; planta de gas natural behind-the-meter cerca de gasoducto principal)</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); [Construction Review](https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Stillwater Technology Park</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Lovejoy, Condado de Clayton, Georgia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Stillwater Development, LLC (cliente hyperscaler final no revelado)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Permisos ("development of regional impact" presentado ante el estado; hasta 15 edificios, 1.25GW, US$13 mil millones; generación de energía aún no confirmada, contempla interconexión con Central Georgia EMC)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,12 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,1421 +416,1458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>America First Refining</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>America First Refining</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Fluor Corporation</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ingeniería/FEED</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ExxonMobil Coastal Plain (cracker + PE)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Calhoun County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ingeniería/FEED</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Golden Triangle Polymers</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Orange, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Chevron Phillips Chemical (CPChem) / QatarEnergy</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>ZDJV (Zachry/DL USA); JKJV (JGC America/Kiewit)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Construcción (comisionamiento)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>CF Industries Blue Point (amoniaco bajo carbono)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>CF Industries / JERA / Mitsui &amp; Co.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Technip Energies</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción (impulso federal de permisos anunciado may-2026 con finalización esperada en 45 días; CF Industries confirma inicio de construcción en 2026)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/); [FuelCellsWorks](https://fuelcellsworks.com/2026/05/07/h2/cf-industries-targets-construction-start-this-year-on-blue-hydrogen-and-ammonia-complex)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Plantas de gas — Cuenca Pérmica</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>West Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Enterprise Products / Targa Resources / Phillips 66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Audubon Companies (parcial); otros no especificados</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Refinería Dos Bocas (Olmeca)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Paraíso, Tabasco, México</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Techint (parcial)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Construcción/ajustes</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Refinería de Tula (modernización)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Tula, Hidalgo, México</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Construcción/modernización</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Rehab. Etano-Etileno (Cangrejera/Morelos)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>POLIOLES S.A. de C.V.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Rehab. Planta de Aromáticos (Cangrejera)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>ICA Fluor Daniel S. de R.L.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Proyecto Escolín (amoniaco/urea)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Poza Rica, Veracruz, México</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Mota-Engil México (EPC confirmado; plazo de construcción 33 meses)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Rehab. Fertinal-ProAgro (urea y fosfatos)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas, Michoacán, México</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Ingeniería/rehabilitación (incorporado al plan de reactivación petroquímica de Pemex, jun-2026; 13,700 millones de pesos asignados para los complejos Lázaro Cárdenas y ProAgro; meta de 2.4 millones ton/año de urea y fertilizantes fosfatados)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); [Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Pacífico Mexinol (metanol ultra bajo carbono)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Transition Industries</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Siemens Energy / Techint E&amp;C (FEED electrolizador)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Construcción (iniciada abr-2026)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>First Ammonia (amoniaco verde)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Victoria, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>First Ammonia / Cox Group USA</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Worley (FEED)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Ingeniería (FEED completo) / FID prevista 2026</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Planta de Amoniaco Topolobampo (GPO)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Gas y Petroquímica de Occidente (GPO) / Proman AG</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Lake Charles Methanol II</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Lake Charles, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Lake Charles Methanol II LLC</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Zachry Group (FEED)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Ingeniería (FEED) / FID prevista</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Planta Coquizadora Salina Cruz</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Salina Cruz, Oaxaca, México</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>ICA Fluor</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Construcción (~74% avance)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Shintech Louisiana — Expansión Plaquemine (2do craqueador de etileno + 4ta unidad cloro-álcali/VCM)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Plaquemine, Iberville Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Shintech Louisiana, LLC</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (construcción por fases, 1a fase prevista 2030)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Sandpiper Chemicals (metanol bajo carbono)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Texas City, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Sandpiper Chemicals, LLC / INEOS Acetyls (colaboración estratégica, abr-2026)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Ingeniería (FEED en curso desde 2T2026; US$1,700 millones, 1.1 MMtpa; INEOS Acetyls tomará 300,000 ton/año para su unidad de ácido acético) / FID prevista 2027, primera producción ~2030</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>[INEOS](https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>OXEA Bay City Capacity Expansion + Air Liquide POX Syngas Unit</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Bay City, Matagorda County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>OXEA (oxo chemicals) / Air Liquide (unidad de syngas)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Air Liquide (unidad propia); OXEA no especificado</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Construcción (FID confirmado 13-jul-2026; preparación de sitio 3T2026; finalización fines de 2028)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Targa Resources East Driver Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Condado de Midland, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Targa Resources Corp.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Construcción (planta criogénica 275 MMcf/d; arranque previsto 3T2026)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Enterprise Products "Athena" Natural Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Cuenca Midland (cuatro condados), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Enterprise Products Partners L.P.</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Enterprise Products (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Construcción (300 MMcf/d + hasta 40,000 bpd de NGLs; en servicio 4T2026)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>MPLX Secretariat II Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Cuenca Pérmica (subcuenca Delaware), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Planeada/desarrollo (300 MMcf/d; en servicio 2S2028)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>MPLX Titan Complex (Northwind) — Expansión de Tratamiento de Gas Amargo</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Condado de Lea, Nuevo México / frontera TX-NM, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Construcción (expansión de capacidad &gt;400 MMcf/d; plenamente operativo 4T2026)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Northern Plains Nitrogen (urea/amoniaco)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Grand Forks, Dakota del Norte, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Northern Plains Nitrogen LLC</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>EPC no designado</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Pre-FEED completo / FID buscada 4T2026</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Iron Mesa (planta de gas)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Goldsmith, Ector County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Construcción (arranque previsto Q1 2027)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Yeti II (planta de gas)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Targa Resources</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Refinería Francisco I. Madero (rehabilitación)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Ciudad Madero, Tamaulipas, México</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Pemex</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Licitación/bidding</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Fermachem Planta de Urea/Amoniaco</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Ejido Sapioris, Lerdo, Durango, México</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Fermaca Dreams (Fermachem)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Construcción (ejecución iniciada jun-2026)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Clean Hydrogen Works</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>McDermott (FEED)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Ingeniería (FEED) / Pre-FID</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Zeus Gas Plant + 3ra Fraccionadora Coastal Bend</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, Texas / Robstown, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Phillips 66</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Ingeniería (sancionado; en línea 2028)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Project Meadowlark (complejo de amoniaco azul/UAN/ATS/DEF)</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Gothenburg, Nebraska, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>J. Westling &amp; Co. (JWC Gburg, LLC)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>No especificado (tecnología licenciada Topsoe SynCOR Ammonia); contrato EPC/fabricación asegurado</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Ingeniería/Permisos (permiso de aire emitido, sitio zonificado; obras civiles previstas 2027, operación comercial 2029)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Wabash Low-Carbon Ammonia Project</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>West Terre Haute, Indiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Wabash Valley Resources</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Samsung E&amp;C (contrato EPF ~US$475 millones)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Construcción (groundbreaking 5-ene-2026; amoniaco bajo en carbono 500,000 ton/año con captura de 1.67 millones ton CO2/año; meta de finalización 2029)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Green Fuels Operating — Refinería Duncan</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Duncan, Stephens County, Oklahoma, EE.UU.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Green Fuels Operating</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Construcción (groundbreaking 29-may-2026; inversión US$400 millones; capacidad inicial 30,000 bbl/d, expandible a 50,000 bbl/d, sobre sitio de refinería histórica de los años 1920)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Energy Transfer Mustang Draw I &amp; II (plantas de gas)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Cuenca Midland, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Energy Transfer LP</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Construcción (Mustang Draw I en comisionamiento, servicio pleno ~jun-2026; Mustang Draw II en construcción, en servicio 4T2026; 275 MMcf/d cada una)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>[Energy Transfer](https://www.energytransfer.com/project-highlights/)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>ONEOK Bighorn / Cutter / Shadowfax (plantas de gas)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Cuenca Delaware (Bighorn), Texas / Cuenca Powder River (Cutter), Wyoming / Cuenca Midland (Shadowfax reubicada), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>ONEOK Inc.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>Construcción (Bighorn US$365 millones/300 MMcf/d tratamiento alto CO2, meta mediados 2027; Cutter 60 MMcf/d en construcción, meta 4T2026; Shadowfax 150 MMcf/d reubicación completada 1T2026, en rampa)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>[Inspectioneering](https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>MPLX Harmon Creek III (planta de gas + de-etanizadora)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Región Marcellus/Utica, noreste de EE.UU. (ubicación exacta no especificada)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>MPLX LP</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Construcción (300 MMcf/d + de-etanizadora 40 Mbpd; en servicio 3T2026)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Rehab. Complejo Cosoleacaque (amoniaco) + Complejo Morelos (etano-etileno)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Cosoleacaque y Complejo Morelos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Pemex Transformación Industrial</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Ingeniería/planeación (parte del plan de reactivación petroquímica de Pemex de 93,000 mdp anunciado jun-2026; 13,000 mdp para 2 plantas de amoniaco en Cosoleacaque, meta 957,000 ton/año; Complejo Morelos incluido en programa de rehabilitación etano-etileno de 30,000 mdp/5 plantas, meta 520,000 ton/año de polietilenos/óxido de etileno/glicoles)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>[Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Enterprise Products — Nuevas Plantas de Gas Permian (Plant 11 Midland / Plant 13 Delaware) + NGL Frac 15 Mont Belvieu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cuenca Midland y Cuenca Delaware, Texas, EE.UU. / Mont Belvieu, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Enterprise Products Partners L.P.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Enterprise Products (propietario-constructor)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Construcción (sancionadas/aprobadas en resultados 2T2026: Plant 11 Midland Basin 300 MMcf/d en servicio 1T2029; Plant 13 Delaware Basin 300 MMcf/d en servicio 3T2028; NGL Frac 15 en Mont Belvieu 150 MBPD en servicio 1T2028; gasto de capital de crecimiento 2026 aumentado en más de US$700 millones por estas sanciones)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1856,1415 +1886,1415 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Rio Grande LNG (Trenes 1-5)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>NextDecade Corporation</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Construcción (FERC aprobó inicio de construcción de Trenes 4 y 5 en mar-2026; NextDecade evalúa un 6to tren para superar 36 mtpa; gasoducto de alimentación Rio Bravo Pipeline —138 millas, JV Whitewater/MPLX/Enbridge— en camino a entrar en servicio 2S2026)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); [Natural Gas Intel](https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Port Arthur LNG Fase 2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Port Arthur, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sempra Infrastructure</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Bechtel Energy Inc.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Woodside Louisiana LNG (ex-Driftwood)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Calcasieu Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Woodside Energy Group</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>CP2 LNG Fase 2</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Venture Global</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Worley</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción (FID alcanzada mar-2026, NTP completo a Worley; Baker Hughes recibió pedido para suministrar 12 módulos de licuefacción, reportado semana del 20-26 jul-2026)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal); [LNG Prime](https://lngprime.com/americas/top-5-news-of-the-week-july-20-26/193119/)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Plaquemines LNG Fase 2</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Venture Global</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>KBR / Zachry Group (KZJV)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Golden Pass LNG (Trenes 1-3)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sabine Pass, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Golden Pass LNG (ExxonMobil/QatarEnergy)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Chiyoda / McDermott (CB&amp;I) / Zachry Group</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Construcción/Producción (Train 1: primer LNG mar-2026, primer cargamento exportado 22-abr-2026; Train 2 objetivo 2S2026; Train 3 objetivo 1S2027)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>[Port Arthur News](https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Corpus Christi Stage 3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Corpus Christi, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Cheniere Energy</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026, y autorizó introducción de gas natural al Train 7, 28-jul-2026; primera producción de LNG esperada ago-2026, servicio comercial sep-2026; Trenes 5 y 6 completados mar/jun-2026; expansión completa de 7 trenes 85.4% de avance, prevista para fin de 2026)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>[PGJ](https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); [LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Delfin FLNG 1</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Golfo de México, costa afuera de Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Delfin Midstream</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Samsung Heavy Industries + Black &amp; Veatch</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Construcción (FID positiva jun-2026)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Saguaro Energía LNG + gasoducto Sierra Madre/Saguaro Connector</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Puerto Libertad, Sonora, México</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Mexico Pacific Limited</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Techint (obras tempranas); GDI Sicim Pipelines/Bonatti (gasoducto); EPC planta no especificado</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Pre-FID PAUSADO (suspensión judicial desde abr-2026 por demanda ambiental sobre ballenas en el Mar de Cortés; presión de activistas contra financiadores JPMorgan/Santander, 17-jul-2026; afiliada de ONEOK solicitó extensión de 3 años del plazo de construcción del Saguaro Connector Pipeline, de feb-2027 a feb-2030, confirmando que la construcción del gasoducto aún no inicia; definición de autorización pendiente para 2026)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>[Dossier Político](https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/); [Natural Gas Intel](https://naturalgasintel.com/news/oneok-affiliate-seeks-3-year-extension-for-saguaro-connector-pipeline/)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Altamira FLNG Train 2</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Altamira, Tamaulipas, México</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>New Fortress Energy</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Texas LNG Brownsville</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Brownsville, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Glenfarne Group</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Kiewit Energy Group</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Construcción (LNTP otorgado a Kiewit 4-jul-2026; HPS Investment Partners/BlackRock invirtió US$500M para obras tempranas, visto como paso final previo a FID; FID prevista fin de 2026)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Commonwealth LNG</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Caturus (Kimmeridge/Mubadala Energy/CPP Investments)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Technip Energies</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Construcción (Full NTP a Technip Energies; contrato de automatización principal a Yokogawa jul-2026)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Galveston LNG (Pelican Island)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Isla Pelican, Galveston, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Power LNG Ventures, LLC</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Permitting temprano (arrendamiento preliminar de 30 acres con Galveston Wharves; solicitud federal de exportación presentada; producción prevista dic-2028)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Energía Costa Azul (ECA LNG) Fase 2</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Ensenada, Baja California, México</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sempra Infrastructure / TotalEnergies</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Ingeniería/Pre-FID (Fase 1 operando desde jul-2026)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ingeniería/Pre-FID (Fase 1: se detectó daño en compresores de refrigerante durante inspección posterior al primer cargamento —cargado 7-jul-2026—, lo que obligó a extender el comisionamiento; finalización sustancial ahora prevista para 4T2026, antes se esperaba para verano 2026; Sempra indica que no afecta su guía de utilidades 2026-2027)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos); [LNG Prime](https://lngprime.com/lng-terminals/sempra-infrastructure-extends-eca-lng-commissioning-due-to-compressor-damage/193584/)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gato Negro LNG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Manzanillo, Colima, México</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Big River Energy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Samsung E&amp;A (ingeniería)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pre-FID (retrasado a fines de 2027)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Gato Negro LNG</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Manzanillo, Colima, México</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Big River Energy</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Samsung E&amp;A (ingeniería)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Pre-FID (retrasado a fines de 2027)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Amigo LNG (FLNG)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Guaymas, Sonora, México</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Amigo LNG (Epsilon LNG / LNG Alliance)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Drydocks World (EPC de barcazas FLNG)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Construcción (conversión de FSU y fabricación de barcazas en Dubái; operación prevista 2a mitad 2028)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Coastal Bend LNG</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Ingleside, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Coastal Bend LNG (Kyomera Ventures/Amirian Group)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>KBR + Técnicas Reunidas (FEED)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ingeniería (FEED)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>[KBR](https://www.kbr.com/en/insights-news/press-release/kbr-awarded-feed-coastal-bend-lng-project)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Gulfstream LNG</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Plaquemines Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Gulfstream LNG Development LLC</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Pre-FID (trámite FERC, docket CP25-519)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Alaska LNG (Fase 1: gasoducto + terminal Nikiski)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>North Slope a Nikiski, Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Glenfarne Group / Alaska Gasline Development Corp</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Pre-FID (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381 necesario para el financiamiento de Glenfarne, 16-jul-2026; gobernador convocó sesión legislativa especial a partir del 27-jul-2026 para reintentar)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>[Alaska Beacon](https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Gasoducto Naco–Guaymas (alimenta Amigo LNG)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Naco (frontera Sonora/Arizona) a Guaymas, Sonora, México</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Cenagas / LNG Alliance / Freedom LNG LLC</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Ingeniería/pre-construcción (ceremonia binacional México-EE.UU. 25-jun-2026 formaliza avance del "Sonora Energy Corridor", 500km/US$2.8bn; aún sin FID)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Gasoducto Mustang Express (alimenta Port Arthur LNG Fase 2)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Katy a Port Arthur, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>ARM Energy Holdings / PIMCO</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Construcción (FID alcanzada)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>PODEBI Coatzacoalcos II (planta LNG)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Villa Allende, Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ursus Energy</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Samsung E&amp;A (FEED+EPC); Honeywell (tecnología)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; primer desembolso de US$100M previsto fines de jul-2026; transición a obra civil, verano 2026)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Delfin FLNG2 (segundo buque FLNG)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Golfo de México, costa afuera de Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Delfin Midstream / MidOcean Energy (EIG)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Siemens Energy (LNTP para equipo de largo plazo)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Pre-FID (LNTP emitido; FID prevista para fines de 2026)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Gasoducto Texas Gateway (alimenta terminales LNG del Golfo)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Carthage, Texas a Beauregard Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Gulf South Pipeline Company (Boardwalk Pipelines)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Open season vinculante (hasta 8-dic-2026) / FAST-41; en servicio previsto nov-2029</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Argent LNG (Port Fourchon)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Port Fourchon, Lafourche Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Argent LNG</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología modular NMBL); GIS Engineering (ingeniería marina/ambiental/de sitio, contrato ampliado)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Permitting avanzado (DOE otorgó autorización de exportación FTA a 20 años para hasta 25 MMtpa, 24-jul-2026); ingeniería en curso; inicio de construcción previsto 2026</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>[World Oil](https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>ST LNG Deepwater Port</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Costa afuera de Matagorda, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>ST LNG, LLC</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Baker Hughes (tecnología)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Permitting/Pre-FID (EIS Final publicado 24-jul-2026, avanzando desde Draft EIS de abr-2026; capacidad 8.4 Mtpa)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Gasoducto Mississippi Crossing (MSX)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Misisipi/Alabama, EE.UU.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Permitting (orden de certificado FERC esperada 31-jul-2026; USD 1.7 mil millones, 208 millas; alimenta demanda de LNG/generación en el sureste de EE.UU.)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Gasoducto South System Expansion 4 (SSE4)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Misisipi/Alabama/Georgia, EE.UU.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Permitting (orden de certificado FERC esperada 31-jul-2026; USD 3.5 mil millones, 291 millas; alimenta demanda de LNG/generación en el sureste de EE.UU.)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Gulf LNG Liquefaction Project</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Pascagoula, Misisipi, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Kinder Morgan (50%) / Thunderbird LNG LLC (30%) / Arc Logistics-Lightfoot Capital (20%)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Pre-FID/Permitting (Kinder Morgan solicitó extensión de permiso DOE no-FTA a jul-2031 tras no cumplir fecha límite de exportación jul-2026; 11.5 MTPA, ~USD 8 mil millones, dos trenes de licuefacción en terminal de importación existente)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Sabine Pass LNG Expansion (Train 7 + unidad de re-licuefacción de boil-off gas)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Cheniere Energy Partners</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Bechtel (EPC); Baker Hughes (equipo mayor)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Construcción/Procura de equipo mayor (EPC firmado 28-may-2026; Baker Hughes recibió pedido de 7 turbinas de gas PGT25+ G4 y 15 compresores centrífugos, ~6 MTPA adicionales; construcción plena prevista inicios de 2027)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>[Baker Hughes](https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Corpus Christi Stage 4</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>San Patricio County / Corpus Christi, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Cheniere Energy</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Permitting (solicitud FERC en proceso desde 17-feb-2026; DOE revisando solicitud de exportación; EIS borrador esperado sep-2026; incluye gasoducto de alimentación CCPL de 42"/26 millas)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>[Federal Register](https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Freeport LNG Train 4</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Freeport, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Freeport LNG Development, L.P.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Pre-FID/Regulatorio (FERC otorgó extensión de 40 meses del plazo de construcción, en servicio ahora hasta dic-2031, aprobada 17-jul-2026; además FERC publicó aviso formal de solicitud para ampliar la tasa máxima horaria de producción de LNG del proyecto de licuefacción existente, Docket CP21-470-000, presentada 7-jul-2026; capacidad 5.1 Mtpa)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/); [Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Gasoducto Coatzacoalcos II (alimenta PODEBI Coatzacoalcos II)</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Coatzacoalcos, Veracruz, México</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>CFE / CENAGAS</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Por definir (licitación pública, adjudicación 15-jul-2026)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Bidding/Construcción inminente (9.69 km en dos etapas; inversión ~US$177 millones; plazo de ejecución 17 meses)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>[Proyectos México](https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Stabilis Galveston LNG (bunkering/carga a pequeña escala)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Puerto de Galveston, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Stabilis Solutions</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Permitting (Carta de Recomendación de la Guardia Costera de EE.UU. para instalación de carga/bunkering de LNG; nueva barcaza de bunkering Jones Act; producción prevista 3T2028)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>[LNG Industry](https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>CP2 LNG Fase 3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Cameron Parish, Luisiana, EE.UU. (adyacente al complejo CP2 Fase 1/2)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Venture Global Inc.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>No especificado (pendiente FID)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Permitting (FERC exoneró proceso de pre-filing 16-abr-2026; solicitud formal presentada 26-may-2026; Notice of Application publicado 12-jun-2026; 6 bloques de licuefacción adicionales/12 trenes, planta de energía de 720MW, tercer atracadero marino; eleva capacidad pico del complejo de 28 a 35 mtpa)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>[Federal Register](https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Cameron LNG Fase 2</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Hackberry, Cameron Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Sempra Infrastructure / TotalEnergies / Mitsui / Mitsubishi / NYK (JV)</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Bechtel (EPC seleccionado 2023)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Pre-FID/Permitting (1 tren adicional de 6.75 mtpa + debottlenecking de 3 trenes existentes; FERC otorgó extensión de 5 años para construcción hasta 2033, nov-2025)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>[LNG Prime](https://lngprime.com/americas/cameron-lng-seeks-ferc-extension-for-expansion-project/167382/)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Magnolia LNG</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Lake Charles, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Magnolia LNG, LLC (LNG Ltd.)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Permitting (estatus inactivo/dormido; solicitó extensión FERC a 5 años hasta abr-2031; aún sin autorización de exportación no-FTA; planta de 8.8 mtpa)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>[Federal Register](https://www.federalregister.gov/documents/2026/02/23/2026-03548/magnolia-lng-llc-notice-of-request-for-extension-of-time)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3285,1859 +3315,1859 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Santa Cruz Copper Project</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ivanhoe Electric Inc.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Fluor Corporation</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ingeniería completada (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año) / construcción prevista H1 2026; EXIM Bank emitió carta de interés para financiamiento de hasta US$825 millones</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); [Ivanhoe Electric](https://ivanhoeelectric.com/news/ivanhoe-electric-receives-indication-for-up-to-825-million-in-financing-from-export-import-bank-of-the-united-states-for-santa/)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Copper World Complex</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Pima County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Hudbay Minerals (70%) / Mitsubishi Corporation (30%)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sundt, M3 Engineering, Ames, DRA Global, Knight Piésold, Mipac, Stantec</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ingeniería/Feasibility (DFS &gt;85% completo; colocación de bonos municipales por US$52 millones completada 24-jun-2026 para financiar el proyecto, ya totalmente permisado para iniciar construcción)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Resolution Copper (Shaft No. 9)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Superior, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Rio Tinto (55%) / BHP (45%) JV</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hatch</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Ingeniería temprana post intercambio de tierras (marzo 2026); firmó Master Supply Agreement (1-jul-2026) con Johnson Controls Inc. y United Association Local 469 (sindicato de plomeros/pipefitters) para mantenimiento de instalaciones y soporte operativo en sitio</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); [Resolution Copper](https://resolutioncopper.com/resolution-copper-and-united-association-local-469-enter-into-master-supply-agreement-supporting-operations-in-arizona/)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Thacker Pass Lithium Mine (Fase I)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Humboldt County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Lithium Americas Corp.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Bechtel</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción (ingeniería de detalle &gt;95% completa, procura &gt;70% completa a may-2026; capex guía 2026 de US$1,300-1,600 millones; terminación mecánica prevista fines de 2027)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>[Mining Weekly](https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); [Lithium Americas](https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>San Nicolás Copper-Zinc Project</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Zacatecas, México</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Teck Resources / Agnico Eagle Mines (JV 50/50)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Construcción, producción esperada 2026</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>El Arco Copper Project</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Baja California, México</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Ingeniería de detalle</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>El Pilar Copper Project</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Permisos ambientales asegurados (proyecto revaluado en US$551 millones; preparación de sitio inicia sep-2026, construcción plena 2027, primer cobre ~2028)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>[BNamericas](https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Buenavista del Cobre — Concentradora No. 2</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cananea, Sonora, México</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corporation</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Ingeniería/ejecución de expansión</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Media Luna Mine (North/EPO)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Guerrero, México</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Construcción (tubería de pasta pendiente)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Pumpkin Hollow Copper Mine (reinicio)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Yerington, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Nevada Copper Corp. (Kinterra Capital)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Planeación de reinicio/construcción</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Hermosa Critical Minerals Project (Taylor/Clark)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Santa Cruz County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>South32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>DMC Mining Services (parcial)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026, cerrando revisión NEPA de infraestructura en Coronado National Forest; autorización final programada para 4-sep-2026; primer proyecto minero aceptado en programa federal FAST-41; ~50% avance en porción privada; primer concentrado ahora proyectado H1-2028, antes H1-2027)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Stibnite Gold Project</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Valley County, Idaho, EE.UU.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Perpetua Resources</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Hatch Ltd. (EPCM)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Construcción temprana</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>El Tigre Project</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Silver Tiger Metals</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Kappes, Cassiday &amp; Associates (EPCM)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Construcción (166 personas en sitio, 100,000 horas-hombre; primer vaciado previsto dic-2027)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Panuco Silver-Gold Project</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Sinaloa, México</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Vizsla Silver Corp.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Ingeniería de detalle/planeación de construcción (post-Feasibility Study)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>South Railroad Project (South Carlin Complex)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Elko/Eureka County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Orla Mining Ltd.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Construcción (inicio previsto mediados 2026, pendiente ROD final de BLM)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Copperstone Gold Project</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>La Paz County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Minera Alamos Inc.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Contratista de minería subterránea por definir</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Construcción (decisión de inversión may-2026)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>CK Gold Project</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Distrito Silver Crown, Laramie Range, Wyoming, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>U.S. Gold Corp</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Halyard-Micon International (feasibility); EPC por asignar</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Ingeniería completa/permisado a nivel estatal; inicio de construcción retrasado de 2026 a 1T2027 (complicaciones de suministro de agua y derecho de vía)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Distrito Santa Elena — Expansión (Santo Niño y Navidad)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>First Majestic Silver Corp.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Construcción (permisos recibidos jun-2026; First Majestic compromete US$12 millones en 2026 para desarrollo de accesos subterráneos y portales)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Galena Complex — Planta de Relleno en Pasta</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Wallace, Idaho, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Americas Gold and Silver Corporation</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Construcción (comisionamiento previsto Q4 2026)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Guanacevi Silver Project (Ocampo Mining)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Durango, México</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Minera Frisco (Grupo Carso)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Construcción (nueva planta de proceso; primera producción prevista fin de 2026)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Arctic Project (Distrito Minero Ambler)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Distrito Minero Ambler, Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ambler Metals LLC (Trilogy Metals / South32, JV 50/50)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Permitting (cronograma coordinado de permisos federales/estatales publicado 16-jul-2026; revisión ambiental integrada de 29 meses liderada por USACE; ROD objetivo sep-2028)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Los Ricos South Mine</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Jalisco, México</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GoGold Resources</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Construcción aprobada por el consejo (permisos SEMARNAT completos jun-2026; presupuesto ~US$227 millones; ventana de construcción de ~24 meses; primer vertido de metal previsto mediados de 2028)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); [Newsfile](https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Cordero Project</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Chihuahua, México</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Discovery Silver</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Ausenco (ingeniería)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Feasibility completa / permitting (MIA pendiente ante SEMARNAT)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Gran Pilar Gold-Silver Project</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Tocvan Ventures</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Construcción (piloto; primer doré previsto Q4 2026)</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Orisyvo Project</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Sierra Madre (Rarámuri), Chihuahua, México</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Fresnillo plc</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Pre-feasibility (transicionando a feasibility, resultados esperados medio 2026)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Planta de Separación de Tierras Raras (US Army)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Tooele Army Depot, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>REalloys Inc.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Acuerdo de arrendamiento condicional otorgado por el Ejército de EE.UU. (confirmado 29-jul-2026, parte de programa en 4 sitios: Anniston AL, Pine Bluff AR, Red River TX, Tooele UT); desarrollo comercial previsto 2027, operaciones iniciales 2028</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>[Army.mil](https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Planta de Purificación de Grafito (US Army)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Pine Bluff Arsenal, Arkansas o Anniston Army Depot, Alabama (sin confirmar), EE.UU.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Titan Mining Corp.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Plantas de Litio y Boro (US Army)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Base militar de EE.UU. sin confirmar</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>EnergyX (litio) / ioneer Ltd. (boro)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Acuerdo firmado/planeación (construcción prevista desde 2027; producción 2028)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Expansión Concentradora La Caridad</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Nacozari, Sonora, México</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Grupo México</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Metso (equipo de trituración)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Construcción/procura de equipo (pedido adicional &gt;EUR 20M de trituración secundaria a Metso, jun-2026, complementa equipos Nordberg MP800 instalados en 2025)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Santo Tomás Copper Project</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Sinaloa, México</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Oroco Resource Corp.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Prefactibilidad (perforación fase 2 en curso; PFS objetivo 2T-3T 2027; capex estimado USD 2.84 mil millones; permisos federales pendientes)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Reapertura Fundición Hayden + Refinería Amarillo</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Hayden, Arizona / Amarillo, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Asarco (Grupo México)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Negociación/planeación (inversión ~USD 230 millones para reactivar fundición cerrada desde 2020; Grupo México evalúa hasta USD 6,000 millones adicionales para expansión de cobre en Arizona)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Cerro de Oro Gold Project</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Zacatecas, México</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Minera Alamos Inc.</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Permitting (proyecto de oro a cielo abierto/heap leach; financiamiento de construcción ya asegurado)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Antler Copper Project</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Condado de Mohave, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>New World Resources Ltd. (respaldado por Kinterra Capital)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Permitting casi completo/inicio de construcción (BLM emitió Determinación de Adecuación NEPA; obras previstas 2do semestre 2026; embarque de concentrado previsto 2027)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Lisbon Valley Copper Project</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Condado de San Juan, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Lisbon Valley Mining Company, LLC</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Permitting federal completo (aprobación BLM + exención de acuífero EPA, oct-2025) / reapertura-construcción (agrega tajo abierto y pozos de recuperación in-situ)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>South West Arkansas Lithium Project (Central Processing Facility)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Sur de Arkansas, EE.UU.</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Smackover Lithium (JV Standard Lithium / Equinor)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>S&amp;B Engineers and Constructors (EPCC); Hatch Ltd. (ingeniería de diseño/comisionamiento)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Ingeniería de detalle/procura temprana (contrato EPCC otorgado, NTP limitado activo; FID esperada en 2026; planta diseñada para 22,500 tpa de carbonato de litio grado batería)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>[InvestingNews](https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Bagdad Mine Concentrator Expansion</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Yavapai County, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental estimado ~US$3,500 millones bajo revisión; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Elk Creek Critical Minerals Project</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Elk Creek, Nebraska, EE.UU.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>NioCorp Developments Ltd.</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; proyecto de niobio/escandio/titanio con planta de superficie que requerirá tubería de proceso)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Goldfield Project</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Goldfield, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Centerra Gold Inc.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Ingeniería/Construcción temprana (ingeniería de detalle y procura de largo plazo en 2026; construcción mayor de pila de lixiviación y circuitos de trituración/procesamiento en 2027; primera producción fin de 2028)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>[E&amp;MJ](https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Cactus Mine (distrito Copper World/Arizona Sonoran)</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Hudbay Minerals (adquisición de Arizona Sonoran Copper Co. anunciada 2-mar-2026)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>Desarrollo/Feasibility (planta SX-EW de cátodos de cobre, ~103,000 t Cu/año proyectadas; Hudbay busca fusionarlo con el distrito Copper World adyacente ya rastreado)</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Doby George Gold Project (Distrito Aura)</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>~120 km al norte de Elko, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Western Exploration Inc.</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>No especificado (WSP realiza feasibility study; Stantec y Kappes Cassidy en estudios ambientales)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Feasibility/Permitting (PEA positiva 2025; Mine Plan of Operations en preparación; proyecto de lixiviación en pilas de óxidos)</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>[Western Exploration](https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Metates Project</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Durango, México</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Chesapeake Gold Corp.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Feasibility (prefeasibility study objetivo 2026; pruebas metalúrgicas de lixiviación de sulfuros y estudios ambientales de línea base en curso; uno de los mayores depósitos de oro-plata no desarrollados de América)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>[Chesapeake Gold Corp.](https://chesapeakegold.com/metates/)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Pathfinder Tonopah (cobre-molibdeno-plata)</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Tonopah, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Pathfinder Minerals (Pathfinder Tonopah)</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Bowman (permisos ambientales, FEED, planta piloto)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Permitting/FEED (avanzando hacia estudio de factibilidad definitivo; carta de interés no vinculante de EXIM Bank por US$896 millones para financiamiento, programa "Make More in America")</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>[Mining Technology](https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>La Colorada Mine — Expansión Veta Madre/Veta Madre Plus</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Heliostar Metals</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>Permisos completos obtenidos (2026); waste stripping programado 3T2026; producción de zona expandida esperada 1S2027</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>[Mexico Business News](https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Libby Project (Cabinet Mountains)</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Condado de Lincoln, Montana, EE.UU.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Hecla Mining Company</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>Permitting federal completado para exploración subterránea (extensión de ~1 milla del socavón Libby Adit; recurso potencial 1,500 millones lb de cobre y 183 millones oz de plata; pendiente permiso de descarga de agua de MT DEQ)</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>[The Western News](https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Donlin Gold</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Alaska, EE.UU.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>NovaGold Corporation (adquiriendo 100%, compra de participación del 40% de Paulson Advisers)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); aún sin decisión de construcción (FID)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Rhyolite Ridge Lithium-Boron Project</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Condado de Esmeralda, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>ioneer Ltd.</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Hyundai Engineering Co. Ltd. (MOU no vinculante, evaluando rol EPC/procura); KIND evaluando inversión de capital</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Permitting confirmado en corte federal (31-mar-2026); préstamo DOE de US$996 millones cerrado; MOUs con KIND/Hyundai firmados inicios jul-2026; FID objetivo 2S2026, primera producción 2029</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>[IM Mining](https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>San Antonio Gold Project</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Axo Metals Corp. (Axo Copper Corp.)</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>Permisos (SEMARNAT aprobó la MIA, 27-jul-2026, habilitando producción; planta de carbón-en-columna ya permisada; aprobaciones de uso de suelo para nuevos yacimientos —Sapuchi, Golfo de Oro, California— en trámite para fin de año)</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>[Resource World](https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Tamarack Nickel-Copper-Cobalt Project</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Aitkin County, Minnesota (mina) / sitio de planta de proceso por definir (Mercer County, Dakota del Norte vs. Eagle Mine/Humboldt Mill, Michigan), EE.UU.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Talon Metals Corp. (51%) / Kennecott Exploration Co. (Rio Tinto) JV</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>Permitting/Feasibility (EIS en scoping, comentarios cierran 14-sep-2026; estudio de factibilidad —incl. decisión de sitio de planta— esperado 2S2026; entendimiento informal de offtake con Tesla)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>[North Dakota Monitor](https://northdakotamonitor.com/2026/07/28/plans-for-north-dakota-nickel-processing-unclear-as-company-also-evaluates-michigan-site/)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>White Mesa Mill — Expansión de Tierras Raras Pesadas</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Blanding, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Energy Fuels Inc.</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>Construcción (planta comercial de tierras raras pesadas —disprosio/terbio— iniciada 29-jul-2026; capex ~US$104 millones, para uso en imanes/defensa/vehículos eléctricos)</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>[Energy Fuels](https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); [PR Newswire](https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
@@ -5154,2457 +5184,2531 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Stargate Frontier Campus</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Shackelford County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Construcción (rompimiento de tierra formal completado; 1,200 acres/10 edificios/1.4GW; VoltaGrid aprobado para operar 210 generadores de gas industrial, 700MW combinados, permitiendo operación fuera de la red pública; primera instalación en servicio 2S2026)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); [Construction Owners](https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Stargate Milam County (fast-build)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Milam County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>OpenAI / Oracle</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Stargate Abilene Campus</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Abilene, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>OpenAI / Oracle</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Crusoe / DPR Construction</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Microsoft Pecos Data Center Campus (Project Kilby)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Pecos/Reeves County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Chevron (acuerdo definitivo de suministro de gas a 20 años firmado 22-jun-2026, sitio &gt;2,000 acres); turbinas mayoritariamente GE Vernova de gran marco + Solar Turbines (Caterpillar) para capacidad adicional</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construcción temprana/Ingeniería (capacidad rampa a 2.67GW; flujo de energía previsto fines de 2028; FID de la planta esperada fines de 2026)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>[Chevron](https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>CloudHQ Querétaro (6 campus, incl. Campus Colón)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Colón y otras ubicaciones, Querétaro, México</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>CloudHQ</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Permisos/preparación de sitio (confirmado oficialmente por gobierno federal 7-jul-2026 bajo Plan México; inversión US$4,800M, 52 hectáreas, 900MW; subestación propia de 2GW prevista Q2 2027)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Meta Hyperion Data Center</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Richland Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Turner Construction / DPR Construction / Mortenson</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Construcción (escalado confirmado a 5GW/USD 50+ mil millones, financiado fuera de balance vía JV con Blue Owl Capital; primeros 2GW en línea 2030, 5GW completo ~2032, finalización 2036; Entergy ahora respalda con 7 plantas adicionales de ciclo combinado a gas, 5,200+ MW, ~240 millas de transmisión 500kV y 3 baterías de red)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>[Global Data Center Hub](https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Vantage Data Centers NV1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Storey County, Nevada, EE.UU.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Vantage Data Centers</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CloudBurst San Marcos Data Center I</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>San Marcos/New Braunfels, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>CloudBurst Data Centers</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Evolve (eVOLVE Data Center Solutions)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Prometheus Hyperscale Dallas Campus</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Entre Talty y Post Oak Bend City, Kaufman County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Prometheus Hyperscale</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>No especificado (socio energía: Engie)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ingeniería/construcción temprana (campus de 200MW/4 edificios; estrategia behind-the-meter con motores de gas Jenbacher J620 + almacenamiento en baterías de Engie; primera instalación 2026, fases hasta 2028)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>GW Ranch Power Campus</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Pecos County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Pacifico Energy</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Permisos obtenidos/inicio construcción</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Amazon Mattermeade Data Center Campus</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Caroline/Spotsylvania County, Virginia, EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Amazon (AWS)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fermaca Digital City (+ gasoducto + planta de ciclo combinado)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Durango, Durango, México</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Grupo Fermaca (inquilino AI hyperscaler sin confirmar)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Permisos/negociación avanzada (inversión total US$3.7 mil millones: US$2.7B centro de datos + US$1B planta de fertilizantes Fermachem; gasoducto de 160km desde Texas; planta de ciclo combinado on-site de 350MW para alimentar data center de 250MW; Congreso de Durango aprobó donación de 50 hectáreas)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); [DCD](https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Circe Energy West Texas AI Infrastructure Campus</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Cuenca Pérmica, West Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Circe Energy</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>No especificado (gen-sets Cummins)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Ingeniería/procurement</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Project Jupiter</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Santa Teresa/Sunland Park, Doña Ana County, Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>BorderPlex Digital Assets/Stack (inquilino Oracle/OpenAI)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>No especificado (rediseño: hasta 2.45GW de celdas de combustible Bloom Energy, reemplazando turbinas de gas/diésel)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Construcción activa con riesgo regulatorio (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 14-jul-2026; NMED pospuso la decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas y programó audiencia pública para 19-oct-2026; meta de entrada en servicio ago-2026 en riesgo)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>PowerPlay AI "Greater Abilene" Data Center</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Área metropolitana de Abilene, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>PowerPlay AI (JV con socio Neocloud cotizado en Nasdaq, sin nombre público)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>IPP en proceso de RFP (aún sin seleccionar)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Ejecución activa post-adquisición de terreno (400MW behind-the-meter iniciales; arranque objetivo 2028)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>[PR Newswire](https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Liberty Energy/PowerBridge "Alpha Digital Campus"</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Condado de Reeves, Texas, EE.UU. (cerca del hub de gas Waha)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>PowerBridge LLC</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Liberty Power Innovations (subsidiaria de Liberty Energy, JV)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>JV firmada/desarrollo temprano (~3,400 acres; primera fase &gt;300MW, primera entrega de energía prevista 4T2027; campus completo 2GW)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>New Era Energy &amp; Digital Hub</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Lea County, Nuevo México, EE.UU.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>New Era Energy &amp; Digital</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Planeación temprana (opción de terreno)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Texas Critical Data Centers (TCDC) Campus</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>New Era Energy &amp; Digital</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Stargate Lordstown</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Lordstown, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Construcción (rompimiento de tierra)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Stargate Wisconsin</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>OpenAI / Oracle / SoftBank</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Vantage Data Centers (en sociedad con Oracle)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>AWS Región Digital Querétaro</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Querétaro, México</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Stargate Michigan (Saline Barn Campus)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Saline Township, Michigan, EE.UU.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Walbridge</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>North Dakota, EE.UU.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Applied Digital / Base Electron</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>AI-GDC / Cipre Holding "Green Data Center"</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>San Pedro Garza García, Nuevo León, México</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Planeación/desarrollo temprano</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>CleanArc Data Centers VA1 Campus</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Caroline County, Virginia, EE.UU.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>CleanArc Data Centers</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Joule Energy and Data Center Campus</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Millard County (Holden), Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Joule Capital Partners</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Construcción</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Amazon Montgomery County Campus</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Anuncio/permisos</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Google Montgomery County Campus</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Anuncio/permisos</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Hood County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Big Digital Energy + 10NetZero (JV)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Planeación/adquisición de sitio</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Williams "Project Socrates"</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>New Albany, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Meta (vía Sidecat, LLC)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Williams Companies / Will-Power</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Meta El Paso Campus (expansión)</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>El Paso, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Permisos</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>SB Energy/SoftBank PORTS Technology Campus</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Pike County, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Planeación avanzada (SB Energy construirá 9.2GW de generación a gas natural, financiamiento de US$33.3 mil millones por SoftBank, más US$4.2 mil millones en transmisión; 26-jul-2026 trascendió que Nvidia negocia garantía financiera de hasta US$250 mil millones para que OpenAI arriende el sitio, primera fase de 800MW en 2028)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Williams "Apollo" Power Generation Project</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Williams "Aquila" Power Project</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Utah, EE.UU. (condado no revelado)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>West Texas, EE.UU. (condado no revelado)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Tallgrass AI Data Center Campus (Project Jade)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Condado de Laramie, Wyoming, EE.UU.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Black Hills Corp. (desarrollador directo) / Tallgrass / cliente de gran carga no revelado (comprometió US$200M+ en hitos de construcción)</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>No especificado (Crusoe Energy se retiró como desarrollador, jun-2026, a solicitud del cliente)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Desarrollo CONTINÚA con nuevo desarrollador (Crusoe salió del proyecto pero Black Hills Corp. avanza directamente con el cliente; permisos locales de Wyoming vigentes; 1.8GW inicial escalable a 10GW)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>[Cowboy State Daily](https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Core Scientific Pecos Campus (expansión IA)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Pecos, Reeves County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Core Scientific</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Stratos Project / Wonder Valley</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>O'Leary Digital (Kevin O'Leary)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fermi America Project Matador</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Carson County (Amarillo), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Fermi America</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas); Energy Transfer (interconexión de gasoducto)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW)</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>NextEra Texas Power Generation Hub</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Anderson County, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>NextEra Energy Resources</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Monongalia County, Virginia Occidental, EE.UU.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Mon Power (FirstEnergy)</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>IEP Greene County Data Center &amp; Power Plant</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Greene County, Pensilvania, EE.UU.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>International Electric Power</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>AWS "Project Eagle"</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>Permisos/Construcción inminente (confirmado inicio de construcción 1-ago-2026; 3 edificios completados ene-2027, 4to edificio ago-2027; USD 1.2 mil millones, ~2,700 acres)</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>[Wharton Post](https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Crusoe/Lancium Childress Data Center Campus</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Condado de Childress, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Williams "Neo" Power Innovation Project</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Cliente de centro de datos no revelado</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Williams "Socrates the Younger" Power Innovation Project</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Meta Platforms (vía Sidecat, LLC)</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Williams Companies</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Crusoe/Google "Goodnight Campus"</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>VoltaGrid/Serverfarm Covington</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Serverfarm</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Homer City Energy Campus</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Condado de Indiana, Pensilvania, EE.UU.</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Homer City Redevelopment (HCR)</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027)</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Nebius Vineland AI Data Center Campus</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Vineland, Nueva Jersey, EE.UU.</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>No especificado — posible cambio de alcance a celdas de combustible Bloom Energy (acuerdo maestro Nebius-Bloom Energy de USD 2,600 millones, 21-may-2026, hasta 328MW; fuentes de menor confianza lo vinculan a Vineland como respuesta a problemas de permisos de aire NJDEP con planta vecina Corning — confirmación directa pendiente)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; NJDEP en revisión hacia aprobación final a mediados jul-2026; meta de entrega nov-2026 en riesgo)</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>TerraVolt Infrastructure AI Data Center Campus</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>CyrusOne SAT14A</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Castroville, San Antonio, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>CyrusOne (sin arrendatario asignado aún)</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>Ingeniería/Permisos (6to campus en San Antonio, 11vo en Texas; USD 500 millones, 460,000 pies²; inicio de construcción previsto dic-2026)</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>EdgeConneX PowerConneX New Albany Energy Center (I, II y III)</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>New Albany, Licking County, Ohio, EE.UU.</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>EdgeConneX (propiedad de EQT Infrastructure)</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>No especificado (desarrollado vía afiliada PowerConneX)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027; PowerConneX III, 430MW, notificación previa ante OPSB abr-2026, elevando capacidad total del sitio a ~766MW de gas)</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); [BeBeez](https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>xAI Colossus 2/Colossus 3 ("MACROHARDRR")</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Southaven, Misisipi / Memphis, Tennessee, EE.UU.</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>xAI</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>Operando parcialmente/en expansión con crisis regulatoria activa (59 turbinas de gas natural operando en Southaven, la mayoría sin permisos federales de Clean Air Act; demanda de NAACP/Southern Environmental Law Center/Earthjustice desde abr-2026; xAI recibió aprobación para 41 turbinas de gas adicionales, ~1.2GW, en el sitio de Southaven para alimentar Colossus 2 y el próximo Colossus 3; DOJ intervino en litigio citando uso de Grok por el Departamento de Defensa; capacidad total del sitio creciendo hacia 2GW+ en tres edificios)</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>[Technology.org](https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); [DCD](https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Applied Digital "Delta Forge 1" (planta de gas dedicada Cleco 756MW)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Rapides Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Applied Digital</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Cleco Power (planta de gas dedicada de 756MW)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Construcción (campus de USD 3.6 mil millones/430MW, la mayor carga individual jamás atendida por Cleco; rompimiento de tierra ene-2026; operaciones iniciales objetivo mediados de 2027)</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Rubix Data Centers (Submer Group)</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Russell, Kentucky, EE.UU. (antiguo sitio de acería AK Steel)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Rubix Data Centers / Submer Group</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>Propuesta/planeación temprana (hasta 2GW, US$8-12 mil millones; moratoria municipal sobre solicitudes de data centers podría complicar el proyecto; fuente de energía aún no especificada)</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>[Kentucky Lantern](https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>QTS/Lancium Hall County Campus</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Cerca de Turkey, Condado de Hall, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Lancium (dueño de sitio/energía) / QTS Data Centers (construcción/operación)</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Lancium (autoabastecimiento solar+baterías; interconexión a red de 1GW; sin planta de gas confirmada)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Anuncio/desarrollo temprano (US$10 mil millones, hasta 11 edificios en 465 acres)</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Anthropic/Nexus Hubbard Campus</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Hubbard, Condado de Hill, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Anthropic (operado por Nexus Data Centers; respaldo financiero de Google)</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Construcción iniciada (primera fase 500-612MW prevista 2026, ampliable a ~7.2-7.7GW; planta de gas natural behind-the-meter cerca de gasoducto principal)</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); [Construction Review](https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/)</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Construcción iniciada (primera fase 500-612MW prevista 2026, ampliable a ~7.2-7.7GW; planta de gas natural behind-the-meter cerca de gasoducto principal; financiamiento avanzado: banca liderada por Morgan Stanley en negociaciones finales para prestar USD 15 mil millones a Nexus Data Centers —incluye préstamo puente de USD 14 mil millones más línea de crédito revolvente—; Google otorgaría garantías sobre obligaciones de arrendamiento y pago de energía de Anthropic a cambio de ~20% de participación accionaria en el proyecto combinado)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); [Construction Review](https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); [CNBC](https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Stillwater Technology Park</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lovejoy, Condado de Clayton, Georgia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Stillwater Development, LLC (cliente hyperscaler final no revelado)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Permisos ("development of regional impact" presentado ante el estado; hasta 15 edificios, 1.25GW, US$13 mil millones; generación de energía aún no confirmada, contempla interconexión con Central Georgia EMC)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Stillwater Technology Park</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Lovejoy, Condado de Clayton, Georgia, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Stillwater Development, LLC (cliente hyperscaler final no revelado)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Permisos ("development of regional impact" presentado ante el estado; hasta 15 edificios, 1.25GW, US$13 mil millones; generación de energía aún no confirmada, contempla interconexión con Central Georgia EMC)</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Paducah Data Center Campus</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Antiguo sitio de enriquecimiento de uranio del DOE, Paducah, Kentucky, EE.UU.</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Coalición: Brookfield / NextEra Energy / Big Rivers Electric / Jackson Purchase Energy Cooperative / Paducah Power System</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>Anuncio/desarrollo temprano (hasta 1.8GW; incluye nueva planta de gas natural de ~2GW y hasta 2.6GW de almacenamiento en baterías; ~US$100 mil millones de inversión privada total, el mayor proyecto de desarrollo económico en la historia de Kentucky)</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); [Kentucky Lantern](https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>OpenAI "Project Camellia"</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Condado de Effingham, cerca de Savannah, Georgia, EE.UU.</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>No especificado (energía: Georgia Power, expansión de ~5.8GW de generación a gas natural)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Anuncio/preconstrucción (carga de 3.2GW, ~US$20-30 mil millones de inversión; capacidad disponible 2028-2032; OpenAI cubre el costo total de la infraestructura)</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>[Axios](https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); [DCD](https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Stream Data Centers "Project Saltworks"</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Condado de Young (cerca de Graham), Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Headwaters Site Development (afiliada de Stream US Data Centers)</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>No especificado (activos de interconexión de energía adquiridos de Plug Power)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Preconstrucción/diseño de sitio (~890 acres, ~US$10 mil millones, 15 edificios planeados; construcción no prevista antes de inicios de 2027; enfrenta oposición comunitaria local)</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>[DCD](https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); [Olney Enterprise](https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Eagle Rock Partners "Meridian Technology Park"</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Cerca de Taylorville, Condado de Christian, Illinois, EE.UU.</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Eagle Rock Partners</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>No especificado (PPA con Kindle Energy LLC para 1,000-1,100MW del proyecto de planta de gas Lincoln Land Energy Center, cerca de Pawnee, desarrollado por EmberClear)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Planeación muy temprana (aún sin solicitud de zonificación presentada; ~US$6 mil millones, 10 edificios planeados; energía esperada para 2029)</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>[Illinois Times](https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Creekstone Energy "Delta Gigasite"</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Cerca de Delta, Condado de Millard, Utah, EE.UU.</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Creekstone Energy LLC</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Zeo Energy (socio de energía)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Construcción (rompimiento de tierra dic-2025; meta de 10GW de capacidad total —2GW de gas on-site + 6GW solar + posibles 1.8GW de la planta de carbón inactiva Intermountain—; &gt;300MW de capacidad a gas prevista en línea 1S2027; US$17 mil millones comprometidos)</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>[KSL](https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); [Utah GOED](https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Amazon Richmond County Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Richmond County (Hamlet), Carolina del Norte, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Construcción (rompimiento de tierra completado jun-2026; campus de USD 10 mil millones, hasta 20 edificios en 800 acres; ubicado junto al complejo Sherwood H. Smith Jr. de Duke Energy —2.24GW de turbinas de gas natural existentes—; Duke Energy planea construir una turbina adicional de 240MW en el mismo complejo, construcción prevista fines de 2027, en línea fines de 2029; 57 generadores diésel temporales de Duke Energy instalándose en terreno de Amazon como respaldo mientras se construye infraestructura permanente; audiencia pública conjunta de NC DEQ sobre permisos de calidad de aire de Amazon y Duke Energy celebrada 31-jul-2026 con fuerte oposición vecinal)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); [WFAE](https://www.wfae.org/energy-environment/2026-07-31/residents-push-back-against-large-amazon-data-center-project-during-packed-public-meeting)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Project Baccara</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cerca de Surprise, Maricopa County, Arizona, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Takanock LLC (respaldado por DigitalBridge)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Permisos obtenidos/construcción inminente (160 acres; dos data centers de ~1 millón pies² c/u + planta de generación a gas natural de 700.2MW en 23.7 acres del sitio; Arizona Corporation Commission aprobó Certificado de Compatibilidad Ambiental 4-feb-2026; Maricopa County Board of Supervisors aprobó permiso de compatibilidad militar 4-1, 6-may-2026, pese a fuerte oposición vecinal por cercanía a Luke Air Force Base; pendiente permiso de calidad de aire EPA; construcción prevista 3T2026; primer edificio en línea 1T2028)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); [DCD](https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1868,6 +1868,80 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Enterprise Products — Plant 12 (Delaware Basin) y Athena 2 (Midland Basin)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cuenca Delaware y Cuenca Midland, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Enterprise Products Partners L.P.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Enterprise Products (propietario-constructor)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Construcción (sancionadas, divulgadas en resultados 2T2026 el 30-jul-2026; Plant 12 Delaware Basin ~300 MMcf/d en servicio 4T2027; Athena 2 Midland Basin en servicio 3T2027)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Targa Resources Roadrunner III / Copperhead II (plantas de gas)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Targa Resources Corp.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Targa Resources (propietario-constructor)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Construcción (aprobadas may-2026; Roadrunner III 265 MMcf/d, Copperhead II 275 MMcf/d; en servicio previsto 1T2028)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[PGJ](https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1882,14 +1956,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3297,6 +3371,43 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gasoducto Trident (alimenta Golden Pass LNG)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Katy a Port Arthur, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Kinder Morgan, Inc.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Construcción (tendido/soldadura de tubería en curso en Waller County; ~216-220 millas, 42"/48", US$1.7-1.8 mil millones; en servicio Fase 1 previsto 1T2027)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[Storage Terminals Magazine](https://storageterminalsmag.com/kinder-morgans-trident-pipeline-project-enters-active-construction-phase-in-southeast-texas/); [Natural Gas Intel](https://www.naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3311,14 +3422,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -5170,6 +5281,80 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Black Butte Copper Project</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Meagher County, Montana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sandfire Resources America Inc. (Sandfire Resources)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Por definir (PFS elaborado por DM Consulting)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Feasibility (PFS actualizado presentado 28-jul-2026 con nuevas reservas Lowry, vida de mina de 12 años; mina subterránea de cobre de alta ley)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Planta de Procesamiento de Litio Red River (US Army)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Bowie County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EnergyX (desarrollador-operador)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Acuerdo de arrendamiento condicional otorgado (confirmado 25-jun-2026; 5to sitio del programa de minerales críticos en bases del Ejército, junto con Tooele, Pine Bluff/Anniston; construcción prevista desde 2027)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[Texarkana Gazette](https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5184,14 +5369,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -7712,6 +7897,80 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Savannah River Site AI Data Center &amp; Energy Campus</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Aiken, Carolina del Sur, EE.UU. (sitio federal DOE/NNSA)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DOE/NNSA (sitio federal)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Amentum (desarrollador seleccionado) / DC BLOX (socio de infraestructura)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Negociación de arrendamiento por fases (seleccionado ~20-23 jul-2026; campus de ~1GW con ~2GW de generación dedicada in-situ, iniciando con gas natural como puente hacia energía nuclear futura)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); [Energy.gov](https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pacifico Cedar Creek Power Campus</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cedar Creek, Bastrop County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Pacifico Energy (Pacifico Cedar Creek LLC); inquilino de centro de datos aún no revelado</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Permisos/incentivos en revisión (solicitud de incentivos ante el Contralor de Texas presentada 24-jun-2026; campus de 2,842 acres; planta de gas natural on-site de 710MW para servir ~490MW de carga de centro de datos, esquema behind-the-meter)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>[Community Impact](https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,10 +20,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -49,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,50 +425,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -1942,6 +1951,43 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Southern Energy Renewables — Complejo de Metanol y SAF</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>St. Charles Parish (Killona), Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Southern Energy Renewables</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Planeación/pre-construcción (inversión US$1,400 millones; convierte biomasa de desecho de madera en metanol verde y combustible de aviación sostenible; construcción prevista a iniciar fines de 2027, producción prevista fines de 2029)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[Hydrocarbon Processing](https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); [Louisiana Economic Development](https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1959,47 +2005,47 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -3422,50 +3468,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -5355,6 +5401,80 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Camino Rojo — Proyecto Subterráneo (extensión)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Zacatecas, México</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Orla Mining Ltd.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Permisos completos/inicio de desarrollo subterráneo (SEMARNAT aprobó MIA 18-mar-2026, habilitando minado del resto del tajo de óxidos y construcción de rampa de exploración subterránea; inicio de obras de acceso subterráneo previsto 2S2026; PEA de proyecto subterráneo indica VPN de US$1,300 millones)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); [Orla Mining](https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cerro Caliche Gold Project</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sonora, México</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sonoro Gold Corp.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EPC por definir (en negociación con múltiples empresas EPC de China)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Permisos/estructuración de financiamiento EPC (plataforma consolidada de 3,924 hectáreas en 25 concesiones; finalización de permisos esperada 1T2026; 4 empresas EPC chinas evaluando financiamiento de deuda y desarrollo)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>[Sonoro Gold Corp.](https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); [Mexico Mining Center](https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -5369,50 +5489,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -7968,6 +8088,43 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bosque County Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Condado de Bosque, Texas, EE.UU. (~30 millas al sur de Dallas-Fort Worth)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Energy Capital Partners (ECP) / KKR (asociación estratégica de US$50 mil millones)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CyrusOne (JV de construcción/operación); Calpine Corp. (suministro de energía dedicada desde Thad Hill Energy Center)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Construcción (primera inversión de la asociación estratégica ECP-KKR; campus de ~700,000 pies², inversión total cercana a US$4,000 millones, capacidad inicial de TI de 144MW sobre 190MW total; operación prevista 4T2026)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>[Data Centre Magazine](https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); [Connect CRE](https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,18 +20,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -57,9 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,47 +419,47 @@
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -2005,47 +1996,47 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -3468,50 +3459,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -5264,7 +5255,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aitkin County, Minnesota (mina) / sitio de planta de proceso por definir (Mercer County, Dakota del Norte vs. Eagle Mine/Humboldt Mill, Michigan), EE.UU.</t>
+          <t>Aitkin County, Minnesota (mina) / Beulah, Dakota del Norte (planta de proceso — Beulah Minerals Processing Facility), EE.UU.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5279,34 +5270,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Permitting/Feasibility (EIS en scoping, comentarios cierran 14-sep-2026; estudio de factibilidad —incl. decisión de sitio de planta— esperado 2S2026; entendimiento informal de offtake con Tesla)</t>
+          <t>Permitting/Feasibility (Talon firmó acuerdo de opción de terreno con Westmoreland Mining, 28-jul-2026, por ~256 acres cerca de Beulah, ND, para la Beulah Minerals Processing Facility —planta de procesamiento de concentrado níquel-cobre respaldada por subvención DOE de US$114.8 millones—; EIS de la mina en scoping, comentarios cierran 14-sep-2026; entendimiento informal de offtake con Tesla)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[North Dakota Monitor](https://northdakotamonitor.com/2026/07/28/plans-for-north-dakota-nickel-processing-unclear-as-company-also-evaluates-michigan-site/)</t>
+          <t>[Talon Metals](https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>White Mesa Mill — Expansión de Tierras Raras Pesadas</t>
+          <t>Bunker Hill Mine — Reinicio + Planta de Relleno en Pasta</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blanding, Utah, EE.UU.</t>
+          <t>Kellogg/Wardner, Idaho, EE.UU. (Distrito Minero Coeur d'Alene)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Energy Fuels Inc.</t>
+          <t>Bunker Hill Mining Corp.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5316,163 +5307,237 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Construcción (planta comercial de tierras raras pesadas —disprosio/terbio— iniciada 29-jul-2026; capex ~US$104 millones, para uso en imanes/defensa/vehículos eléctricos)</t>
+          <t>Construcción/Comisionamiento (primer embarque de concentrado a la fundición Trail de Teck tras 45+ años de cierre; nueva planta de proceso de 1,800 tpd comisionada; planta de relleno en pasta en sitio Wardner sustancialmente completa, comisionamiento final previsto ~3 semanas tras el anuncio; meta de producción comercial plena fin de 2026)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[Energy Fuels](https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); [PR Newswire](https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Black Butte Copper Project</t>
+          <t>NewRange Copper Nickel (Proyecto NorthMet) — Rediseño Mayor</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Meagher County, Montana, EE.UU.</t>
+          <t>Babbitt/Hoyt Lakes, Minnesota, EE.UU. (Iron Range)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sandfire Resources America Inc. (Sandfire Resources)</t>
+          <t>NewRange Copper Nickel (JV PolyMet/Glencore + Teck)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Por definir (PFS elaborado por DM Consulting)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Feasibility (PFS actualizado presentado 28-jul-2026 con nuevas reservas Lowry, vida de mina de 12 años; mina subterránea de cobre de alta ley)</t>
+          <t>Permitting (rediseño mayor elimina la represa de jales propuesta —roca estéril se almacenaría en tajos de mineral de hierro existentes—; solicitud de permiso de humedales Sección 404/Clean Water Act presentada ante USACE; revisión ambiental suplementaria (SEIS) solicitada a Minnesota DNR)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
+          <t>[MPR News](https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Planta de Procesamiento de Litio Red River (US Army)</t>
+          <t>White Mesa Mill — Expansión de Tierras Raras Pesadas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bowie County, Texas, EE.UU.</t>
+          <t>Blanding, Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
+          <t>Energy Fuels Inc.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EnergyX (desarrollador-operador)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Acuerdo de arrendamiento condicional otorgado (confirmado 25-jun-2026; 5to sitio del programa de minerales críticos en bases del Ejército, junto con Tooele, Pine Bluff/Anniston; construcción prevista desde 2027)</t>
+          <t>Construcción (planta comercial de tierras raras pesadas —disprosio/terbio— iniciada 29-jul-2026; capex ~US$104 millones, para uso en imanes/defensa/vehículos eléctricos)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[Texarkana Gazette](https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
+          <t>[Energy Fuels](https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); [PR Newswire](https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Camino Rojo — Proyecto Subterráneo (extensión)</t>
+          <t>Black Butte Copper Project</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zacatecas, México</t>
+          <t>Meagher County, Montana, EE.UU.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Orla Mining Ltd.</t>
+          <t>Sandfire Resources America Inc. (Sandfire Resources)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Por definir (PFS elaborado por DM Consulting)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Permisos completos/inicio de desarrollo subterráneo (SEMARNAT aprobó MIA 18-mar-2026, habilitando minado del resto del tajo de óxidos y construcción de rampa de exploración subterránea; inicio de obras de acceso subterráneo previsto 2S2026; PEA de proyecto subterráneo indica VPN de US$1,300 millones)</t>
+          <t>Feasibility (PFS actualizado presentado 28-jul-2026 con nuevas reservas Lowry, vida de mina de 12 años; mina subterránea de cobre de alta ley)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); [Orla Mining](https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Planta de Procesamiento de Litio Red River (US Army)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bowie County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EnergyX (desarrollador-operador)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Acuerdo de arrendamiento condicional otorgado (confirmado 25-jun-2026; 5to sitio del programa de minerales críticos en bases del Ejército, junto con Tooele, Pine Bluff/Anniston; construcción prevista desde 2027)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>[Texarkana Gazette](https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Camino Rojo — Proyecto Subterráneo (extensión)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Zacatecas, México</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Orla Mining Ltd.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Permisos completos/inicio de desarrollo subterráneo (SEMARNAT aprobó MIA 18-mar-2026, habilitando minado del resto del tajo de óxidos y construcción de rampa de exploración subterránea; inicio de obras de acceso subterráneo previsto 2S2026; PEA de proyecto subterráneo indica VPN de US$1,300 millones)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>[Mining.com](https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); [Orla Mining](https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Cerro Caliche Gold Project</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Sonora, México</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Sonoro Gold Corp.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>EPC por definir (en negociación con múltiples empresas EPC de China)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Permisos/estructuración de financiamiento EPC (plataforma consolidada de 3,924 hectáreas en 25 concesiones; finalización de permisos esperada 1T2026; 4 empresas EPC chinas evaluando financiamiento de deuda y desarrollo)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>[Sonoro Gold Corp.](https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); [Mexico Mining Center](https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -5492,47 +5557,47 @@
   <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -416,15 +416,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -801,217 +801,217 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rehab. Fertinal-ProAgro (urea y fosfatos)</t>
+          <t>Proyecto Escolín (amoniaco/urea)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lázaro Cárdenas, Michoacán, México</t>
+          <t>Poza Rica, Veracruz, México</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pemex</t>
+          <t>Pemex Transformación Industrial</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Mota-Engil México (EPC confirmado; plazo de construcción 33 meses)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ingeniería/rehabilitación (incorporado al plan de reactivación petroquímica de Pemex, jun-2026; 13,700 millones de pesos asignados para los complejos Lázaro Cárdenas y ProAgro; meta de 2.4 millones ton/año de urea y fertilizantes fosfatados)</t>
+          <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); [Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pacífico Mexinol (metanol ultra bajo carbono)</t>
+          <t>Rehab. Fertinal-ProAgro (urea y fosfatos)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Topolobampo, Sinaloa, México</t>
+          <t>Lázaro Cárdenas, Michoacán, México</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Transition Industries</t>
+          <t>Pemex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Siemens Energy / Techint E&amp;C (FEED electrolizador)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Construcción (iniciada abr-2026)</t>
+          <t>Ingeniería/rehabilitación (incorporado al plan de reactivación petroquímica de Pemex, jun-2026; 13,700 millones de pesos asignados para los complejos Lázaro Cárdenas y ProAgro; meta de 2.4 millones ton/año de urea y fertilizantes fosfatados)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
+          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); [Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>First Ammonia (amoniaco verde)</t>
+          <t>Pacífico Mexinol (metanol ultra bajo carbono)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Victoria, Texas, EE.UU.</t>
+          <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Ammonia / Cox Group USA</t>
+          <t>Transition Industries</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Worley (FEED)</t>
+          <t>Siemens Energy / Techint E&amp;C (FEED electrolizador)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED completo) / FID prevista 2026</t>
+          <t>Construcción (iniciada abr-2026)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
+          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Planta de Amoniaco Topolobampo (GPO)</t>
+          <t>First Ammonia (amoniaco verde)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Topolobampo, Sinaloa, México</t>
+          <t>Victoria, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gas y Petroquímica de Occidente (GPO) / Proman AG</t>
+          <t>First Ammonia / Cox Group USA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Worley (FEED)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
+          <t>Ingeniería (FEED completo) / FID prevista 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
+          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lake Charles Methanol II</t>
+          <t>Planta de Amoniaco Topolobampo (GPO)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lake Charles, Luisiana, EE.UU.</t>
+          <t>Topolobampo, Sinaloa, México</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lake Charles Methanol II LLC</t>
+          <t>Gas y Petroquímica de Occidente (GPO) / Proman AG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zachry Group (FEED)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED) / FID prevista</t>
+          <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
+          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Planta Coquizadora Salina Cruz</t>
+          <t>Lake Charles Methanol II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salina Cruz, Oaxaca, México</t>
+          <t>Lake Charles, Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pemex</t>
+          <t>Lake Charles Methanol II LLC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ICA Fluor</t>
+          <t>Zachry Group (FEED)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Construcción (~74% avance)</t>
+          <t>Ingeniería (FEED) / FID prevista</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
+          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1023,54 +1023,54 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shintech Louisiana — Expansión Plaquemine (2do craqueador de etileno + 4ta unidad cloro-álcali/VCM)</t>
+          <t>Planta Coquizadora Salina Cruz</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plaquemine, Iberville Parish, Luisiana, EE.UU.</t>
+          <t>Salina Cruz, Oaxaca, México</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shintech Louisiana, LLC</t>
+          <t>Pemex</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>ICA Fluor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ingeniería/planeación (construcción por fases, 1a fase prevista 2030)</t>
+          <t>Construcción (~74% avance)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
+          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sandpiper Chemicals (metanol bajo carbono)</t>
+          <t>Shintech Louisiana — Expansión Plaquemine (2do craqueador de etileno + 4ta unidad cloro-álcali/VCM)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Texas City, Texas, EE.UU.</t>
+          <t>Plaquemine, Iberville Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sandpiper Chemicals, LLC / INEOS Acetyls (colaboración estratégica, abr-2026)</t>
+          <t>Shintech Louisiana, LLC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1080,86 +1080,86 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED en curso desde 2T2026; US$1,700 millones, 1.1 MMtpa; INEOS Acetyls tomará 300,000 ton/año para su unidad de ácido acético) / FID prevista 2027, primera producción ~2030</t>
+          <t>Ingeniería/planeación (construcción por fases, 1a fase prevista 2030)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[INEOS](https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OXEA Bay City Capacity Expansion + Air Liquide POX Syngas Unit</t>
+          <t>Sandpiper Chemicals (metanol bajo carbono)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bay City, Matagorda County, Texas, EE.UU.</t>
+          <t>Texas City, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OXEA (oxo chemicals) / Air Liquide (unidad de syngas)</t>
+          <t>Sandpiper Chemicals, LLC / INEOS Acetyls (colaboración estratégica, abr-2026)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Air Liquide (unidad propia); OXEA no especificado</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Construcción (FID confirmado 13-jul-2026; preparación de sitio 3T2026; finalización fines de 2028)</t>
+          <t>Ingeniería (FEED en curso desde 2T2026; US$1,700 millones, 1.1 MMtpa; INEOS Acetyls tomará 300,000 ton/año para su unidad de ácido acético) / FID prevista 2027, primera producción ~2030</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
+          <t>[INEOS](https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Targa Resources East Driver Gas Processing Plant</t>
+          <t>OXEA Bay City Capacity Expansion + Air Liquide POX Syngas Unit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Condado de Midland, Texas, EE.UU.</t>
+          <t>Bay City, Matagorda County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>OXEA (oxo chemicals) / Air Liquide (unidad de syngas)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Targa Resources (propietario-constructor)</t>
+          <t>Air Liquide (unidad propia); OXEA no especificado</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Construcción (planta criogénica 275 MMcf/d; arranque previsto 3T2026)</t>
+          <t>Construcción (FID confirmado 13-jul-2026; preparación de sitio 3T2026; finalización fines de 2028)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1171,32 +1171,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enterprise Products "Athena" Natural Gas Processing Plant</t>
+          <t>Targa Resources East Driver Gas Processing Plant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cuenca Midland (cuatro condados), Texas, EE.UU.</t>
+          <t>Condado de Midland, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L.P.</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Enterprise Products (propietario-constructor)</t>
+          <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Construcción (300 MMcf/d + hasta 40,000 bpd de NGLs; en servicio 4T2026)</t>
+          <t>Construcción (planta criogénica 275 MMcf/d; arranque previsto 3T2026)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1208,32 +1208,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MPLX Secretariat II Gas Processing Plant</t>
+          <t>Enterprise Products "Athena" Natural Gas Processing Plant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuenca Pérmica (subcuenca Delaware), Texas/Nuevo México, EE.UU.</t>
+          <t>Cuenca Midland (cuatro condados), Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MPLX LP</t>
+          <t>Enterprise Products Partners L.P.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MPLX (propietario-constructor)</t>
+          <t>Enterprise Products (propietario-constructor)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Planeada/desarrollo (300 MMcf/d; en servicio 2S2028)</t>
+          <t>Construcción (300 MMcf/d + hasta 40,000 bpd de NGLs; en servicio 4T2026)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MPLX Titan Complex (Northwind) — Expansión de Tratamiento de Gas Amargo</t>
+          <t>MPLX Secretariat II Gas Processing Plant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Condado de Lea, Nuevo México / frontera TX-NM, EE.UU.</t>
+          <t>Cuenca Pérmica (subcuenca Delaware), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Construcción (expansión de capacidad &gt;400 MMcf/d; plenamente operativo 4T2026)</t>
+          <t>Planeada/desarrollo (300 MMcf/d; en servicio 2S2028)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1282,32 +1282,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Northern Plains Nitrogen (urea/amoniaco)</t>
+          <t>MPLX Titan Complex (Northwind) — Expansión de Tratamiento de Gas Amargo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grand Forks, Dakota del Norte, EE.UU.</t>
+          <t>Condado de Lea, Nuevo México / frontera TX-NM, EE.UU.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Plains Nitrogen LLC</t>
+          <t>MPLX LP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EPC no designado</t>
+          <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pre-FEED completo / FID buscada 4T2026</t>
+          <t>Construcción (expansión de capacidad &gt;400 MMcf/d; plenamente operativo 4T2026)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
+          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1319,54 +1319,54 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Iron Mesa (planta de gas)</t>
+          <t>Northern Plains Nitrogen (urea/amoniaco)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Goldsmith, Ector County, Texas, EE.UU.</t>
+          <t>Grand Forks, Dakota del Norte, EE.UU.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Northern Plains Nitrogen LLC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>EPC no designado</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Construcción (arranque previsto Q1 2027)</t>
+          <t>Pre-FEED completo / FID buscada 4T2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Yeti II (planta de gas)</t>
+          <t>Iron Mesa (planta de gas)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
+          <t>Goldsmith, Ector County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
+          <t>Construcción (arranque previsto Q1 2027)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1393,32 +1393,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Refinería Francisco I. Madero (rehabilitación)</t>
+          <t>Yeti II (planta de gas)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ciudad Madero, Tamaulipas, México</t>
+          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pemex</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación/bidding</t>
+          <t>Ingeniería/planeación (en línea previsto Q4 2027)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1430,69 +1430,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fermachem Planta de Urea/Amoniaco</t>
+          <t>Refinería Francisco I. Madero (rehabilitación)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ejido Sapioris, Lerdo, Durango, México</t>
+          <t>Ciudad Madero, Tamaulipas, México</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fermaca Dreams (Fermachem)</t>
+          <t>Pemex</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
+          <t>Múltiples contratistas por licitar (30+ licitaciones)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Construcción (ejecución iniciada jun-2026)</t>
+          <t>Licitación/bidding</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
+          <t>Fermachem Planta de Urea/Amoniaco</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
+          <t>Ejido Sapioris, Lerdo, Durango, México</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clean Hydrogen Works</t>
+          <t>Fermaca Dreams (Fermachem)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>McDermott (FEED)</t>
+          <t>Técnicas Reunidas (licencia/tecnología KBR-Stamicarbon)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ingeniería (FEED) / Pre-FID</t>
+          <t>Construcción (ejecución iniciada jun-2026)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1504,32 +1504,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zeus Gas Plant + 3ra Fraccionadora Coastal Bend</t>
+          <t>Ascension Clean Energy (ACE) — amoniaco azul</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cuenca Pérmica, Texas / Robstown, Texas, EE.UU.</t>
+          <t>Donaldsonville, Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Clean Hydrogen Works</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>McDermott (FEED)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ingeniería (sancionado; en línea 2028)</t>
+          <t>Ingeniería (FEED) / Pre-FID</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
+          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1541,128 +1541,128 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Project Meadowlark (complejo de amoniaco azul/UAN/ATS/DEF)</t>
+          <t>Zeus Gas Plant + 3ra Fraccionadora Coastal Bend</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gothenburg, Nebraska, EE.UU.</t>
+          <t>Cuenca Pérmica, Texas / Robstown, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>J. Westling &amp; Co. (JWC Gburg, LLC)</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No especificado (tecnología licenciada Topsoe SynCOR Ammonia); contrato EPC/fabricación asegurado</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ingeniería/Permisos (permiso de aire emitido, sitio zonificado; obras civiles previstas 2027, operación comercial 2029)</t>
+          <t>Ingeniería (sancionado; en línea 2028)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wabash Low-Carbon Ammonia Project</t>
+          <t>Project Meadowlark (complejo de amoniaco azul/UAN/ATS/DEF)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>West Terre Haute, Indiana, EE.UU.</t>
+          <t>Gothenburg, Nebraska, EE.UU.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wabash Valley Resources</t>
+          <t>J. Westling &amp; Co. (JWC Gburg, LLC)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Samsung E&amp;C (contrato EPF ~US$475 millones)</t>
+          <t>No especificado (tecnología licenciada Topsoe SynCOR Ammonia); contrato EPC/fabricación asegurado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Construcción (groundbreaking 5-ene-2026; amoniaco bajo en carbono 500,000 ton/año con captura de 1.67 millones ton CO2/año; meta de finalización 2029)</t>
+          <t>Ingeniería/Permisos (permiso de aire emitido, sitio zonificado; obras civiles previstas 2027, operación comercial 2029)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Green Fuels Operating — Refinería Duncan</t>
+          <t>Wabash Low-Carbon Ammonia Project</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Duncan, Stephens County, Oklahoma, EE.UU.</t>
+          <t>West Terre Haute, Indiana, EE.UU.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Green Fuels Operating</t>
+          <t>Wabash Valley Resources</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Samsung E&amp;C (contrato EPF ~US$475 millones)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Construcción (groundbreaking 29-may-2026; inversión US$400 millones; capacidad inicial 30,000 bbl/d, expandible a 50,000 bbl/d, sobre sitio de refinería histórica de los años 1920)</t>
+          <t>Construcción (groundbreaking 5-ene-2026; amoniaco bajo en carbono 500,000 ton/año con captura de 1.67 millones ton CO2/año; meta de finalización 2029)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Energy Transfer Mustang Draw I &amp; II (plantas de gas)</t>
+          <t>Green Fuels Operating — Refinería Duncan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cuenca Midland, Texas, EE.UU.</t>
+          <t>Duncan, Stephens County, Oklahoma, EE.UU.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energy Transfer LP</t>
+          <t>Green Fuels Operating</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1672,34 +1672,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Construcción (Mustang Draw I en comisionamiento, servicio pleno ~jun-2026; Mustang Draw II en construcción, en servicio 4T2026; 275 MMcf/d cada una)</t>
+          <t>Construcción (groundbreaking 29-may-2026; inversión US$400 millones; capacidad inicial 30,000 bbl/d, expandible a 50,000 bbl/d, sobre sitio de refinería histórica de los años 1920)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[Energy Transfer](https://www.energytransfer.com/project-highlights/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ONEOK Bighorn / Cutter / Shadowfax (plantas de gas)</t>
+          <t>Energy Transfer Mustang Draw I &amp; II (plantas de gas)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cuenca Delaware (Bighorn), Texas / Cuenca Powder River (Cutter), Wyoming / Cuenca Midland (Shadowfax reubicada), Texas, EE.UU.</t>
+          <t>Cuenca Midland, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ONEOK Inc.</t>
+          <t>Energy Transfer LP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Construcción (Bighorn US$365 millones/300 MMcf/d tratamiento alto CO2, meta mediados 2027; Cutter 60 MMcf/d en construcción, meta 4T2026; Shadowfax 150 MMcf/d reubicación completada 1T2026, en rampa)</t>
+          <t>Construcción (Mustang Draw I en comisionamiento, servicio pleno ~jun-2026; Mustang Draw II en construcción, en servicio 4T2026; 275 MMcf/d cada una)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[Inspectioneering](https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant)</t>
+          <t>[Energy Transfer](https://www.energytransfer.com/project-highlights/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1726,32 +1726,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MPLX Harmon Creek III (planta de gas + de-etanizadora)</t>
+          <t>ONEOK Bighorn / Cutter / Shadowfax (plantas de gas)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Región Marcellus/Utica, noreste de EE.UU. (ubicación exacta no especificada)</t>
+          <t>Cuenca Delaware (Bighorn), Texas / Cuenca Powder River (Cutter), Wyoming / Cuenca Midland (Shadowfax reubicada), Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MPLX LP</t>
+          <t>ONEOK Inc.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MPLX (propietario-constructor)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Construcción (300 MMcf/d + de-etanizadora 40 Mbpd; en servicio 3T2026)</t>
+          <t>Construcción (Bighorn US$365 millones/300 MMcf/d tratamiento alto CO2, meta mediados 2027; Cutter 60 MMcf/d en construcción, meta 4T2026; Shadowfax 150 MMcf/d reubicación completada 1T2026, en rampa)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+          <t>[Inspectioneering](https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1763,86 +1763,86 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rehab. Complejo Cosoleacaque (amoniaco) + Complejo Morelos (etano-etileno)</t>
+          <t>MPLX Harmon Creek III (planta de gas + de-etanizadora)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cosoleacaque y Complejo Morelos, Veracruz, México</t>
+          <t>Región Marcellus/Utica, noreste de EE.UU. (ubicación exacta no especificada)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pemex Transformación Industrial</t>
+          <t>MPLX LP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mota-Engil México (plantas VI/VII y TASP Pajaritos); ICA (paquete relacionado)</t>
+          <t>MPLX (propietario-constructor)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ingeniería/planeación (parte del plan de reactivación petroquímica de Pemex de 93,000 mdp anunciado jun-2026; 13,000 mdp para 2 plantas de amoniaco en Cosoleacaque, meta 957,000 ton/año; Complejo Morelos incluido en programa de rehabilitación etano-etileno de 30,000 mdp/5 plantas, meta 520,000 ton/año de polietilenos/óxido de etileno/glicoles; contratos de rehabilitación y confiabilidad adjudicados dic-2025, confirmados ene-2026)</t>
+          <t>Construcción (300 MMcf/d + de-etanizadora 40 Mbpd; en servicio 3T2026)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/); [El Diario de Juárez](https://diario.mx/nacional/2026/jan/22/adjudica-pemex-contratos-a-favoritas-1102601.html)</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Products — Nuevas Plantas de Gas Permian (Plant 11 Midland / Plant 13 Delaware) + NGL Frac 15 Mont Belvieu</t>
+          <t>Rehab. Complejo Cosoleacaque (amoniaco) + Complejo Morelos (etano-etileno)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cuenca Midland y Cuenca Delaware, Texas, EE.UU. / Mont Belvieu, Texas, EE.UU.</t>
+          <t>Cosoleacaque y Complejo Morelos, Veracruz, México</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L.P.</t>
+          <t>Pemex Transformación Industrial</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Enterprise Products (propietario-constructor)</t>
+          <t>Mota-Engil México (plantas VI/VII y TASP Pajaritos); ICA (paquete relacionado)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Construcción (sancionadas/aprobadas en resultados 2T2026: Plant 11 Midland Basin 300 MMcf/d en servicio 1T2029; Plant 13 Delaware Basin 300 MMcf/d en servicio 3T2028; NGL Frac 15 en Mont Belvieu 150 MBPD en servicio 1T2028; gasto de capital de crecimiento 2026 aumentado en más de US$700 millones por estas sanciones)</t>
+          <t>Ingeniería/planeación (parte del plan de reactivación petroquímica de Pemex de 93,000 mdp anunciado jun-2026; 13,000 mdp para 2 plantas de amoniaco en Cosoleacaque, meta 957,000 ton/año; Complejo Morelos incluido en programa de rehabilitación etano-etileno de 30,000 mdp/5 plantas, meta 520,000 ton/año de polietilenos/óxido de etileno/glicoles; contratos de rehabilitación y confiabilidad adjudicados dic-2025, confirmados ene-2026)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+          <t>[Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/); [El Diario de Juárez](https://diario.mx/nacional/2026/jan/22/adjudica-pemex-contratos-a-favoritas-1102601.html)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Products — Plant 12 (Delaware Basin) y Athena 2 (Midland Basin)</t>
+          <t>Enterprise Products — Nuevas Plantas de Gas Permian (Plant 11 Midland / Plant 13 Delaware) + NGL Frac 15 Mont Belvieu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cuenca Delaware y Cuenca Midland, Texas, EE.UU.</t>
+          <t>Cuenca Midland y Cuenca Delaware, Texas, EE.UU. / Mont Belvieu, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Construcción (sancionadas, divulgadas en resultados 2T2026 el 30-jul-2026; Plant 12 Delaware Basin ~300 MMcf/d en servicio 4T2027; Athena 2 Midland Basin en servicio 3T2027)</t>
+          <t>Construcción (sancionadas/aprobadas en resultados 2T2026: Plant 11 Midland Basin 300 MMcf/d en servicio 1T2029; Plant 13 Delaware Basin 300 MMcf/d en servicio 3T2028; NGL Frac 15 en Mont Belvieu 150 MBPD en servicio 1T2028; gasto de capital de crecimiento 2026 aumentado en más de US$700 millones por estas sanciones)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1867,39 +1867,39 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Targa Resources Roadrunner III / Copperhead II (plantas de gas)</t>
+          <t>Enterprise Products — Plant 12 (Delaware Basin) y Athena 2 (Midland Basin)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
+          <t>Cuenca Delaware y Cuenca Midland, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>Enterprise Products Partners L.P.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Targa Resources (propietario-constructor)</t>
+          <t>Enterprise Products (propietario-constructor)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Construcción (aprobadas may-2026; Roadrunner III 265 MMcf/d, Copperhead II 275 MMcf/d; en servicio previsto 1T2028)</t>
+          <t>Construcción (sancionadas, divulgadas en resultados 2T2026 el 30-jul-2026; Plant 12 Delaware Basin ~300 MMcf/d en servicio 4T2027; Athena 2 Midland Basin en servicio 3T2027)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
+          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1911,54 +1911,54 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Southern Energy Renewables — Complejo de Metanol y SAF</t>
+          <t>Targa Resources Roadrunner III / Copperhead II (plantas de gas)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>St. Charles Parish (Killona), Luisiana, EE.UU.</t>
+          <t>Cuenca Delaware (Permian), Texas/Nuevo México, EE.UU.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Southern Energy Renewables</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Planeación/pre-construcción (inversión US$1,400 millones; convierte biomasa de desecho de madera en metanol verde y combustible de aviación sostenible; construcción prevista a iniciar fines de 2027, producción prevista fines de 2029)</t>
+          <t>Construcción (aprobadas may-2026; Roadrunner III 265 MMcf/d, Copperhead II 275 MMcf/d; en servicio previsto 1T2028)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Processing](https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); [Louisiana Economic Development](https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Atlas Agro — Pacific Green Fertilizer Plant</t>
+          <t>Southern Energy Renewables — Complejo de Metanol y SAF</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Richland, Washington, EE.UU.</t>
+          <t>St. Charles Parish (Killona), Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlas Agro</t>
+          <t>Southern Energy Renewables</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1968,49 +1968,49 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingeniería/FEED (diseño ~70% completo, USD 315 millones de capital levantado, permisos en proceso; planta de fertilizante nitrato ~0.7 Mt/año, inversión USD 1,100-1,500 millones; debe iniciar construcción antes de fines de 2027 para calificar a créditos fiscales federales; construcción estimada en 36 meses)</t>
+          <t>Planeación/pre-construcción (inversión US$1,400 millones; convierte biomasa de desecho de madera en metanol verde y combustible de aviación sostenible; construcción prevista a iniciar fines de 2027, producción prevista fines de 2029)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[Tri-Cities Area Journal of Business](https://www.tricitiesbusinessnews.com/articles/atlas-agro-plant-nears-decision-point); [Washington State Standard](https://washingtonstatestandard.com/2025/10/30/plan-for-1-5b-fertilizer-plant-in-central-wa-still-alive-despite-loss-of-federal-funds/)</t>
+          <t>[Hydrocarbon Processing](https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); [Louisiana Economic Development](https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hydrogen City (complejo Power-to-X / e-metanol)</t>
+          <t>Atlas Agro — Pacific Green Fertilizer Plant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Piedras Pintas Salt Dome, Condado de Duval, sur de Texas, EE.UU.</t>
+          <t>Richland, Washington, EE.UU.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Green Hydrogen International (GHI)</t>
+          <t>Atlas Agro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ABB (automatización/control, vía MOU)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ingeniería/FEED (inversión USD 6,000-10,000 millones; electrolizador de 2.2 GW; producirá 1.4 Mt/año de e-metanol y capturará ~2 Mt/año de CO2; construcción planeada desde 2026, primera producción estimada 2030)</t>
+          <t>Ingeniería/FEED (diseño ~70% completo, USD 315 millones de capital levantado, permisos en proceso; planta de fertilizante nitrato ~0.7 Mt/año, inversión USD 1,100-1,500 millones; debe iniciar construcción antes de fines de 2027 para calificar a créditos fiscales federales; construcción estimada en 36 meses)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[The Engineer](https://www.theengineer.co.uk/content/news/abb-joins-team-for-22gw-hydrogen-city-project-in-texas); [Energy Capital HTX](https://energycapitalhtx.com/green-hydrogen-city-abb-mou)</t>
+          <t>[Tri-Cities Area Journal of Business](https://www.tricitiesbusinessnews.com/articles/atlas-agro-plant-nears-decision-point); [Washington State Standard](https://washingtonstatestandard.com/2025/10/30/plan-for-1-5b-fertilizer-plant-in-central-wa-still-alive-despite-loss-of-federal-funds/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2022,35 +2022,72 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Hydrogen City (complejo Power-to-X / e-metanol)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Piedras Pintas Salt Dome, Condado de Duval, sur de Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Green Hydrogen International (GHI)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ABB (automatización/control, vía MOU)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ingeniería/FEED (inversión USD 6,000-10,000 millones; electrolizador de 2.2 GW; producirá 1.4 Mt/año de e-metanol y capturará ~2 Mt/año de CO2; construcción planeada desde 2026, primera producción estimada 2030)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[The Engineer](https://www.theengineer.co.uk/content/news/abb-joins-team-for-22gw-hydrogen-city-project-in-texas); [Energy Capital HTX](https://energycapitalhtx.com/green-hydrogen-city-abb-mou)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Targa Resources Falcon II Gas Processing Plant</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Cuenca Delaware, Permian Basin, Texas, EE.UU.</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Targa Resources Corp.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Targa Resources (propietario-constructor)</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Construcción/Comisionamiento (planta criogénica 275 MMcf/d; arranque adelantado a 1T2026, dos trimestres antes de lo previsto)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>[Oil &amp; Gas Journal](https://www.ogj.com/refining-processing/gas-processing/capacities/article/55240691/targa-advances-expansion-plans-for-permian-basin-gas-processing)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
@@ -2067,15 +2104,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3556,6 +3593,43 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gasoducto TTC Connector (alimenta Freeport LNG)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Condados de Colorado y Wharton, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Desarrollador: TTC Connector, LLC; opción de compra: Enbridge Inc.; cliente de capacidad: bp</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Construcción (25 millas/300 MMpc/d; en servicio previsto fines de 2026)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[LNG Industry](https://www.lngindustry.com/liquid-natural-gas/07082026/enbridge-signs-option-to-acquire-ttc-connector/)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -3570,15 +3644,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -6169,6 +6243,265 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Lone Tree Plant (Refurbishment Autoclave/CIL)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lovelock, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>i-80 Gold Corp</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Hatch (EPCM)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Construcción (obras tempranas y movilización de contratistas en curso; construcción mayor prevista 4T2026)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Round Mountain Phase X — Planta de Paste Backfill</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nye County, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Kinross Gold Corporation</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>No especificado (paquetes de equipo móvil, ventiladores y planta CRF ya adjudicados)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Construcción/Ingeniería detallada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Bald Mountain Redbird 2 — Planta SART (ácido/lixiviación)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>White Pine County, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Kinross Gold Corporation</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Contratista de ingeniería detallada ya seleccionado, no revelado en la fuente</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ingeniería (básica ~50% completa)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Bear Lodge Rare Earth Project</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Crook County, Wyoming, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Rare Element Resources Ltd. (afiliada de General Atomics/Synchron)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Permitting (designación FAST-41; aviso NEPA publicado en Federal Register 29-jul-2026)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Proyecto de Cobre Angangueo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Angangueo, Michoacán, México</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Southern Copper Corporation (Grupo México)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pre-desarrollo (en negociación de permisos con gobierno federal)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Proyecto de Cobre Chalchihuites</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Chalchihuites, Zacatecas, México</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Southern Copper Corporation (Grupo México)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pre-desarrollo (en negociación de permisos)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Modernización Complejo Metalúrgico Empalme</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Empalme, Sonora, México</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Southern Copper Corporation (Grupo México)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pre-desarrollo (en negociación de permisos; fundición existente a modernizar)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -6183,15 +6516,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -6578,7 +6911,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pacifico Energy</t>
+          <t>Pacifico Energy; inquilino confirmado: Amazon (AWS)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6588,17 +6921,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Permisos obtenidos/inicio construcción (TCEQ otorgó permiso de aire para 7.65GW de generación a gas, el más grande emitido en EE.UU. hasta la fecha; Fase 1 de 1GW prevista en operación 1S2027)</t>
+          <t>Construcción de edificios de centro de datos iniciada (TCEQ ya había otorgado permiso de aire para 7.65GW de generación a gas; Amazon presentó a inicios de ago-2026 permisos de construcción para 3 edificios de centro de datos —"Pecos County Data Center", Buildings A/B/C, ~189,060 pies² c/u, ~US$300M c/u—; construcción de edificios prevista ago-dic 2026; Fase 1 de 1GW de generación prevista en operación 1S2027)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); [US Data Center Projects](https://usdatacenterprojects.com/texas/amazon-files-plans-for-new-data-center-buildings-in-texas-across-three-sites)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -7994,17 +8327,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Construcción DETENIDA (orden de suspensión de la agencia ambiental de Georgia -EPD- por construir sin permisos, 2-jul-2026)</t>
+          <t>Construcción REANUDADA (tras orden de suspensión de la agencia ambiental de Georgia -EPD- del 2-jul-2026 por construir sin permisos; a 31-jul-2026 la construcción de la planta de 90MW está en marcha de nuevo, con 6 de 33 motores a gas ya instalados)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/)</t>
+          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); [Inside Climate News](https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -9115,6 +9448,80 @@
       <c r="G79" t="inlineStr">
         <is>
           <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Galaxy Digital Project Merlin</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>McGregor, Condado de McLennan, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Galaxy Digital</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Planeación/permitting inicial (500 acres adquiridos; acuerdo de desarrollo aprobado por el ayuntamiento de McGregor 24-jun-2026; subestación eléctrica propia en construcción; enfriamiento de circuito cerrado, sin planta de gas on-site confirmada; Fase 1 de 74MW prevista 2028)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Nexus Fulcrum Gas Plant (TRIC)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tahoe-Reno Industrial Center, Condado de Storey, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nexus Fulcrum LLC (abastecerá al hub industrial/de centros de datos de TRIC, donde operan Switch, Google, Tract, entre otros)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Permitting (solicitud regulatoria presentada ante reguladores estatales de energía de Nevada para planta de gas natural de 510MW)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>[The Nevada Independent](https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,10 +20,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -49,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,46 +429,46 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -493,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx); [Tech Times](https://www.techtimes.com/articles/323235/20260805/trumps-flagship-texas-refinery-races-permit-deadline-after-326b-grid-loan.htm)</t>
+          <t>Fluor newsroom (https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx); Tech Times (https://www.techtimes.com/articles/323235/20260805/trumps-flagship-texas-refinery-races-permit-deadline-after-326b-grid-loan.htm)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,69 +514,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ExxonMobil Coastal Plain (cracker + PE)</t>
+          <t>CF Industries Blue Point (amoniaco bajo carbono)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Calhoun County, Texas, EE.UU.</t>
+          <t>Ascension Parish, Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>CF Industries / JERA / Mitsui &amp; Co.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Technip Energies</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ingeniería/FEED</t>
+          <t>Construcción (Luisiana y el U.S. Army Corps of Engineers emitieron en jul-2026 los permisos de construcción civil necesarios; CF Industries confirmó en su reporte 2T2026 —8-K, 5-ago-2026— el inicio de construcción en ago-2026 de la planta de amoniaco bajo carbono, ~708,000-1.4 MTPA, ~US$3.7-4,000 millones; producción prevista 2029)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
+          <t>FuelCellsWorks (https://fuelcellsworks.com/2026/08/06/clean-energy/cf-industries-to-begin-construction-of-3-7bn-louisiana-blue-ammonia-plant); gasworld (https://www.gasworld.com/story/cf-industries-to-begin-construction-of-4bn-louisiana-blue-ammonia-project/2256572.article/)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Golden Triangle Polymers</t>
+          <t>ExxonMobil Coastal Plain (cracker + PE)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orange, Texas, EE.UU.</t>
+          <t>Calhoun County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chevron Phillips Chemical (CPChem) / QatarEnergy</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ZDJV (Zachry/DL USA); JKJV (JGC America/Kiewit)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Construcción (comisionamiento)</t>
+          <t>Ingeniería/FEED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
+          <t>AllStream Insiders (https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -579,37 +588,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF Industries Blue Point (amoniaco bajo carbono)</t>
+          <t>Golden Triangle Polymers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ascension Parish, Luisiana, EE.UU.</t>
+          <t>Orange, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF Industries / JERA / Mitsui &amp; Co.</t>
+          <t>Chevron Phillips Chemical (CPChem) / QatarEnergy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technip Energies</t>
+          <t>ZDJV (Zachry/DL USA); JKJV (JGC America/Kiewit)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Construcción (impulso federal de permisos anunciado may-2026 con finalización esperada en 45 días; CF Industries confirma inicio de construcción en 2026)</t>
+          <t>Construcción (comisionamiento)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[Construction Front](https://constructionfront.com/2025-04-13-technip-energies-to-deliver-blue-point-worlds-largest-low-carbon-ammonia-facility-in-louisiana/); [FuelCellsWorks](https://fuelcellsworks.com/2026/05/07/h2/cf-industries-targets-construction-start-this-year-on-blue-hydrogen-and-ammonia-complex)</t>
+          <t>BIC Magazine (https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -641,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
+          <t>East Daley (https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -678,7 +687,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
+          <t>Techint (https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -715,7 +724,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
+          <t>OGJ (https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -752,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+          <t>Forbes México (https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +798,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+          <t>Forbes México (https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -826,7 +835,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
+          <t>Forbes México (https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -863,7 +872,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); [Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
+          <t>Tribuna (https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); Contralínea (https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -900,7 +909,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
+          <t>PV Magazine México (https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -937,7 +946,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
+          <t>H2 View (https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -974,7 +983,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Debate](https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
+          <t>Debate (https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1011,7 +1020,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
+          <t>ICIS (https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1048,7 +1057,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
+          <t>Diario del Istmo (https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1085,7 +1094,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
+          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1122,7 +1131,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[INEOS](https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
+          <t>INEOS (https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1159,7 +1168,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
+          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1196,7 +1205,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
+          <t>OGJ (https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1233,7 +1242,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
+          <t>Business Wire (https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1270,7 +1279,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+          <t>Natural Gas Intel (https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1307,7 +1316,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
+          <t>East Daley (https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1344,7 +1353,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
+          <t>Grand Forks Herald (https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,7 +1390,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+          <t>Phillips 66 (https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1418,7 +1427,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+          <t>Targa Resources (https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1455,7 +1464,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+          <t>Elefante Blanco (https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1492,7 +1501,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+          <t>La Jornada (https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1529,7 +1538,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+          <t>Downstream Calendar (https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1566,7 +1575,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
+          <t>Business Wire (https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1603,7 +1612,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
+          <t>USDA (https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1640,7 +1649,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
+          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1677,7 +1686,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
+          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1714,7 +1723,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[Energy Transfer](https://www.energytransfer.com/project-highlights/)</t>
+          <t>Energy Transfer (https://www.energytransfer.com/project-highlights/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1746,17 +1755,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Construcción (Bighorn US$365 millones/300 MMcf/d tratamiento alto CO2, meta mediados 2027; Cutter 60 MMcf/d en construcción, meta 4T2026; Shadowfax 150 MMcf/d reubicación completada 1T2026, en rampa)</t>
+          <t>Construcción (según reporte 2T2026 de ONEOK, ~4-8-ago-2026: Bighorn ampliada de 300 a 400 MMcf/d, tratamiento alto CO2, meta mediados 2027; Cutter 60 MMcf/d en construcción, meta 4T2026; Shadowfax 150 MMcf/d reubicada a la cuenca Midland durante el trimestre, en rampa)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[Inspectioneering](https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant)</t>
+          <t>Inspectioneering (https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant); BigGo Finance (https://finance.biggo.com/news/US_OKE_2026-08-04)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1783,17 +1792,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Construcción (300 MMcf/d + de-etanizadora 40 Mbpd; en servicio 3T2026)</t>
+          <t>Operando (arranque/startup completado ago-2026, según reporte 2T2026 de MPLX; eleva capacidad de procesamiento de MPLX en el noreste a 8.1 Bcf/d; planta de 300 MMcf/d + de-etanizadora 40 Mbpd)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+          <t>Marcellus Drilling News (https://marcellusdrilling.com/2026/08/mplx-marcellus-proc-plants-96-full-harmon-creek-iii-starts-up/); StockTitan (https://www.stocktitan.net/news/MPLX/mplx-lp-reports-second-quarter-2026-financial-9tcvq4saz6sr.html)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1834,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/); [El Diario de Juárez](https://diario.mx/nacional/2026/jan/22/adjudica-pemex-contratos-a-favoritas-1102601.html)</t>
+          <t>Contralínea (https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/); El Diario de Juárez (https://diario.mx/nacional/2026/jan/22/adjudica-pemex-contratos-a-favoritas-1102601.html)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1862,7 +1871,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+          <t>Enterprise Reports Second Quarter 2026 Earnings (https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1899,7 +1908,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+          <t>Enterprise Reports Second Quarter 2026 Earnings (https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1936,7 +1945,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
+          <t>PGJ (https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1973,7 +1982,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[Hydrocarbon Processing](https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); [Louisiana Economic Development](https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
+          <t>Hydrocarbon Processing (https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); Louisiana Economic Development (https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2010,7 +2019,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[Tri-Cities Area Journal of Business](https://www.tricitiesbusinessnews.com/articles/atlas-agro-plant-nears-decision-point); [Washington State Standard](https://washingtonstatestandard.com/2025/10/30/plan-for-1-5b-fertilizer-plant-in-central-wa-still-alive-despite-loss-of-federal-funds/)</t>
+          <t>Tri-Cities Area Journal of Business (https://www.tricitiesbusinessnews.com/articles/atlas-agro-plant-nears-decision-point); Washington State Standard (https://washingtonstatestandard.com/2025/10/30/plan-for-1-5b-fertilizer-plant-in-central-wa-still-alive-despite-loss-of-federal-funds/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2047,7 +2056,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[The Engineer](https://www.theengineer.co.uk/content/news/abb-joins-team-for-22gw-hydrogen-city-project-in-texas); [Energy Capital HTX](https://energycapitalhtx.com/green-hydrogen-city-abb-mou)</t>
+          <t>The Engineer (https://www.theengineer.co.uk/content/news/abb-joins-team-for-22gw-hydrogen-city-project-in-texas); Energy Capital HTX (https://energycapitalhtx.com/green-hydrogen-city-abb-mou)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2084,7 +2093,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[Oil &amp; Gas Journal](https://www.ogj.com/refining-processing/gas-processing/capacities/article/55240691/targa-advances-expansion-plans-for-permian-basin-gas-processing)</t>
+          <t>Oil &amp; Gas Journal (https://www.ogj.com/refining-processing/gas-processing/capacities/article/55240691/targa-advances-expansion-plans-for-permian-basin-gas-processing)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2108,46 +2117,46 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -2181,7 +2190,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); [Natural Gas Intel](https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/); [Federal Register](https://www.federalregister.gov/documents/2026/08/03/2026-15695/rio-grande-lng-train-6-llc-notice-of-intent-to-prepare-an-environmental-impact-statement-for-the); [LNG Prime](https://lngprime.com/americas/nextdecade-seeks-ferc-ok-for-sixth-rio-grande-lng-train/187820/)</t>
+          <t>Bechtel (https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); Natural Gas Intel (https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/); Federal Register (https://www.federalregister.gov/documents/2026/08/03/2026-15695/rio-grande-lng-train-6-llc-notice-of-intent-to-prepare-an-environmental-impact-statement-for-the); LNG Prime (https://lngprime.com/americas/nextdecade-seeks-ferc-ok-for-sixth-rio-grande-lng-train/187820/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2218,7 +2227,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
+          <t>Bechtel (https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2255,7 +2264,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
+          <t>Woodside (https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2292,7 +2301,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal); [LNG Prime](https://lngprime.com/americas/top-5-news-of-the-week-july-20-26/193119/)</t>
+          <t>GEM.wiki (https://www.gem.wiki/CP2_LNG_Terminal); LNG Prime (https://lngprime.com/americas/top-5-news-of-the-week-july-20-26/193119/)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2329,7 +2338,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/); [Argus Media](https://www.argusmedia.com/en/news-and-insights/latest-market-news/2755512-vg-files-expansion-plan-to-double-plaquemines-lng)</t>
+          <t>Offshore Energy (https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/); Argus Media (https://www.argusmedia.com/en/news-and-insights/latest-market-news/2755512-vg-files-expansion-plan-to-double-plaquemines-lng)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2366,7 +2375,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[Port Arthur News](https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
+          <t>Port Arthur News (https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2403,7 +2412,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); [LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/); [energiesmedia](https://energiesmedia.com/ferc-approves-cheniere-train-7-energies/)</t>
+          <t>PGJ (https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); LNG Prime (https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/); energiesmedia (https://energiesmedia.com/ferc-approves-cheniere-train-7-energies/)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2435,17 +2444,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Construcción (FID positiva jun-2026)</t>
+          <t>Construcción (FID positiva jun-2026; TDI-Brooks International adjudicado 10-ago-2026 para levantamientos geofísicos/geotécnicos submarinos del puerto de aguas profundas —inicio geofísico fin ago-2026, geotécnico fin sep-2026—, en apoyo de hasta 3 unidades FLNG, ~13.2 Mtpa)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html); World Oil (https://www.worldoil.com/news/2026/8/10/tdi-brooks-wins-survey-contract-for-delfin-lng-deepwater-port/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2486,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[Dossier Político](https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/); [Natural Gas Intel](https://naturalgasintel.com/news/oneok-affiliate-seeks-3-year-extension-for-saguaro-connector-pipeline/)</t>
+          <t>Dossier Político (https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/); Natural Gas Intel (https://naturalgasintel.com/news/oneok-affiliate-seeks-3-year-extension-for-saguaro-connector-pipeline/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2514,7 +2523,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
+          <t>GEM Wiki (https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2551,7 +2560,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
+          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2588,7 +2597,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal); [PR Newswire/Caturus](https://www.prnewswire.com/news-releases/caturus-announces-final-investment-decision-for-9-5-mtpa-commonwealth-lng-export-facility-in-cameron-la-302773264.html)</t>
+          <t>PGJ (https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal); PR Newswire/Caturus (https://www.prnewswire.com/news-releases/caturus-announces-final-investment-decision-for-9-5-mtpa-commonwealth-lng-export-facility-in-cameron-la-302773264.html)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2625,7 +2634,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
+          <t>Houston Public Media (https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2662,7 +2671,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos); [LNG Prime](https://lngprime.com/lng-terminals/sempra-infrastructure-extends-eca-lng-commissioning-due-to-compressor-damage/193584/)</t>
+          <t>Sempra (https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos); LNG Prime (https://lngprime.com/lng-terminals/sempra-infrastructure-extends-eca-lng-commissioning-due-to-compressor-damage/193584/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2699,7 +2708,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
+          <t>LNG Prime (https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2736,7 +2745,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2773,7 +2782,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[Rigzone](https://www.rigzone.com/news/coastal_bend_lng_enters_permitting_phase-05-aug-2026-184302-article/); [PGJ](https://pgjonline.com/news/2026/august/coastal-bend-lng-initiates-formal-permitting-and-consultation-process)</t>
+          <t>Rigzone (https://www.rigzone.com/news/coastal_bend_lng_enters_permitting_phase-05-aug-2026-184302-article/); PGJ (https://pgjonline.com/news/2026/august/coastal-bend-lng-initiates-formal-permitting-and-consultation-process)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2810,7 +2819,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
+          <t>FERC (https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2842,17 +2851,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pre-FID (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381 necesario para el financiamiento de Glenfarne, 16-jul-2026; gobernador convocó sesión legislativa especial a partir del 27-jul-2026 para reintentar)</t>
+          <t>Pre-FID (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381, 16-jul-2026; gobernador Dunleavy convocó nueva sesión legislativa especial para el 20-ago-2026 con una ley de incentivos actualizada para reintentar destrabar el financiamiento)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[Alaska Beacon](https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/)</t>
+          <t>Alaska Beacon (https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/); Your Alaska Link (https://www.youralaskalink.com/news/local/dunleavy-plans-updated-lng-bill-calls-lawmakers-back-august-20/article_4ea0fcfa-386b-45c1-815d-8fff56088739.html)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2893,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
+          <t>PGJ (https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2921,7 +2930,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
+          <t>OGJ (https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2958,7 +2967,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2995,7 +3004,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3032,7 +3041,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
+          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3069,7 +3078,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[World Oil](https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/); [PGJ](https://pgjonline.com/news/2026/august/argent-lng-submits-wsa-to-the-us-coast-guard-advancing-its-25-mmtpy-louisiana-lng-project)</t>
+          <t>World Oil (https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/); PGJ (https://pgjonline.com/news/2026/august/argent-lng-submits-wsa-to-the-us-coast-guard-advancing-its-25-mmtpy-louisiana-lng-project)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3106,7 +3115,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
+          <t>Federal Register (https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3143,7 +3152,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Mississippi Today](https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
+          <t>Mississippi Today (https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3180,7 +3189,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[Mississippi Today](https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
+          <t>Mississippi Today (https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3217,7 +3226,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
+          <t>LNG Prime (https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3254,7 +3263,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[Baker Hughes](https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
+          <t>Baker Hughes (https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3291,7 +3300,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
+          <t>Federal Register (https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3328,7 +3337,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/); [Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc)</t>
+          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/); Federal Register (https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3365,7 +3374,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[Proyectos México](https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
+          <t>Proyectos México (https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3402,7 +3411,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[LNG Industry](https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/)</t>
+          <t>LNG Industry (https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3439,7 +3448,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
+          <t>Federal Register (https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3476,7 +3485,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[LNG Prime](https://lngprime.com/americas/cameron-lng-seeks-ferc-extension-for-expansion-project/167382/)</t>
+          <t>LNG Prime (https://lngprime.com/americas/cameron-lng-seeks-ferc-extension-for-expansion-project/167382/)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3513,7 +3522,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/02/23/2026-03548/magnolia-lng-llc-notice-of-request-for-extension-of-time)</t>
+          <t>Federal Register (https://www.federalregister.gov/documents/2026/02/23/2026-03548/magnolia-lng-llc-notice-of-request-for-extension-of-time)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3550,7 +3559,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[Storage Terminals Magazine](https://storageterminalsmag.com/kinder-morgans-trident-pipeline-project-enters-active-construction-phase-in-southeast-texas/); [Natural Gas Intel](https://www.naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+          <t>Storage Terminals Magazine (https://storageterminalsmag.com/kinder-morgans-trident-pipeline-project-enters-active-construction-phase-in-southeast-texas/); Natural Gas Intel (https://www.naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3587,7 +3596,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[Global Energy Monitor](https://www.gem.wiki/Centauro_del_Norte_Gas_Pipeline); [BNamericas](https://www.bnamericas.com/en/news/mexico-grants-permits-for-three-sonora-gas-projects)</t>
+          <t>Global Energy Monitor (https://www.gem.wiki/Centauro_del_Norte_Gas_Pipeline); BNamericas (https://www.bnamericas.com/en/news/mexico-grants-permits-for-three-sonora-gas-projects)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3624,7 +3633,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[LNG Industry](https://www.lngindustry.com/liquid-natural-gas/07082026/enbridge-signs-option-to-acquire-ttc-connector/)</t>
+          <t>LNG Industry (https://www.lngindustry.com/liquid-natural-gas/07082026/enbridge-signs-option-to-acquire-ttc-connector/)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3644,50 +3653,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -3716,17 +3725,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ingeniería completada (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año) / construcción prevista H1 2026; EXIM Bank emitió carta de interés para financiamiento de hasta US$825 millones</t>
+          <t>Ingeniería completada (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año) / construcción prevista H1 2026; EXIM Bank gestiona ahora más de US$1,000 millones en financiamiento, como parte del paquete federal de US$3,000 millones en minerales críticos anunciado 7-8-ago-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); [Ivanhoe Electric](https://ivanhoeelectric.com/news/ivanhoe-electric-receives-indication-for-up-to-825-million-in-financing-from-export-import-bank-of-the-united-states-for-santa/)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); MINING.COM (https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3767,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
+          <t>SEC/Hudbay (https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3790,17 +3799,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ingeniería temprana post intercambio de tierras (marzo 2026); firmó Master Supply Agreement (1-jul-2026) con Johnson Controls Inc. y United Association Local 469 (sindicato de plomeros/pipefitters) para mantenimiento de instalaciones y soporte operativo en sitio</t>
+          <t>Ingeniería temprana post intercambio de tierras (marzo 2026); firmó Master Supply Agreement (1-jul-2026) con Johnson Controls Inc. y UA Local 469; otorgó ~US$110 millones en contratos a Major Drilling America Inc. y Redpath USA Corporation (10-ago-2026) para acelerar exploración y desarrollo subterráneo, parte de programa de inversión de ~US$500 millones</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); [Resolution Copper](https://resolutioncopper.com/resolution-copper-and-united-association-local-469-enter-into-master-supply-agreement-supporting-operations-in-arizona/)</t>
+          <t>SEC (https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); International Mining (https://im-mining.com/2026/08/10/resolution-copper-accelerates-exploration-underground-development-with-major-drilling-redpath-contracts/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3841,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); [Lithium Americas](https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); Lithium Americas (https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3869,7 +3878,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
+          <t>Mining.com (https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3906,7 +3915,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
+          <t>Energy Magazine MX (https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3943,7 +3952,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
+          <t>BNamericas (https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3980,7 +3989,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
+          <t>M3 Engineering (https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4017,7 +4026,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4054,7 +4063,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
+          <t>Mining.com (https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4091,7 +4100,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
+          <t>USDA (https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4128,7 +4137,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); [Departamento de Justicia de EE.UU.](https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); Departamento de Justicia de EE.UU. (https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4165,7 +4174,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
+          <t>Silver Tiger Metals (https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4202,7 +4211,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4239,7 +4248,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
+          <t>Orla Mining (https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4276,7 +4285,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28); [Minera Alamos](https://mineraalamos.com/news/2026/minera-alamos-announces-positive-pre-feasibility-study-for-the-copperstone-gold-project-in-arizona/)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28); Minera Alamos (https://mineraalamos.com/news/2026/minera-alamos-announces-positive-pre-feasibility-study-for-the-copperstone-gold-project-in-arizona/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4313,7 +4322,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html); [Discovery Alert](https://discoveryalert.com.au/ck-gold-project-permitting-construction-ready-valuation-2026/)</t>
+          <t>Wyoming News (https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html); Discovery Alert (https://discoveryalert.com.au/ck-gold-project-permitting-construction-ready-valuation-2026/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4350,7 +4359,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
+          <t>First Majestic (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4387,7 +4396,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
+          <t>SEC/Americas Gold and Silver (https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4424,7 +4433,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
+          <t>Kitco (https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4461,7 +4470,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4498,7 +4507,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); [Newsfile](https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
+          <t>Northern Miner (https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); Newsfile (https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4535,7 +4544,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
+          <t>BNamericas (https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4572,7 +4581,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
+          <t>Resource World (https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4609,7 +4618,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
+          <t>Fresnillo plc (https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4646,7 +4655,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[Army.mil](https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
+          <t>Army.mil (https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4683,7 +4692,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4720,7 +4729,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4757,7 +4766,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
+          <t>IM Mining (https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4794,7 +4803,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4831,7 +4840,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4868,7 +4877,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
+          <t>Minera Alamos (https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4905,7 +4914,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
+          <t>Global Mining Review (https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4942,7 +4951,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
+          <t>BLM (https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4979,7 +4988,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[InvestingNews](https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/); [StockTitan/SEC 6-K](https://www.stocktitan.net/sec-filings/SLI/6-k-standard-lithium-ltd-current-report-foreign-issuer-ef7db860baa3.html)</t>
+          <t>InvestingNews (https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/); StockTitan/SEC 6-K (https://www.stocktitan.net/sec-filings/SLI/6-k-standard-lithium-ltd-current-report-foreign-issuer-ef7db860baa3.html)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5016,7 +5025,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
+          <t>SEC/Freeport-McMoRan (https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5053,7 +5062,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
+          <t>NioCorp (https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5090,7 +5099,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[E&amp;MJ](https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
+          <t>E&amp;MJ (https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5127,7 +5136,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html); [Arizona Sonoran](https://arizonasonoran.com/news-releases/arizona-sonoran-pre-feasibility-study-delivers-exceptional-results-for-the-cactus-project-outlining-long-life-low-cost-copper-1/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html); Arizona Sonoran (https://arizonasonoran.com/news-releases/arizona-sonoran-pre-feasibility-study-delivers-exceptional-results-for-the-cactus-project-outlining-long-life-low-cost-copper-1/)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5164,7 +5173,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[Western Exploration](https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx); [StreetWise Reports](https://www.streetwisereports.com/article/2026/08/03/nevada-gold-project-launches-drill-campaign-at-doby-george.html)</t>
+          <t>Western Exploration (https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx); StreetWise Reports (https://www.streetwisereports.com/article/2026/08/03/nevada-gold-project-launches-drill-campaign-at-doby-george.html)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5201,7 +5210,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[Chesapeake Gold Corp.](https://chesapeakegold.com/metates/)</t>
+          <t>Chesapeake Gold Corp. (https://chesapeakegold.com/metates/)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5238,7 +5247,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[Mining Technology](https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
+          <t>Mining Technology (https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5275,7 +5284,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5312,7 +5321,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[The Western News](https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
+          <t>The Western News (https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5349,7 +5358,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
+          <t>Mining News North (https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5386,7 +5395,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[IM Mining](https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
+          <t>IM Mining (https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5423,7 +5432,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[Resource World](https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
+          <t>Resource World (https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5460,7 +5469,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[Talon Metals](https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
+          <t>Talon Metals (https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5497,7 +5506,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5534,7 +5543,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[MPR News](https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
+          <t>MPR News (https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5571,7 +5580,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[Energy Fuels](https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); [PR Newswire](https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
+          <t>Energy Fuels (https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); PR Newswire (https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5608,7 +5617,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5645,7 +5654,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[Texarkana Gazette](https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
+          <t>Texarkana Gazette (https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5682,7 +5691,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[Mining.com](https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); [Orla Mining](https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
+          <t>Mining.com (https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); Orla Mining (https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5719,7 +5728,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[Sonoro Gold Corp.](https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); [Mexico Mining Center](https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
+          <t>Sonoro Gold Corp. (https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); Mexico Mining Center (https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5756,7 +5765,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/guardian-metals-outlines-viable-tungsten-trioxide-operation-in-nevada-2026-06-30); [StockTitan](https://www.stocktitan.net/news/GMTL/guardian-metal-resources-plc-announces-pilot-mountain-pre-tftnlr9fu3if.html)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/guardian-metals-outlines-viable-tungsten-trioxide-operation-in-nevada-2026-06-30); StockTitan (https://www.stocktitan.net/news/GMTL/guardian-metal-resources-plc-announces-pilot-mountain-pre-tftnlr9fu3if.html)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5793,7 +5802,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[Newswire](https://www.newswire.ca/news-releases/p2-gold-gabbs-project-update-feasibility-study-on-track-840759204.html)</t>
+          <t>Newswire (https://www.newswire.ca/news-releases/p2-gold-gabbs-project-update-feasibility-study-on-track-840759204.html)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5830,7 +5839,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/buscar-company-announces-major-advancement-in-the-permitting-process-for-the-treasure-canyon-gold-mine-project-in-california-302772744.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/buscar-company-announces-major-advancement-in-the-permitting-process-for-the-treasure-canyon-gold-mine-project-in-california-302772744.html)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5867,7 +5876,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/01/29/3229150/0/en/Paramount-Gold-Receives-Federal-Approval-for-the-Grassy-Mountain-Gold-Project.html); [OPB](https://www.opb.org/article/2026/01/29/oregon-gold-mine-grassy-mountain/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/01/29/3229150/0/en/Paramount-Gold-Receives-Federal-Approval-for-the-Grassy-Mountain-Gold-Project.html); OPB (https://www.opb.org/article/2026/01/29/oregon-gold-mine-grassy-mountain/)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5904,7 +5913,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[CNBC](https://www.cnbc.com/2026/02/26/mp-materials-selects-texas-for-rare-earth-magnet-manufacturing-site.html)</t>
+          <t>CNBC (https://www.cnbc.com/2026/02/26/mp-materials-selects-texas-for-rare-earth-magnet-manufacturing-site.html)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5941,7 +5950,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/the-united-states-is-investing-in-its-domestic-rare-earth-industry-302838375.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/the-united-states-is-investing-in-its-domestic-rare-earth-industry-302838375.html)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5978,7 +5987,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>[Newsfile Corp](https://www.newsfilecorp.com/release/283399/Americas-Gold-and-Silver-Signs-Joint-Venture-Agreement-with-US-Antimony-to-Construct-Antimony-Processing-Facility-in-Idahos-Silver-Valley-Unlocking-Value-from-Its-Antimony-Production-and-Strengthening-U.S.-Critical-Mineral-Security)</t>
+          <t>Newsfile Corp (https://www.newsfilecorp.com/release/283399/Americas-Gold-and-Silver-Signs-Joint-Venture-Agreement-with-US-Antimony-to-Construct-Antimony-Processing-Facility-in-Idahos-Silver-Valley-Unlocking-Value-from-Its-Antimony-Production-and-Strengthening-U.S.-Critical-Mineral-Security)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6015,7 +6024,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[DOE-LPO](https://www.energy.gov/lpo/articles/lpo-announces-conditional-commitment-michigan-potash-produce-fertilizer-us-farmers); [Northern Miner](https://www.northernminer.com/news/us-boosts-potash-projects-in-utah-michigan/1003886533/)</t>
+          <t>DOE-LPO (https://www.energy.gov/lpo/articles/lpo-announces-conditional-commitment-michigan-potash-produce-fertilizer-us-farmers); Northern Miner (https://www.northernminer.com/news/us-boosts-potash-projects-in-utah-michigan/1003886533/)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6052,7 +6061,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>[BLM](https://www.blm.gov/announcement/blm-approves-construction-sevier-playa-potash-mining-project)</t>
+          <t>BLM (https://www.blm.gov/announcement/blm-approves-construction-sevier-playa-potash-mining-project)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6089,7 +6098,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[Ur-Energy](https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
+          <t>Ur-Energy (https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6126,7 +6135,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/silverco-targets-late-2026-restart-past-producing-cusi-mine); [Investing News Network](https://investingnews.com/silverco-mining-begins-underground-development-at-cusi-restart-remains-on-budget-and-on-schedule/)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/mining/news/silverco-targets-late-2026-restart-past-producing-cusi-mine); Investing News Network (https://investingnews.com/silverco-mining-begins-underground-development-at-cusi-restart-remains-on-budget-and-on-schedule/)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6163,7 +6172,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>[Junior Mining Network](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/2342-tsx/ti/199070-titan-mining-to-start-shipping-first-graphite-product-and-feasibility-study-underway-for-40-000-tpa-integrated-kilbourne-graphite-project.html)</t>
+          <t>Junior Mining Network (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/2342-tsx/ti/199070-titan-mining-to-start-shipping-first-graphite-product-and-feasibility-study-underway-for-40-000-tpa-integrated-kilbourne-graphite-project.html)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6200,7 +6209,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>[Permitting Council](https://www.permitting.gov/newsroom/success-stories/project-spotlight-graphite-creek-project)</t>
+          <t>Permitting Council (https://www.permitting.gov/newsroom/success-stories/project-spotlight-graphite-creek-project)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6237,7 +6246,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[Pan American Silver](https://panamericansilver.com/news/pan-american-announces-revised-pea-for-the-la-colorada-skarn-project-positions-la-colorada-as-a-future-top-tier-silver-mine/); [SEC 6-K](https://www.sec.gov/Archives/edgar/data/771992/000077199226000031/a2026_03x24lacoloradapeaup.htm)</t>
+          <t>Pan American Silver (https://panamericansilver.com/news/pan-american-announces-revised-pea-for-the-la-colorada-skarn-project-positions-la-colorada-as-a-future-top-tier-silver-mine/); SEC 6-K (https://www.sec.gov/Archives/edgar/data/771992/000077199226000031/a2026_03x24lacoloradapeaup.htm)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6274,7 +6283,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6311,7 +6320,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6348,7 +6357,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6385,7 +6394,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
+          <t>Federal Register (https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6422,7 +6431,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6459,7 +6468,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6496,12 +6505,123 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Coosa Graphite Project (Kellyton Graphite Plant)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Condado de Coosa, Alabama, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Westwater Resources Inc.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Financiamiento/planeación (préstamo EXIM Bank de US$25 millones anunciado 7-ago-2026 para mina de grafito natural y planta de procesamiento, primera fuente de grafito natural producida en EE.UU.)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Yellowhammer News (https://yellowhammernews.com/trump-administration-announces-25-million-exim-loan-for-westwaters-coosa-county-graphite-plant/); EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Expansión de Procesamiento de Tantalio/Niobio (Global Advanced Metals)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pensilvania, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Global Advanced Metals</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Financiamiento/planeación (préstamo EXIM Bank de US$25 millones anunciado 7-ago-2026 para ampliar capacidad de procesamiento)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable); SME (https://me.smenet.org/trump-administration-to-back-three-mineral-projects-with-58-million-in-financing/)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Boron Americas Project (Fort Cady)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>California, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>5E Advanced Materials</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Financiamiento/planeación (préstamo EXIM Bank de US$8 millones anunciado 7-ago-2026 para proyecto de boro, lixiviación/procesamiento)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6516,50 +6636,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -6593,7 +6713,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); [Construction Owners](https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); Construction Owners (https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6630,7 +6750,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
+          <t>Epoch AI (https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6667,7 +6787,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6704,7 +6824,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[Chevron](https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
+          <t>Chevron (https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6741,7 +6861,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
+          <t>Gobierno de México (https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6778,7 +6898,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[Global Data Center Hub](https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
+          <t>Global Data Center Hub (https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6815,7 +6935,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
+          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6852,7 +6972,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6889,7 +7009,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6921,17 +7041,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Construcción de edificios de centro de datos iniciada (TCEQ ya había otorgado permiso de aire para 7.65GW de generación a gas; Amazon presentó a inicios de ago-2026 permisos de construcción para 3 edificios de centro de datos —"Pecos County Data Center", Buildings A/B/C, ~189,060 pies² c/u, ~US$300M c/u—; construcción de edificios prevista ago-dic 2026; Fase 1 de 1GW de generación prevista en operación 1S2027)</t>
+          <t>Construcción de edificios de centro de datos iniciada (TCEQ emitió permiso de aire final para la planta —35 turbinas de gas natural, hasta 33 millones de toneladas de CO2/año—; Amazon presentó a inicios de ago-2026 permisos de construcción para 3 edificios de centro de datos —"Pecos County Data Center", Buildings A/B/C, ~189,060 pies² c/u, ~US$300M c/u—; construcción de edificios prevista ago-dic 2026; primera entrega de energía prevista 1T2027, operando inicialmente fuera de la red de ERCOT)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); [US Data Center Projects](https://usdatacenterprojects.com/texas/amazon-files-plans-for-new-data-center-buildings-in-texas-across-three-sites)</t>
+          <t>Business Wire (https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); Tom's Hardware (https://www.tomshardware.com/tech-industry/data-centers/amazons-new-7-65gw-texas-ai-data-center-power-plant-could-become-the-largest-source-of-co2-pollution-in-the-us-custom-35-turbine-gas-plant-authorized-to-emit-33-million-tons-of-annual-greenhouse-gases)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6963,7 +7083,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7000,7 +7120,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); [DCD](https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
+          <t>Mexico News Daily (https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); DCD (https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7037,7 +7157,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7074,7 +7194,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
+          <t>Source NM (https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7111,7 +7231,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7148,7 +7268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7185,7 +7305,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
+          <t>PowerMag (https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7222,7 +7342,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7259,7 +7379,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7296,7 +7416,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7333,7 +7453,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
+          <t>Mexico News Daily (https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7370,7 +7490,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7407,7 +7527,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
+          <t>Valley News Live (https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7444,7 +7564,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
+          <t>Energy Magazine MX (https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7481,7 +7601,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
+          <t>Construction Dive (https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7518,7 +7638,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
+          <t>KSL (https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7555,7 +7675,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
+          <t>Governor.mo.gov (https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7592,7 +7712,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
+          <t>STLPR (https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7629,7 +7749,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7666,7 +7786,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7703,7 +7823,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7740,7 +7860,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7777,7 +7897,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7814,7 +7934,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
+          <t>Williams Companies (https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7851,7 +7971,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7888,7 +8008,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[Cowboy State Daily](https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
+          <t>Cowboy State Daily (https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7925,7 +8045,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
+          <t>HPCwire (https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7962,7 +8082,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
+          <t>Utah News Dispatch (https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7999,7 +8119,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
+          <t>StockTitan (https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8036,7 +8156,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
+          <t>KLTV (https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8073,7 +8193,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+          <t>WV MetroNews (https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8110,7 +8230,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
+          <t>Utility Dive (https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8147,7 +8267,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[Wharton Post](https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
+          <t>Wharton Post (https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8184,7 +8304,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+          <t>Crusoe (https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8221,7 +8341,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8258,7 +8378,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
+          <t>PowerMag (https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8295,7 +8415,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
+          <t>Aterio (https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8332,7 +8452,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); [Inside Climate News](https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
+          <t>AJC (https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); Inside Climate News (https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8369,7 +8489,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8406,7 +8526,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation); [Indiana Gazette](https://www.indianagazette.com/local_news/amazon-hcr-are-conducting-commercial-discussions-on-data-center/article_733afa63-9d58-42d0-b16e-6dc61b71689b.html)</t>
+          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation); Indiana Gazette (https://www.indianagazette.com/local_news/amazon-hcr-are-conducting-commercial-discussions-on-data-center/article_733afa63-9d58-42d0-b16e-6dc61b71689b.html)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8443,7 +8563,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
+          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8480,7 +8600,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8517,7 +8637,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -8554,7 +8674,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); [BeBeez](https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
+          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); BeBeez (https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8591,7 +8711,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[Technology.org](https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); [DCD](https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
+          <t>Technology.org (https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); DCD (https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8628,7 +8748,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
+          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8665,7 +8785,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[Kentucky Lantern](https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
+          <t>Kentucky Lantern (https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8702,7 +8822,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8739,7 +8859,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); [Construction Review](https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); [CNBC](https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); Construction Review (https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); CNBC (https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8776,7 +8896,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8813,7 +8933,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); [Kentucky Lantern](https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
+          <t>Bloomberg (https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); Kentucky Lantern (https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8850,7 +8970,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>[Axios](https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); [DCD](https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
+          <t>Axios (https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); DCD (https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8887,7 +9007,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); [Olney Enterprise](https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); Olney Enterprise (https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8924,7 +9044,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>[Illinois Times](https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
+          <t>Illinois Times (https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8961,7 +9081,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[KSL](https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); [Utah GOED](https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
+          <t>KSL (https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); Utah GOED (https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8998,7 +9118,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); [WFAE](https://www.wfae.org/energy-environment/2026-07-31/residents-push-back-against-large-amazon-data-center-project-during-packed-public-meeting)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); WFAE (https://www.wfae.org/energy-environment/2026-07-31/residents-push-back-against-large-amazon-data-center-project-during-packed-public-meeting)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9035,7 +9155,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); [DCD](https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); DCD (https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9072,7 +9192,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); [Energy.gov](https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); Energy.gov (https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9109,7 +9229,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[Community Impact](https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
+          <t>Community Impact (https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9146,7 +9266,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>[Data Centre Magazine](https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); [Connect CRE](https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
+          <t>Data Centre Magazine (https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); Connect CRE (https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9183,7 +9303,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>[WLBT](https://www.wlbt.com/2026/05/29/psc-wont-issue-opinion-hypothetical-electrical-plant-proposed-tech-site/)</t>
+          <t>WLBT (https://www.wlbt.com/2026/05/29/psc-wont-issue-opinion-hypothetical-electrical-plant-proposed-tech-site/)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9220,7 +9340,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/avaio-to-develop-6bn-data-center-campus-in-little-rock-arkansas/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/avaio-to-develop-6bn-data-center-campus-in-little-rock-arkansas/)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -9257,7 +9377,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>[Mississippi Today](https://mississippitoday.org/2026/04/22/ridgeland-data-center-entergy-mississippi-power/)</t>
+          <t>Mississippi Today (https://mississippitoday.org/2026/04/22/ridgeland-data-center-entergy-mississippi-power/)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -9294,7 +9414,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/red-post-energy-and-wise-innovation-hub-venture-oasis-execute-letter-of-intent-to-advance-power-infrastructure-for-major-data-center-development-in-southwest-virginia-302645511.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/red-post-energy-and-wise-innovation-hub-venture-oasis-execute-letter-of-intent-to-advance-power-infrastructure-for-major-data-center-development-in-southwest-virginia-302645511.html)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9331,7 +9451,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>[Virginia Mercury](https://virginiamercury.com/2026/07/20/data-centers-want-to-build-their-own-gas-turbines-would-that-skirt-state-renewable-energy-laws/)</t>
+          <t>Virginia Mercury (https://virginiamercury.com/2026/07/20/data-centers-want-to-build-their-own-gas-turbines-would-that-skirt-state-renewable-energy-laws/)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9368,7 +9488,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>[WBOY](https://www.wboy.com/news/tucker/state-board-approves-tucker-county-data-center-air-quality-permit/)</t>
+          <t>WBOY (https://www.wboy.com/news/tucker/state-board-approves-tucker-county-data-center-air-quality-permit/)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -9405,7 +9525,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>[DCD](https://www.datacenterdynamics.com/en/news/nextera-teams-up-with-exxonmobil-to-develop-12gw-natural-gas-plant-to-power-us-data-center-sector/)</t>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/nextera-teams-up-with-exxonmobil-to-develop-12gw-natural-gas-plant-to-power-us-data-center-sector/)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9442,7 +9562,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>[Utility Dive](https://www.utilitydive.com/news/nrg-nears-12-gw-hyperscaler-deal-amid-texas-data-center-pause/827212/)</t>
+          <t>Utility Dive (https://www.utilitydive.com/news/nrg-nears-12-gw-hyperscaler-deal-amid-texas-data-center-pause/827212/)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9479,7 +9599,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9516,12 +9636,49 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>[The Nevada Independent](https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
+          <t>The Nevada Independent (https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dove Creek Technology Campus</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Condado de Tom Green (cerca de San Angelo), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Beacon Data Centers (vía Westline TX Holdings LLC)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>No especificado (generación con motores reciprocantes de gas natural)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Permitting temprano (solicitud de permiso de aire ante TCEQ presentada 10-ago-2026, hasta 2,409 MW dedicados; sitio de ~1,240 acres construibles; construcción proyectada primavera/verano 2027 si avanza)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>San Angelo Live (https://sanangelolive.com/news/san-angelo/2026-08-10/dove-creek-data-center-has-applied-tceq-permit-heres-what-know); Concho Observer (https://conchoobserver.com/data-center-permits-detail-proposed-air-quality-footprint/)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -29,12 +29,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -425,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2102,6 +2097,43 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cassidy II Gas Processing Plant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Condado de Glasscock, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazos Midstream</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Anuncio/Construcción (planta criogénica de 300 MMcf/d adicional a Cassidy I —300 MMcf/d, en servicio antes de fin de 2026—; eleva capacidad total de Brazos en Midland Basin a ~1.1 Bcf/d; respaldada por ~575,000 acres bajo dedicación; entrada en operación prevista verano 2027; anunciado 11-ago-2026)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Inspectioneering (https://inspectioneering.com/news/2026-08-11/12145/brazos-midstream-announces-new-natural-gas-processing-plant-to-support-continued); Rigzone (https://www.rigzone.com/news/brazos_to_grow_midland_gas_processing_capacity_to_11_bcfd-11-aug-2026-184346-article/)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2113,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2952,7 +2984,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ursus Energy</t>
+          <t>Ursus Energy / Praespero-Ursus E&amp;I (JV con Praespero Energy Management y Periodic Energy, EE.UU./Canadá)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2962,17 +2994,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; primer desembolso de US$100M previsto fines de jul-2026; transición a obra civil, verano 2026)</t>
+          <t>Ingeniería (inversión ampliada a US$2.1-2.2 mil millones, desde US$450M iniciales; formación del consorcio Praespero-Ursus E&amp;I con compromiso de capital adicional de US$350+ millones; primer tranche de US$100M desplegado fines de jul-2026; transición a obra civil, verano 2026; capacidad ~2.1 Mtpa, primera exportación prevista fines de 2029)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mexico Business News (https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion); energynews.mx (https://energynews.mx/nace-praespero-ursus-ei-megaproyecto-de-8000-millones-de-dolares-para-veracruz/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -3639,6 +3671,80 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bay Runner Twin Pipeline (alimenta Rio Grande LNG)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agua Dulce a Rio Grande, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JV Whistler (Enbridge 19% / MPLX / WhiteWater)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Construcción (FID/sancionado 31-jul-2026; añade hasta 2.6 Bcf/d entre Agua Dulce y Rio Grande para trenes adicionales de Rio Grande LNG; contratos take-or-pay de largo plazo; entrada en servicio prevista 2030)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Enbridge (https://www.enbridge.com/stories/2026/august/bay-runner-twin-permian-gas-pipelines-feeder-gulf-coast-lng-exports); PGJ (https://pgjonline.com/news/2026/august/enbridge-partners-announce-pipeline-s-sanctioning-blackcomb-commissioning-as-permian-gas-exports-ramp-up)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gasoducto Blackcomb (alimenta hub Agua Dulce — Corpus Christi/Rio Grande LNG)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cuenca Pérmica a Agua Dulce, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>JV Enbridge/MPLX/WhiteWater (70%) / Targa Resources (30%)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Construcción/Comisionamiento (~365 millas, 42", 2.5 Bcf/d; inició comisionamiento y entrada en servicio/rampa 2S2026)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PGJ (https://pgjonline.com/news/2026/august/enbridge-partners-announce-pipeline-s-sanctioning-blackcomb-commissioning-as-permian-gas-exports-ramp-up)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -3648,2989 +3754,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ubicación</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente/Dueño</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>EPC/Contratista</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Fase</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Última actualización</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Santa Cruz Copper Project</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Casa Grande, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ivanhoe Electric Inc.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Fluor Corporation</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Ingeniería completada (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año) / construcción prevista H1 2026; EXIM Bank gestiona ahora más de US$1,000 millones en financiamiento, como parte del paquete federal de US$3,000 millones en minerales críticos anunciado 7-8-ago-2026</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); MINING.COM (https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Copper World Complex</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pima County, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Hudbay Minerals (70%) / Mitsubishi Corporation (30%)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sundt, M3 Engineering, Ames, DRA Global, Knight Piésold, Mipac, Stantec</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ingeniería/Feasibility (DFS &gt;85% completo; colocación de bonos municipales por US$52 millones completada 24-jun-2026 para financiar el proyecto, ya totalmente permisado para iniciar construcción)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SEC/Hudbay (https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Resolution Copper (Shaft No. 9)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Superior, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Rio Tinto (55%) / BHP (45%) JV</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Hatch</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ingeniería temprana post intercambio de tierras (marzo 2026); firmó Master Supply Agreement (1-jul-2026) con Johnson Controls Inc. y UA Local 469; otorgó ~US$110 millones en contratos a Major Drilling America Inc. y Redpath USA Corporation (10-ago-2026) para acelerar exploración y desarrollo subterráneo, parte de programa de inversión de ~US$500 millones</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SEC (https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); International Mining (https://im-mining.com/2026/08/10/resolution-copper-accelerates-exploration-underground-development-with-major-drilling-redpath-contracts/)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thacker Pass Lithium Mine (Fase I)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Humboldt County, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Lithium Americas Corp.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bechtel</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Construcción (ingeniería de detalle &gt;95% completa, procura &gt;70% completa a may-2026; capex guía 2026 de US$1,300-1,600 millones; terminación mecánica prevista fines de 2027)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); Lithium Americas (https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>San Nicolás Copper-Zinc Project</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Zacatecas, México</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Teck Resources / Agnico Eagle Mines (JV 50/50)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Construcción, producción esperada 2026</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>El Arco Copper Project</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Baja California, México</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Grupo México / Southern Copper Corporation</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ingeniería de detalle</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Energy Magazine MX (https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Pilar Copper Project</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Grupo México / Southern Copper Corporation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Permisos ambientales asegurados (proyecto revaluado en US$551 millones; preparación de sitio inicia sep-2026, construcción plena 2027, primer cobre ~2028)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BNamericas (https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Buenavista del Cobre — Concentradora No. 2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cananea, Sonora, México</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Southern Copper Corporation (Grupo México)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>M3 Engineering &amp; Technology Corporation</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ingeniería/ejecución de expansión</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>M3 Engineering (https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Media Luna Mine (North/EPO)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Guerrero, México</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Torex Gold Resources Inc.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Construcción (tubería de pasta pendiente)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Pumpkin Hollow Copper Mine (reinicio)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Yerington, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nevada Copper Corp. (Kinterra Capital)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Planeación de reinicio/construcción</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Hermosa Critical Minerals Project (Taylor/Clark)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Santa Cruz County, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>South32</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DMC Mining Services (parcial)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026, cerrando revisión NEPA de infraestructura en Coronado National Forest; autorización final programada para 4-sep-2026; primer proyecto minero aceptado en programa federal FAST-41; ~50% avance en porción privada; primer concentrado ahora proyectado H1-2028, antes H1-2027)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>USDA (https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stibnite Gold Project</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Valley County, Idaho, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Perpetua Resources</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Hatch Ltd. (EPCM)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Construcción (corte federal de Idaho negó en jun-2026 moción para detener obras; Export-Import Bank de EE.UU. aprobó en may-2026 préstamo garantizado de USD 2,900 millones, desembolso esperado 2S2026)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); Departamento de Justicia de EE.UU. (https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>El Tigre Project</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Silver Tiger Metals</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Kappes, Cassiday &amp; Associates (EPCM)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Construcción (166 personas en sitio, 100,000 horas-hombre; primer vaciado previsto dic-2027)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Silver Tiger Metals (https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Panuco Silver-Gold Project</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sinaloa, México</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Vizsla Silver Corp.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ingeniería de detalle/planeación de construcción (post-Feasibility Study)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>South Railroad Project (South Carlin Complex)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Elko/Eureka County, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Orla Mining Ltd.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Construcción (inicio previsto mediados 2026, pendiente ROD final de BLM)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Orla Mining (https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Copperstone Gold Project</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>La Paz County, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Minera Alamos Inc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Contratista de minería subterránea por definir</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Construcción (decisión de inversión may-2026; PFS positivo anunciado; construcción estimada en ~1 año; primera producción de oro prevista mediados de 2027)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28); Minera Alamos (https://mineraalamos.com/news/2026/minera-alamos-announces-positive-pre-feasibility-study-for-the-copperstone-gold-project-in-arizona/)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CK Gold Project</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Distrito Silver Crown, Laramie Range, Wyoming, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>U.S. Gold Corp</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Halyard-Micon International (feasibility); EPC por asignar</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Permiso de Emplazamiento Industrial (Industrial Siting Permit) otorgado por Wyoming DEQ el 20-jun-2026, habilitando construcción y operación sin requerir NEPA (no involucra tierra federal); construcción pesada prevista hasta 2027, producción 2028</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Wyoming News (https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html); Discovery Alert (https://discoveryalert.com.au/ck-gold-project-permitting-construction-ready-valuation-2026/)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Distrito Santa Elena — Expansión (Santo Niño y Navidad)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>First Majestic Silver Corp.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Construcción (permisos recibidos jun-2026; First Majestic compromete US$12 millones en 2026 para desarrollo de accesos subterráneos y portales)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>First Majestic (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Galena Complex — Planta de Relleno en Pasta</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Wallace, Idaho, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Americas Gold and Silver Corporation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Construcción (comisionamiento previsto Q4 2026)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SEC/Americas Gold and Silver (https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Guanacevi Silver Project (Ocampo Mining)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Durango, México</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Minera Frisco (Grupo Carso)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Construcción (nueva planta de proceso; primera producción prevista fin de 2026)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Kitco (https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Arctic Project (Distrito Minero Ambler)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Distrito Minero Ambler, Alaska, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ambler Metals LLC (Trilogy Metals / South32, JV 50/50)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Permitting (cronograma coordinado de permisos federales/estatales publicado 16-jul-2026; revisión ambiental integrada de 29 meses liderada por USACE; ROD objetivo sep-2028)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Los Ricos South Mine</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Jalisco, México</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GoGold Resources</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Construcción aprobada por el consejo (permisos SEMARNAT completos jun-2026; presupuesto ~US$227 millones; ventana de construcción de ~24 meses; primer vertido de metal previsto mediados de 2028)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Northern Miner (https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); Newsfile (https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cordero Project</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Chihuahua, México</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Discovery Silver</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Ausenco (ingeniería)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Feasibility completa / permitting (MIA pendiente ante SEMARNAT)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BNamericas (https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Gran Pilar Gold-Silver Project</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Tocvan Ventures</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Construcción (piloto; primer doré previsto Q4 2026)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Resource World (https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Orisyvo Project</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Sierra Madre (Rarámuri), Chihuahua, México</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fresnillo plc</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Pre-feasibility (transicionando a feasibility, resultados esperados medio 2026)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Fresnillo plc (https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Planta de Separación de Tierras Raras (US Army)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tooele Army Depot, Utah, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>REalloys Inc.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Acuerdo de arrendamiento condicional otorgado por el Ejército de EE.UU. (confirmado 29-jul-2026, parte de programa en 4 sitios: Anniston AL, Pine Bluff AR, Red River TX, Tooele UT); desarrollo comercial previsto 2027, operaciones iniciales 2028</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Army.mil (https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Planta de Purificación de Grafito (US Army)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Pine Bluff Arsenal, Arkansas o Anniston Army Depot, Alabama (sin confirmar), EE.UU.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Titan Mining Corp.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Plantas de Litio y Boro (US Army)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Base militar de EE.UU. sin confirmar</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>EnergyX (litio) / ioneer Ltd. (boro)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Acuerdo firmado/planeación (construcción prevista desde 2027; producción 2028)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Expansión Concentradora La Caridad</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Nacozari, Sonora, México</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Grupo México</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Metso (equipo de trituración)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Construcción/procura de equipo (pedido adicional &gt;EUR 20M de trituración secundaria a Metso, jun-2026, complementa equipos Nordberg MP800 instalados en 2025)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>IM Mining (https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Santo Tomás Copper Project</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Sinaloa, México</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Oroco Resource Corp.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Prefactibilidad (perforación fase 2 en curso; PFS objetivo 2T-3T 2027; capex estimado USD 2.84 mil millones; permisos federales pendientes)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Reapertura Fundición Hayden + Refinería Amarillo</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Hayden, Arizona / Amarillo, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Asarco (Grupo México)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Negociación/planeación (inversión ~USD 230 millones para reactivar fundición cerrada desde 2020; Grupo México evalúa hasta USD 6,000 millones adicionales para expansión de cobre en Arizona)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Cerro de Oro Gold Project</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Zacatecas, México</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Minera Alamos Inc.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Permitting (proyecto de oro a cielo abierto/heap leach; financiamiento de construcción ya asegurado)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Minera Alamos (https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Antler Copper Project</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Condado de Mohave, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>New World Resources Ltd. (respaldado por Kinterra Capital)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Permitting casi completo/inicio de construcción (BLM emitió Determinación de Adecuación NEPA; obras previstas 2do semestre 2026; embarque de concentrado previsto 2027)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Global Mining Review (https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Lisbon Valley Copper Project</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Condado de San Juan, Utah, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Lisbon Valley Mining Company, LLC</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Permitting federal completo (aprobación BLM + exención de acuífero EPA, oct-2025) / reapertura-construcción (agrega tajo abierto y pozos de recuperación in-situ)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>BLM (https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>South West Arkansas Lithium Project (Central Processing Facility)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sur de Arkansas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Smackover Lithium (JV Standard Lithium / Equinor)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>S&amp;B Engineers and Constructors (EPCC); Hatch Ltd. (ingeniería de diseño/comisionamiento)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Ingeniería de detalle/procura temprana (contrato EPCC otorgado, NTP limitado activo; FID esperada en 2026; planta diseñada para 22,500 tpa de carbonato de litio grado batería; DOE emitió FONSI —Finding of No Significant Impact—, paso clave hacia la FID; producción comercial estimada 2029)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>InvestingNews (https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/); StockTitan/SEC 6-K (https://www.stocktitan.net/sec-filings/SLI/6-k-standard-lithium-ltd-current-report-foreign-issuer-ef7db860baa3.html)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Bagdad Mine Concentrator Expansion</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Yavapai County, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Freeport-McMoRan</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental estimado ~US$3,500 millones bajo revisión; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>SEC/Freeport-McMoRan (https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Elk Creek Critical Minerals Project</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Elk Creek, Nebraska, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>NioCorp Developments Ltd.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; proyecto de niobio/escandio/titanio con planta de superficie que requerirá tubería de proceso)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NioCorp (https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Goldfield Project</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Goldfield, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Centerra Gold Inc.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Ingeniería/Construcción temprana (ingeniería de detalle y procura de largo plazo en 2026; construcción mayor de pila de lixiviación y circuitos de trituración/procesamiento en 2027; primera producción fin de 2028)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>E&amp;MJ (https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cactus Mine (distrito Copper World/Arizona Sonoran)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Casa Grande, Arizona, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Hudbay Minerals (adquisición de Arizona Sonoran Copper Co. anunciada 2-mar-2026)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Desarrollo/Feasibility (planta SX-EW de cátodos de cobre, ~103,000 t Cu/año proyectadas; Hudbay busca fusionarlo con el distrito Copper World adyacente ya rastreado; DFS en curso con FID apuntada para 4T2026 y construcción prevista en 2027)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html); Arizona Sonoran (https://arizonasonoran.com/news-releases/arizona-sonoran-pre-feasibility-study-delivers-exceptional-results-for-the-cactus-project-outlining-long-life-low-cost-copper-1/)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Doby George Gold Project (Distrito Aura)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>~120 km al norte de Elko, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Western Exploration Inc.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>No especificado (WSP realiza feasibility study; Stantec y Kappes Cassidy en estudios ambientales)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Feasibility/Permitting (PEA positiva 2025; campaña de perforación iniciada, hasta 3,000m/15 pozos para estudios base y PFS; sometimiento del Mine Plan of Operations ahora esperado a inicios de ago-2026; proyecto de lixiviación en pilas de óxidos)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Western Exploration (https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx); StreetWise Reports (https://www.streetwisereports.com/article/2026/08/03/nevada-gold-project-launches-drill-campaign-at-doby-george.html)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Metates Project</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Durango, México</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Chesapeake Gold Corp.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Feasibility (prefeasibility study objetivo 2026; pruebas metalúrgicas de lixiviación de sulfuros y estudios ambientales de línea base en curso; uno de los mayores depósitos de oro-plata no desarrollados de América)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Chesapeake Gold Corp. (https://chesapeakegold.com/metates/)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Pathfinder Tonopah (cobre-molibdeno-plata)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tonopah, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Pathfinder Minerals (Pathfinder Tonopah)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Bowman (permisos ambientales, FEED, planta piloto)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Permitting/FEED (avanzando hacia estudio de factibilidad definitivo; carta de interés no vinculante de EXIM Bank por US$896 millones para financiamiento, programa "Make More in America")</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Mining Technology (https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>La Colorada Mine — Expansión Veta Madre/Veta Madre Plus</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Heliostar Metals</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Permisos completos obtenidos (2026); waste stripping programado 3T2026; producción de zona expandida esperada 1S2027</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Libby Project (Cabinet Mountains)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Condado de Lincoln, Montana, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Hecla Mining Company</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Permitting federal completado para exploración subterránea (extensión de ~1 milla del socavón Libby Adit; recurso potencial 1,500 millones lb de cobre y 183 millones oz de plata; pendiente permiso de descarga de agua de MT DEQ)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>The Western News (https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Donlin Gold</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Alaska, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>NovaGold Corporation (adquiriendo 100%, compra de participación del 40% de Paulson Advisers)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); aún sin decisión de construcción (FID)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Mining News North (https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Rhyolite Ridge Lithium-Boron Project</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Condado de Esmeralda, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ioneer Ltd.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Hyundai Engineering Co. Ltd. (MOU no vinculante, evaluando rol EPC/procura); KIND evaluando inversión de capital</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Permitting confirmado en corte federal (31-mar-2026); préstamo DOE de US$996 millones cerrado; MOUs con KIND/Hyundai firmados inicios jul-2026; FID objetivo 2S2026, primera producción 2029</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>IM Mining (https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>San Antonio Gold Project</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Axo Metals Corp. (Axo Copper Corp.)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Permisos (SEMARNAT aprobó la MIA, 27-jul-2026, habilitando producción; planta de carbón-en-columna ya permisada; aprobaciones de uso de suelo para nuevos yacimientos —Sapuchi, Golfo de Oro, California— en trámite para fin de año)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Resource World (https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Tamarack Nickel-Copper-Cobalt Project</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Aitkin County, Minnesota (mina) / Beulah, Dakota del Norte (planta de proceso — Beulah Minerals Processing Facility), EE.UU.</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Talon Metals Corp. (51%) / Kennecott Exploration Co. (Rio Tinto) JV</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Permitting/Feasibility (Talon firmó acuerdo de opción de terreno con Westmoreland Mining, 28-jul-2026, por ~256 acres cerca de Beulah, ND, para la Beulah Minerals Processing Facility —planta de procesamiento de concentrado níquel-cobre respaldada por subvención DOE de US$114.8 millones—; EIS de la mina en scoping, comentarios cierran 14-sep-2026; entendimiento informal de offtake con Tesla)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Talon Metals (https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Bunker Hill Mine — Reinicio + Planta de Relleno en Pasta</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Kellogg/Wardner, Idaho, EE.UU. (Distrito Minero Coeur d'Alene)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Bunker Hill Mining Corp.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Construcción/Comisionamiento (primer embarque de concentrado a la fundición Trail de Teck tras 45+ años de cierre; nueva planta de proceso de 1,800 tpd comisionada; planta de relleno en pasta en sitio Wardner sustancialmente completa, comisionamiento final previsto ~3 semanas tras el anuncio; meta de producción comercial plena fin de 2026)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NewRange Copper Nickel (Proyecto NorthMet) — Rediseño Mayor</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Babbitt/Hoyt Lakes, Minnesota, EE.UU. (Iron Range)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>NewRange Copper Nickel (JV PolyMet/Glencore + Teck)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Permitting (rediseño mayor elimina la represa de jales propuesta —roca estéril se almacenaría en tajos de mineral de hierro existentes—; solicitud de permiso de humedales Sección 404/Clean Water Act presentada ante USACE; revisión ambiental suplementaria (SEIS) solicitada a Minnesota DNR)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>MPR News (https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>White Mesa Mill — Expansión de Tierras Raras Pesadas</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Blanding, Utah, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Energy Fuels Inc.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Construcción (planta comercial de tierras raras pesadas —disprosio/terbio— iniciada 29-jul-2026; capex ~US$104 millones, para uso en imanes/defensa/vehículos eléctricos)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Energy Fuels (https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); PR Newswire (https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Black Butte Copper Project</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Meagher County, Montana, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Sandfire Resources America Inc. (Sandfire Resources)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Por definir (PFS elaborado por DM Consulting)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Feasibility (PFS actualizado presentado 28-jul-2026 con nuevas reservas Lowry, vida de mina de 12 años; mina subterránea de cobre de alta ley)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Planta de Procesamiento de Litio Red River (US Army)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Bowie County, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>EnergyX (desarrollador-operador)</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Acuerdo de arrendamiento condicional otorgado (confirmado 25-jun-2026; 5to sitio del programa de minerales críticos en bases del Ejército, junto con Tooele, Pine Bluff/Anniston; construcción prevista desde 2027)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Texarkana Gazette (https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Camino Rojo — Proyecto Subterráneo (extensión)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Zacatecas, México</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Orla Mining Ltd.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Permisos completos/inicio de desarrollo subterráneo (SEMARNAT aprobó MIA 18-mar-2026, habilitando minado del resto del tajo de óxidos y construcción de rampa de exploración subterránea; inicio de obras de acceso subterráneo previsto 2S2026; PEA de proyecto subterráneo indica VPN de US$1,300 millones)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Mining.com (https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); Orla Mining (https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Cerro Caliche Gold Project</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Sonora, México</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Sonoro Gold Corp.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>EPC por definir (en negociación con múltiples empresas EPC de China)</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Permisos/estructuración de financiamiento EPC (plataforma consolidada de 3,924 hectáreas en 25 concesiones; finalización de permisos esperada 1T2026; 4 empresas EPC chinas evaluando financiamiento de deuda y desarrollo)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Sonoro Gold Corp. (https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); Mexico Mining Center (https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Pilot Mountain Tungsten Project</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Mineral County, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Guardian Metal Resources PLC (vía Golden Metal Resources USA LLC)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Ingeniería/Feasibility (PFS positivo completado jun-2026, respaldado por USD 6.2 millones del Departamento de Guerra/DPA Title III; presentación del Mine Plan of Operations federal prevista ago-2026; producción 4T2028)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/guardian-metals-outlines-viable-tungsten-trioxide-operation-in-nevada-2026-06-30); StockTitan (https://www.stocktitan.net/news/GMTL/guardian-metal-resources-plc-announces-pilot-mountain-pre-tftnlr9fu3if.html)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Gabbs Project</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Walker-Lane Trend, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>P2 Gold Inc.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Ingeniería/Feasibility (proyecto oro-cobre; feasibility study en curso, meta 4T2026)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Newswire (https://www.newswire.ca/news-releases/p2-gold-gabbs-project-update-feasibility-study-on-track-840759204.html)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Treasure Canyon Gold Mine</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Plumas National Forest, cerca de Taylorsville, California, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Buscar Company (CGLD)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Permitting (Plan de Operaciones sometido a US Forest Service feb-2026; en revisión por agencias federales/estatales)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/buscar-company-announces-major-advancement-in-the-permitting-process-for-the-treasure-canyon-gold-mine-project-in-california-302772744.html)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Grassy Mountain Gold Project</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Malheur County, Oregon, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Paramount Gold Nevada Corp. (vía Calico Resources)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Permitting (Record of Decision federal firmado 29-ene-2026 bajo NEPA; permisos estatales pendientes, esperados 2S2026; Feasibility Study ya completo con VPN de USD 375 millones)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/01/29/3229150/0/en/Paramount-Gold-Receives-Federal-Approval-for-the-Grassy-Mountain-Gold-Project.html); OPB (https://www.opb.org/article/2026/01/29/oregon-gold-mine-grassy-mountain/)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MP Materials 10X Magnet Manufacturing Facility</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Northlake, Texas, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>MP Materials</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Construcción (rompimiento de tierra 1T2026; planta de imanes de tierras raras de USD 1,250 millones; ~7,000 t/año de capacidad adicional)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>CNBC (https://www.cnbc.com/2026/02/26/mp-materials-selects-texas-for-rare-earth-magnet-manufacturing-site.html)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Expansión de Separación de Tierras Raras Pesadas — Mountain Pass</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Mountain Pass, California, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>MP Materials</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Ingeniería/Construcción temprana (financiamiento de USD 550 millones del Departamento de Defensa, feb-2026, para agregar capacidad de separación de tierras raras pesadas en la mina/planta existente)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/the-united-states-is-investing-in-its-domestic-rare-earth-industry-302838375.html)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Planta de Procesamiento de Antimonio (JV Galena Complex)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Silver Valley, Wallace, Idaho, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>JV Americas Gold and Silver Corporation (51%) / United States Antimony Corp (49%)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Ingeniería/Construcción (JV firmado feb-2026 para construir y operar planta de procesamiento de antimonio dentro de los permisos existentes del Galena Complex)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Newsfile Corp (https://www.newsfilecorp.com/release/283399/Americas-Gold-and-Silver-Signs-Joint-Venture-Agreement-with-US-Antimony-to-Construct-Antimony-Processing-Facility-in-Idahos-Silver-Valley-Unlocking-Value-from-Its-Antimony-Production-and-Strengthening-U.S.-Critical-Mineral-Security)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Michigan Potash Project</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Osceola County, Michigan, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Michigan Potash &amp; Salt Co.</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Financiamiento/pre-construcción (mina de solución de potasa + planta de proceso; garantía de préstamo condicional DOE de USD 1,260 millones; posible aprobación FAST-41 en 2026; ~726,000 t/año)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>DOE-LPO (https://www.energy.gov/lpo/articles/lpo-announces-conditional-commitment-michigan-potash-produce-fertilizer-us-farmers); Northern Miner (https://www.northernminer.com/news/us-boosts-potash-projects-in-utah-michigan/1003886533/)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Sevier Playa Potash Project</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Millard County, Utah, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Peak Minerals (respaldado por EMR Capital)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Construcción (BLM aprobó construcción de la etapa inicial de 195,000 t en jun-2026; capex total USD 435 millones; subvención USDA de USD 80 millones)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>BLM (https://www.blm.gov/announcement/blm-approves-construction-sevier-playa-potash-mining-project)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Shirley Basin Uranium Project</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Wyoming, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ur-Energy Inc.</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Construcción/Inicio de operación (planta satélite ISR integrada con Lost Creek; inicio de minado abr-2026; envío de resina cargada a Lost Creek previsto verano 2026)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Ur-Energy (https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Cusi Mine (Reinicio)</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Chihuahua, México</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Silverco Mining Ltd.</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Construcción (reinicio 68% completo; rehabilitación de la planta Mal Paso; primer concentrado previsto 4T2026)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/silverco-targets-late-2026-restart-past-producing-cusi-mine); Investing News Network (https://investingnews.com/silverco-mining-begins-underground-development-at-cusi-restart-remains-on-budget-and-on-schedule/)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Kilbourne Graphite Project</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Nueva York, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Titan Mining Corporation</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Ingeniería/Feasibility (planta demostrativa ya en producción/calificación de clientes 2026; decisión de construcción esperada fines de 2026/2027; proyecto integrado de 40,000 tpa)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Junior Mining Network (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/2342-tsx/ti/199070-titan-mining-to-start-shipping-first-graphite-product-and-feasibility-study-underway-for-40-000-tpa-integrated-kilbourne-graphite-project.html)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Graphite Creek Project</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Alaska, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Graphite One Inc.</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Permitting (permitting federal en curso bajo programa FAST-41, finalización prevista 29-sep-2026)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Permitting Council (https://www.permitting.gov/newsroom/success-stories/project-spotlight-graphite-creek-project)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>La Colorada Skarn Project</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Zacatecas, México</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Pan American Silver Corp.</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Ingeniería/Feasibility (PEA revisada publicada mar-2026 para nueva planta de flotación selectiva de 15,000 t/d en área Candelaria oriente; gasto de capital 2026 estimado USD 92-95 millones, incluye "588 Decline Project" de 12.4 km de rampa; producción media proyectada de 19.1 Moz Ag/año en años pico)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Pan American Silver (https://panamericansilver.com/news/pan-american-announces-revised-pea-for-the-la-colorada-skarn-project-positions-la-colorada-as-a-future-top-tier-silver-mine/); SEC 6-K (https://www.sec.gov/Archives/edgar/data/771992/000077199226000031/a2026_03x24lacoloradapeaup.htm)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Lone Tree Plant (Refurbishment Autoclave/CIL)</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Lovelock, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>i-80 Gold Corp</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Hatch (EPCM)</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Construcción (obras tempranas y movilización de contratistas en curso; construcción mayor prevista 4T2026)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Round Mountain Phase X — Planta de Paste Backfill</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Nye County, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>No especificado (paquetes de equipo móvil, ventiladores y planta CRF ya adjudicados)</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Construcción/Ingeniería detallada</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Bald Mountain Redbird 2 — Planta SART (ácido/lixiviación)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>White Pine County, Nevada, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Contratista de ingeniería detallada ya seleccionado, no revelado en la fuente</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Ingeniería (básica ~50% completa)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Bear Lodge Rare Earth Project</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Crook County, Wyoming, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Rare Element Resources Ltd. (afiliada de General Atomics/Synchron)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Permitting (designación FAST-41; aviso NEPA publicado en Federal Register 29-jul-2026)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Proyecto de Cobre Angangueo</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Angangueo, Michoacán, México</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Southern Copper Corporation (Grupo México)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Pre-desarrollo (en negociación de permisos con gobierno federal)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Proyecto de Cobre Chalchihuites</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Chalchihuites, Zacatecas, México</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Southern Copper Corporation (Grupo México)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Pre-desarrollo (en negociación de permisos)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Modernización Complejo Metalúrgico Empalme</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Empalme, Sonora, México</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Southern Copper Corporation (Grupo México)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Pre-desarrollo (en negociación de permisos; fundición existente a modernizar)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Coosa Graphite Project (Kellyton Graphite Plant)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Condado de Coosa, Alabama, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Westwater Resources Inc.</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Financiamiento/planeación (préstamo EXIM Bank de US$25 millones anunciado 7-ago-2026 para mina de grafito natural y planta de procesamiento, primera fuente de grafito natural producida en EE.UU.)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Yellowhammer News (https://yellowhammernews.com/trump-administration-announces-25-million-exim-loan-for-westwaters-coosa-county-graphite-plant/); EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Expansión de Procesamiento de Tantalio/Niobio (Global Advanced Metals)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Pensilvania, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Global Advanced Metals</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Financiamiento/planeación (préstamo EXIM Bank de US$25 millones anunciado 7-ago-2026 para ampliar capacidad de procesamiento)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable); SME (https://me.smenet.org/trump-administration-to-back-three-mineral-projects-with-58-million-in-financing/)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Boron Americas Project (Fort Cady)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>California, EE.UU.</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>5E Advanced Materials</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Financiamiento/planeación (préstamo EXIM Bank de US$8 millones anunciado 7-ago-2026 para proyecto de boro, lixiviación/procesamiento)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6688,165 +3811,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stargate Frontier Campus</t>
+          <t>Santa Cruz Copper Project</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shackelford County, Texas, EE.UU.</t>
+          <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle / SoftBank</t>
+          <t>Ivanhoe Electric Inc.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Construcción (rompimiento de tierra formal completado; 1,200 acres/10 edificios/1.4GW; VoltaGrid aprobado para operar 210 generadores de gas industrial, 700MW combinados, permitiendo operación fuera de la red pública; primera instalación en servicio 2S2026)</t>
+          <t>Ingeniería completada (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año) / construcción prevista H1 2026; EXIM Bank gestiona ahora más de US$1,000 millones en financiamiento, como parte del paquete federal de US$3,000 millones en minerales críticos anunciado 7-8-ago-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); Construction Owners (https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); MINING.COM (https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stargate Milam County (fast-build)</t>
+          <t>Copper World Complex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Milam County, Texas, EE.UU.</t>
+          <t>Pima County, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle</t>
+          <t>Hudbay Minerals (70%) / Mitsubishi Corporation (30%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SB Energy (SoftBank)</t>
+          <t>Sundt, M3 Engineering, Ames, DRA Global, Knight Piésold, Mipac, Stantec</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Ingeniería/Feasibility (DFS &gt;85% completo; colocación de bonos municipales por US$52 millones completada 24-jun-2026 para financiar el proyecto, ya totalmente permisado para iniciar construcción)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Epoch AI (https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
+          <t>SEC/Hudbay (https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Stargate Abilene Campus</t>
+          <t>Resolution Copper (Shaft No. 9)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abilene, Texas, EE.UU.</t>
+          <t>Superior, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle</t>
+          <t>Rio Tinto (55%) / BHP (45%) JV</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Crusoe / DPR Construction</t>
+          <t>Hatch</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Ingeniería temprana post intercambio de tierras (marzo 2026); firmó Master Supply Agreement (1-jul-2026) con Johnson Controls Inc. y UA Local 469; otorgó ~US$110 millones en contratos a Major Drilling America Inc. y Redpath USA Corporation (10-ago-2026) para acelerar exploración y desarrollo subterráneo, parte de programa de inversión de ~US$500 millones</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
+          <t>SEC (https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); International Mining (https://im-mining.com/2026/08/10/resolution-copper-accelerates-exploration-underground-development-with-major-drilling-redpath-contracts/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Microsoft Pecos Data Center Campus (Project Kilby)</t>
+          <t>Thacker Pass Lithium Mine (Fase I)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pecos/Reeves County, Texas, EE.UU.</t>
+          <t>Humboldt County, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Lithium Americas Corp.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chevron (acuerdo definitivo de suministro de gas a 20 años firmado 22-jun-2026, sitio &gt;2,000 acres); turbinas mayoritariamente GE Vernova de gran marco + Solar Turbines (Caterpillar) para capacidad adicional</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Construcción temprana/Ingeniería (capacidad rampa a 2.67GW; flujo de energía previsto fines de 2028; FID de la planta esperada fines de 2026)</t>
+          <t>Construcción (ingeniería de detalle &gt;95% completa, procura &gt;70% completa a may-2026; capex guía 2026 de US$1,300-1,600 millones; terminación mecánica prevista fines de 2027)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chevron (https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); Lithium Americas (https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CloudHQ Querétaro (6 campus, incl. Campus Colón)</t>
+          <t>San Nicolás Copper-Zinc Project</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colón y otras ubicaciones, Querétaro, México</t>
+          <t>Zacatecas, México</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CloudHQ</t>
+          <t>Teck Resources / Agnico Eagle Mines (JV 50/50)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6856,71 +3979,71 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Permisos/preparación de sitio (confirmado oficialmente por gobierno federal 7-jul-2026 bajo Plan México; inversión US$4,800M, 52 hectáreas, 900MW; subestación propia de 2GW prevista Q2 2027)</t>
+          <t>Construcción, producción esperada 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gobierno de México (https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
+          <t>Mining.com (https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Meta Hyperion Data Center</t>
+          <t>El Arco Copper Project</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richland Parish, Luisiana, EE.UU.</t>
+          <t>Baja California, México</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Turner Construction / DPR Construction / Mortenson</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Construcción (escalado confirmado a 5GW/USD 50+ mil millones, financiado fuera de balance vía JV con Blue Owl Capital; primeros 2GW en línea 2030, 5GW completo ~2032, finalización 2036; Entergy ahora respalda con 7 plantas adicionales de ciclo combinado a gas, 5,200+ MW, ~240 millas de transmisión 500kV y 3 baterías de red)</t>
+          <t>Ingeniería de detalle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Global Data Center Hub (https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
+          <t>Energy Magazine MX (https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vantage Data Centers NV1</t>
+          <t>El Pilar Copper Project</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storey County, Nevada, EE.UU.</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Grupo México / Southern Copper Corporation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6930,49 +4053,49 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Permisos ambientales asegurados (proyecto revaluado en US$551 millones; preparación de sitio inicia sep-2026, construcción plena 2027, primer cobre ~2028)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
+          <t>BNamericas (https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CloudBurst San Marcos Data Center I</t>
+          <t>Buenavista del Cobre — Concentradora No. 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Marcos/New Braunfels, Texas, EE.UU.</t>
+          <t>Cananea, Sonora, México</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CloudBurst Data Centers</t>
+          <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evolve (eVOLVE Data Center Solutions)</t>
+          <t>M3 Engineering &amp; Technology Corporation</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Ingeniería/ejecución de expansión</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
+          <t>M3 Engineering (https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6984,54 +4107,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Prometheus Hyperscale Dallas Campus</t>
+          <t>Media Luna Mine (North/EPO)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entre Talty y Post Oak Bend City, Kaufman County, Texas, EE.UU.</t>
+          <t>Guerrero, México</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prometheus Hyperscale</t>
+          <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No especificado (socio energía: Engie)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ingeniería/construcción temprana (campus de 200MW/4 edificios; estrategia behind-the-meter con motores de gas Jenbacher J620 + almacenamiento en baterías de Engie; primera instalación 2026, fases hasta 2028)</t>
+          <t>Construcción (tubería de pasta pendiente)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GW Ranch Power Campus</t>
+          <t>Pumpkin Hollow Copper Mine (reinicio)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pecos County, Texas, EE.UU.</t>
+          <t>Yerington, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pacifico Energy; inquilino confirmado: Amazon (AWS)</t>
+          <t>Nevada Copper Corp. (Kinterra Capital)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7041,404 +4164,404 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Construcción de edificios de centro de datos iniciada (TCEQ emitió permiso de aire final para la planta —35 turbinas de gas natural, hasta 33 millones de toneladas de CO2/año—; Amazon presentó a inicios de ago-2026 permisos de construcción para 3 edificios de centro de datos —"Pecos County Data Center", Buildings A/B/C, ~189,060 pies² c/u, ~US$300M c/u—; construcción de edificios prevista ago-dic 2026; primera entrega de energía prevista 1T2027, operando inicialmente fuera de la red de ERCOT)</t>
+          <t>Planeación de reinicio/construcción</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); Tom's Hardware (https://www.tomshardware.com/tech-industry/data-centers/amazons-new-7-65gw-texas-ai-data-center-power-plant-could-become-the-largest-source-of-co2-pollution-in-the-us-custom-35-turbine-gas-plant-authorized-to-emit-33-million-tons-of-annual-greenhouse-gases)</t>
+          <t>Mining.com (https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amazon Mattermeade Data Center Campus</t>
+          <t>Hermosa Critical Minerals Project (Taylor/Clark)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caroline/Spotsylvania County, Virginia, EE.UU.</t>
+          <t>Santa Cruz County, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amazon (AWS)</t>
+          <t>South32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>DMC Mining Services (parcial)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026, cerrando revisión NEPA de infraestructura en Coronado National Forest; autorización final programada para 4-sep-2026; primer proyecto minero aceptado en programa federal FAST-41; ~50% avance en porción privada; primer concentrado ahora proyectado H1-2028, antes H1-2027)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
+          <t>USDA (https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fermaca Digital City (+ gasoducto + planta de ciclo combinado)</t>
+          <t>Stibnite Gold Project</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Durango, Durango, México</t>
+          <t>Valley County, Idaho, EE.UU.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Grupo Fermaca (inquilino AI hyperscaler sin confirmar)</t>
+          <t>Perpetua Resources</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Hatch Ltd. (EPCM)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Permisos/negociación avanzada (inversión total US$3.7 mil millones: US$2.7B centro de datos + US$1B planta de fertilizantes Fermachem; gasoducto de 160km desde Texas; planta de ciclo combinado on-site de 350MW para alimentar data center de 250MW; Congreso de Durango aprobó donación de 50 hectáreas)</t>
+          <t>Construcción (corte federal de Idaho negó en jun-2026 moción para detener obras; Export-Import Bank de EE.UU. aprobó en may-2026 préstamo garantizado de USD 2,900 millones, desembolso esperado 2S2026)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mexico News Daily (https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); DCD (https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); Departamento de Justicia de EE.UU. (https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Circe Energy West Texas AI Infrastructure Campus</t>
+          <t>El Tigre Project</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cuenca Pérmica, West Texas, EE.UU.</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Circe Energy</t>
+          <t>Silver Tiger Metals</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No especificado (gen-sets Cummins)</t>
+          <t>Kappes, Cassiday &amp; Associates (EPCM)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ingeniería/procurement</t>
+          <t>Construcción (166 personas en sitio, 100,000 horas-hombre; primer vaciado previsto dic-2027)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
+          <t>Silver Tiger Metals (https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Project Jupiter</t>
+          <t>Panuco Silver-Gold Project</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Santa Teresa/Sunland Park, Doña Ana County, Nuevo México, EE.UU.</t>
+          <t>Sinaloa, México</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BorderPlex Digital Assets/Stack (inquilino Oracle/OpenAI)</t>
+          <t>Vizsla Silver Corp.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No especificado (rediseño: hasta 2.45GW de celdas de combustible Bloom Energy, reemplazando turbinas de gas/diésel)</t>
+          <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción activa con riesgo regulatorio (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 14-jul-2026; NMED pospuso la decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas y programó audiencia pública para 19-oct-2026; meta de entrada en servicio ago-2026 en riesgo)</t>
+          <t>Ingeniería de detalle/planeación de construcción (post-Feasibility Study)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Source NM (https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PowerPlay AI "Greater Abilene" Data Center</t>
+          <t>South Railroad Project (South Carlin Complex)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Área metropolitana de Abilene, Texas, EE.UU.</t>
+          <t>Elko/Eureka County, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PowerPlay AI (JV con socio Neocloud cotizado en Nasdaq, sin nombre público)</t>
+          <t>Orla Mining Ltd.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IPP en proceso de RFP (aún sin seleccionar)</t>
+          <t>M3 Engineering &amp; Technology Corp. (EPCM)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ejecución activa post-adquisición de terreno (400MW behind-the-meter iniciales; arranque objetivo 2028)</t>
+          <t>Construcción (inicio previsto mediados 2026, pendiente ROD final de BLM)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
+          <t>Orla Mining (https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Liberty Energy/PowerBridge "Alpha Digital Campus"</t>
+          <t>Copperstone Gold Project</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Condado de Reeves, Texas, EE.UU. (cerca del hub de gas Waha)</t>
+          <t>La Paz County, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PowerBridge LLC</t>
+          <t>Minera Alamos Inc.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Liberty Power Innovations (subsidiaria de Liberty Energy, JV)</t>
+          <t>Contratista de minería subterránea por definir</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JV firmada/desarrollo temprano (~3,400 acres; primera fase &gt;300MW, primera entrega de energía prevista 4T2027; campus completo 2GW)</t>
+          <t>Construcción (decisión de inversión may-2026; PFS positivo anunciado; construcción estimada en ~1 año; primera producción de oro prevista mediados de 2027)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28); Minera Alamos (https://mineraalamos.com/news/2026/minera-alamos-announces-positive-pre-feasibility-study-for-the-copperstone-gold-project-in-arizona/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>New Era Energy &amp; Digital Hub</t>
+          <t>CK Gold Project</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lea County, Nuevo México, EE.UU.</t>
+          <t>Distrito Silver Crown, Laramie Range, Wyoming, EE.UU.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New Era Energy &amp; Digital</t>
+          <t>U.S. Gold Corp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Halyard-Micon International (feasibility); EPC por asignar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Planeación temprana (opción de terreno)</t>
+          <t>Permiso de Emplazamiento Industrial (Industrial Siting Permit) otorgado por Wyoming DEQ el 20-jun-2026, habilitando construcción y operación sin requerir NEPA (no involucra tierra federal); construcción pesada prevista hasta 2027, producción 2028</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PowerMag (https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
+          <t>Wyoming News (https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html); Discovery Alert (https://discoveryalert.com.au/ck-gold-project-permitting-construction-ready-valuation-2026/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Texas Critical Data Centers (TCDC) Campus</t>
+          <t>Distrito Santa Elena — Expansión (Santo Niño y Navidad)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Era Energy &amp; Digital</t>
+          <t>First Majestic Silver Corp.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
+          <t>Construcción (permisos recibidos jun-2026; First Majestic compromete US$12 millones en 2026 para desarrollo de accesos subterráneos y portales)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+          <t>First Majestic (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stargate Lordstown</t>
+          <t>Galena Complex — Planta de Relleno en Pasta</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lordstown, Ohio, EE.UU.</t>
+          <t>Wallace, Idaho, EE.UU.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle / SoftBank</t>
+          <t>Americas Gold and Silver Corporation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SB Energy (SoftBank)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Construcción (rompimiento de tierra)</t>
+          <t>Construcción (comisionamiento previsto Q4 2026)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>SEC/Americas Gold and Silver (https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stargate Wisconsin</t>
+          <t>Guanacevi Silver Project (Ocampo Mining)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
+          <t>Durango, México</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle / SoftBank</t>
+          <t>Minera Frisco (Grupo Carso)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vantage Data Centers (en sociedad con Oracle)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo temprano</t>
+          <t>Construcción (nueva planta de proceso; primera producción prevista fin de 2026)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>Kitco (https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Región Digital Querétaro</t>
+          <t>Arctic Project (Distrito Minero Ambler)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Querétaro, México</t>
+          <t>Distrito Minero Ambler, Alaska, EE.UU.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Ambler Metals LLC (Trilogy Metals / South32, JV 50/50)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7448,108 +4571,108 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
+          <t>Permitting (cronograma coordinado de permisos federales/estatales publicado 16-jul-2026; revisión ambiental integrada de 29 meses liderada por USACE; ROD objetivo sep-2028)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mexico News Daily (https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stargate Michigan (Saline Barn Campus)</t>
+          <t>Los Ricos South Mine</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saline Township, Michigan, EE.UU.</t>
+          <t>Jalisco, México</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
+          <t>GoGold Resources</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Walbridge</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Construcción aprobada por el consejo (permisos SEMARNAT completos jun-2026; presupuesto ~US$227 millones; ventana de construcción de ~24 meses; primer vertido de metal previsto mediados de 2028)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
+          <t>Northern Miner (https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); Newsfile (https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
+          <t>Cordero Project</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>North Dakota, EE.UU.</t>
+          <t>Chihuahua, México</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Applied Digital / Base Electron</t>
+          <t>Discovery Silver</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
+          <t>Ausenco (ingeniería)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
+          <t>Feasibility completa / permitting (MIA pendiente ante SEMARNAT)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Valley News Live (https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
+          <t>BNamericas (https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI-GDC / Cipre Holding "Green Data Center"</t>
+          <t>Gran Pilar Gold-Silver Project</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>San Pedro Garza García, Nuevo León, México</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
+          <t>Tocvan Ventures</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7559,34 +4682,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo temprano</t>
+          <t>Construcción (piloto; primer doré previsto Q4 2026)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energy Magazine MX (https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
+          <t>Resource World (https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CleanArc Data Centers VA1 Campus</t>
+          <t>Orisyvo Project</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caroline County, Virginia, EE.UU.</t>
+          <t>Sierra Madre (Rarámuri), Chihuahua, México</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CleanArc Data Centers</t>
+          <t>Fresnillo plc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7596,219 +4719,219 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Pre-feasibility (transicionando a feasibility, resultados esperados medio 2026)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Construction Dive (https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
+          <t>Fresnillo plc (https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Joule Energy and Data Center Campus</t>
+          <t>Planta de Separación de Tierras Raras (US Army)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Millard County (Holden), Utah, EE.UU.</t>
+          <t>Tooele Army Depot, Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Joule Capital Partners</t>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>REalloys Inc.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Acuerdo de arrendamiento condicional otorgado por el Ejército de EE.UU. (confirmado 29-jul-2026, parte de programa en 4 sitios: Anniston AL, Pine Bluff AR, Red River TX, Tooele UT); desarrollo comercial previsto 2027, operaciones iniciales 2028</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KSL (https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
+          <t>Army.mil (https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amazon Montgomery County Campus</t>
+          <t>Planta de Purificación de Grafito (US Army)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+          <t>Pine Bluff Arsenal, Arkansas o Anniston Army Depot, Alabama (sin confirmar), EE.UU.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Titan Mining Corp.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Anuncio/permisos</t>
+          <t>Acuerdo firmado/planeación (construcción prevista desde 2027)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Governor.mo.gov (https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
+          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Google Montgomery County Campus</t>
+          <t>Plantas de Litio y Boro (US Army)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+          <t>Base militar de EE.UU. sin confirmar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>EnergyX (litio) / ioneer Ltd. (boro)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Anuncio/permisos</t>
+          <t>Acuerdo firmado/planeación (construcción prevista desde 2027; producción 2028)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>STLPR (https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
+          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
+          <t>Expansión Concentradora La Caridad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hood County, Texas, EE.UU.</t>
+          <t>Nacozari, Sonora, México</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Big Digital Energy + 10NetZero (JV)</t>
+          <t>Grupo México</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Metso (equipo de trituración)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Planeación/adquisición de sitio</t>
+          <t>Construcción/procura de equipo (pedido adicional &gt;EUR 20M de trituración secundaria a Metso, jun-2026, complementa equipos Nordberg MP800 instalados en 2025)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
+          <t>IM Mining (https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Williams "Project Socrates"</t>
+          <t>Santo Tomás Copper Project</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New Albany, Ohio, EE.UU.</t>
+          <t>Sinaloa, México</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Meta (vía Sidecat, LLC)</t>
+          <t>Oroco Resource Corp.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Williams Companies / Will-Power</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
+          <t>Prefactibilidad (perforación fase 2 en curso; PFS objetivo 2T-3T 2027; capex estimado USD 2.84 mil millones; permisos federales pendientes)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Meta El Paso Campus (expansión)</t>
+          <t>Reapertura Fundición Hayden + Refinería Amarillo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>El Paso, Texas, EE.UU.</t>
+          <t>Hayden, Arizona / Amarillo, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Asarco (Grupo México)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -7818,34 +4941,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Permisos</t>
+          <t>Negociación/planeación (inversión ~USD 230 millones para reactivar fundición cerrada desde 2020; Grupo México evalúa hasta USD 6,000 millones adicionales para expansión de cobre en Arizona)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SB Energy/SoftBank PORTS Technology Campus</t>
+          <t>Cerro de Oro Gold Project</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pike County, Ohio, EE.UU.</t>
+          <t>Zacatecas, México</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
+          <t>Minera Alamos Inc.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7855,182 +4978,182 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Planeación avanzada (SB Energy construirá 9.2GW de generación a gas natural, financiamiento de US$33.3 mil millones por SoftBank, más US$4.2 mil millones en transmisión; 26-jul-2026 trascendió que Nvidia negocia garantía financiera de hasta US$250 mil millones para que OpenAI arriende el sitio, primera fase de 800MW en 2028)</t>
+          <t>Permitting (proyecto de oro a cielo abierto/heap leach; financiamiento de construcción ya asegurado)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
+          <t>Minera Alamos (https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Williams "Apollo" Power Generation Project</t>
+          <t>Antler Copper Project</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
+          <t>Condado de Mohave, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
+          <t>New World Resources Ltd. (respaldado por Kinterra Capital)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
+          <t>Permitting casi completo/inicio de construcción (BLM emitió Determinación de Adecuación NEPA; obras previstas 2do semestre 2026; embarque de concentrado previsto 2027)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>Global Mining Review (https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Williams "Aquila" Power Project</t>
+          <t>Lisbon Valley Copper Project</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Utah, EE.UU. (condado no revelado)</t>
+          <t>Condado de San Juan, Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
+          <t>Lisbon Valley Mining Company, LLC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+          <t>Permitting federal completo (aprobación BLM + exención de acuífero EPA, oct-2025) / reapertura-construcción (agrega tajo abierto y pozos de recuperación in-situ)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Williams Companies (https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
+          <t>BLM (https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
+          <t>South West Arkansas Lithium Project (Central Processing Facility)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>West Texas, EE.UU. (condado no revelado)</t>
+          <t>Sur de Arkansas, EE.UU.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
+          <t>Smackover Lithium (JV Standard Lithium / Equinor)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>S&amp;B Engineers and Constructors (EPCC); Hatch Ltd. (ingeniería de diseño/comisionamiento)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
+          <t>Ingeniería de detalle/procura temprana (contrato EPCC otorgado, NTP limitado activo; FID esperada en 2026; planta diseñada para 22,500 tpa de carbonato de litio grado batería; DOE emitió FONSI —Finding of No Significant Impact—, paso clave hacia la FID; producción comercial estimada 2029)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
+          <t>InvestingNews (https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/); StockTitan/SEC 6-K (https://www.stocktitan.net/sec-filings/SLI/6-k-standard-lithium-ltd-current-report-foreign-issuer-ef7db860baa3.html)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tallgrass AI Data Center Campus (Project Jade)</t>
+          <t>Bagdad Mine Concentrator Expansion</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Condado de Laramie, Wyoming, EE.UU.</t>
+          <t>Yavapai County, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Black Hills Corp. (desarrollador directo) / Tallgrass / cliente de gran carga no revelado (comprometió US$200M+ en hitos de construcción)</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No especificado (Crusoe Energy se retiró como desarrollador, jun-2026, a solicitud del cliente)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Desarrollo CONTINÚA con nuevo desarrollador (Crusoe salió del proyecto pero Black Hills Corp. avanza directamente con el cliente; permisos locales de Wyoming vigentes; 1.8GW inicial escalable a 10GW)</t>
+          <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental estimado ~US$3,500 millones bajo revisión; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cowboy State Daily (https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
+          <t>SEC/Freeport-McMoRan (https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Core Scientific Pecos Campus (expansión IA)</t>
+          <t>Elk Creek Critical Minerals Project</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pecos, Reeves County, Texas, EE.UU.</t>
+          <t>Elk Creek, Nebraska, EE.UU.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>NioCorp Developments Ltd.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8040,34 +5163,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
+          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; estudio de factibilidad actualizado publicado 11-ago-2026 —VPN8% antes de impuestos US$4,100 millones, capex inicial US$1,850 millones a 35 meses—; avanzando a ingeniería detallada, procura y contratación EPC; proyecto de niobio/escandio/titanio con planta de superficie que requerirá tubería de proceso)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HPCwire (https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
+          <t>NioCorp (https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); Mining.com (https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stratos Project / Wonder Valley</t>
+          <t>Goldfield Project</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
+          <t>Goldfield, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>O'Leary Digital (Kevin O'Leary)</t>
+          <t>Centerra Gold Inc.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8077,108 +5200,108 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
+          <t>Ingeniería/Construcción temprana (ingeniería de detalle y procura de largo plazo en 2026; construcción mayor de pila de lixiviación y circuitos de trituración/procesamiento en 2027; primera producción fin de 2028)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Utah News Dispatch (https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
+          <t>E&amp;MJ (https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fermi America Project Matador</t>
+          <t>Cactus Mine (distrito Copper World/Arizona Sonoran)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Carson County (Amarillo), Texas, EE.UU.</t>
+          <t>Casa Grande, Arizona, EE.UU.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fermi America</t>
+          <t>Hudbay Minerals (adquisición de Arizona Sonoran Copper Co. anunciada 2-mar-2026)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas); Energy Transfer (interconexión de gasoducto)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW)</t>
+          <t>Desarrollo/Feasibility (planta SX-EW de cátodos de cobre, ~103,000 t Cu/año proyectadas; Hudbay busca fusionarlo con el distrito Copper World adyacente ya rastreado; DFS en curso con FID apuntada para 4T2026 y construcción prevista en 2027)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>StockTitan (https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html); Arizona Sonoran (https://arizonasonoran.com/news-releases/arizona-sonoran-pre-feasibility-study-delivers-exceptional-results-for-the-cactus-project-outlining-long-life-low-cost-copper-1/)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NextEra Texas Power Generation Hub</t>
+          <t>Doby George Gold Project (Distrito Aura)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Anderson County, Texas, EE.UU.</t>
+          <t>~120 km al norte de Elko, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NextEra Energy Resources</t>
+          <t>Western Exploration Inc.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>No especificado (WSP realiza feasibility study; Stantec y Kappes Cassidy en estudios ambientales)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
+          <t>Feasibility/Permitting (PEA positiva 2025; campaña de perforación iniciada, hasta 3,000m/15 pozos para estudios base y PFS; sometimiento del Mine Plan of Operations ahora esperado a inicios de ago-2026; proyecto de lixiviación en pilas de óxidos)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KLTV (https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
+          <t>Western Exploration (https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx); StreetWise Reports (https://www.streetwisereports.com/article/2026/08/03/nevada-gold-project-launches-drill-campaign-at-doby-george.html)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
+          <t>Metates Project</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Monongalia County, Virginia Occidental, EE.UU.</t>
+          <t>Durango, México</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mon Power (FirstEnergy)</t>
+          <t>Chesapeake Gold Corp.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8188,71 +5311,71 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
+          <t>Feasibility (prefeasibility study objetivo 2026; pruebas metalúrgicas de lixiviación de sulfuros y estudios ambientales de línea base en curso; uno de los mayores depósitos de oro-plata no desarrollados de América)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WV MetroNews (https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+          <t>Chesapeake Gold Corp. (https://chesapeakegold.com/metates/)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IEP Greene County Data Center &amp; Power Plant</t>
+          <t>Pathfinder Tonopah (cobre-molibdeno-plata)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Greene County, Pensilvania, EE.UU.</t>
+          <t>Tonopah, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>International Electric Power</t>
+          <t>Pathfinder Minerals (Pathfinder Tonopah)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Bowman (permisos ambientales, FEED, planta piloto)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
+          <t>Permitting/FEED (avanzando hacia estudio de factibilidad definitivo; carta de interés no vinculante de EXIM Bank por US$896 millones para financiamiento, programa "Make More in America")</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Utility Dive (https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
+          <t>Mining Technology (https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AWS "Project Eagle"</t>
+          <t>La Colorada Mine — Expansión Veta Madre/Veta Madre Plus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Amazon Web Services</t>
+          <t>Heliostar Metals</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -8262,34 +5385,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Permisos/Construcción inminente (confirmado inicio de construcción 1-ago-2026; 3 edificios completados ene-2027, 4to edificio ago-2027; USD 1.2 mil millones, ~2,700 acres)</t>
+          <t>Permisos completos obtenidos (2026); waste stripping programado 3T2026; producción de zona expandida esperada 1S2027</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wharton Post (https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Crusoe/Lancium Childress Data Center Campus</t>
+          <t>Libby Project (Cabinet Mountains)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Condado de Childress, Texas, EE.UU.</t>
+          <t>Condado de Lincoln, Montana, EE.UU.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
+          <t>Hecla Mining Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -8299,108 +5422,108 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
+          <t>Permitting federal completado para exploración subterránea (extensión de ~1 milla del socavón Libby Adit; recurso potencial 1,500 millones lb de cobre y 183 millones oz de plata; pendiente permiso de descarga de agua de MT DEQ)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crusoe (https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+          <t>The Western News (https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Williams "Neo" Power Innovation Project</t>
+          <t>Donlin Gold</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
+          <t>Alaska, EE.UU.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cliente de centro de datos no revelado</t>
+          <t>NovaGold Corporation (adquiriendo 100%, compra de participación del 40% de Paulson Advisers)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+          <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); aún sin decisión de construcción (FID)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>Mining News North (https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Williams "Socrates the Younger" Power Innovation Project</t>
+          <t>Rhyolite Ridge Lithium-Boron Project</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
+          <t>Condado de Esmeralda, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Meta Platforms (vía Sidecat, LLC)</t>
+          <t>ioneer Ltd.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Hyundai Engineering Co. Ltd. (MOU no vinculante, evaluando rol EPC/procura); KIND evaluando inversión de capital</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+          <t>Permitting confirmado en corte federal (31-mar-2026); préstamo DOE de US$996 millones cerrado; MOUs con KIND/Hyundai firmados inicios jul-2026; FID objetivo 2S2026, primera producción 2029</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PowerMag (https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
+          <t>IM Mining (https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Crusoe/Google "Goodnight Campus"</t>
+          <t>San Antonio Gold Project</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
+          <t>Axo Metals Corp. (Axo Copper Corp.)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8410,71 +5533,71 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
+          <t>Permisos (SEMARNAT aprobó la MIA, 27-jul-2026, habilitando producción; planta de carbón-en-columna ya permisada; aprobaciones de uso de suelo para nuevos yacimientos —Sapuchi, Golfo de Oro, California— en trámite para fin de año)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aterio (https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
+          <t>Resource World (https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VoltaGrid/Serverfarm Covington</t>
+          <t>Tamarack Nickel-Copper-Cobalt Project</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
+          <t>Aitkin County, Minnesota (mina) / Beulah, Dakota del Norte (planta de proceso — Beulah Minerals Processing Facility), EE.UU.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serverfarm</t>
+          <t>Talon Metals Corp. (51%) / Kennecott Exploration Co. (Rio Tinto) JV</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Construcción REANUDADA (tras orden de suspensión de la agencia ambiental de Georgia -EPD- del 2-jul-2026 por construir sin permisos; a 31-jul-2026 la construcción de la planta de 90MW está en marcha de nuevo, con 6 de 33 motores a gas ya instalados)</t>
+          <t>Permitting/Feasibility (Talon firmó acuerdo de opción de terreno con Westmoreland Mining, 28-jul-2026, por ~256 acres cerca de Beulah, ND, para la Beulah Minerals Processing Facility —planta de procesamiento de concentrado níquel-cobre respaldada por subvención DOE de US$114.8 millones—; EIS de la mina en scoping, comentarios cierran 14-sep-2026; entendimiento informal de offtake con Tesla)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AJC (https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); Inside Climate News (https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
+          <t>Talon Metals (https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
+          <t>Bunker Hill Mine — Reinicio + Planta de Relleno en Pasta</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
+          <t>Kellogg/Wardner, Idaho, EE.UU. (Distrito Minero Coeur d'Alene)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
+          <t>Bunker Hill Mining Corp.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8484,293 +5607,293 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
+          <t>Construcción/Comisionamiento (primer embarque de concentrado a la fundición Trail de Teck tras 45+ años de cierre; nueva planta de proceso de 1,800 tpd comisionada; planta de relleno en pasta en sitio Wardner sustancialmente completa, comisionamiento final previsto ~3 semanas tras el anuncio; meta de producción comercial plena fin de 2026)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Homer City Energy Campus</t>
+          <t>NewRange Copper Nickel (Proyecto NorthMet) — Rediseño Mayor</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Condado de Indiana, Pensilvania, EE.UU.</t>
+          <t>Babbitt/Hoyt Lakes, Minnesota, EE.UU. (Iron Range)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Homer City Redevelopment (HCR)</t>
+          <t>NewRange Copper Nickel (JV PolyMet/Glencore + Teck)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027; Amazon confirmó públicamente estar en "discusiones comerciales" activas con HCR para ubicar un data center adyacente a la planta, avanzando desde el rumor previo, aún sin acuerdo definitivo firmado)</t>
+          <t>Permitting (rediseño mayor elimina la represa de jales propuesta —roca estéril se almacenaría en tajos de mineral de hierro existentes—; solicitud de permiso de humedales Sección 404/Clean Water Act presentada ante USACE; revisión ambiental suplementaria (SEIS) solicitada a Minnesota DNR)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation); Indiana Gazette (https://www.indianagazette.com/local_news/amazon-hcr-are-conducting-commercial-discussions-on-data-center/article_733afa63-9d58-42d0-b16e-6dc61b71689b.html)</t>
+          <t>MPR News (https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nebius Vineland AI Data Center Campus</t>
+          <t>White Mesa Mill — Expansión de Tierras Raras Pesadas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vineland, Nueva Jersey, EE.UU.</t>
+          <t>Blanding, Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
+          <t>Energy Fuels Inc.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No especificado — posible cambio de alcance a celdas de combustible Bloom Energy (acuerdo maestro Nebius-Bloom Energy de USD 2,600 millones, 21-may-2026, hasta 328MW; fuentes de menor confianza lo vinculan a Vineland como respuesta a problemas de permisos de aire NJDEP con planta vecina Corning — confirmación directa pendiente)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; NJDEP en revisión hacia aprobación final a mediados jul-2026; meta de entrega nov-2026 en riesgo)</t>
+          <t>Construcción (planta comercial de tierras raras pesadas —disprosio/terbio— iniciada 29-jul-2026; capex ~US$104 millones, para uso en imanes/defensa/vehículos eléctricos)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
+          <t>Energy Fuels (https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); PR Newswire (https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TerraVolt Infrastructure AI Data Center Campus</t>
+          <t>Black Butte Copper Project</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
+          <t>Meagher County, Montana, EE.UU.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
+          <t>Sandfire Resources America Inc. (Sandfire Resources)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Por definir (PFS elaborado por DM Consulting)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
+          <t>Feasibility (PFS actualizado presentado 28-jul-2026 con nuevas reservas Lowry, vida de mina de 12 años; mina subterránea de cobre de alta ley)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CyrusOne SAT14A</t>
+          <t>Planta de Procesamiento de Litio Red River (US Army)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Castroville, San Antonio, Texas, EE.UU.</t>
+          <t>Bowie County, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CyrusOne (sin arrendatario asignado aún)</t>
+          <t>Pentágono / Departamento del Ejército de EE.UU.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>EnergyX (desarrollador-operador)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ingeniería/Permisos (6to campus en San Antonio, 11vo en Texas; USD 500 millones, 460,000 pies²; inicio de construcción previsto dic-2026)</t>
+          <t>Acuerdo de arrendamiento condicional otorgado (confirmado 25-jun-2026; 5to sitio del programa de minerales críticos en bases del Ejército, junto con Tooele, Pine Bluff/Anniston; construcción prevista desde 2027)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
+          <t>Texarkana Gazette (https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EdgeConneX PowerConneX New Albany Energy Center (I, II y III)</t>
+          <t>Camino Rojo — Proyecto Subterráneo (extensión)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New Albany, Licking County, Ohio, EE.UU.</t>
+          <t>Zacatecas, México</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EdgeConneX (propiedad de EQT Infrastructure)</t>
+          <t>Orla Mining Ltd.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No especificado (desarrollado vía afiliada PowerConneX)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027; PowerConneX III, 430MW, notificación previa ante OPSB abr-2026, elevando capacidad total del sitio a ~766MW de gas)</t>
+          <t>Permisos completos/inicio de desarrollo subterráneo (SEMARNAT aprobó MIA 18-mar-2026, habilitando minado del resto del tajo de óxidos y construcción de rampa de exploración subterránea; inicio de obras de acceso subterráneo previsto 2S2026; PEA de proyecto subterráneo indica VPN de US$1,300 millones)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); BeBeez (https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
+          <t>Mining.com (https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); Orla Mining (https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>xAI Colossus 2/Colossus 3 ("MACROHARDRR")</t>
+          <t>Cerro Caliche Gold Project</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Southaven, Misisipi / Memphis, Tennessee, EE.UU.</t>
+          <t>Sonora, México</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Sonoro Gold Corp.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>EPC por definir (en negociación con múltiples empresas EPC de China)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Operando parcialmente/en expansión con crisis regulatoria activa (59 turbinas de gas natural operando en Southaven, la mayoría sin permisos federales de Clean Air Act; demanda de NAACP/Southern Environmental Law Center/Earthjustice desde abr-2026; xAI recibió aprobación para 41 turbinas de gas adicionales, ~1.2GW, en el sitio de Southaven para alimentar Colossus 2 y el próximo Colossus 3; DOJ intervino en litigio citando uso de Grok por el Departamento de Defensa; capacidad total del sitio creciendo hacia 2GW+ en tres edificios)</t>
+          <t>Permisos/estructuración de financiamiento EPC (plataforma consolidada de 3,924 hectáreas en 25 concesiones; finalización de permisos esperada 1T2026; 4 empresas EPC chinas evaluando financiamiento de deuda y desarrollo)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Technology.org (https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); DCD (https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
+          <t>Sonoro Gold Corp. (https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); Mexico Mining Center (https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Applied Digital "Delta Forge 1" (planta de gas dedicada Cleco 756MW)</t>
+          <t>Pilot Mountain Tungsten Project</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rapides Parish, Luisiana, EE.UU.</t>
+          <t>Mineral County, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Applied Digital</t>
+          <t>Guardian Metal Resources PLC (vía Golden Metal Resources USA LLC)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cleco Power (planta de gas dedicada de 756MW)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Construcción (campus de USD 3.6 mil millones/430MW, la mayor carga individual jamás atendida por Cleco; rompimiento de tierra ene-2026; operaciones iniciales objetivo mediados de 2027)</t>
+          <t>Ingeniería/Feasibility (PFS positivo completado jun-2026, respaldado por USD 6.2 millones del Departamento de Guerra/DPA Title III; presentación del Mine Plan of Operations federal prevista ago-2026; producción 4T2028)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
+          <t>Mining Weekly (https://www.miningweekly.com/article/guardian-metals-outlines-viable-tungsten-trioxide-operation-in-nevada-2026-06-30); StockTitan (https://www.stocktitan.net/news/GMTL/guardian-metal-resources-plc-announces-pilot-mountain-pre-tftnlr9fu3if.html)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rubix Data Centers (Submer Group)</t>
+          <t>Gabbs Project</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Russell, Kentucky, EE.UU. (antiguo sitio de acería AK Steel)</t>
+          <t>Walker-Lane Trend, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rubix Data Centers / Submer Group</t>
+          <t>P2 Gold Inc.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8780,71 +5903,71 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Propuesta/planeación temprana (hasta 2GW, US$8-12 mil millones; moratoria municipal sobre solicitudes de data centers podría complicar el proyecto; fuente de energía aún no especificada)</t>
+          <t>Ingeniería/Feasibility (proyecto oro-cobre; feasibility study en curso, meta 4T2026)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kentucky Lantern (https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
+          <t>Newswire (https://www.newswire.ca/news-releases/p2-gold-gabbs-project-update-feasibility-study-on-track-840759204.html)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QTS/Lancium Hall County Campus</t>
+          <t>Treasure Canyon Gold Mine</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cerca de Turkey, Condado de Hall, Texas, EE.UU.</t>
+          <t>Plumas National Forest, cerca de Taylorsville, California, EE.UU.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lancium (dueño de sitio/energía) / QTS Data Centers (construcción/operación)</t>
+          <t>Buscar Company (CGLD)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lancium (autoabastecimiento solar+baterías; interconexión a red de 1GW; sin planta de gas confirmada)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Anuncio/desarrollo temprano (US$10 mil millones, hasta 11 edificios en 465 acres)</t>
+          <t>Permitting (Plan de Operaciones sometido a US Forest Service feb-2026; en revisión por agencias federales/estatales)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/buscar-company-announces-major-advancement-in-the-permitting-process-for-the-treasure-canyon-gold-mine-project-in-california-302772744.html)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Anthropic/Nexus Hubbard Campus</t>
+          <t>Grassy Mountain Gold Project</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hubbard, Condado de Hill, Texas, EE.UU.</t>
+          <t>Malheur County, Oregon, EE.UU.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Anthropic (operado por Nexus Data Centers; respaldo financiero de Google)</t>
+          <t>Paramount Gold Nevada Corp. (vía Calico Resources)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8854,34 +5977,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Construcción iniciada (primera fase 500-612MW prevista 2026, ampliable a ~7.2-7.7GW; planta de gas natural behind-the-meter cerca de gasoducto principal; financiamiento avanzado: banca liderada por Morgan Stanley en negociaciones finales para prestar USD 15 mil millones a Nexus Data Centers —incluye préstamo puente de USD 14 mil millones más línea de crédito revolvente—; Google otorgaría garantías sobre obligaciones de arrendamiento y pago de energía de Anthropic a cambio de ~20% de participación accionaria en el proyecto combinado)</t>
+          <t>Permitting (Record of Decision federal firmado 29-ene-2026 bajo NEPA; permisos estatales pendientes, esperados 2S2026; Feasibility Study ya completo con VPN de USD 375 millones)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); Construction Review (https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); CNBC (https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/01/29/3229150/0/en/Paramount-Gold-Receives-Federal-Approval-for-the-Grassy-Mountain-Gold-Project.html); OPB (https://www.opb.org/article/2026/01/29/oregon-gold-mine-grassy-mountain/)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Stillwater Technology Park</t>
+          <t>MP Materials 10X Magnet Manufacturing Facility</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lovejoy, Condado de Clayton, Georgia, EE.UU.</t>
+          <t>Northlake, Texas, EE.UU.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Stillwater Development, LLC (cliente hyperscaler final no revelado)</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8891,34 +6014,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Permisos ("development of regional impact" presentado ante el estado; hasta 15 edificios, 1.25GW, US$13 mil millones; generación de energía aún no confirmada, contempla interconexión con Central Georgia EMC)</t>
+          <t>Construcción (rompimiento de tierra 1T2026; planta de imanes de tierras raras de USD 1,250 millones; ~7,000 t/año de capacidad adicional)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
+          <t>CNBC (https://www.cnbc.com/2026/02/26/mp-materials-selects-texas-for-rare-earth-magnet-manufacturing-site.html)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Paducah Data Center Campus</t>
+          <t>Expansión de Separación de Tierras Raras Pesadas — Mountain Pass</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Antiguo sitio de enriquecimiento de uranio del DOE, Paducah, Kentucky, EE.UU.</t>
+          <t>Mountain Pass, California, EE.UU.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Coalición: Brookfield / NextEra Energy / Big Rivers Electric / Jackson Purchase Energy Cooperative / Paducah Power System</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8928,182 +6051,182 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Anuncio/desarrollo temprano (hasta 1.8GW; incluye nueva planta de gas natural de ~2GW y hasta 2.6GW de almacenamiento en baterías; ~US$100 mil millones de inversión privada total, el mayor proyecto de desarrollo económico en la historia de Kentucky)</t>
+          <t>Ingeniería/Construcción temprana (financiamiento de USD 550 millones del Departamento de Defensa, feb-2026, para agregar capacidad de separación de tierras raras pesadas en la mina/planta existente)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bloomberg (https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); Kentucky Lantern (https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/the-united-states-is-investing-in-its-domestic-rare-earth-industry-302838375.html)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OpenAI "Project Camellia"</t>
+          <t>Planta de Procesamiento de Antimonio (JV Galena Complex)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Condado de Effingham, cerca de Savannah, Georgia, EE.UU.</t>
+          <t>Silver Valley, Wallace, Idaho, EE.UU.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>JV Americas Gold and Silver Corporation (51%) / United States Antimony Corp (49%)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No especificado (energía: Georgia Power, expansión de ~5.8GW de generación a gas natural)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Anuncio/preconstrucción (carga de 3.2GW, ~US$20-30 mil millones de inversión; capacidad disponible 2028-2032; OpenAI cubre el costo total de la infraestructura)</t>
+          <t>Ingeniería/Construcción (JV firmado feb-2026 para construir y operar planta de procesamiento de antimonio dentro de los permisos existentes del Galena Complex)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Axios (https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); DCD (https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
+          <t>Newsfile Corp (https://www.newsfilecorp.com/release/283399/Americas-Gold-and-Silver-Signs-Joint-Venture-Agreement-with-US-Antimony-to-Construct-Antimony-Processing-Facility-in-Idahos-Silver-Valley-Unlocking-Value-from-Its-Antimony-Production-and-Strengthening-U.S.-Critical-Mineral-Security)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Stream Data Centers "Project Saltworks"</t>
+          <t>Michigan Potash Project</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Condado de Young (cerca de Graham), Texas, EE.UU.</t>
+          <t>Osceola County, Michigan, EE.UU.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Headwaters Site Development (afiliada de Stream US Data Centers)</t>
+          <t>Michigan Potash &amp; Salt Co.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No especificado (activos de interconexión de energía adquiridos de Plug Power)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Preconstrucción/diseño de sitio (~890 acres, ~US$10 mil millones, 15 edificios planeados; construcción no prevista antes de inicios de 2027; enfrenta oposición comunitaria local)</t>
+          <t>Financiamiento/pre-construcción (mina de solución de potasa + planta de proceso; garantía de préstamo condicional DOE de USD 1,260 millones; posible aprobación FAST-41 en 2026; ~726,000 t/año)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); Olney Enterprise (https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
+          <t>DOE-LPO (https://www.energy.gov/lpo/articles/lpo-announces-conditional-commitment-michigan-potash-produce-fertilizer-us-farmers); Northern Miner (https://www.northernminer.com/news/us-boosts-potash-projects-in-utah-michigan/1003886533/)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Eagle Rock Partners "Meridian Technology Park"</t>
+          <t>Sevier Playa Potash Project</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cerca de Taylorville, Condado de Christian, Illinois, EE.UU.</t>
+          <t>Millard County, Utah, EE.UU.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eagle Rock Partners</t>
+          <t>Peak Minerals (respaldado por EMR Capital)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No especificado (PPA con Kindle Energy LLC para 1,000-1,100MW del proyecto de planta de gas Lincoln Land Energy Center, cerca de Pawnee, desarrollado por EmberClear)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Planeación muy temprana (aún sin solicitud de zonificación presentada; ~US$6 mil millones, 10 edificios planeados; energía esperada para 2029)</t>
+          <t>Construcción (BLM aprobó construcción de la etapa inicial de 195,000 t en jun-2026; capex total USD 435 millones; subvención USDA de USD 80 millones)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Illinois Times (https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
+          <t>BLM (https://www.blm.gov/announcement/blm-approves-construction-sevier-playa-potash-mining-project)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Creekstone Energy "Delta Gigasite"</t>
+          <t>Shirley Basin Uranium Project</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cerca de Delta, Condado de Millard, Utah, EE.UU.</t>
+          <t>Wyoming, EE.UU.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Creekstone Energy LLC</t>
+          <t>Ur-Energy Inc.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Zeo Energy (socio de energía)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Construcción (rompimiento de tierra dic-2025; meta de 10GW de capacidad total —2GW de gas on-site + 6GW solar + posibles 1.8GW de la planta de carbón inactiva Intermountain—; &gt;300MW de capacidad a gas prevista en línea 1S2027; US$17 mil millones comprometidos)</t>
+          <t>Construcción/Inicio de operación (planta satélite ISR integrada con Lost Creek; inicio de minado abr-2026; envío de resina cargada a Lost Creek previsto verano 2026)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KSL (https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); Utah GOED (https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
+          <t>Ur-Energy (https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Amazon Richmond County Data Center Campus</t>
+          <t>Cusi Mine (Reinicio)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Richmond County (Hamlet), Carolina del Norte, EE.UU.</t>
+          <t>Chihuahua, México</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amazon (AWS)</t>
+          <t>Silverco Mining Ltd.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9113,34 +6236,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Construcción (rompimiento de tierra completado jun-2026; campus de USD 10 mil millones, hasta 20 edificios en 800 acres; ubicado junto al complejo Sherwood H. Smith Jr. de Duke Energy —2.24GW de turbinas de gas natural existentes—; Duke Energy planea construir una turbina adicional de 240MW en el mismo complejo, construcción prevista fines de 2027, en línea fines de 2029; 57 generadores diésel temporales de Duke Energy instalándose en terreno de Amazon como respaldo mientras se construye infraestructura permanente; audiencia pública conjunta de NC DEQ sobre permisos de calidad de aire de Amazon y Duke Energy celebrada 31-jul-2026 con fuerte oposición vecinal)</t>
+          <t>Construcción (reinicio 68% completo; rehabilitación de la planta Mal Paso; primer concentrado previsto 4T2026)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); WFAE (https://www.wfae.org/energy-environment/2026-07-31/residents-push-back-against-large-amazon-data-center-project-during-packed-public-meeting)</t>
+          <t>Mexico Business News (https://mexicobusiness.news/mining/news/silverco-targets-late-2026-restart-past-producing-cusi-mine); Investing News Network (https://investingnews.com/silverco-mining-begins-underground-development-at-cusi-restart-remains-on-budget-and-on-schedule/)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Project Baccara</t>
+          <t>Kilbourne Graphite Project</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cerca de Surprise, Maricopa County, Arizona, EE.UU.</t>
+          <t>Nueva York, EE.UU.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Takanock LLC (respaldado por DigitalBridge)</t>
+          <t>Titan Mining Corporation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9150,71 +6273,71 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Permisos obtenidos/construcción inminente (160 acres; dos data centers de ~1 millón pies² c/u + planta de generación a gas natural de 700.2MW en 23.7 acres del sitio; Arizona Corporation Commission aprobó Certificado de Compatibilidad Ambiental 4-feb-2026; Maricopa County Board of Supervisors aprobó permiso de compatibilidad militar 4-1, 6-may-2026, pese a fuerte oposición vecinal por cercanía a Luke Air Force Base; pendiente permiso de calidad de aire EPA; construcción prevista 3T2026; primer edificio en línea 1T2028)</t>
+          <t>Ingeniería/Feasibility (planta demostrativa ya en producción/calificación de clientes 2026; decisión de construcción esperada fines de 2026/2027; proyecto integrado de 40,000 tpa)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); DCD (https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
+          <t>Junior Mining Network (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/2342-tsx/ti/199070-titan-mining-to-start-shipping-first-graphite-product-and-feasibility-study-underway-for-40-000-tpa-integrated-kilbourne-graphite-project.html)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Savannah River Site AI Data Center &amp; Energy Campus</t>
+          <t>Graphite Creek Project</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aiken, Carolina del Sur, EE.UU. (sitio federal DOE/NNSA)</t>
+          <t>Alaska, EE.UU.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DOE/NNSA (sitio federal)</t>
+          <t>Graphite One Inc.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Amentum (desarrollador seleccionado) / DC BLOX (socio de infraestructura)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Negociación de arrendamiento por fases (seleccionado ~20-23 jul-2026; campus de ~1GW con ~2GW de generación dedicada in-situ, iniciando con gas natural como puente hacia energía nuclear futura)</t>
+          <t>Permitting (permitting federal en curso bajo programa FAST-41, finalización prevista 29-sep-2026)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); Energy.gov (https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
+          <t>Permitting Council (https://www.permitting.gov/newsroom/success-stories/project-spotlight-graphite-creek-project)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pacifico Cedar Creek Power Campus</t>
+          <t>La Colorada Skarn Project</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cedar Creek, Bastrop County, Texas, EE.UU.</t>
+          <t>Zacatecas, México</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pacifico Energy (Pacifico Cedar Creek LLC); inquilino de centro de datos aún no revelado</t>
+          <t>Pan American Silver Corp.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9224,219 +6347,219 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Permisos/incentivos en revisión (solicitud de incentivos ante el Contralor de Texas presentada 24-jun-2026; campus de 2,842 acres; planta de gas natural on-site de 710MW para servir ~490MW de carga de centro de datos, esquema behind-the-meter)</t>
+          <t>Ingeniería/Feasibility (PEA revisada publicada mar-2026 para nueva planta de flotación selectiva de 15,000 t/d en área Candelaria oriente; gasto de capital 2026 estimado USD 92-95 millones, incluye "588 Decline Project" de 12.4 km de rampa; producción media proyectada de 19.1 Moz Ag/año en años pico)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Community Impact (https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
+          <t>Pan American Silver (https://panamericansilver.com/news/pan-american-announces-revised-pea-for-the-la-colorada-skarn-project-positions-la-colorada-as-a-future-top-tier-silver-mine/); SEC 6-K (https://www.sec.gov/Archives/edgar/data/771992/000077199226000031/a2026_03x24lacoloradapeaup.htm)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bosque County Data Center Campus</t>
+          <t>Lone Tree Plant (Refurbishment Autoclave/CIL)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Condado de Bosque, Texas, EE.UU. (~30 millas al sur de Dallas-Fort Worth)</t>
+          <t>Lovelock, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Energy Capital Partners (ECP) / KKR (asociación estratégica de US$50 mil millones)</t>
+          <t>i-80 Gold Corp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CyrusOne (JV de construcción/operación); Calpine Corp. (suministro de energía dedicada desde Thad Hill Energy Center)</t>
+          <t>Hatch (EPCM)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Construcción (primera inversión de la asociación estratégica ECP-KKR; campus de ~700,000 pies², inversión total cercana a US$4,000 millones, capacidad inicial de TI de 144MW sobre 190MW total; operación prevista 4T2026)</t>
+          <t>Construcción (obras tempranas y movilización de contratistas en curso; construcción mayor prevista 4T2026)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Data Centre Magazine (https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); Connect CRE (https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Prado AI Industrial Campus</t>
+          <t>Round Mountain Phase X — Planta de Paste Backfill</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ridgeland, área metropolitana de Jackson, Misisipi, EE.UU.</t>
+          <t>Nye County, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prado AI (desarrollador Gabriel Prado)</t>
+          <t>Kinross Gold Corporation</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>No especificado (paquetes de equipo móvil, ventiladores y planta CRF ya adjudicados)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Planeación (planta de gas natural dedicada de 350MW, fuera de la red eléctrica; Comisión de Servicios Públicos de Misisipi declinó emitir opinión declaratoria may-2026, interpretado por el desarrollador como luz verde para avanzar)</t>
+          <t>Construcción/Ingeniería detallada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WLBT (https://www.wlbt.com/2026/05/29/psc-wont-issue-opinion-hypothetical-electrical-plant-proposed-tech-site/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AVAIO Digital Little Rock Data Center &amp; Power Campus</t>
+          <t>Bald Mountain Redbird 2 — Planta SART (ácido/lixiviación)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Little Rock, Condado de Pulaski, Arkansas, EE.UU.</t>
+          <t>White Pine County, Nevada, EE.UU.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AVAIO Digital</t>
+          <t>Kinross Gold Corporation</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Contratista de ingeniería detallada ya seleccionado, no revelado en la fuente</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Construcción iniciando (760 acres; primera fase USD 6,000 millones, hasta USD 21,000 millones de desarrollo total; contrato con Entergy Arkansas por 150MW con infraestructura sustancial de gas natural en sitio; demanda potencial hasta 1GW; inicio de construcción 1T2026, energización jun-2027)</t>
+          <t>Ingeniería (básica ~50% completa)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/avaio-to-develop-6bn-data-center-campus-in-little-rock-arkansas/)</t>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Amazon Ridgeland Data Center</t>
+          <t>Bear Lodge Rare Earth Project</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ridgeland, Misisipi, EE.UU.</t>
+          <t>Crook County, Wyoming, EE.UU.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Amazon Web Services</t>
+          <t>Rare Element Resources Ltd. (afiliada de General Atomics/Synchron)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Entergy Mississippi (generación)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Planeación/Construcción (Entergy construyendo planta de gas natural dedicada para respaldar la operación; inversión total de AWS en Misisipi de USD 13,000 millones)</t>
+          <t>Permitting (designación FAST-41; aviso NEPA publicado en Federal Register 29-jul-2026)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mississippi Today (https://mississippitoday.org/2026/04/22/ridgeland-data-center-entergy-mississippi-power/)</t>
+          <t>Federal Register (https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Wise Innovation Hub / "Maverick Project" (OASIS)</t>
+          <t>Proyecto de Cobre Angangueo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Condado de Wise, Virginia, EE.UU. (Lonesome Pine Regional Business and Technology Park)</t>
+          <t>Angangueo, Michoacán, México</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wise Innovation Hub Venture LLC ("OASIS")</t>
+          <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Red Post Energy (desarrollo de energía)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Planeación/Letter of Intent (campus fasado a 10 años, ~2 millones de pies² respaldados por generación a gas natural en sitio; capacidad planeada hasta 600MW, fase inicial ~100MW)</t>
+          <t>Pre-desarrollo (en negociación de permisos con gobierno federal)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/red-post-energy-and-wise-innovation-hub-venture-oasis-execute-letter-of-intent-to-advance-power-infrastructure-for-major-data-center-development-in-southwest-virginia-302645511.html)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vantage Data Centers VA2</t>
+          <t>Proyecto de Cobre Chalchihuites</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sterling/Ashburn, Condado de Loudoun, Virginia, EE.UU.</t>
+          <t>Chalchihuites, Zacatecas, México</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9446,34 +6569,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Operación (único data center en Virginia con permiso de aire de la DEQ para generación a gas en sitio; opera 8 turbinas de gas natural 24/7 bajo modelo "bring your own power")</t>
+          <t>Pre-desarrollo (en negociación de permisos)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Virginia Mercury (https://virginiamercury.com/2026/07/20/data-centers-want-to-build-their-own-gas-turbines-would-that-skirt-state-renewable-energy-laws/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Fundamental Data "Ridgeline Power Plant" y Data Center</t>
+          <t>Modernización Complejo Metalúrgico Empalme</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Condado de Tucker, Virginia Occidental, EE.UU. (entre Davis y Thomas)</t>
+          <t>Empalme, Sonora, México</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fundamental Data LLC</t>
+          <t>Southern Copper Corporation (Grupo México)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9483,108 +6606,108 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Permisos (en litigio/apelación; permiso de calidad de aire R13-3713 aprobado por WV DEP para planta de gas y diésel en sitio de 500 acres; segunda apelación de grupos ambientalistas presentada en 2026)</t>
+          <t>Pre-desarrollo (en negociación de permisos; fundición existente a modernizar)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>WBOY (https://www.wboy.com/news/tucker/state-board-approves-tucker-county-data-center-air-quality-permit/)</t>
+          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NextEra/ExxonMobil Gas + CCS Plant para Data Centers</t>
+          <t>Coosa Graphite Project (Kellyton Graphite Plant)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sureste de EE.UU. (ubicación exacta no revelada, ~2,500 acres cerca de infraestructura de CO2 de Exxon)</t>
+          <t>Condado de Coosa, Alabama, EE.UU.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cliente hyperscaler aún sin contratar</t>
+          <t>Westwater Resources Inc.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NextEra Energy / ExxonMobil</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Anuncio/MOU (planta de gas natural de 1.2GW con captura y secuestro de carbono; comercialización a desarrolladores hyperscale prevista desde 1T2026)</t>
+          <t>Financiamiento/planeación (préstamo EXIM Bank de US$25 millones anunciado 7-ago-2026 para mina de grafito natural y planta de procesamiento, primera fuente de grafito natural producida en EE.UU.)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/nextera-teams-up-with-exxonmobil-to-develop-12gw-natural-gas-plant-to-power-us-data-center-sector/)</t>
+          <t>Yellowhammer News (https://yellowhammernews.com/trump-administration-announces-25-million-exim-loan-for-westwaters-coosa-county-graphite-plant/); EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NRG/LandBridge Delaware Basin Gas Plant</t>
+          <t>Expansión de Procesamiento de Tantalio/Niobio (Global Advanced Metals)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Condado de Reeves (Cuenca Delaware, Permian), Texas, EE.UU.</t>
+          <t>Pensilvania, EE.UU.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NRG Energy (planta) / LandBridge (sitio); cliente hyperscaler de nube/IA no revelado</t>
+          <t>Global Advanced Metals</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GE Vernova (turbinas); Kiewit-TIC (JV de EPC)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Términos comerciales acordados con hyperscaler, FID aún pendiente de aprobaciones internas (planta de ciclo combinado a gas natural de 1.2GW, USD 3,200 millones; operación comercial prevista fines de 2029)</t>
+          <t>Financiamiento/planeación (préstamo EXIM Bank de US$25 millones anunciado 7-ago-2026 para ampliar capacidad de procesamiento)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utility Dive (https://www.utilitydive.com/news/nrg-nears-12-gw-hyperscaler-deal-amid-texas-data-center-pause/827212/)</t>
+          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable); SME (https://me.smenet.org/trump-administration-to-back-three-mineral-projects-with-58-million-in-financing/)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Galaxy Digital Project Merlin</t>
+          <t>Boron Americas Project (Fort Cady)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McGregor, Condado de McLennan, Texas, EE.UU.</t>
+          <t>California, EE.UU.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Galaxy Digital</t>
+          <t>5E Advanced Materials</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9594,60 +6717,3117 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Planeación/permitting inicial (500 acres adquiridos; acuerdo de desarrollo aprobado por el ayuntamiento de McGregor 24-jun-2026; subestación eléctrica propia en construcción; enfriamiento de circuito cerrado, sin planta de gas on-site confirmada; Fase 1 de 74MW prevista 2028)</t>
+          <t>Financiamiento/planeación (préstamo EXIM Bank de US$8 millones anunciado 7-ago-2026 para proyecto de boro, lixiviación/procesamiento)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
+          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Nexus Fulcrum Gas Plant (TRIC)</t>
+          <t>Brook Mine (tierras raras/minerales críticos de carbón)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tahoe-Reno Industrial Center, Condado de Storey, Nevada, EE.UU.</t>
+          <t>Ranchester/Sheridan, Wyoming, EE.UU.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nexus Fulcrum LLC (abastecerá al hub industrial/de centros de datos de TRIC, donde operan Switch, Google, Tract, entre otros)</t>
+          <t>Ramaco Resources</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Hatch Associates Consultants (ingeniería/estudio)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Permitting (solicitud regulatoria presentada ante reguladores estatales de energía de Nevada para planta de gas natural de 510MW)</t>
+          <t>Ingeniería/Construcción de planta piloto (Hatch publicó Initial Assessment Report jul-2026 con capex preliminar ~US$3,200 millones + US$800 millones de contingencia, VPN interno ~US$8,000 millones; planta piloto en construcción desde oct-2025; primer procesamiento de concentrados de óxido de tierras raras para la Defense Logistics Agency, ago-2026; construcción de planta comercial podría iniciar fines de 2026, producción comercial 2028)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>The Nevada Independent (https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/ramaco-resources-releases-hatch-report-and-shareholder-letter-on-exploratory-brook-mine-critical-minerals-project-302838319.html); Mining.com (https://www.mining.com/ramaco-eyes-ree-stockpile-at-wyoming-mine/)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Dewey-Burdock Uranium ISR Project</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fall River/Custer Counties, Dakota del Sur, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>enCore Energy (Powertech USA)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Construcción autorizada/permitting (BLM autorizó inicio de construcción de infraestructura —caminos, pozos de monitoreo, líneas eléctricas— jun-2026; NRC renovó la licencia, publicado en Federal Register 7-ago-2026; pendiente permiso estatal de Dakota del Sur, proceso reiniciado tras 13 años de pausa)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/encore-energy-receives-bureau-of-land-management-authorization-to-begin-construction-at-dewey-burdock-uranium-project-302804230.html); Federal Register (https://www.federalregister.gov/documents/2026/08/07/2026-16132/powertech-usa-inc-dewey-burdock-uranium-in-situ-recovery-project-license-renewal)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente/Dueño</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>EPC/Contratista</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fase</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Stargate Frontier Campus</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Shackelford County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle / SoftBank</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Construcción (rompimiento de tierra formal completado; 1,200 acres/10 edificios/1.4GW; VoltaGrid aprobado para operar 210 generadores de gas industrial, 700MW combinados, permitiendo operación fuera de la red pública; primera instalación en servicio 2S2026)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); Construction Owners (https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stargate Milam County (fast-build)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Milam County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SB Energy (SoftBank)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Epoch AI (https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Stargate Abilene Campus</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Abilene, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Crusoe / DPR Construction</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Microsoft Pecos Data Center Campus (Project Kilby)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pecos/Reeves County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Chevron (acuerdo definitivo de suministro de gas a 20 años firmado 22-jun-2026, sitio &gt;2,000 acres); turbinas mayoritariamente GE Vernova de gran marco + Solar Turbines (Caterpillar) para capacidad adicional</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Construcción temprana/Ingeniería (capacidad rampa a 2.67GW; flujo de energía previsto fines de 2028; FID de la planta esperada fines de 2026)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chevron (https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CloudHQ Querétaro (6 campus, incl. Campus Colón)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Colón y otras ubicaciones, Querétaro, México</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CloudHQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Permisos/preparación de sitio (confirmado oficialmente por gobierno federal 7-jul-2026 bajo Plan México; inversión US$4,800M, 52 hectáreas, 900MW; subestación propia de 2GW prevista Q2 2027)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gobierno de México (https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Meta Hyperion Data Center</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Richland Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Turner Construction / DPR Construction / Mortenson</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Construcción (escalado confirmado a 5GW/USD 50+ mil millones, financiado fuera de balance vía JV con Blue Owl Capital; primeros 2GW en línea 2030, 5GW completo ~2032, finalización 2036; Entergy ahora respalda con 7 plantas adicionales de ciclo combinado a gas, 5,200+ MW, ~240 millas de transmisión 500kV y 3 baterías de red)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Global Data Center Hub (https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers NV1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Storey County, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CloudBurst San Marcos Data Center I</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>San Marcos/New Braunfels, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CloudBurst Data Centers</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evolve (eVOLVE Data Center Solutions)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Prometheus Hyperscale Dallas Campus</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Entre Talty y Post Oak Bend City, Kaufman County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Prometheus Hyperscale</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>No especificado (socio energía: Engie)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ingeniería/construcción temprana (campus de 200MW/4 edificios; estrategia behind-the-meter con motores de gas Jenbacher J620 + almacenamiento en baterías de Engie; primera instalación 2026, fases hasta 2028)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GW Ranch Power Campus</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pecos County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pacifico Energy; inquilino confirmado: Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Construcción de edificios de centro de datos iniciada (TCEQ emitió permiso de aire final para la planta —35 turbinas de gas natural, hasta 33 millones de toneladas de CO2/año—; Amazon presentó a inicios de ago-2026 permisos de construcción para 3 edificios de centro de datos —"Pecos County Data Center", Buildings A/B/C, ~189,060 pies² c/u, ~US$300M c/u—; construcción de edificios prevista ago-dic 2026; primera entrega de energía prevista 1T2027, operando inicialmente fuera de la red de ERCOT)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Business Wire (https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); Tom's Hardware (https://www.tomshardware.com/tech-industry/data-centers/amazons-new-7-65gw-texas-ai-data-center-power-plant-could-become-the-largest-source-of-co2-pollution-in-the-us-custom-35-turbine-gas-plant-authorized-to-emit-33-million-tons-of-annual-greenhouse-gases)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Amazon Mattermeade Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Caroline/Spotsylvania County, Virginia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fermaca Digital City (+ gasoducto + planta de ciclo combinado)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Durango, Durango, México</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grupo Fermaca (inquilino AI hyperscaler sin confirmar)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Permisos/negociación avanzada (inversión total US$3.7 mil millones: US$2.7B centro de datos + US$1B planta de fertilizantes Fermachem; gasoducto de 160km desde Texas; planta de ciclo combinado on-site de 350MW para alimentar data center de 250MW; Congreso de Durango aprobó donación de 50 hectáreas)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mexico News Daily (https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); DCD (https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Circe Energy West Texas AI Infrastructure Campus</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cuenca Pérmica, West Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Circe Energy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No especificado (gen-sets Cummins)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ingeniería/procurement</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Project Jupiter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Santa Teresa/Sunland Park, Doña Ana County, Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BorderPlex Digital Assets/Stack (inquilino Oracle/OpenAI)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No especificado (rediseño: hasta 2.45GW de celdas de combustible Bloom Energy, reemplazando turbinas de gas/diésel)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Construcción activa con riesgo regulatorio (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 14-jul-2026; NMED pospuso la decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas y programó audiencia pública para 19-oct-2026; meta de entrada en servicio ago-2026 en riesgo)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Source NM (https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PowerPlay AI "Greater Abilene" Data Center</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Área metropolitana de Abilene, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PowerPlay AI (JV con socio Neocloud cotizado en Nasdaq, sin nombre público)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>IPP en proceso de RFP (aún sin seleccionar)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ejecución activa post-adquisición de terreno (400MW behind-the-meter iniciales; arranque objetivo 2028)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Liberty Energy/PowerBridge "Alpha Digital Campus"</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Condado de Reeves, Texas, EE.UU. (cerca del hub de gas Waha)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PowerBridge LLC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Liberty Power Innovations (subsidiaria de Liberty Energy, JV)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>JV firmada/desarrollo temprano (~3,400 acres; primera fase &gt;300MW, primera entrega de energía prevista 4T2027; campus completo 2GW)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>New Era Energy &amp; Digital Hub</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lea County, Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New Era Energy &amp; Digital</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Planeación temprana (opción de terreno)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PowerMag (https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Texas Critical Data Centers (TCDC) Campus</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ector County (cerca de Odessa), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New Era Energy &amp; Digital</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Stargate Lordstown</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lordstown, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle / SoftBank</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SB Energy (SoftBank)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Construcción (rompimiento de tierra)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Stargate Wisconsin</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wisconsin, EE.UU. (ubicación exacta no divulgada)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle / SoftBank</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers (en sociedad con Oracle)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo temprano</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AWS Región Digital Querétaro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Querétaro, México</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Construcción/desarrollo (anunciado 2025, en curso)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mexico News Daily (https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Stargate Michigan (Saline Barn Campus)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Saline Township, Michigan, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OpenAI / Oracle (desarrollador: Related Digital)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Walbridge</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Applied Digital AI Factory Campuses (Polaris Forge, Ellendale/Harwood; nuevo campus Oliver County)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>North Dakota, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Applied Digital / Base Electron</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Babcock &amp; Wilcox (generación); Siemens Energy (turbinas de vapor)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Construcción (Polaris Forge 1 Edificio 2 Fase 1 alcanzó Ready-for-Service 1-jul-2026, 175MW operativos; acuerdo de uso de caminos firmado 10-jul-2026 para tercer campus cerca de Center, Oliver County)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Valley News Live (https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI-GDC / Cipre Holding "Green Data Center"</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>San Pedro Garza García, Nuevo León, México</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AI-GDC + Cipre Holding (Nvidia, socio tecnológico)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo temprano</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Energy Magazine MX (https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CleanArc Data Centers VA1 Campus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Caroline County, Virginia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CleanArc Data Centers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Construction Dive (https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Joule Energy and Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Millard County (Holden), Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Joule Capital Partners</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KSL (https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Amazon Montgomery County Campus</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Anuncio/permisos</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Governor.mo.gov (https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Google Montgomery County Campus</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>New Florence, Montgomery County, Missouri, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Anuncio/permisos</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STLPR (https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Big Digital Energy / 10NetZero AI Datacenter Campus</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hood County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Big Digital Energy + 10NetZero (JV)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Planeación/adquisición de sitio</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Williams "Project Socrates"</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>New Albany, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Meta (vía Sidecat, LLC)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Williams Companies / Will-Power</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Construcción (financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR cerrado jul-2026 por 49% de participación no controladora en 5 proyectos Power Innovation de Williams; Socrates Norte/Sur, 400MW combinados, en servicio 3T/4T2026)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Meta El Paso Campus (expansión)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>El Paso, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Permisos</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SB Energy/SoftBank PORTS Technology Campus</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pike County, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SB Energy (SoftBank) / DOE / AEP Ohio</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Planeación avanzada (SB Energy construirá 9.2GW de generación a gas natural, financiamiento de US$33.3 mil millones por SoftBank, más US$4.2 mil millones en transmisión; 26-jul-2026 trascendió que Nvidia negocia garantía financiera de hasta US$250 mil millones para que OpenAI arriende el sitio, primera fase de 800MW en 2028)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Williams "Apollo" Power Generation Project</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Wood County (Middleton Township), Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Meta Platforms (planta: Will-Power OH, LLC / Williams Companies)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Construcción (aprobado por Ohio Power Siting Board feb-2026; financiamiento de USD 5.34 mil millones cerrado con Blackstone/Apollo/KKR jul-2026)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Williams "Aquila" Power Project</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Utah, EE.UU. (condado no revelado)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cliente de centro de datos no revelado (planta: Williams Companies)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Construcción/desarrollo (520MW; entrada en servicio prevista H1 2027; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Williams Companies (https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CleanCore/HST Technologies West Texas Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>West Texas, EE.UU. (condado no revelado)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CleanCore Solutions (ZONE) / HST Technologies (JV)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cierre de transacción (200MW fase inicial, jul-2026; expansión a 500MW+ prevista para 2030)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tallgrass AI Data Center Campus (Project Jade)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Condado de Laramie, Wyoming, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Black Hills Corp. (desarrollador directo) / Tallgrass / cliente de gran carga no revelado (comprometió US$200M+ en hitos de construcción)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No especificado (Crusoe Energy se retiró como desarrollador, jun-2026, a solicitud del cliente)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Desarrollo CONTINÚA con nuevo desarrollador (Crusoe salió del proyecto pero Black Hills Corp. avanza directamente con el cliente; permisos locales de Wyoming vigentes; 1.8GW inicial escalable a 10GW)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cowboy State Daily (https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Core Scientific Pecos Campus (expansión IA)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pecos, Reeves County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Core Scientific</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Construcción (primera nave de datos en construcción vertical; expansión a 1.5GW bruto; primera capacidad prevista inicios de 2027)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HPCwire (https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Stratos Project / Wonder Valley</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Condado de Box Elder (Hansel Valley), Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>O'Leary Digital (Kevin O'Leary)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Permisos/desarrollo temprano (aprobado por comisión del condado may-2026; hasta 9GW planeados; alimentado por gasoducto Ruby; obras tempranas previstas otoño 2026)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Utah News Dispatch (https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Fermi America Project Matador</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Carson County (Amarillo), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fermi America</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas); Energy Transfer (interconexión de gasoducto)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>StockTitan (https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NextEra Texas Power Generation Hub</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Anderson County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NextEra Energy Resources</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aprobado/planeación (5.2GW a gas; primera fase en línea 2028; data center asociado aún no contratado)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>KLTV (https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mon Power/FirstEnergy Gas Plant (Maidsville Energy Center)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Monongalia County, Virginia Occidental, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mon Power (FirstEnergy)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Planeación/regulatorio (USD 2.4 mil millones, 1,200MW; audiencia probatoria concluida 16/17-jul-2026 ante PSC; Mon Power confirmó pláticas con 3 desarrolladores de data centers no identificados; op. comercial prevista 31-dic-2031)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>WV MetroNews (https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IEP Greene County Data Center &amp; Power Plant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Greene County, Pensilvania, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>International Electric Power</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Permisos (aprobación preliminar de desarrollo de terreno; planta CCGT de 944MW; COD previsto Q1 2029)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Utility Dive (https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AWS "Project Eagle"</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Boling, Wharton County, Texas, EE.UU. (SO de Houston)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Permisos/Construcción inminente (confirmado inicio de construcción 1-ago-2026; 3 edificios completados ene-2027, 4to edificio ago-2027; USD 1.2 mil millones, ~2,700 acres)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Wharton Post (https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Crusoe/Lancium Childress Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Condado de Childress, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Crusoe (operador) / Lancium (infraestructura energética)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Anuncio/planeación (construcción prevista 3T2026; campus de 1.0-1.4GW)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Crusoe (https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Williams "Neo" Power Innovation Project</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ohio, EE.UU. (sitio exacto no revelado)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cliente de centro de datos no revelado</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Planeación/desarrollo (682MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Williams "Socrates the Younger" Power Innovation Project</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>New Albany, Ohio, EE.UU. (adyacente a Project Socrates)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Meta Platforms (vía Sidecat, LLC)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Williams Companies</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Construcción (aprobada por Ohio Power Siting Board 9-jun-2026; 340MW; en servicio 2S2028; parte del financiamiento de USD 5.34 mil millones de Blackstone/Apollo/KKR)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PowerMag (https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Crusoe/Google "Goodnight Campus"</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Condado de Armstrong (Claude), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Google (negociación de arrendamiento) / Crusoe Energy (desarrollador)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Construcción (4 de 7 edificios en obra; campus de USD 29 mil millones, ~1,030MW; planta de gas propia de 933MW en trámite ante TCEQ, respaldada por parque eólico Goodnight de 265.5MW)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Aterio (https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VoltaGrid/Serverfarm Covington</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Condado de Newton (Covington), Georgia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Serverfarm</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VoltaGrid (planta de energía "pop-up", 33 motores de combustión interna)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Construcción REANUDADA (tras orden de suspensión de la agencia ambiental de Georgia -EPD- del 2-jul-2026 por construir sin permisos; a 31-jul-2026 la construcción de la planta de 90MW está en marcha de nuevo, con 6 de 33 motores a gas ya instalados)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AJC (https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); Inside Climate News (https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Stark Power/Sagebrush Infrastructure Partners (SAGE)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Múltiples sitios, EE.UU. Central (ubicaciones no reveladas)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Stark Power (adquirió SAGE, 8-jun-2026)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Adquisición/planeación temprana (portafolio de 5 campus hyperscale con generación de gas co-localizada, 5.6GW agregados)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Homer City Energy Campus</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Condado de Indiana, Pensilvania, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Homer City Redevelopment (HCR)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Kiewit Power Constructors Co.; turbinas GE Vernova (7x 7HA.02 con capacidad de hidrógeno)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Construcción (excavación/demolición completadas; planta de gas de 4.5GW, la más grande planeada en EE.UU.; primeras entregas de turbinas 2026, operación comercial 2027; Amazon confirmó públicamente estar en "discusiones comerciales" activas con HCR para ubicar un data center adyacente a la planta, avanzando desde el rumor previo, aún sin acuerdo definitivo firmado)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation); Indiana Gazette (https://www.indianagazette.com/local_news/amazon-hcr-are-conducting-commercial-discussions-on-data-center/article_733afa63-9d58-42d0-b16e-6dc61b71689b.html)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Nebius Vineland AI Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Vineland, Nueva Jersey, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nebius Group (cómputo entregado a Microsoft bajo acuerdo de USD 17.4 mil millones)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>No especificado — posible cambio de alcance a celdas de combustible Bloom Energy (acuerdo maestro Nebius-Bloom Energy de USD 2,600 millones, 21-may-2026, hasta 328MW; fuentes de menor confianza lo vinculan a Vineland como respuesta a problemas de permisos de aire NJDEP con planta vecina Corning — confirmación directa pendiente)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; NJDEP en revisión hacia aprobación final a mediados jul-2026; meta de entrega nov-2026 en riesgo)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TerraVolt Infrastructure AI Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sureste de Idaho, EE.UU. (sobre gasoducto Northwest Natural Gas Pipeline)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TerraVolt Infrastructure, Inc. (subsidiaria de CalEthos, Inc.)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ingeniería/Planeación (acuerdo de suministro de gas natural firmado, 55,000 MMBtu/día, para planta on-site de 200-240MW)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CyrusOne SAT14A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Castroville, San Antonio, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CyrusOne (sin arrendatario asignado aún)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ingeniería/Permisos (6to campus en San Antonio, 11vo en Texas; USD 500 millones, 460,000 pies²; inicio de construcción previsto dic-2026)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EdgeConneX PowerConneX New Albany Energy Center (I, II y III)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>New Albany, Licking County, Ohio, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EdgeConneX (propiedad de EQT Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>No especificado (desarrollado vía afiliada PowerConneX)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Construcción (PowerConneX I, 120MW, certificado OPSB 22-jul-2025, construcción iniciada sep-2025, operación comercial posible 3T2026; PowerConneX II, 216MW, solicitado ante OPSB, operación comercial objetivo 2T2027; PowerConneX III, 430MW, notificación previa ante OPSB abr-2026, elevando capacidad total del sitio a ~766MW de gas)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); BeBeez (https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>xAI Colossus 2/Colossus 3 ("MACROHARDRR")</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Southaven, Misisipi / Memphis, Tennessee, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Operando parcialmente/en expansión con crisis regulatoria activa (59 turbinas de gas natural operando en Southaven, la mayoría sin permisos federales de Clean Air Act; demanda de NAACP/Southern Environmental Law Center/Earthjustice desde abr-2026; xAI recibió aprobación para 41 turbinas de gas adicionales, ~1.2GW, en el sitio de Southaven para alimentar Colossus 2 y el próximo Colossus 3; DOJ intervino en litigio citando uso de Grok por el Departamento de Defensa; capacidad total del sitio creciendo hacia 2GW+ en tres edificios)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Technology.org (https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); DCD (https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Applied Digital "Delta Forge 1" (planta de gas dedicada Cleco 756MW)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rapides Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cleco Power (planta de gas dedicada de 756MW)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Construcción (campus de USD 3.6 mil millones/430MW, la mayor carga individual jamás atendida por Cleco; rompimiento de tierra ene-2026; operaciones iniciales objetivo mediados de 2027)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rubix Data Centers (Submer Group)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Russell, Kentucky, EE.UU. (antiguo sitio de acería AK Steel)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rubix Data Centers / Submer Group</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Propuesta/planeación temprana (hasta 2GW, US$8-12 mil millones; moratoria municipal sobre solicitudes de data centers podría complicar el proyecto; fuente de energía aún no especificada)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kentucky Lantern (https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QTS/Lancium Hall County Campus</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cerca de Turkey, Condado de Hall, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lancium (dueño de sitio/energía) / QTS Data Centers (construcción/operación)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lancium (autoabastecimiento solar+baterías; interconexión a red de 1GW; sin planta de gas confirmada)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Anuncio/desarrollo temprano (US$10 mil millones, hasta 11 edificios en 465 acres)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Anthropic/Nexus Hubbard Campus</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hubbard, Condado de Hill, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Anthropic (operado por Nexus Data Centers; respaldo financiero de Google)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Construcción iniciada (primera fase 500-612MW prevista 2026, ampliable a ~7.2-7.7GW; planta de gas natural behind-the-meter cerca de gasoducto principal; financiamiento avanzado: banca liderada por Morgan Stanley en negociaciones finales para prestar USD 15 mil millones a Nexus Data Centers —incluye préstamo puente de USD 14 mil millones más línea de crédito revolvente—; Google otorgaría garantías sobre obligaciones de arrendamiento y pago de energía de Anthropic a cambio de ~20% de participación accionaria en el proyecto combinado)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); Construction Review (https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); CNBC (https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Stillwater Technology Park</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lovejoy, Condado de Clayton, Georgia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Stillwater Development, LLC (cliente hyperscaler final no revelado)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Permisos ("development of regional impact" presentado ante el estado; hasta 15 edificios, 1.25GW, US$13 mil millones; generación de energía aún no confirmada, contempla interconexión con Central Georgia EMC)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Paducah Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Antiguo sitio de enriquecimiento de uranio del DOE, Paducah, Kentucky, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Coalición: Brookfield / NextEra Energy / Big Rivers Electric / Jackson Purchase Energy Cooperative / Paducah Power System</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Anuncio/desarrollo temprano (hasta 1.8GW; incluye nueva planta de gas natural de ~2GW y hasta 2.6GW de almacenamiento en baterías; ~US$100 mil millones de inversión privada total, el mayor proyecto de desarrollo económico en la historia de Kentucky)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bloomberg (https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); Kentucky Lantern (https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OpenAI "Project Camellia"</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Condado de Effingham, cerca de Savannah, Georgia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>No especificado (energía: Georgia Power, expansión de ~5.8GW de generación a gas natural)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Anuncio/preconstrucción (carga de 3.2GW, ~US$20-30 mil millones de inversión; capacidad disponible 2028-2032; OpenAI cubre el costo total de la infraestructura)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Axios (https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); DCD (https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Stream Data Centers "Project Saltworks"</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Condado de Young (cerca de Graham), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Headwaters Site Development (afiliada de Stream US Data Centers)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>No especificado (activos de interconexión de energía adquiridos de Plug Power)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Preconstrucción/diseño de sitio (~890 acres, ~US$10 mil millones, 15 edificios planeados; construcción no prevista antes de inicios de 2027; enfrenta oposición comunitaria local)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); Olney Enterprise (https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Eagle Rock Partners "Meridian Technology Park"</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Cerca de Taylorville, Condado de Christian, Illinois, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Eagle Rock Partners</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>No especificado (PPA con Kindle Energy LLC para 1,000-1,100MW del proyecto de planta de gas Lincoln Land Energy Center, cerca de Pawnee, desarrollado por EmberClear)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Planeación muy temprana (aún sin solicitud de zonificación presentada; ~US$6 mil millones, 10 edificios planeados; energía esperada para 2029)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Illinois Times (https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Creekstone Energy "Delta Gigasite"</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cerca de Delta, Condado de Millard, Utah, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Creekstone Energy LLC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Zeo Energy (socio de energía)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Construcción (rompimiento de tierra dic-2025; meta de 10GW de capacidad total —2GW de gas on-site + 6GW solar + posibles 1.8GW de la planta de carbón inactiva Intermountain—; &gt;300MW de capacidad a gas prevista en línea 1S2027; US$17 mil millones comprometidos)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>KSL (https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); Utah GOED (https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Amazon Richmond County Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Richmond County (Hamlet), Carolina del Norte, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Construcción (rompimiento de tierra completado jun-2026; campus de USD 10 mil millones, hasta 20 edificios en 800 acres; ubicado junto al complejo Sherwood H. Smith Jr. de Duke Energy —2.24GW de turbinas de gas natural existentes—; Duke Energy presentó formalmente permiso de aire para la turbina adicional de 240MW específica para este centro de datos, construcción prevista fines de 2027, en línea fines de 2029; generadores diésel temporales de Duke Energy instalándose en terreno de Amazon como respaldo mientras se construye infraestructura permanente; estudio de NC State University sobre impacto de contaminación del aire publicado ago-2026; SELC/NAACP amplían señalamientos sobre posible evasión de la Clean Air Act)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); DCD - Clean Air Act (https://www.datacenterdynamics.com/en/news/amazon-duke-energy-accused-of-evading-clean-air-act-at-under-development-data-center-in-hamlet-north-carolina/); NCSU (https://cnr.ncsu.edu/news/2026/08/richmond-county-data-center-air-pollution/)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Project Baccara</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cerca de Surprise, Maricopa County, Arizona, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Takanock LLC (respaldado por DigitalBridge)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Permisos obtenidos/construcción inminente (160 acres; dos data centers de ~1 millón pies² c/u + planta de generación a gas natural de 700.2MW en 23.7 acres del sitio; Arizona Corporation Commission aprobó Certificado de Compatibilidad Ambiental 4-feb-2026; Maricopa County Board of Supervisors aprobó permiso de compatibilidad militar 4-1, 6-may-2026, pese a fuerte oposición vecinal por cercanía a Luke Air Force Base; pendiente permiso de calidad de aire EPA; construcción prevista 3T2026; primer edificio en línea 1T2028)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); DCD (https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Savannah River Site AI Data Center &amp; Energy Campus</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Aiken, Carolina del Sur, EE.UU. (sitio federal DOE/NNSA)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DOE/NNSA (sitio federal)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Amentum (desarrollador seleccionado) / DC BLOX (socio de infraestructura)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Negociación de arrendamiento por fases (seleccionado ~20-23 jul-2026; campus de ~1GW con ~2GW de generación dedicada in-situ, iniciando con gas natural como puente hacia energía nuclear futura)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); Energy.gov (https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pacifico Cedar Creek Power Campus</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cedar Creek, Bastrop County, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Pacifico Energy (Pacifico Cedar Creek LLC); inquilino de centro de datos aún no revelado</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Permisos/incentivos en revisión (solicitud de incentivos ante el Contralor de Texas presentada 24-jun-2026; campus de 2,842 acres; planta de gas natural on-site de 710MW para servir ~490MW de carga de centro de datos, esquema behind-the-meter)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Community Impact (https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bosque County Data Center Campus</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Condado de Bosque, Texas, EE.UU. (~30 millas al sur de Dallas-Fort Worth)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Energy Capital Partners (ECP) / KKR (asociación estratégica de US$50 mil millones)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CyrusOne (JV de construcción/operación); Calpine Corp. (suministro de energía dedicada desde Thad Hill Energy Center)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Construcción (primera inversión de la asociación estratégica ECP-KKR; campus de ~700,000 pies², inversión total cercana a US$4,000 millones, capacidad inicial de TI de 144MW sobre 190MW total; operación prevista 4T2026)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Data Centre Magazine (https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); Connect CRE (https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Prado AI Industrial Campus</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ridgeland, área metropolitana de Jackson, Misisipi, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Prado AI (desarrollador Gabriel Prado)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Planeación (planta de gas natural dedicada de 350MW, fuera de la red eléctrica; Comisión de Servicios Públicos de Misisipi declinó emitir opinión declaratoria may-2026, interpretado por el desarrollador como luz verde para avanzar)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>WLBT (https://www.wlbt.com/2026/05/29/psc-wont-issue-opinion-hypothetical-electrical-plant-proposed-tech-site/)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AVAIO Digital Little Rock Data Center &amp; Power Campus</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Little Rock, Condado de Pulaski, Arkansas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AVAIO Digital</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Construcción iniciando (760 acres; primera fase USD 6,000 millones, hasta USD 21,000 millones de desarrollo total; contrato con Entergy Arkansas por 150MW con infraestructura sustancial de gas natural en sitio; demanda potencial hasta 1GW; inicio de construcción 1T2026, energización jun-2027)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/avaio-to-develop-6bn-data-center-campus-in-little-rock-arkansas/)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Amazon Ridgeland Data Center</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ridgeland, Misisipi, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Entergy Mississippi (generación)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Planeación/Construcción (Entergy construyendo planta de gas natural dedicada para respaldar la operación; inversión total de AWS en Misisipi de USD 13,000 millones)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mississippi Today (https://mississippitoday.org/2026/04/22/ridgeland-data-center-entergy-mississippi-power/)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Wise Innovation Hub / "Maverick Project" (OASIS)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Condado de Wise, Virginia, EE.UU. (Lonesome Pine Regional Business and Technology Park)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wise Innovation Hub Venture LLC ("OASIS")</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Red Post Energy (desarrollo de energía)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Planeación/Letter of Intent (campus fasado a 10 años, ~2 millones de pies² respaldados por generación a gas natural en sitio; capacidad planeada hasta 600MW, fase inicial ~100MW)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/red-post-energy-and-wise-innovation-hub-venture-oasis-execute-letter-of-intent-to-advance-power-infrastructure-for-major-data-center-development-in-southwest-virginia-302645511.html)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers VA2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sterling/Ashburn, Condado de Loudoun, Virginia, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Operación (único data center en Virginia con permiso de aire de la DEQ para generación a gas en sitio; opera 8 turbinas de gas natural 24/7 bajo modelo "bring your own power")</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Virginia Mercury (https://virginiamercury.com/2026/07/20/data-centers-want-to-build-their-own-gas-turbines-would-that-skirt-state-renewable-energy-laws/)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fundamental Data "Ridgeline Power Plant" y Data Center</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Condado de Tucker, Virginia Occidental, EE.UU. (entre Davis y Thomas)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fundamental Data LLC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Permisos (en litigio/apelación; permiso de calidad de aire R13-3713 aprobado por WV DEP para planta de gas y diésel en sitio de 500 acres; segunda apelación de grupos ambientalistas presentada en 2026)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>WBOY (https://www.wboy.com/news/tucker/state-board-approves-tucker-county-data-center-air-quality-permit/)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>NextEra/ExxonMobil Gas + CCS Plant para Data Centers</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sureste de EE.UU. (ubicación exacta no revelada, ~2,500 acres cerca de infraestructura de CO2 de Exxon)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Cliente hyperscaler aún sin contratar</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NextEra Energy / ExxonMobil</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Anuncio/MOU (planta de gas natural de 1.2GW con captura y secuestro de carbono; comercialización a desarrolladores hyperscale prevista desde 1T2026)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DCD (https://www.datacenterdynamics.com/en/news/nextera-teams-up-with-exxonmobil-to-develop-12gw-natural-gas-plant-to-power-us-data-center-sector/)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>NRG/LandBridge Delaware Basin Gas Plant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Condado de Reeves (Cuenca Delaware, Permian), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NRG Energy (planta) / LandBridge (sitio); cliente hyperscaler de nube/IA no revelado</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GE Vernova (turbinas); Kiewit-TIC (JV de EPC)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Términos comerciales acordados con hyperscaler, FID aún pendiente de aprobaciones internas (planta de ciclo combinado a gas natural de 1.2GW, USD 3,200 millones; operación comercial prevista fines de 2029)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Utility Dive (https://www.utilitydive.com/news/nrg-nears-12-gw-hyperscaler-deal-amid-texas-data-center-pause/827212/)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Galaxy Digital Project Merlin</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>McGregor, Condado de McLennan, Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Galaxy Digital</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Planeación/permitting inicial (500 acres adquiridos; acuerdo de desarrollo aprobado por el ayuntamiento de McGregor 24-jun-2026; subestación eléctrica propia en construcción; enfriamiento de circuito cerrado, sin planta de gas on-site confirmada; Fase 1 de 74MW prevista 2028)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PR Newswire (https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Nexus Fulcrum Gas Plant (TRIC)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tahoe-Reno Industrial Center, Condado de Storey, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nexus Fulcrum LLC (abastecerá al hub industrial/de centros de datos de TRIC, donde operan Switch, Google, Tract, entre otros)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Permitting (solicitud regulatoria presentada ante reguladores estatales de energía de Nevada para planta de gas natural de 510MW)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>The Nevada Independent (https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Dove Creek Technology Campus</t>
         </is>
       </c>
@@ -9668,17 +9848,54 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Permitting temprano (solicitud de permiso de aire ante TCEQ presentada 10-ago-2026, hasta 2,409 MW dedicados; sitio de ~1,240 acres construibles; construcción proyectada primavera/verano 2027 si avanza)</t>
+          <t>Permitting temprano (solicitud de permiso de aire ante TCEQ presentada 10-ago-2026, hasta 2,409 MW dedicados; sitio de ~1,240 acres construibles; construcción proyectada primavera/verano 2027 si avanza; diputado estatal Drew Darby solicitó formalmente audiencia pública de TCEQ ante oposición vecinal)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Angelo Live (https://sanangelolive.com/news/san-angelo/2026-08-10/dove-creek-data-center-has-applied-tceq-permit-heres-what-know); Concho Observer (https://conchoobserver.com/data-center-permits-detail-proposed-air-quality-footprint/)</t>
+          <t>San Angelo Live (https://sanangelolive.com/news/san-angelo/2026-08-10/dove-creek-data-center-has-applied-tceq-permit-heres-what-know); Concho Valley Homepage (https://www.conchovalleyhomepage.com/news/local-news/concho-valley-data-centers/darby-calls-for-clarity-from-beacon-data-centers-requests-public-tceq-meeting/)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Invitium (JV PPL–Blackstone) — cartera de generación para data centers</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pensilvania, EE.UU. (múltiples sitios)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PPL Corporation (51%) / Blackstone Infrastructure (JV)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Desarrollo de cartera (JV aseguró reservas de más de 5GW de turbinas de gas de ciclo combinado y sitios con capacidad para hasta 14GW de generación nueva en Pensilvania; parte del pipeline de PPL de 31.8GW en data centers, 11GW ya con acuerdos firmados)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Utility Dive (https://www.utilitydive.com/news/ppl-blackstone-joint-venture-secures-5-gw-of-gas-turbines-for-data-centers/827408/); DCD (https://www.datacenterdynamics.com/en/news/pennsylvania-utility-ppl-sees-advanced-stage-data-center-pipeline-grow-to-318gw/)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,9 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,50 +416,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -497,7 +493,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fluor newsroom (https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx); Tech Times (https://www.techtimes.com/articles/323235/20260805/trumps-flagship-texas-refinery-races-permit-deadline-after-326b-grid-loan.htm)</t>
+          <t>[Fluor newsroom](https://newsroom.fluor.com/news-releases/news-details/2026/Fluor-Awarded-Contract-to-Engineer-and-Design-the-America-First-Refining-Facility-in-Brownsville-Texas/default.aspx); [Tech Times](https://www.techtimes.com/articles/323235/20260805/trumps-flagship-texas-refinery-races-permit-deadline-after-326b-grid-loan.htm)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +530,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FuelCellsWorks (https://fuelcellsworks.com/2026/08/06/clean-energy/cf-industries-to-begin-construction-of-3-7bn-louisiana-blue-ammonia-plant); gasworld (https://www.gasworld.com/story/cf-industries-to-begin-construction-of-4bn-louisiana-blue-ammonia-project/2256572.article/)</t>
+          <t>[FuelCellsWorks](https://fuelcellsworks.com/2026/08/06/clean-energy/cf-industries-to-begin-construction-of-3-7bn-louisiana-blue-ammonia-plant); [gasworld](https://www.gasworld.com/story/cf-industries-to-begin-construction-of-4bn-louisiana-blue-ammonia-project/2256572.article/)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -571,7 +567,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AllStream Insiders (https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
+          <t>[AllStream Insiders](https://allstreaminsiders.com/us-exxonmobil-may-build-cracker-pe-plant-in-texas-with-an-8-6-billion-investment/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -608,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BIC Magazine (https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
+          <t>[BIC Magazine](https://www.bicmagazine.com/departments/operations/cpchem-golden-triangle-polymers-facility-startup-phase/)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -645,7 +641,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>East Daley (https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
+          <t>[East Daley](https://eastdaley.com/media-and-news/the-race-is-on-to-build-permian-processing)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -682,7 +678,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Techint (https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
+          <t>[Techint](https://www.techint.com/en/our-projects/dos-bocas-refinery)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -719,7 +715,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OGJ (https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/refining/optimization/article/17279334/pemex-to-proceed-with-dos-bocas-refinery-project)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -756,7 +752,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Forbes México (https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Forbes México (https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
+          <t>[Forbes México](https://forbes.com.mx/pemex-invertira-5300-millones-de-dolares-para-reactivar-la-industria-petroquimica/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +826,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Forbes México (https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -867,7 +863,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tribuna (https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); Contralínea (https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
+          <t>[Tribuna](https://tribuna.com.mx/mexico/2026/06/05/sheinbaum-anuncia-inversion-de-93-mil-mdp-para-reactivar-la-industria-petroquimica-y-de-fertilizantes-en-veracruz_560837/); [Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -904,7 +900,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PV Magazine México (https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
+          <t>[PV Magazine México](https://www.pv-magazine-mexico.com/2026/04/28/inician-en-sinaloa-la-construccion-de-la-mayor-planta-de-metanol-ultrabajo-en-carbono-a-partir-de-hidrogeno-verde/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -941,7 +937,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>H2 View (https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
+          <t>[H2 View](https://www.h2-view.com/story/first-ammonia-project-on-track-for-2026-fid-despite-topsoe-deal-collapse/2138792.article/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -953,12 +949,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Planta de Amoniaco Topolobampo (GPO)</t>
+          <t>Planta de Amoniaco Topolobampo (GPO) — Bahía de Ohuira</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Topolobampo, Sinaloa, México</t>
+          <t>Topolobampo, Ahome, Sinaloa, México</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,17 +969,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción (avance ~80% confirmado por Secretaría de Economía jul-2026; op. comercial H1 2027)</t>
+          <t>Construcción parcial/PAUSA parcial (unidad de amoniaco ~95% completa según Presidencia, ago-2026; unidades de urea/metanol y terminal marina PAUSADAS en espera de acuerdo ambiental; gobierno de Sinaloa presentó "Plan Integral" de conservación/desarrollo sostenible de la Bahía de Ohuira, 4-ago-2026, para destrabar continuidad del proyecto)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Debate (https://www.debate.com.mx/economia/secretaria-de-economia-complejo-de-amoniaco-en-topolobampo-prioritario-para-el-gobierno-de-mexico-20260713-0092.html)</t>
+          <t>[Ríodoce](https://riodoce.mx/2026/08/10/pausan-urea-y-metanol-pero-avanza-amoniaco-en-industria-en-la-bahia-de-ohuira/); [Gobierno de Sinaloa](https://sinaloa.gob.mx/presentan-plan-integral-para-la-conservacion-ambiental-el-bienestar-comunitario-y-el-desarrollo-sostenible-de-la-bahia-de-ohuira/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1011,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ICIS (https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
+          <t>[ICIS](https://www.icis.com/explore/resources/news/2025/11/13/11155109/lake-charles-methanol-ii-awards-feed-fid-expected-in-q2-2026/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1047,17 +1043,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Construcción (~74% avance)</t>
+          <t>Construcción (~74% avance; Pemex confirmó retraso en el cronograma, finalización ahora prevista para 2S2027)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diario del Istmo (https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321)</t>
+          <t>[Diario del Istmo](https://diariodelistmo.com/nacional/este-es-el-avance-que-lleva-la-planta-coquizadora-en-la-refineria-de-salina-cruz/50642321); [Mexico Business News](https://mexicobusiness.news/oilandgas/news/salina-cruz-refinery-miss-construction-deadline-pemex)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1085,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/06032026/shintech-announces-us34-billion-at-louisiana-petrochemicals-complex/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1126,7 +1122,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>INEOS (https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
+          <t>[INEOS](https://www.ineos.com/news/shared-news/ineos-acetyls-and-sandpiper-chemicals-announce-strategic-collaboration-for-the-development-of-a-low-carbon-methanol-project-in-texas-city-texas/)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1163,7 +1159,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/petrochemicals/13072026/oxea-confirms-fid-for-major-capacity-expansion/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1200,7 +1196,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OGJ (https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
+          <t>[OGJ](https://www.ogj.com/refining-processing/gas-processing/news/55320579/targa-advances-permian-gas-pipeline-processing-expansion)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20250806663187/en/Enterprise-Agrees-to-Acquire-Occidentals-Gas-Gathering-Affiliate-Enters-Into-Natural-Gas-Processing-Agreement-Announces-New-Midland-Basin-Natural-Gas-Processing-Plant)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1274,7 +1270,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Natural Gas Intel (https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
+          <t>[Natural Gas Intel](https://naturalgasintel.com/news/mplx-scales-up-for-power-hungry-future-with-natural-gas-focused-growth-plan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1311,7 +1307,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>East Daley (https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
+          <t>[East Daley](https://eastdaley.com/daley-note/mplx-acquires-northwind-for-2-375b-acquires-more-ngls-for-jv-project)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1348,7 +1344,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grand Forks Herald (https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
+          <t>[Grand Forks Herald](https://www.grandforksherald.com/news/local/northern-plains-nitrogen-proposal-receiving-more-attention-amid-global-fertilizer-pressure)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phillips 66 (https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
+          <t>[Phillips 66](https://www.phillips66.com/newsroom/iron-mesa-safely-enters-next-phase-of-construction/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Targa Resources (https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
+          <t>[Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-permian-growth-projects-and)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elefante Blanco (https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
+          <t>[Elefante Blanco](https://elefanteblanco.mx/2026/01/02/pemex-abre-30-licitaciones-para-obras-en-la-refineria-madero/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1496,7 +1492,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>La Jornada (https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Downstream Calendar (https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
+          <t>[Downstream Calendar](https://downstreamcalendar.com/mcdermott-secures-feed-contract-for-ascension-clean-energy-project/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1570,7 +1566,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260517310811/en/Phillips-66-announces-Zeus-Gas-Plant-and-a-third-Coastal-Bend-Fractionator)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1607,7 +1603,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USDA (https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/01/secretary-rollins-announces-500-million-fertilizer-investment-and-expansion-program-strengthen)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/clean-fuels/06012026/samsung-ea-announces-groundbreaking-of-low-carbon-ammonia-plant/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hydrocarbon Engineering (https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
+          <t>[Hydrocarbon Engineering](https://www.hydrocarbonengineering.com/refining/03062026/green-fuels-hosts-groundbreaking-ceremony-for-new-refinery/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Energy Transfer (https://www.energytransfer.com/project-highlights/)</t>
+          <t>[Energy Transfer](https://www.energytransfer.com/project-highlights/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1755,7 +1751,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inspectioneering (https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant); BigGo Finance (https://finance.biggo.com/news/US_OKE_2026-08-04)</t>
+          <t>[Inspectioneering](https://inspectioneering.com/news/2025-08-07/11702/oneok-greenlights-new-365m-delaware-basin-gas-plant); [BigGo Finance](https://finance.biggo.com/news/US_OKE_2026-08-04)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1792,7 +1788,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Marcellus Drilling News (https://marcellusdrilling.com/2026/08/mplx-marcellus-proc-plants-96-full-harmon-creek-iii-starts-up/); StockTitan (https://www.stocktitan.net/news/MPLX/mplx-lp-reports-second-quarter-2026-financial-9tcvq4saz6sr.html)</t>
+          <t>[Marcellus Drilling News](https://marcellusdrilling.com/2026/08/mplx-marcellus-proc-plants-96-full-harmon-creek-iii-starts-up/); [StockTitan](https://www.stocktitan.net/news/MPLX/mplx-lp-reports-second-quarter-2026-financial-9tcvq4saz6sr.html)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Contralínea (https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/); El Diario de Juárez (https://diario.mx/nacional/2026/jan/22/adjudica-pemex-contratos-a-favoritas-1102601.html)</t>
+          <t>[Contralínea](https://contralinea.com.mx/interno/semana/presentan-plan-con-inversion-de-93-mil-mdp-para-rescatar-la-petroquimica-nacional/); [El Diario de Juárez](https://diario.mx/nacional/2026/jan/22/adjudica-pemex-contratos-a-favoritas-1102601.html)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1866,7 +1862,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Enterprise Reports Second Quarter 2026 Earnings (https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1903,7 +1899,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Enterprise Reports Second Quarter 2026 Earnings (https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
+          <t>[Enterprise Reports Second Quarter 2026 Earnings](https://ir.enterpriseproducts.com/news-releases/news-release-details/enterprise-reports-second-quarter-2026-earnings)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1940,7 +1936,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PGJ (https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/may/targa-expands-permian-gas-processing-delaware-express-pipeline-capacity)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1977,7 +1973,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hydrocarbon Processing (https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); Louisiana Economic Development (https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
+          <t>[Hydrocarbon Processing](https://www.hydrocarbonprocessing.com/news/2026/03/southern-energy-renewables-announce-14-b-methanol-and-saf-complex-in-louisiana/); [Louisiana Economic Development](https://www.opportunitylouisiana.gov/news/southern-energy-renewables-announce-1-4-billion-methanol-and-sustainable-aviation-fuel-facility-in-st-charles-parish)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2014,7 +2010,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tri-Cities Area Journal of Business (https://www.tricitiesbusinessnews.com/articles/atlas-agro-plant-nears-decision-point); Washington State Standard (https://washingtonstatestandard.com/2025/10/30/plan-for-1-5b-fertilizer-plant-in-central-wa-still-alive-despite-loss-of-federal-funds/)</t>
+          <t>[Tri-Cities Area Journal of Business](https://www.tricitiesbusinessnews.com/articles/atlas-agro-plant-nears-decision-point); [Washington State Standard](https://washingtonstatestandard.com/2025/10/30/plan-for-1-5b-fertilizer-plant-in-central-wa-still-alive-despite-loss-of-federal-funds/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2051,7 +2047,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Engineer (https://www.theengineer.co.uk/content/news/abb-joins-team-for-22gw-hydrogen-city-project-in-texas); Energy Capital HTX (https://energycapitalhtx.com/green-hydrogen-city-abb-mou)</t>
+          <t>[The Engineer](https://www.theengineer.co.uk/content/news/abb-joins-team-for-22gw-hydrogen-city-project-in-texas); [Energy Capital HTX](https://energycapitalhtx.com/green-hydrogen-city-abb-mou)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2088,7 +2084,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Journal (https://www.ogj.com/refining-processing/gas-processing/capacities/article/55240691/targa-advances-expansion-plans-for-permian-basin-gas-processing)</t>
+          <t>[Oil &amp; Gas Journal](https://www.ogj.com/refining-processing/gas-processing/capacities/article/55240691/targa-advances-expansion-plans-for-permian-basin-gas-processing)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2125,12 +2121,123 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inspectioneering (https://inspectioneering.com/news/2026-08-11/12145/brazos-midstream-announces-new-natural-gas-processing-plant-to-support-continued); Rigzone (https://www.rigzone.com/news/brazos_to_grow_midland_gas_processing_capacity_to_11_bcfd-11-aug-2026-184346-article/)</t>
+          <t>[Inspectioneering](https://inspectioneering.com/news/2026-08-11/12145/brazos-midstream-announces-new-natural-gas-processing-plant-to-support-continued); [Rigzone](https://www.rigzone.com/news/brazos_to_grow_midland_gas_processing_capacity_to_11_bcfd-11-aug-2026-184346-article/)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kings Landing II Gas Processing Plant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Kinetik Holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Construcción (FID alcanzada; US$260 millones; finalización prevista 2S2028)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>[Investing.com](https://www.investing.com/news/company-news/kinetik-approves-260m-gas-processing-plant-in-new-mexico-93CH-4698224)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Apollo Gas Plant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Condado de Eddy, Nuevo México, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Trace Midstream Partners II</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Anuncio/planeación (planta criogénica de 250 MMcf/d)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>[Gas Compression Magazine](https://gascompressionmagazine.com/2026/06/29/new-mexico-gains-major-gas-processing-hub/)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IGP Gulf Coast Methanol Complex (4 unidades)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Plaquemine Parish (Myrtle Grove), Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>IGP Methanol LLC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Permiso de calidad del aire asegurado / pre-construcción (US$3,600 millones)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>[Industrial Info Resources](https://www.industrialinfo.com/news/article.jsp?newsitemID=262022)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2148,47 +2255,47 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -2222,7 +2329,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bechtel (https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); Natural Gas Intel (https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/); Federal Register (https://www.federalregister.gov/documents/2026/08/03/2026-15695/rio-grande-lng-train-6-llc-notice-of-intent-to-prepare-an-environmental-impact-statement-for-the); LNG Prime (https://lngprime.com/americas/nextdecade-seeks-ferc-ok-for-sixth-rio-grande-lng-train/187820/)</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); [Natural Gas Intel](https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/); [Federal Register](https://www.federalregister.gov/documents/2026/08/03/2026-15695/rio-grande-lng-train-6-llc-notice-of-intent-to-prepare-an-environmental-impact-statement-for-the); [LNG Prime](https://lngprime.com/americas/nextdecade-seeks-ferc-ok-for-sixth-rio-grande-lng-train/187820/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2259,7 +2366,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bechtel (https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/sempra-infrastructure-announces-epc-contract-with-bechtel-for-port-arthur-lng-phase-2/)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2296,7 +2403,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Woodside (https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
+          <t>[Woodside](https://www.woodside.com/what-we-do/growth-projects/woodside-louisiana-lng)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2333,7 +2440,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GEM.wiki (https://www.gem.wiki/CP2_LNG_Terminal); LNG Prime (https://lngprime.com/americas/top-5-news-of-the-week-july-20-26/193119/)</t>
+          <t>[GEM.wiki](https://www.gem.wiki/CP2_LNG_Terminal); [LNG Prime](https://lngprime.com/americas/top-5-news-of-the-week-july-20-26/193119/)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2350,7 +2457,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plaquemines Parish, Luisiana, EE.UU.</t>
+          <t>Plaquemines Parish (Myrtle Grove/Port Sulphur), Luisiana, EE.UU.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2365,17 +2472,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Construcción (Venture Global presentó solicitud FERC para expansión adicional de 31 mtpa —24 trenes, ~USD 18,000 millones—; inicio de construcción de la expansión esperado a inicios de 2027, primera producción fin de 2028)</t>
+          <t>Construcción/Permitting acelerado (Venture Global presentó solicitud FERC para expansión adicional de 31 mtpa —24 trenes, ~USD 18,000 millones—; U.S. Army Corps of Engineers otorgó permitting expedito bajo "emergencia energética nacional" —periodo de comentario público reducido de 30 a 10 días, cerrado 2-jul-2026—, ampliaría el sitio de 590 a 1,220 acres; DOE aprobó exportaciones adicionales inmediatas desde Plaquemines; inicio de construcción de la expansión esperado a inicios de 2027, primera producción fin de 2028)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Offshore Energy (https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/); Argus Media (https://www.argusmedia.com/en/news-and-insights/latest-market-news/2755512-vg-files-expansion-plan-to-double-plaquemines-lng)</t>
+          <t>[Offshore Energy](https://www.offshore-energy.biz/kbr-zachry-to-work-on-ventures-plaquemines-lng/); [Verite News](https://veritenews.org/2026/08/12/lng-expansion-could-be-fast-tracked); [DOE](https://www.energy.gov/node/4856848)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2514,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Port Arthur News (https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
+          <t>[Port Arthur News](https://panews.com/2026/04/24/golden-pass-lng-makes-history-with-first-export-from-sabine-pass-terminal/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2444,7 +2551,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PGJ (https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); LNG Prime (https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/); energiesmedia (https://energiesmedia.com/ferc-approves-cheniere-train-7-energies/)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); [LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/); [energiesmedia](https://energiesmedia.com/ferc-approves-cheniere-train-7-energies/)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2481,7 +2588,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html); World Oil (https://www.worldoil.com/news/2026/8/10/tdi-brooks-wins-survey-contract-for-delfin-lng-deepwater-port/)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/03/3306350/0/en/delfin-midstream-announces-5-billion-final-investment-decision-for-first-flng-vessel.html); [World Oil](https://www.worldoil.com/news/2026/8/10/tdi-brooks-wins-survey-contract-for-delfin-lng-deepwater-port/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2518,7 +2625,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dossier Político (https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/); Natural Gas Intel (https://naturalgasintel.com/news/oneok-affiliate-seeks-3-year-extension-for-saguaro-connector-pipeline/)</t>
+          <t>[Dossier Político](https://dossierpolitico.com/2026/07/17/activistas-entregan-90-mil-firmas-para-frenar-proyecto-saguaro-energia-en-sonora/); [Natural Gas Intel](https://naturalgasintel.com/news/oneok-affiliate-seeks-3-year-extension-for-saguaro-connector-pipeline/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2555,7 +2662,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GEM Wiki (https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
+          <t>[GEM Wiki](https://www.gem.wiki/New_Fortress_Altamira_FLNG_Terminal)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2592,7 +2699,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/glenfarne-lands-investment-for-early-work-on-texas-lng-ahead-of-fid/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2629,7 +2736,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PGJ (https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal); PR Newswire/Caturus (https://www.prnewswire.com/news-releases/caturus-announces-final-investment-decision-for-9-5-mtpa-commonwealth-lng-export-facility-in-cameron-la-302773264.html)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/commonwealth-lng-awards-main-automation-contract-for-louisiana-export-terminal); [PR Newswire/Caturus](https://www.prnewswire.com/news-releases/caturus-announces-final-investment-decision-for-9-5-mtpa-commonwealth-lng-export-facility-in-cameron-la-302773264.html)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2666,7 +2773,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Houston Public Media (https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
+          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2703,7 +2810,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sempra (https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos); LNG Prime (https://lngprime.com/lng-terminals/sempra-infrastructure-extends-eca-lng-commissioning-due-to-compressor-damage/193584/)</t>
+          <t>[Sempra](https://www.sempra.com/newsroom/press-releases/sempra-infrastructures-eca-lng-phase-1-exports-first-lng-cargo-mexicos); [LNG Prime](https://lngprime.com/lng-terminals/sempra-infrastructure-extends-eca-lng-commissioning-due-to-compressor-damage/193584/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2740,7 +2847,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LNG Prime (https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
+          <t>[LNG Prime](https://lngprime.com/americas/gato-negro-eyes-fid-on-mexico-lng-plant-in-late-2026/165906/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2777,7 +2884,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2814,7 +2921,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rigzone (https://www.rigzone.com/news/coastal_bend_lng_enters_permitting_phase-05-aug-2026-184302-article/); PGJ (https://pgjonline.com/news/2026/august/coastal-bend-lng-initiates-formal-permitting-and-consultation-process)</t>
+          <t>[Rigzone](https://www.rigzone.com/news/coastal_bend_lng_enters_permitting_phase-05-aug-2026-184302-article/); [PGJ](https://pgjonline.com/news/2026/august/coastal-bend-lng-initiates-formal-permitting-and-consultation-process)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2851,7 +2958,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FERC (https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
+          <t>[FERC](https://www.ferc.gov/gulfstream-lng-terminal-project)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2883,17 +2990,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pre-FID (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381, 16-jul-2026; gobernador Dunleavy convocó nueva sesión legislativa especial para el 20-ago-2026 con una ley de incentivos actualizada para reintentar destrabar el financiamiento)</t>
+          <t>Pre-FID/Retraso legislativo (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381, 16-jul-2026; tercera sesión legislativa especial, convocada por el gobernador Dunleavy, concluyó 13-ago-2026 SIN votación del proyecto de ley de incentivos fiscales necesario para avanzar el financiamiento; incierto si el proyecto avanza antes de que asuman nuevo gobernador/legislatura)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alaska Beacon (https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/); Your Alaska Link (https://www.youralaskalink.com/news/local/dunleavy-plans-updated-lng-bill-calls-lawmakers-back-august-20/article_4ea0fcfa-386b-45c1-815d-8fff56088739.html)</t>
+          <t>[Alaska Beacon](https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/); [Alaska's News Source](https://www.alaskasnewssource.com/2026/08/13/alaska-lng-pipeline-bill-collapses-house-majority-says-it-lacks-votes/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2925,7 +3032,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PGJ (https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/311-mile-sonora-gas-pipeline-project-advances-in-mexico)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2962,7 +3069,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OGJ (https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
+          <t>[OGJ](https://www.ogj.com/pipelines-transportation/pipelines/news/55322537/arm-energy-takes-fid-on-23-billion-mustang-express-pipeline)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2999,7 +3106,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mexico Business News (https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion); energynews.mx (https://energynews.mx/nace-praespero-ursus-ei-megaproyecto-de-8000-millones-de-dolares-para-veracruz/)</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/energy/news/ursus-energy-scales-investment-us21-billion); [energynews.mx](https://energynews.mx/nace-praespero-ursus-ei-megaproyecto-de-8000-millones-de-dolares-para-veracruz/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3036,7 +3143,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/15/3327983/0/en/Delfin-Midstream-Partners-With-EIG-s-MidOcean-Energy-to-Advance-Second-FLNG-Vessel-Issues-Limited-Notice-to-Proceed-to-Siemens-Energy.html)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3073,7 +3180,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/texas-gateway-open-season-expands-haynesville-natural-gas-links-amid-lng-growth/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3110,7 +3217,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>World Oil (https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/); PGJ (https://pgjonline.com/news/2026/august/argent-lng-submits-wsa-to-the-us-coast-guard-advancing-its-25-mmtpy-louisiana-lng-project)</t>
+          <t>[World Oil](https://worldoil.com/news/2026/7/24/doe-approves-20-year-export-authorization-for-argent-lng-project/); [PGJ](https://pgjonline.com/news/2026/august/argent-lng-submits-wsa-to-the-us-coast-guard-advancing-its-25-mmtpy-louisiana-lng-project)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3147,7 +3254,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-14963/deepwater-port-license-application-st-lng-deepwater-port-development-project-final-environmental)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3184,7 +3291,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mississippi Today (https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
+          <t>[Mississippi Today](https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3221,7 +3328,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mississippi Today (https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
+          <t>[Mississippi Today](https://mississippitoday.org/2026/08/05/ferc-new-gas-pipeline-mississippi/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3258,7 +3365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LNG Prime (https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
+          <t>[LNG Prime](https://lngprime.com/americas/kinder-morgan-seeks-doe-extension-for-gulf-lng-export-project/184334/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3295,7 +3402,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Baker Hughes (https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
+          <t>[Baker Hughes](https://investors.bakerhughes.com/news/press-releases/news-details/2026/Baker-Hughes-Secures-Substantial-Equipment-and-Services-Awards-for-Chenieres-Sabine-Pass-LNG-Facility/default.aspx)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3332,7 +3439,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/05/05/2026-08654/cheniere-corpus-christi-pipeline-lp-corpus-christi-liquefaction-stage-iv-llc-corpus-christi)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3369,7 +3476,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Natural Gas Intel (https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/); Federal Register (https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc)</t>
+          <t>[Natural Gas Intel](https://www.naturalgasintel.com/news/ferc-approves-extension-for-freeport-lngs-fourth-train-expansion-project/); [Federal Register](https://www.federalregister.gov/documents/2026/07/24/2026-15040/freeport-lng-development-lp-flng-liquefaction-llc-flng-liquefaction-2-llc-flng-liquefaction-3-llc)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3406,7 +3513,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Proyectos México (https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
+          <t>[Proyectos México](https://www.proyectosmexico.gob.mx/proyecto_inversion/1076-gasoducto-coatzacoalcos-ii/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3443,7 +3550,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LNG Industry (https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/)</t>
+          <t>[LNG Industry](https://www.lngindustry.com/liquefaction/24072026/stabilis-solutions-receives-lor-from-us-coast-guard/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3480,7 +3587,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3517,7 +3624,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LNG Prime (https://lngprime.com/americas/cameron-lng-seeks-ferc-extension-for-expansion-project/167382/)</t>
+          <t>[LNG Prime](https://lngprime.com/americas/cameron-lng-seeks-ferc-extension-for-expansion-project/167382/)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3554,7 +3661,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/02/23/2026-03548/magnolia-lng-llc-notice-of-request-for-extension-of-time)</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/02/23/2026-03548/magnolia-lng-llc-notice-of-request-for-extension-of-time)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3591,7 +3698,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Storage Terminals Magazine (https://storageterminalsmag.com/kinder-morgans-trident-pipeline-project-enters-active-construction-phase-in-southeast-texas/); Natural Gas Intel (https://www.naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
+          <t>[Storage Terminals Magazine](https://storageterminalsmag.com/kinder-morgans-trident-pipeline-project-enters-active-construction-phase-in-southeast-texas/); [Natural Gas Intel](https://www.naturalgasintel.com/news/kinder-morgan-greenlights-7b-in-natural-gas-pipeline-projects-amid-regulatory-speedup/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3628,7 +3735,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Global Energy Monitor (https://www.gem.wiki/Centauro_del_Norte_Gas_Pipeline); BNamericas (https://www.bnamericas.com/en/news/mexico-grants-permits-for-three-sonora-gas-projects)</t>
+          <t>[Global Energy Monitor](https://www.gem.wiki/Centauro_del_Norte_Gas_Pipeline); [BNamericas](https://www.bnamericas.com/en/news/mexico-grants-permits-for-three-sonora-gas-projects)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3665,7 +3772,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LNG Industry (https://www.lngindustry.com/liquid-natural-gas/07082026/enbridge-signs-option-to-acquire-ttc-connector/)</t>
+          <t>[LNG Industry](https://www.lngindustry.com/liquid-natural-gas/07082026/enbridge-signs-option-to-acquire-ttc-connector/)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3702,7 +3809,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Enbridge (https://www.enbridge.com/stories/2026/august/bay-runner-twin-permian-gas-pipelines-feeder-gulf-coast-lng-exports); PGJ (https://pgjonline.com/news/2026/august/enbridge-partners-announce-pipeline-s-sanctioning-blackcomb-commissioning-as-permian-gas-exports-ramp-up)</t>
+          <t>[Enbridge](https://www.enbridge.com/stories/2026/august/bay-runner-twin-permian-gas-pipelines-feeder-gulf-coast-lng-exports); [PGJ](https://pgjonline.com/news/2026/august/enbridge-partners-announce-pipeline-s-sanctioning-blackcomb-commissioning-as-permian-gas-exports-ramp-up)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3739,7 +3846,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PGJ (https://pgjonline.com/news/2026/august/enbridge-partners-announce-pipeline-s-sanctioning-blackcomb-commissioning-as-permian-gas-exports-ramp-up)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/august/enbridge-partners-announce-pipeline-s-sanctioning-blackcomb-commissioning-as-permian-gas-exports-ramp-up)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3759,50 +3866,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -3836,7 +3943,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); MINING.COM (https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/)</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); [MINING.COM](https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3873,7 +3980,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SEC/Hudbay (https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); GlobeNewswire (https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
+          <t>[SEC/Hudbay](https://www.sec.gov/Archives/edgar/data/1322422/000106299326001973/exhibit99-2.htm); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/06/24/3317147/0/en/hudbay-completes-offering-of-us-52-million-of-4-50-municipal-bonds-for-copper-world.html)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3910,7 +4017,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEC (https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); International Mining (https://im-mining.com/2026/08/10/resolution-copper-accelerates-exploration-underground-development-with-major-drilling-redpath-contracts/)</t>
+          <t>[SEC](https://www.sec.gov/Archives/edgar/data/863064/000086306426000019/ex12d16mr_resolutionland.htm); [International Mining](https://im-mining.com/2026/08/10/resolution-copper-accelerates-exploration-underground-development-with-major-drilling-redpath-contracts/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3947,7 +4054,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); Lithium Americas (https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/thacker-pass-lithium-project-us-update-2026-05-22); [Lithium Americas](https://lithiumamericas.com/news/news-details/2026/Lithium-Americas-Provides-a-Project-Update-and-2026-Capex-Guidance-for-Thacker-Pass/default.aspx)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3984,7 +4091,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mining.com (https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
+          <t>[Mining.com](https://www.mining.com/teck-agnico-team-up-at-san-nicolas-copper-project-in-mexico/)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4021,7 +4128,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Energy Magazine MX (https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2025/10/grupo-mexico-espera-autorizacion-federal-para-continuar-proyectos-mineros-por-10-mil-200-mdd/)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4058,7 +4165,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BNamericas (https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/southern-copper-wins-permits-for-us551mn-el-pilar-in-mexico)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4095,7 +4202,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M3 Engineering (https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
+          <t>[M3 Engineering](https://m3eng.com/portfolio/buenavista-del-cobre-concentradora-no-2/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4132,7 +4239,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/04/torex-gold-alcanza-velocidad-de-crucero-en-media-luna-9-meses-adelante-de-cronograma/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4169,7 +4276,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mining.com (https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
+          <t>[Mining.com](https://www.mining.com/nevada-copper-unveils-restart-and-financing-plan-for-pumpkin-hollow/)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4206,7 +4313,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USDA (https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4243,7 +4350,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); Departamento de Justicia de EE.UU. (https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); [Departamento de Justicia de EE.UU.](https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4280,7 +4387,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silver Tiger Metals (https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
+          <t>[Silver Tiger Metals](https://silvertigermetals.com/news/2026/silver-tiger-metals-awards-engineering-procurement-and-construction-management-contract-and-provides-construction-update)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4317,7 +4424,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/vizsla-silver-awards-epcm-and-mine-design-contracts-for-the-development-of-the-panuco-silver-gold-project-302750621.html)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4354,7 +4461,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orla Mining (https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
+          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4391,7 +4498,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28); Minera Alamos (https://mineraalamos.com/news/2026/minera-alamos-announces-positive-pre-feasibility-study-for-the-copperstone-gold-project-in-arizona/)</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/minera-alamos-confirms-low-cost-near-term-mining-possible-at-copperstone-in-arizona-2026-05-28); [Minera Alamos](https://mineraalamos.com/news/2026/minera-alamos-announces-positive-pre-feasibility-study-for-the-copperstone-gold-project-in-arizona/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4428,7 +4535,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wyoming News (https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html); Discovery Alert (https://discoveryalert.com.au/ck-gold-project-permitting-construction-ready-valuation-2026/)</t>
+          <t>[Wyoming News](https://www.wyomingnews.com/rawlinstimes/plans-move-forward-for-ck-gold-project-as-developers-target-2026-construction-start/article_b2bb147e-2f92-4ca2-bf86-fcc9983917a7.html); [Discovery Alert](https://discoveryalert.com.au/ck-gold-project-permitting-construction-ready-valuation-2026/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4465,7 +4572,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>First Majestic (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
+          <t>[First Majestic](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/1082-tsx/ag/206222-first-majestic-receives-construction-permits-for-santo-nino-and-navidad-advances-development-across-the-santa-elena-district.html)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4502,7 +4609,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEC/Americas Gold and Silver (https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
+          <t>[SEC/Americas Gold and Silver](https://www.sec.gov/Archives/edgar/data/0001286973/000106299326002645/exhibit99-2.htm)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4539,7 +4646,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kitco (https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
+          <t>[Kitco](https://www.kitco.com/news/off-the-wire/2026-06-08/minera-frisco-restarts-two-mexico-mines-plans-new-silver-unit)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4576,7 +4683,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/trilogy-metals-announces-publication-of-federal-and-state-permitting-schedule-for-arctic-project-establishing-defined-timeline-toward-a-record-of-decision-by-september-2028-302827083.html)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4613,7 +4720,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Northern Miner (https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); Newsfile (https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
+          <t>[Northern Miner](https://www.northernminer.com/news/gogold-approved-to-build-227m-mine-in-mexico/1003891932/); [Newsfile](https://www.newsfilecorp.com/release/300455/GoGold-Achieves-Major-Milestone-Final-Remaining-Permits-Secured-and-Construction-Approved-for-Los-Ricos-South-Underground-Mine)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4650,7 +4757,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BNamericas (https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
+          <t>[BNamericas](https://www.bnamericas.com/en/news/discovery-advances-permitting-financing-at-us606mn-cordero-in-mexico)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4687,7 +4794,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Resource World (https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
+          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4724,7 +4831,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fresnillo plc (https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
+          <t>[Fresnillo plc](https://www.fresnilloplc.com/portfolio/exploration/orisyvo/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4761,7 +4868,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Army.mil (https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
+          <t>[Army.mil](https://www.army.mil/article/293503/army_announces_conditional_lease_awards_for_domestic_critical_mineral_processing_facilities_to_secure_defense_supply_chains)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4798,7 +4905,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4835,7 +4942,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mining.com (https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
+          <t>[Mining.com](https://www.mining.com/web/us-army-bases-to-host-critical-minerals-plants-in-onshoring-push/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4872,7 +4979,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IM Mining (https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
+          <t>[IM Mining](https://im-mining.com/2026/06/29/metso-to-supply-additional-crushing-package-for-grupo-mexico-la-caridad-copper-concentrator/)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4909,7 +5016,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/05/21/3299182)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4946,7 +5053,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/grupo-mexicos-asarco-may-reopen-united-states)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4983,7 +5090,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Minera Alamos (https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
+          <t>[Minera Alamos](https://mineraalamos.com/our-assets/cerro-de-oro-project/)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5020,7 +5127,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Global Mining Review (https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
+          <t>[Global Mining Review](https://www.globalminingreview.com/mining/11022025/antler-copper-project-achieves-critical-federal-permitting-milestone/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5057,7 +5164,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BLM (https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
+          <t>[BLM](https://www.blm.gov/press-release/blm-approves-lisbon-valley-copper-mine-expansion-utah)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5094,7 +5201,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>InvestingNews (https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/); StockTitan/SEC 6-K (https://www.stocktitan.net/sec-filings/SLI/6-k-standard-lithium-ltd-current-report-foreign-issuer-ef7db860baa3.html)</t>
+          <t>[InvestingNews](https://investingnews.com/smackover-lithium-announces-the-award-of-last-key-construction-contract-for-the-south-west-arkansas-project-ahead-of-final-investment-decision/); [StockTitan/SEC 6-K](https://www.stocktitan.net/sec-filings/SLI/6-k-standard-lithium-ltd-current-report-foreign-issuer-ef7db860baa3.html)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5131,7 +5238,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SEC/Freeport-McMoRan (https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
+          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5168,7 +5275,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NioCorp (https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); Mining.com (https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/)</t>
+          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); [Mining.com](https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5205,7 +5312,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>E&amp;MJ (https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
+          <t>[E&amp;MJ](https://www.e-mj.com/breaking-news/centerra-advances-goldfield-project-in-nevada/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5242,7 +5349,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html); Arizona Sonoran (https://arizonasonoran.com/news-releases/arizona-sonoran-pre-feasibility-study-delivers-exceptional-results-for-the-cactus-project-outlining-long-life-low-cost-copper-1/)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/03/02/3247157/0/en/hudbay-to-acquire-arizona-sonoran-creating-the-third-largest-copper-district-in-north-america.html); [Arizona Sonoran](https://arizonasonoran.com/news-releases/arizona-sonoran-pre-feasibility-study-delivers-exceptional-results-for-the-cactus-project-outlining-long-life-low-cost-copper-1/)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5279,7 +5386,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Western Exploration (https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx); StreetWise Reports (https://www.streetwisereports.com/article/2026/08/03/nevada-gold-project-launches-drill-campaign-at-doby-george.html)</t>
+          <t>[Western Exploration](https://www.westernexploration.com/news-and-updates/news/news-details/2026/Western-Exploration-Outlines-2026-Program-to-Advance-Doby-George-Permitting-and-Expand-Gravel-Creek-Resources-2026-aaotfYHcV7/default.aspx); [StreetWise Reports](https://www.streetwisereports.com/article/2026/08/03/nevada-gold-project-launches-drill-campaign-at-doby-george.html)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5316,7 +5423,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chesapeake Gold Corp. (https://chesapeakegold.com/metates/)</t>
+          <t>[Chesapeake Gold Corp.](https://chesapeakegold.com/metates/)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5353,7 +5460,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mining Technology (https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
+          <t>[Mining Technology](https://www.mining-technology.com/news/pathfinder-896m-loi-us-exim-copper-mine/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5390,7 +5497,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/heliostar-advances-la-colorada-pit-permits-drill-data)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5427,7 +5534,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The Western News (https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
+          <t>[The Western News](https://thewesternnews.com/news/2026/jul/24/libby-mining-project-takes-another-step-forward-with-federal-ok/)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5464,7 +5571,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mining News North (https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
+          <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5501,7 +5608,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IM Mining (https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
+          <t>[IM Mining](https://im-mining.com/2026/06/23/ioneer-signals-progress-on-rhyolite-ridge-lithium-boron-project-with-kind-and-hyundai-engineering-pacts/)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5538,7 +5645,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Resource World (https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
+          <t>[Resource World](https://resourceworld.com/axo-metals-secures-major-environmental-permit-approval-clears-path-for-production-at-the-san-antonio-gold-project/)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5575,7 +5682,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talon Metals (https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
+          <t>[Talon Metals](https://talonmetals.com/talon-metals-and-westmoreland-mining-sign-land-agreement-to-progress-north-dakota-minerals-processing-facility/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5612,7 +5719,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5649,7 +5756,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MPR News (https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
+          <t>[MPR News](https://www.mprnews.org/story/2026/07/30/newrange-copper-nickel-proposes-major-changes-to-copper-mine-plan)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5686,7 +5793,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Energy Fuels (https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); PR Newswire (https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
+          <t>[Energy Fuels](https://investors.energyfuels.com/2026-07-29-Commercial-Scale-Heavy-Rare-Earth-Plant-Now-Under-Construction-in-Utah); [PR Newswire](https://www.prnewswire.com/news-releases/commercial-scale-heavy-rare-earth-plant-now-under-construction-in-utah-302837314.html)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5723,7 +5830,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3334925/0/en/sandfire-resources-america-files-black-butte-copper-project-preliminary-feasibility-study.html)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5760,7 +5867,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Texarkana Gazette (https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
+          <t>[Texarkana Gazette](https://www.texarkanagazette.com/news/2026/jun/30/army-awards-lithium-company-energyx-conditional/)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5797,7 +5904,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mining.com (https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); Orla Mining (https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
+          <t>[Mining.com](https://www.mining.com/orla-secures-final-permit-to-advance-underground-mining-at-camino-rojo/); [Orla Mining](https://orlamining.com/news/orla-mining-receives-permits-to-extend-operations-in-mexico-supporting-companys-long-term-commitment-to-camino-rojo/)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5834,7 +5941,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sonoro Gold Corp. (https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); Mexico Mining Center (https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
+          <t>[Sonoro Gold Corp.](https://sonorogold.com/wp-content/uploads/2026/03/2026.03.01_Sonoro-Gold-Corporate-Presentation.pdf); [Mexico Mining Center](https://www.mexicominingcenter.com/sonoro-continues-discussions-with-china-based-epc-companies-and-potential-equity-investors/)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5871,7 +5978,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mining Weekly (https://www.miningweekly.com/article/guardian-metals-outlines-viable-tungsten-trioxide-operation-in-nevada-2026-06-30); StockTitan (https://www.stocktitan.net/news/GMTL/guardian-metal-resources-plc-announces-pilot-mountain-pre-tftnlr9fu3if.html)</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/guardian-metals-outlines-viable-tungsten-trioxide-operation-in-nevada-2026-06-30); [StockTitan](https://www.stocktitan.net/news/GMTL/guardian-metal-resources-plc-announces-pilot-mountain-pre-tftnlr9fu3if.html)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5908,7 +6015,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Newswire (https://www.newswire.ca/news-releases/p2-gold-gabbs-project-update-feasibility-study-on-track-840759204.html)</t>
+          <t>[Newswire](https://www.newswire.ca/news-releases/p2-gold-gabbs-project-update-feasibility-study-on-track-840759204.html)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5945,7 +6052,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/buscar-company-announces-major-advancement-in-the-permitting-process-for-the-treasure-canyon-gold-mine-project-in-california-302772744.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/buscar-company-announces-major-advancement-in-the-permitting-process-for-the-treasure-canyon-gold-mine-project-in-california-302772744.html)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5982,7 +6089,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/01/29/3229150/0/en/Paramount-Gold-Receives-Federal-Approval-for-the-Grassy-Mountain-Gold-Project.html); OPB (https://www.opb.org/article/2026/01/29/oregon-gold-mine-grassy-mountain/)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/01/29/3229150/0/en/Paramount-Gold-Receives-Federal-Approval-for-the-Grassy-Mountain-Gold-Project.html); [OPB](https://www.opb.org/article/2026/01/29/oregon-gold-mine-grassy-mountain/)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6019,7 +6126,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CNBC (https://www.cnbc.com/2026/02/26/mp-materials-selects-texas-for-rare-earth-magnet-manufacturing-site.html)</t>
+          <t>[CNBC](https://www.cnbc.com/2026/02/26/mp-materials-selects-texas-for-rare-earth-magnet-manufacturing-site.html)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6056,7 +6163,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/the-united-states-is-investing-in-its-domestic-rare-earth-industry-302838375.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/the-united-states-is-investing-in-its-domestic-rare-earth-industry-302838375.html)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6093,7 +6200,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Newsfile Corp (https://www.newsfilecorp.com/release/283399/Americas-Gold-and-Silver-Signs-Joint-Venture-Agreement-with-US-Antimony-to-Construct-Antimony-Processing-Facility-in-Idahos-Silver-Valley-Unlocking-Value-from-Its-Antimony-Production-and-Strengthening-U.S.-Critical-Mineral-Security)</t>
+          <t>[Newsfile Corp](https://www.newsfilecorp.com/release/283399/Americas-Gold-and-Silver-Signs-Joint-Venture-Agreement-with-US-Antimony-to-Construct-Antimony-Processing-Facility-in-Idahos-Silver-Valley-Unlocking-Value-from-Its-Antimony-Production-and-Strengthening-U.S.-Critical-Mineral-Security)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6130,7 +6237,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DOE-LPO (https://www.energy.gov/lpo/articles/lpo-announces-conditional-commitment-michigan-potash-produce-fertilizer-us-farmers); Northern Miner (https://www.northernminer.com/news/us-boosts-potash-projects-in-utah-michigan/1003886533/)</t>
+          <t>[DOE-LPO](https://www.energy.gov/lpo/articles/lpo-announces-conditional-commitment-michigan-potash-produce-fertilizer-us-farmers); [Northern Miner](https://www.northernminer.com/news/us-boosts-potash-projects-in-utah-michigan/1003886533/)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6167,7 +6274,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BLM (https://www.blm.gov/announcement/blm-approves-construction-sevier-playa-potash-mining-project)</t>
+          <t>[BLM](https://www.blm.gov/announcement/blm-approves-construction-sevier-playa-potash-mining-project)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6204,7 +6311,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ur-Energy (https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
+          <t>[Ur-Energy](https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6241,7 +6348,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mexico Business News (https://mexicobusiness.news/mining/news/silverco-targets-late-2026-restart-past-producing-cusi-mine); Investing News Network (https://investingnews.com/silverco-mining-begins-underground-development-at-cusi-restart-remains-on-budget-and-on-schedule/)</t>
+          <t>[Mexico Business News](https://mexicobusiness.news/mining/news/silverco-targets-late-2026-restart-past-producing-cusi-mine); [Investing News Network](https://investingnews.com/silverco-mining-begins-underground-development-at-cusi-restart-remains-on-budget-and-on-schedule/)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6278,7 +6385,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Junior Mining Network (https://www.juniorminingnetwork.com/junior-miner-news/press-releases/2342-tsx/ti/199070-titan-mining-to-start-shipping-first-graphite-product-and-feasibility-study-underway-for-40-000-tpa-integrated-kilbourne-graphite-project.html)</t>
+          <t>[Junior Mining Network](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/2342-tsx/ti/199070-titan-mining-to-start-shipping-first-graphite-product-and-feasibility-study-underway-for-40-000-tpa-integrated-kilbourne-graphite-project.html)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6315,7 +6422,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Permitting Council (https://www.permitting.gov/newsroom/success-stories/project-spotlight-graphite-creek-project)</t>
+          <t>[Permitting Council](https://www.permitting.gov/newsroom/success-stories/project-spotlight-graphite-creek-project)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6352,7 +6459,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pan American Silver (https://panamericansilver.com/news/pan-american-announces-revised-pea-for-the-la-colorada-skarn-project-positions-la-colorada-as-a-future-top-tier-silver-mine/); SEC 6-K (https://www.sec.gov/Archives/edgar/data/771992/000077199226000031/a2026_03x24lacoloradapeaup.htm)</t>
+          <t>[Pan American Silver](https://panamericansilver.com/news/pan-american-announces-revised-pea-for-the-la-colorada-skarn-project-positions-la-colorada-as-a-future-top-tier-silver-mine/); [SEC 6-K](https://www.sec.gov/Archives/edgar/data/771992/000077199226000031/a2026_03x24lacoloradapeaup.htm)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6389,7 +6496,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/i-80-gold-provides-update-on-lone-tree-plant-refurbishment-project-remains-on-schedule-and-on-budget-302836341.html)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6426,7 +6533,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6463,7 +6570,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/29/3335652/0/en/Kinross-reports-strong-2026-second-quarter-results.html)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6500,7 +6607,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Federal Register (https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
+          <t>[Federal Register](https://www.federalregister.gov/documents/2026/07/29/2026-15255/black-hills-national-forest-wyoming-bear-lodge-rare-earth-project)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6537,7 +6644,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6574,7 +6681,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6611,7 +6718,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Minería en Línea (https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
+          <t>[Minería en Línea](https://mineriaenlinea.com/2026/07/southern-copper-obtiene-permisos-ambientales-para-el-pilar-produccion-a-partir-de-2029/)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6648,7 +6755,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yellowhammer News (https://yellowhammernews.com/trump-administration-announces-25-million-exim-loan-for-westwaters-coosa-county-graphite-plant/); EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
+          <t>[Yellowhammer News](https://yellowhammernews.com/trump-administration-announces-25-million-exim-loan-for-westwaters-coosa-county-graphite-plant/); [EXIM.GOV](https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6685,7 +6792,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable); SME (https://me.smenet.org/trump-administration-to-back-three-mineral-projects-with-58-million-in-financing/)</t>
+          <t>[EXIM.GOV](https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable); [SME](https://me.smenet.org/trump-administration-to-back-three-mineral-projects-with-58-million-in-financing/)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6722,7 +6829,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>EXIM.GOV (https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
+          <t>[EXIM.GOV](https://www.exim.gov/news/trump-administration-announces-58m-major-new-critical-mineral-deals-white-house-roundtable)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6759,7 +6866,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/ramaco-resources-releases-hatch-report-and-shareholder-letter-on-exploratory-brook-mine-critical-minerals-project-302838319.html); Mining.com (https://www.mining.com/ramaco-eyes-ree-stockpile-at-wyoming-mine/)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/ramaco-resources-releases-hatch-report-and-shareholder-letter-on-exploratory-brook-mine-critical-minerals-project-302838319.html); [Mining.com](https://www.mining.com/ramaco-eyes-ree-stockpile-at-wyoming-mine/)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6796,12 +6903,86 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/encore-energy-receives-bureau-of-land-management-authorization-to-begin-construction-at-dewey-burdock-uranium-project-302804230.html); Federal Register (https://www.federalregister.gov/documents/2026/08/07/2026-16132/powertech-usa-inc-dewey-burdock-uranium-in-situ-recovery-project-license-renewal)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/encore-energy-receives-bureau-of-land-management-authorization-to-begin-construction-at-dewey-burdock-uranium-project-302804230.html); [Federal Register](https://www.federalregister.gov/documents/2026/08/07/2026-16132/powertech-usa-inc-dewey-burdock-uranium-in-situ-recovery-project-license-renewal)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Niron Magnetics — Planta de Imanes Permanentes sin Tierras Raras</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Minnesota, EE.UU. (ubicación exacta no especificada)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Niron Magnetics</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Financiamiento asegurado (US$150 millones del Departamento de Defensa/Office of Strategic Capital, anunciado 7-8-ago-2026, parte de paquete federal de US$3,000 millones en minerales críticos)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>[MINING.COM](https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/); [CNBC](https://www.cnbc.com/2026/08/08/trump-admin-to-invest-3-billion-in-defense-linked-minerals-projects.html)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Louisiana Strategic Metals Complex</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Alexandria, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ucore Rare Metals Inc.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Construcción (planta de procesamiento de tierras raras medianas/pesadas —terbio/disprosio—)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>[Ucore Rare Metals](https://ucore.com/ucore-readies-for-louisiana-2026-heavy-rare-earth-element-processing/)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6819,47 +7000,47 @@
   <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -6893,7 +7074,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); Construction Owners (https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/vantage-breaks-ground-on-texas-gigawatt-data-center-campus-for-openai/); [Construction Owners](https://www.constructionowners.com/news/oracle-and-openai-to-power-new-texas-data-center-off-the-grid)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6930,7 +7111,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Epoch AI (https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
+          <t>[Epoch AI](https://epoch.ai/publications/openai-stargate-where-the-us-sites-stand)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6967,7 +7148,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/crusoe-tops-out-final-building-at-openai-stargate-data-center-campus-in-abilene-texas/)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7004,7 +7185,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chevron (https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
+          <t>[Chevron](https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7041,7 +7222,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gobierno de México (https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
+          <t>[Gobierno de México](https://www.gob.mx/presidencia/prensa/plan-mexico-avanza-se-anuncia-inversion-de-4-mil-800-mdd-de-cloudhq-para-la-construccion-de-6-centros-de-datos-en-queretaro)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7078,7 +7259,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Global Data Center Hub (https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
+          <t>[Global Data Center Hub](https://www.globaldatacenterhub.com/p/meta-scales-hyperion-to-5gw-and-over)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7115,7 +7296,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55305086/nv1-and-the-nevada-hyperscale-boom-vantage-data-centers-bets-3b-on-the-ai-future)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7152,7 +7333,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cloudburst-breaks-ground-on-gigawatt-scale-data-center-campus-in-texas/)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7189,7 +7370,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/prometheus-hyperscale-details-plans-for-dallas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7226,7 +7407,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Business Wire (https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); Tom's Hardware (https://www.tomshardware.com/tech-industry/data-centers/amazons-new-7-65gw-texas-ai-data-center-power-plant-could-become-the-largest-source-of-co2-pollution-in-the-us-custom-35-turbine-gas-plant-authorized-to-emit-33-million-tons-of-annual-greenhouse-gases)</t>
+          <t>[Business Wire](https://www.businesswire.com/news/home/20260126236053/en/Pacifico-Energy-Secures-7.65-GW-Power-Generation-Permit-for-GW-Ranch-Project); [Tom's Hardware](https://www.tomshardware.com/tech-industry/data-centers/amazons-new-7-65gw-texas-ai-data-center-power-plant-could-become-the-largest-source-of-co2-pollution-in-the-us-custom-35-turbine-gas-plant-authorized-to-emit-33-million-tons-of-annual-greenhouse-gases)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7263,7 +7444,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-looks-to-build-large-scale-data-center-campus-next-to-nuclear-plant-in-texas/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7300,7 +7481,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mexico News Daily (https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); DCD (https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/durango-data-center-fertilizer-plant-investment-fermaca/); [DCD](https://www.datacenterdynamics.com/en/news/250mw-natural-gas-powered-data-center-campus-announced-in-durango-mexico/)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7337,7 +7518,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/circe-energy-secures-2gw-of-natural-gas-capacity-for-west-texas-data-center-campus/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7374,7 +7555,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Source NM (https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
+          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7411,7 +7592,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/powerplay-ai-announces-400-mw-behind-the-meter-ai-data-center-development-in-greater-abilene-with-nasdaq-listed-neocloud-joint-venture-partner-302829610.html)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7448,7 +7629,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/liberty-energy-powerbridge-form-jv-to-power-planned-2gw-data-center-in-west-texas/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7485,7 +7666,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PowerMag (https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
+          <t>[PowerMag](https://www.powermag.com/nuclear-natural-gas-power-generation-planned-for-massive-new-mexico-data-center-site/)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7522,7 +7703,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7559,7 +7740,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7596,7 +7777,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OpenAI (https://openai.com/index/five-new-stargate-sites/)</t>
+          <t>[OpenAI](https://openai.com/index/five-new-stargate-sites/)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7633,7 +7814,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mexico News Daily (https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
+          <t>[Mexico News Daily](https://mexiconewsdaily.com/business/aws-invest-5b-mexico-data-region/)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7670,7 +7851,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/oracle-and-openai-start-construction-on-stargate-data-center-campus-in-saline-township-michigan/)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7707,7 +7888,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Valley News Live (https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
+          <t>[Valley News Live](https://www.valleynewslive.com/2026/07/13/applied-digital-expands-north-dakota-eyes-oliver-county-third-data-center/)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7744,7 +7925,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energy Magazine MX (https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
+          <t>[Energy Magazine MX](https://energymagazine.mx/2026/01/el-data-center-verde-que-encendio-la-polemica-asi-sera-el-proyecto-de-ia-en-nuevo-leon-que-usara-tecnologia-de-nvidia/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7781,7 +7962,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Construction Dive (https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
+          <t>[Construction Dive](https://www.constructiondive.com/news/data-center-cleanarc-breaks-ground-virginia-campus/806489/)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7818,7 +7999,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KSL (https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
+          <t>[KSL](https://www.ksl.com/article/51402125/groundbreaking-for-new-millard-county-artificial-intelligence-data-center)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7855,7 +8036,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Governor.mo.gov (https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
+          <t>[Governor.mo.gov](https://governor.mo.gov/press-releases/archive/amazon-investing-10-billion-montgomery-county)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7892,7 +8073,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>STLPR (https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
+          <t>[STLPR](https://www.stlpr.org/government-politics-issues/2026-05-21/missouri-governor-google-announce-15-billion-data-center-montgomery-county)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7929,7 +8110,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GlobeNewswire (https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/06/3322404/0/en/big-digital-energy-announces-partnership-with-10netzero-to-acquire-power-ready-hood-county-texas-site-for-ai-datacenter-development.html)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7966,7 +8147,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8003,7 +8184,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/meta-files-to-expand-campus-in-el-paso-texas-with-12-new-buildings/)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8040,7 +8221,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); Bloomberg (https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/softbank-eyes-10gw-data-center-at-former-doe-nuclear-enrichment-site-in-ohio/); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-26/nvidia-in-talks-on-250-billion-backing-for-openai-hub-wsj-says)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8077,7 +8258,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8114,7 +8295,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Williams Companies (https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
+          <t>[Williams Companies](https://www.williams.com/2026/07/13/williams-announces-5-34-billion-investment-in-power-innovation-joint-venture-from-blackstone/)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8151,7 +8332,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/cleancore-solutions-zone-announces-closing-of-first-data-center-project-establishing-its-critical-infrastructure-buildout-for-the-ai-economy-302821421.html)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8188,7 +8369,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cowboy State Daily (https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
+          <t>[Cowboy State Daily](https://cowboystatedaily.com/2026/06/11/partner-pulling-out-doesnt-slow-huge-2-7gw-cheyenne-project-jade-data-center/)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8225,7 +8406,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HPCwire (https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
+          <t>[HPCwire](https://www.hpcwire.com/off-the-wire/core-scientific-plans-expansion-to-1-5gw-of-gross-power-at-pecos-texas-campus/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8262,7 +8443,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Utah News Dispatch (https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
+          <t>[Utah News Dispatch](https://utahnewsdispatch.com/2026/05/19/renderings-show-massive-data-center-box-elder-utah-permits-could-take-years/)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -8299,7 +8480,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>StockTitan (https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
+          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8336,7 +8517,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KLTV (https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
+          <t>[KLTV](https://www.kltv.com/2026/03/20/president-trump-approves-16-billion-natural-gas-generator-be-installed-anderson-county/)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8373,7 +8554,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WV MetroNews (https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
+          <t>[WV MetroNews](https://wvmetronews.com/2026/07/16/mon-power-president-says-data-centers-will-end-up-paying-for-natural-gas-powered-power-plant/)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8410,7 +8591,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Utility Dive (https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
+          <t>[Utility Dive](https://www.utilitydive.com/news/iep-plans-944-mw-behind-the-meter-gas-plant-in-pennsylvania-to-power-data-c/758830/)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8447,7 +8628,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wharton Post (https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
+          <t>[Wharton Post](https://whartonpost.com/2026/06/25/amazon-data-center-boling/)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8484,7 +8665,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crusoe (https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
+          <t>[Crusoe](https://www.crusoe.ai/resources/newsroom/crusoe-and-lancium-announce-1-gigawatt-ai-data-center-campus-in-childress-texas)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8521,7 +8702,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/blackstone-invests-534bn-in-williams-behind-the-meter-natural-gas-power-projects-for-the-data-center-sector/)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8558,7 +8739,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PowerMag (https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
+          <t>[PowerMag](https://www.powermag.com/new-200-mw-gas-fired-plant-in-ohio-will-power-meta-data-center/)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8595,7 +8776,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aterio (https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
+          <t>[Aterio](https://www.aterio.io/blog/crusoe-launches-usd29b-goodnight-campus-in-claude-mirroring-openai-s-stargate)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8632,7 +8813,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AJC (https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); Inside Climate News (https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
+          <t>[AJC](https://www.ajc.com/business/2026/07/officials-order-georgia-data-centers-pop-up-power-plant-to-halt-construction/); [Inside Climate News](https://insideclimatenews.org/news/31072026/georgia-data-center-private-power-plant/)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8669,7 +8850,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/stark-power-lands-56gw-data-center-development-portfolio-in-sagebrush-acquisition/)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8706,7 +8887,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Data Center Frontier (https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation); Indiana Gazette (https://www.indianagazette.com/local_news/amazon-hcr-are-conducting-commercial-discussions-on-data-center/article_733afa63-9d58-42d0-b16e-6dc61b71689b.html)</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55281341/pennsylvanias-homer-city-energy-campus-a-brownfield-transformed-for-data-center-innovation); [Indiana Gazette](https://www.indianagazette.com/local_news/amazon-hcr-are-conducting-commercial-discussions-on-data-center/article_733afa63-9d58-42d0-b16e-6dc61b71689b.html)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8743,7 +8924,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8780,7 +8961,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/terravolt-inks-natural-gas-supply-deal-for-onsite-power-plant-at-planned-data-center-campus-in-idaho/)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8817,7 +8998,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/cyrusone-announces-sixth-data-center-campus-in-san-antonio-texas/)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -8854,7 +9035,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); BeBeez (https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/edgeconnex-plans-120mw-gas-plant-to-power-ohio-data-center/); [BeBeez](https://bebeez.eu/2026/04/14/edgeconnex-affiliate-proposes-430mw-natural-gas-plant-to-power-data-center-campus-in-new-albany-ohio/)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8891,7 +9072,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Technology.org (https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); DCD (https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
+          <t>[Technology.org](https://www.technology.org/2026/07/15/xai-59-unpermitted-gas-turbines-southaven-colossus-2/); [DCD](https://www.datacenterdynamics.com/en/news/musks-xai-gets-go-ahead-for-41-natural-gas-turbines-in-mississippi-to-power-colossus-data-centers/)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8928,7 +9109,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Data Center Dynamics (https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/cleco-to-construct-756mw-natural-gas-plant-to-serve-applied-digitals-data-center-in-rapides-parish-louisiana-report/)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8965,7 +9146,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kentucky Lantern (https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
+          <t>[Kentucky Lantern](https://kentuckylantern.com/2026/07/22/developer-proposes-hyperscale-data-center-at-the-site-at-former-eastern-kentucky-steel-mill/)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -9002,7 +9183,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/qts-to-build-11-data-centers-on-lancium-campus-in-hall-county-texas/)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -9039,7 +9220,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); Construction Review (https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); CNBC (https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/600mw-natural-gas-powered-data-center-campus-proposed-in-hubbard-texas/); [Construction Review](https://constructionreviewonline.com/5bn-anthropic-data-center-in-texas-receives-critical-financial-backing-from-google/); [CNBC](https://www.cnbc.com/2026/07/30/nexus-data-centers-in-advanced-talks-to-secure-15b-for-google-backed-anthropic-data-center.html)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -9076,7 +9257,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/gigawatt-scale-data-center-campus-planned-outside-atlanta-georgia/)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -9113,7 +9294,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bloomberg (https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); Kentucky Lantern (https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
+          <t>[Bloomberg](https://www.bloomberg.com/news/articles/2026-07-29/nextera-brookfield-to-build-100-billion-kentucky-data-campus); [Kentucky Lantern](https://kentuckylantern.com/2026/07/29/hyperscale-data-center-natural-gas-fired-project-planned-for-paducahs-former-nuclear-plant/)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -9150,7 +9331,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Axios (https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); DCD (https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
+          <t>[Axios](https://www.axios.com/2026/07/22/openai-savannah-georgia-data-center-project); [DCD](https://www.datacenterdynamics.com/en/news/openai-reveals-32gw-data-center-project-in-effingham-county-georgia/)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -9187,7 +9368,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); Olney Enterprise (https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/developer-proposes-867-acre-project-saltworks-data-center-in-graham-texas/); [Olney Enterprise](https://www.olneyenterprise.com/news/stream-plug-power-deal-moves-young-county-data-center-closer-reality)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9224,7 +9405,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Illinois Times (https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
+          <t>[Illinois Times](https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9261,7 +9442,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KSL (https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); Utah GOED (https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
+          <t>[KSL](https://www.ksl.com/article/51355852/worlds-largest-data-center-campus-could-be-coming-to-central-utah); [Utah GOED](https://business.utah.gov/tax-credits/creekstone-energy-llc-commits-17-billion-to-millard-county-data-center-project/)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9298,7 +9479,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); DCD - Clean Air Act (https://www.datacenterdynamics.com/en/news/amazon-duke-energy-accused-of-evading-clean-air-act-at-under-development-data-center-in-hamlet-north-carolina/); NCSU (https://cnr.ncsu.edu/news/2026/08/richmond-county-data-center-air-pollution/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/amazon-breaks-ground-on-10bn-data-center-complex-in-richmond-county-north-carolina/); [DCD - Clean Air Act](https://www.datacenterdynamics.com/en/news/amazon-duke-energy-accused-of-evading-clean-air-act-at-under-development-data-center-in-hamlet-north-carolina/); [NCSU](https://cnr.ncsu.edu/news/2026/08/richmond-county-data-center-air-pollution/)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9335,7 +9516,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); DCD (https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/160-acre-project-baccara-is-recommended-for-approval-in-maricopa-county-arizona/); [DCD](https://www.datacenterdynamics.com/en/news/two-data-center-projects-proposed-near-phoenix-arizona/)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9372,7 +9553,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); Energy.gov (https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/doe-selects-amentum-dc-blox-to-develop-behind-the-meter-ai-data-center-at-savannah-river-site-in-south-carolina/); [Energy.gov](https://www.energy.gov/nnsa/articles/nnsa-selects-amentum-ai-data-center-and-energy-project-savannah-river-site)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9409,7 +9590,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Community Impact (https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
+          <t>[Community Impact](https://communityimpact.com/bastrop-cedar-creek/business/new-22b-cedar-creek-data-center-project-abatements-under-review/)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9446,7 +9627,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Data Centre Magazine (https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); Connect CRE (https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
+          <t>[Data Centre Magazine](https://datacentremagazine.com/news/ecp-and-kkr-to-build-4bn-190mw-hyperscale-data-centre); [Connect CRE](https://www.connectcre.com/stories/energy-capital-kkr-joint-forces-on-bosque-county-data-center/)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9483,7 +9664,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WLBT (https://www.wlbt.com/2026/05/29/psc-wont-issue-opinion-hypothetical-electrical-plant-proposed-tech-site/)</t>
+          <t>[WLBT](https://www.wlbt.com/2026/05/29/psc-wont-issue-opinion-hypothetical-electrical-plant-proposed-tech-site/)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9520,7 +9701,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/avaio-to-develop-6bn-data-center-campus-in-little-rock-arkansas/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/avaio-to-develop-6bn-data-center-campus-in-little-rock-arkansas/)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -9557,7 +9738,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mississippi Today (https://mississippitoday.org/2026/04/22/ridgeland-data-center-entergy-mississippi-power/)</t>
+          <t>[Mississippi Today](https://mississippitoday.org/2026/04/22/ridgeland-data-center-entergy-mississippi-power/)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -9594,7 +9775,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/red-post-energy-and-wise-innovation-hub-venture-oasis-execute-letter-of-intent-to-advance-power-infrastructure-for-major-data-center-development-in-southwest-virginia-302645511.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/red-post-energy-and-wise-innovation-hub-venture-oasis-execute-letter-of-intent-to-advance-power-infrastructure-for-major-data-center-development-in-southwest-virginia-302645511.html)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9631,7 +9812,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Virginia Mercury (https://virginiamercury.com/2026/07/20/data-centers-want-to-build-their-own-gas-turbines-would-that-skirt-state-renewable-energy-laws/)</t>
+          <t>[Virginia Mercury](https://virginiamercury.com/2026/07/20/data-centers-want-to-build-their-own-gas-turbines-would-that-skirt-state-renewable-energy-laws/)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9668,7 +9849,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>WBOY (https://www.wboy.com/news/tucker/state-board-approves-tucker-county-data-center-air-quality-permit/)</t>
+          <t>[WBOY](https://www.wboy.com/news/tucker/state-board-approves-tucker-county-data-center-air-quality-permit/)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -9705,7 +9886,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DCD (https://www.datacenterdynamics.com/en/news/nextera-teams-up-with-exxonmobil-to-develop-12gw-natural-gas-plant-to-power-us-data-center-sector/)</t>
+          <t>[DCD](https://www.datacenterdynamics.com/en/news/nextera-teams-up-with-exxonmobil-to-develop-12gw-natural-gas-plant-to-power-us-data-center-sector/)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9742,7 +9923,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utility Dive (https://www.utilitydive.com/news/nrg-nears-12-gw-hyperscaler-deal-amid-texas-data-center-pause/827212/)</t>
+          <t>[Utility Dive](https://www.utilitydive.com/news/nrg-nears-12-gw-hyperscaler-deal-amid-texas-data-center-pause/827212/)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9779,7 +9960,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PR Newswire (https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/galaxy-expands-data-center-footprint-with-acquisition-of-500-acre-campus-in-mcgregor-texas-302836014.html)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9816,7 +9997,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>The Nevada Independent (https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
+          <t>[The Nevada Independent](https://thenevadaindependent.com/article/nevada-data-center-rush-drives-request-for-a-novel-type-of-gas-power-plant)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9853,7 +10034,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Angelo Live (https://sanangelolive.com/news/san-angelo/2026-08-10/dove-creek-data-center-has-applied-tceq-permit-heres-what-know); Concho Valley Homepage (https://www.conchovalleyhomepage.com/news/local-news/concho-valley-data-centers/darby-calls-for-clarity-from-beacon-data-centers-requests-public-tceq-meeting/)</t>
+          <t>[San Angelo Live](https://sanangelolive.com/news/san-angelo/2026-08-10/dove-creek-data-center-has-applied-tceq-permit-heres-what-know); [Concho Valley Homepage](https://www.conchovalleyhomepage.com/news/local-news/concho-valley-data-centers/darby-calls-for-clarity-from-beacon-data-centers-requests-public-tceq-meeting/)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9890,7 +10071,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utility Dive (https://www.utilitydive.com/news/ppl-blackstone-joint-venture-secures-5-gw-of-gas-turbines-for-data-centers/827408/); DCD (https://www.datacenterdynamics.com/en/news/pennsylvania-utility-ppl-sees-advanced-stage-data-center-pipeline-grow-to-318gw/)</t>
+          <t>[Utility Dive](https://www.utilitydive.com/news/ppl-blackstone-joint-venture-secures-5-gw-of-gas-turbines-for-data-centers/827408/); [DCD](https://www.datacenterdynamics.com/en/news/pennsylvania-utility-ppl-sees-advanced-stage-data-center-pipeline-grow-to-318gw/)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2238,6 +2238,43 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Eastern Montana Fertilizer Project (planta de urea)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Culbertson, Montana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cyan H2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KBR (MoU: tecnología, ingeniería, procura y gestión de construcción)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Desarrollo/financiamiento (busca cierre de subvención USDA de US$150 millones —vence 17-ago-2026— y préstamo DOE de US$1,000 millones; groundbreaking previsto fin de 2026)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>[Northern Plains Independent](https://www.northernplainsindependent.com/2026/08/13/proposed-fertilizer-plant-making-strides/); [World Fertilizer](https://www.worldfertilizer.com/project-news/26112025/cyan-h2-signs-mou-for-montana-fertilizer-project/)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2795,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Power LNG Ventures, LLC</t>
+          <t>Power LNG Ventures, LLC / Énestas (socio estratégico de capital, ago-2026)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2768,17 +2805,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Permitting temprano (arrendamiento preliminar de 30 acres con Galveston Wharves; solicitud federal de exportación presentada; producción prevista dic-2028)</t>
+          <t>Permitting/pre-FID (Power LNG y Énestas firmaron asociación estratégica 12-ago-2026 —Énestas aporta capital, equipos de transporte/almacenamiento de GNL y arranque de distribución por camión mientras avanza la terminal "Harborside"/Project Seawolf—; terminal valuada en ~US$250 millones; arrendamiento preliminar de 30 acres con Galveston Wharves; solicitud federal de exportación presentada; producción prevista dic-2028)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/)</t>
+          <t>[Houston Public Media](https://www.houstonpublicmedia.org/articles/galveston-county/2026/07/14/557086/galveston-pelican-island-lng/); [LNG Industry](https://www.lngindustry.com/small-scale-lng/13082026/nestas-and-power-lng-establish-strategic-partnership-for-port-of-galveston/)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -4345,17 +4382,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Construcción (corte federal de Idaho negó en jun-2026 moción para detener obras; Export-Import Bank de EE.UU. aprobó en may-2026 préstamo garantizado de USD 2,900 millones, desembolso esperado 2S2026)</t>
+          <t>Construcción (corte federal de Idaho negó en jun-2026 moción para detener obras; Export-Import Bank de EE.UU. aprobó en may-2026 préstamo garantizado de USD 2,900 millones, desembolso esperado 2S2026; nuevos objetivos de exploración de oro/antimonio de alta ley identificados y posible nueva fuente de tungsteno reportados 7-ago-2026)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); [Departamento de Justicia de EE.UU.](https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/perpetua-resources-advances-construction-of-the-stibnite-gold-project-302787012.html); [Departamento de Justicia de EE.UU.](https://www.justice.gov/opa/pr/justice-department-secures-motion-allow-continued-construction-idaho-gold-mine-critical); [StreetWise Reports](https://www.streetwisereports.com/article/2026/08/10/idaho-gold-antimony-project-hits-high-grade-intercepts-at-stibnite.html)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -4789,17 +4826,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Construcción (piloto; primer doré previsto Q4 2026)</t>
+          <t>Construcción (piloto; primer doré previsto Q4 2026; nuevo hallazgo de mineralización aurífera de alta ley reportado 10/12-ago-2026 —215m, incluyendo intervalo de 16.0 g/t Au—)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/)</t>
+          <t>[Resource World](https://resourceworld.com/tocvan-ventures-eyes-mexican-gold-pour-by-q4-2026/); [Minería en Línea](https://mineriaenlinea.com/2026/08/tocvan-descubre-215-metros-de-mineralizacion-aurifera-de-alta-ley-en-gran-pilar-sonora/)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -5233,17 +5270,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental estimado ~US$3,500 millones bajo revisión; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
+          <t>Pre-FID/ingeniería avanzada (estudio para más que duplicar capacidad del concentrador, +200-250 Mlb/año cobre; capex incremental revisado al alza ~30% a ~US$4,500 millones —antes ~US$3,500 millones—, reportado 7/8-ago-2026; US$150M asignados en 2026 para ingeniería y obras tempranas; decisión de inversión esperada 2S-2026)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm)</t>
+          <t>[SEC/Freeport-McMoRan](https://www.sec.gov/Archives/edgar/data/0000831259/000083125926000033/a2q2026exhibit991.htm); [ABC15](https://www.abc15.com/news/business/freeport-mcmoran-eyes-4-5b-expansion-of-arizona-mine-as-investment-decision-looms)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6343,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Construcción/Inicio de operación (planta satélite ISR integrada con Lost Creek; inicio de minado abr-2026; envío de resina cargada a Lost Creek previsto verano 2026)</t>
+          <t>Producción (autorización final del estado de Wyoming para operar a plena producción, reportada 10-ago-2026; planta satélite ISR integrada con Lost Creek; infraestructura de planta y transporte ya en sitio)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[Ur-Energy](https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr)</t>
+          <t>[Ur-Energy](https://www.ur-energy.com/news-media/press-releases/detail/401/ur-energy-commences-operations-at-its-shirley-basin-isr); [Junior Mining Network](https://www.juniorminingnetwork.com/junior-miner-news/press-releases/557-tsx/ure/208831-ur-energy-reports-second-quarter-2026-results.html)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -8470,22 +8507,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas); Energy Transfer (interconexión de gasoducto)</t>
+          <t>Primoris Services Corporation (balance of plant, turbinas de gas); Siemens Energy (suministro de turbinas); Energy Transfer (interconexión de gasoducto); Hillcore Energy Capital (nuevo esquema BOOT "Hillcore Power Center", acuerdo anunciado 11-ago-2026)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW)</t>
+          <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; nuevo acuerdo con Hillcore Energy Capital para "Hillcore Power Center" de ~2.6GW —2.5GW gas natural + 100MW solar/batería—, primer bloque de ~350MW inicia construcción al firmarse acuerdos definitivos, duplicando la generación en sitio a 4.8GW en ~30 meses; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html)</t>
+          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html); [DCD](https://www.datacenterdynamics.com/en/news/fermi-taps-hillcore-to-construct-26gw-gas-plant-for-up-to-11gw-project-matador-in-amarillo-texas/)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -419,13 +419,13 @@
   <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2292,13 +2292,13 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Permitting (FERC exoneró proceso de pre-filing 16-abr-2026; solicitud formal presentada 26-may-2026; Notice of Application publicado 12-jun-2026; 6 bloques de licuefacción adicionales/12 trenes, planta de energía de 720MW, tercer atracadero marino; eleva capacidad pico del complejo de 28 a 35 mtpa)</t>
+          <t>Permitting (FERC exoneró proceso de pre-filing 16-abr-2026; solicitud formal presentada 26-may-2026; Notice of Application publicado 12-jun-2026; FERC abrió formalmente el periodo de scoping NEPA el 17-ago-2026 —Docket CP26-530/533—, con comentario público hasta 11-sep-2026 y sesiones de scoping presenciales en Cameron Parish, LA y Jasper County, TX; 6 bloques de licuefacción adicionales/12 trenes, planta de energía de 720MW, tercer atracadero marino, más ~1,900 MMpc/d de capacidad incremental en el gasoducto CP Express; eleva capacidad pico del complejo de 28 a 35 mtpa)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[Federal Register](https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing)</t>
+          <t>[Federal Register - Notice of Application](https://www.federalregister.gov/documents/2026/06/12/2026-11881/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-application-and-establishing); [Federal Register - Notice of Scoping Period](https://www.federalregister.gov/documents/2026/08/17/2026-16739/venture-global-cp2-lng-llc-venture-global-cp-express-llc-notice-of-scoping-period-requesting)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3906,13 +3906,13 @@
   <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orla Mining Ltd.</t>
+          <t>Equinox Gold Corp. (tras fusión con Orla Mining Ltd.)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Construcción (inicio previsto mediados 2026, pendiente ROD final de BLM)</t>
+          <t>Construcción (BLM emitió Record of Decision positivo el 17-ago-2026, completando el permiso federal NEPA bajo el proceso acelerado FAST-41 —primera mina a cielo abierto procesada bajo este esquema—, habilitando el inicio de construcción; mina de oro/plata a cielo abierto con lixiviación en pilas, ~130,000 oz Au/año promedio en los primeros 5 años; capex inicial ~US$395 millones; ~600 empleos en construcción)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[Orla Mining](https://orlamining.com/news/orla-announces-results-of-updated-feasibility-study-for-south-railroad-project/)</t>
+          <t>[StockTitan/Equinox Gold](https://www.stocktitan.net/news/EQX/equinox-gold-receives-positive-record-of-decision-for-south-railroad-ds4bk9llu3hv.html); [BLM.gov](https://www.blm.gov/announcement/blm-approves-nevada-gold-and-silver-mine-support-american-mineral-production)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7034,16 +7034,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7587,17 +7587,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción activa con riesgo regulatorio (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer, 14-jul-2026; NMED pospuso la decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas y programó audiencia pública para 19-oct-2026; meta de entrada en servicio ago-2026 en riesgo)</t>
+          <t>Construcción activa con retraso regulatorio confirmado (Comisionada de Tierras de NM rechazó por segunda vez el derecho de vía en terrenos estatales para el gasoducto "Green Chile" de Energy Transfer/Transwestern Pipeline, 14-jul-2026; filing regulatorio reportado 14-ago-2026 confirma que la fecha de entrada en servicio del gasoducto —que alimentará hasta 2.5GW de celdas de combustible Bloom Energy— se retrasó de 15-ago-2026 a 1-feb-2027; NMED pospuso decisión final sobre permisos de calidad de aire de las dos plantas de gas gemelas, audiencia pública programada 19-oct-2026; analistas citados advierten riesgo de nuevo retraso a 2S2027)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/)</t>
+          <t>[Source NM](https://sourcenm.com/2026/07/16/new-mexico-land-commissioner-blocks-project-jupiter-related-pipeline-from-building-on-state-land/); [Bloomberg](https://www.bloomberg.com/news/articles/2026-08-14/new-mexico-gas-pipeline-for-oracle-data-center-delayed-to-2027)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -7730,22 +7730,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (carta de acuerdo no vinculante para ~250MW de gen. de gas behind-the-meter)</t>
+          <t>Stream Data Centers (JV vía LOI); Thunderhead Energy Solutions (~250MW de gen. de gas behind-the-meter)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ingeniería Fase Two (438 acres totales; permiso de aire en trámite; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
+          <t>Permisos de construcción obtenidos (New Era Energy &amp; Digital anunció 14-ago-2026, junto con su reporte 10-Q 2T2026, que ya cuenta con los permisos de construcción para TCDC; sitio escalable hacia 1.4GW; construcción total prevista en 2026, primeros 100MW dic-2026)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play)</t>
+          <t>[Data Center Frontier](https://www.datacenterfrontier.com/site-selection/article/55289667/powering-ai-in-the-permian-texas-critical-data-centers-sustainable-energy-play); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/08/14/3345632/0/en/new-era-energy-digital-files-q2-2026-form-10-q-and-announces-tcdc-construction-permits.html)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -10114,6 +10114,43 @@
       <c r="G83" t="inlineStr">
         <is>
           <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Alpha Compute Corp — Campus de Data Center a Gas Natural</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Norte de Pensilvania, EE.UU. (región de gas Marcellus)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Alpha Compute Corp</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pre-construcción (term sheet vinculante firmado 11-ago-2026 para adquirir ~1,800 acres de derechos minerales de petróleo/gas —Formación Marcellus— más activos de superficie/espacio de poro, para desarrollar campus de data center a gas natural behind-the-meter; fase inicial 200MW, expansión potencial a 1GW; precio base de compra US$55 millones; pendiente permisos de PA DEP/Susquehanna River Basin Commission, financiamiento y acuerdos definitivos)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/08/11/3343083/0/en/alpha-compute-signs-binding-term-sheet-for-planned-200-mw-natural-gas-powered-data-center-campus-in-pennsylvania-with-potential-expansion-to-1-gw.html)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -20,10 +20,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -49,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,50 +425,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -816,22 +825,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mota-Engil México (EPC confirmado; plazo de construcción 33 meses)</t>
+          <t>Mota-Engil México (EPC confirmado, US$1,200 millones, 47 meses); Duro Felguera (España) se integró formalmente 17-ago-2026 al contrato para gestión de proyecto y coordinación técnica de la ingeniería (supervisión de ingeniería externa, coordinación de suministros del tecnólogo, gestión de sistemas auxiliares)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones)</t>
+          <t>Ingeniería/inicio de construcción (inversión confirmada US$1,553 millones; capacidad objetivo &gt;700,000 ton/año de amoniaco, urea y AdBlue)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/)</t>
+          <t>[Forbes México](https://forbes.com.mx/asi-es-la-inversion-de-1553-mdd-por-parte-de-pemex-en-una-planta-de-fertilizantes-en-veracruz/); [El Español](https://www.elespanol.com/invertia/empresas/energia/20260817/duro-felguera-convoca-junta-extraordinaria-septiembre-aprobar-proyecto-clave-mota-engil-mexico/1003744355543_0.html)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -1487,17 +1496,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Construcción (ejecución iniciada jun-2026)</t>
+          <t>Construcción con retraso administrativo (obra pausada ~mes y medio por revisión legal/administrativa; Secretario de Desarrollo Económico de Durango confirmó 13-ago-2026 que Semarnat y Profepa no encontraron impedimento, reanudación de obra esperada en 1-2 semanas)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem)</t>
+          <t>[La Jornada](https://www.jornada.com.mx/noticia/2026/06/08/economia/da-inicio-ejecucion-de-planta-de-fertilizantes-en-durango-por-parte-de-fermachem); [Grem Noticieros](https://www.noticierosgrem.com.mx/costruccion-de-fermachem-podria-arrancar-en-dos-semanas-desarrollo-economico-de-durango/)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -2275,6 +2284,80 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Targa Resources — Plantas Wrangler, Ranger y Ranger II (procesamiento de gas)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cuenca Delaware (Permian), Texas, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Targa Resources Corp. (acuerdo de 20 años con subsidiarias de ExxonMobil)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Anuncio/Planeación (anunciado 17-ago-2026; tres nuevas plantas criogénicas con capacidad combinada ~825 MMcf/d, más nuevo gasoducto de ~70 millas "Bull Run II" hacia el hub de Waha; entrada en servicio prevista 1S2028)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>[EnergyNow](https://energynow.com/2026/08/targa-to-build-three-permian-gas-processing-plants-new-pipeline/)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>México Amoníaco y Urea (MAYU)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Costa del Pacífico, Sonora, México (ciudad exacta no especificada)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>México Amoníaco y Urea (desarrollador privado)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Desarrollo muy temprano (planta de amoniaco azul y urea bajo en carbono, capacidad &gt;900,000 ton/año, usando gas natural de la Cuenca Pérmica vía costa del Pacífico; sin autorización de impacto ambiental ni contrato EPC confirmado públicamente a la fecha)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[MAYU](https://mayu.com.mx/en/)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -2292,47 +2375,47 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -2911,22 +2994,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Drydocks World (EPC de barcazas FLNG)</t>
+          <t>Drydocks World (EPC de barcazas FLNG, conversión de FSU y fabricación de barcazas en Dubái)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Construcción (conversión de FSU y fabricación de barcazas en Dubái; operación prevista 2a mitad 2028)</t>
+          <t>Construcción con litigio activo (llegada de primeras piezas modulares al Puerto de Guaymas reportada ago-2026, pese a que un juzgado federal mantiene suspensión definitiva sobre nuevas autorizaciones de impacto ambiental —amparo de Artículo 19 y Nuestro Futuro A.C. por deficiencias en consulta pública—; gobierno de Sonora sostiene que el proyecto ya cuenta con todos los permisos; operación prevista 2a mitad 2028)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html)</t>
+          <t>[PR Newswire](https://www.prnewswire.com/news-releases/amigo-lng-awards-landmark-epc-contract-to-dubai-based-drydocks-world-for-worlds-largest-flng-facility-302537739.html); [Mural Sonorense](https://muralsonorense.com/pese-a-restricciones-legales-avanza-el-proyecto-que-instalaria-la-planta-de-licuefaccion-de-gas-en-guaymas/)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3110,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pre-FID/Retraso legislativo (Cámara de Representantes de Alaska rechazó proyecto de ley de incentivos fiscales HB 381, 16-jul-2026; tercera sesión legislativa especial, convocada por el gobernador Dunleavy, concluyó 13-ago-2026 SIN votación del proyecto de ley de incentivos fiscales necesario para avanzar el financiamiento; incierto si el proyecto avanza antes de que asuman nuevo gobernador/legislatura)</t>
+          <t>Pre-FID/Retraso legislativo persistente (tras el fracaso del HB 381, la coalición mayoritaria de la Cámara de Alaska anunció 13/14-ago-2026 que el nuevo proyecto de ley HB 4001 —exenciones fiscales necesarias para el gasoducto de 20 Mtpa— tampoco tiene los votos para pasar, por diferencias sobre alivio de impuesto predial; gobernador Dunleavy llamó a reconvocar sesión el 20-ago-2026; pese al estancamiento legislativo, avances comerciales recientes incluyen acuerdo de suministro de acero con POSCO vía Glenfarne y acuerdos preliminares de compra con JERA y Tokyo Gas por 2 Mtpa; Glenfarne aún no alcanza el umbral de contratos vinculantes por el 80% de la capacidad)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3037,7 +3120,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -3906,47 +3989,47 @@
   <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -4345,17 +4428,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026, cerrando revisión NEPA de infraestructura en Coronado National Forest; autorización final programada para 4-sep-2026; primer proyecto minero aceptado en programa federal FAST-41; ~50% avance en porción privada; primer concentrado ahora proyectado H1-2028, antes H1-2027)</t>
+          <t>Construcción (Record of Decision final emitido por USFS 7-jul-2026 para infraestructura en Coronado National Forest; ~50% avance en porción privada) / Permitting adicional para desarrollo completo (USFS publicó 15-ago-2026 el Draft EIS y Draft Record of Decision para el desarrollo completo de Hermosa, abriendo periodo de objeción de 45 días seguido de 45 días de resolución; decisión final esperada verano 2026; primer proyecto minero aceptado en programa federal FAST-41; primer concentrado proyectado H1-2028)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); [Bloomberg](https://www.bloomberg.com/news/articles/2026-07-06/south32-s-arizona-zinc-and-manganese-mine-set-to-get-us-approval)</t>
+          <t>[USDA](https://www.usda.gov/about-usda/news/press-releases/2026/07/07/usda-advances-trump-administration-effort-boost-us-mineral-energy-production); [Tucson Sentinel](https://www.tucsonsentinel.com/local/report/030626_hermosa_mine_review/hermosa-mine-hits-milestone-after-forest-service-releases-enviro-review/)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -5307,17 +5390,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; estudio de factibilidad actualizado publicado 11-ago-2026 —VPN8% antes de impuestos US$4,100 millones, capex inicial US$1,850 millones a 35 meses—; avanzando a ingeniería detallada, procura y contratación EPC; proyecto de niobio/escandio/titanio con planta de superficie que requerirá tubería de proceso)</t>
+          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; nuevo Feasibility Study NI 43-101 —publicado 11/15-ago-2026— amplía el proyecto a 8 productos, incluyendo óxidos de disprosio y terbio, VPN8% antes de impuestos US$4,100 millones, vida de mina de 40 años, capex inicial US$1,850 millones a 35 meses; MOU firmado con Lockheed Martin para venta de ~16.5 ton/año de escandio; avanzando a ingeniería detallada, procura y contratación EPC; proyecto de niobio/escandio/titanio/tierras raras con planta de superficie que requerirá tubería de proceso)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); [Mining.com](https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/)</t>
+          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); [Mining.com](https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/); [Daily Political](https://www.dailypolitical.com/2026/08/15/niocorps-elk-creek-study-sees-4-1b-npv-40-year-critical-minerals-mine.html)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -5603,17 +5686,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); aún sin decisión de construcción (FID)</t>
+          <t>Totalmente permisado / consolidación de propiedad (acuerdo de US$4.2 mil millones, cierre previsto 4T2026); estructuración de financiamiento en marcha (NovaGold y Paulson Advisers anunciaron 11-ago-2026 designación de Endeavour Financial y Macquarie Capital como asesores financieros para estructurar el financiamiento del proyecto y su infraestructura, incluyendo gasoducto de 315 millas); aún sin decisión de construcción (FID)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html)</t>
+          <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/07/24/news/donlin-gold-partners-form-new-novagold/9781.html); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/08/11/3343196/0/en/novagold-paulson-announce-the-appointment-of-endeavour-financial-and-macquarie-capital-as-financial-advisors-to-the-donlin-gold-project.html)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -5751,17 +5834,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Construcción/Comisionamiento (primer embarque de concentrado a la fundición Trail de Teck tras 45+ años de cierre; nueva planta de proceso de 1,800 tpd comisionada; planta de relleno en pasta en sitio Wardner sustancialmente completa, comisionamiento final previsto ~3 semanas tras el anuncio; meta de producción comercial plena fin de 2026)</t>
+          <t>Construcción/Comisionamiento avanzado (primera voladura de "stope" de producción anunciada 17-ago-2026; primer embarque de concentrado a la fundición Trail de Teck tras 45+ años de cierre; nueva planta de proceso de 1,800 tpd comisionada; planta de relleno en pasta en sitio Wardner sustancialmente completa; compañía en línea para producción comercial plena en Q4-2026)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html)</t>
+          <t>[GlobeNewswire](https://www.globenewswire.com/news-release/2026/07/31/3337077/0/en/bunker-hill-ships-first-concentrate-to-trail-smelter-and-announces-drawdown-of-standby-facility.html); [GlobeNewswire](https://www.globenewswire.com/news-release/2026/08/17/3345915/0/en/bunker-hill-mining-announces-first-stope-blast-on-track-for-commercial-production-in-q4-2026.html)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -7037,47 +7120,47 @@
   <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cliente/Dueño</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EPC/Contratista</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
@@ -8951,22 +9034,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No especificado — posible cambio de alcance a celdas de combustible Bloom Energy (acuerdo maestro Nebius-Bloom Energy de USD 2,600 millones, 21-may-2026, hasta 328MW; fuentes de menor confianza lo vinculan a Vineland como respuesta a problemas de permisos de aire NJDEP con planta vecina Corning — confirmación directa pendiente)</t>
+          <t>Bloom Energy (celdas de combustible de óxido sólido, 300MW, confirmado en earnings call 2T2026 —12/13-ago-2026—, sustituyendo turbinas de gas para evitar proceso PSD/Clean Air Act)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Construcción/Permisos (planta de gas de hasta 400MW enfrenta retrasos por Ley de Justicia Ambiental de NJ; NJDEP en revisión hacia aprobación final a mediados jul-2026; meta de entrega nov-2026 en riesgo)</t>
+          <t>Construcción con fricción de permisos (ciudad de Vineland emitió orden de "stop-construction" el 10-ago-2026 por instalación de unidades Bloom Energy sin permisos ni planos aprobados; Nebius declaró 13-ago-2026 que el proyecto sigue "on track" pese a la orden)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/)</t>
+          <t>[Data Center Dynamics](https://www.datacenterdynamics.com/en/news/nebius-to-deploy-bloom-energy-fuel-cells-to-power-its-us-data-centers/); [Hunterbrook](https://hntrbrk.com/breaking-news/vineland); [FuelCellsWorks](https://fuelcellsworks.com/2026/08/12/fuel-cells/nebius-says-switch-to-bloom-fuel-cells-strengthens-300mw-new-jersey-ai-data-centre-plan)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -431,9 +431,9 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -978,17 +978,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Construcción parcial/PAUSA parcial (unidad de amoniaco ~95% completa según Presidencia, ago-2026; unidades de urea/metanol y terminal marina PAUSADAS en espera de acuerdo ambiental; gobierno de Sinaloa presentó "Plan Integral" de conservación/desarrollo sostenible de la Bahía de Ohuira, 4-ago-2026, para destrabar continuidad del proyecto)</t>
+          <t>Construcción parcial/PAUSA parcial (unidad de amoniaco ~95% completa según Presidencia, ago-2026, aunque reportes locales citan avance de solo ~60% con obra detenida por bloqueo; movimiento indígena yoreme-mayo "¡Aquí No!" mantiene plantón bloqueando el acceso de personal a la obra desde el 7-jun-2026; GPO ofreció (8/10-ago-2026) pausar formalmente las fases de urea, metanol y terminal marina como condición para levantar el bloqueo; Secretaría de Economía sostuvo reuniones con comunidades de Ohuira, Paredones, Lázaro Cárdenas y Topolobampo presentando el "Plan Integral", pero las comunidades respondieron con desconfianza y mantienen el plantón indefinido)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[Ríodoce](https://riodoce.mx/2026/08/10/pausan-urea-y-metanol-pero-avanza-amoniaco-en-industria-en-la-bahia-de-ohuira/); [Gobierno de Sinaloa](https://sinaloa.gob.mx/presentan-plan-integral-para-la-conservacion-ambiental-el-bienestar-comunitario-y-el-desarrollo-sostenible-de-la-bahia-de-ohuira/)</t>
+          <t>[Ríodoce](https://riodoce.mx/2026/08/10/pausan-urea-y-metanol-pero-avanza-amoniaco-en-industria-en-la-bahia-de-ohuira/); [La Silla Rota](https://lasillarota.com/estados/2026/8/8/planta-de-amoniaco-en-sinaloa-gobierno-busca-luz-verde-al-proyecto-en-ohuira-523789.html); [Gobierno de Sinaloa](https://sinaloa.gob.mx/presentan-plan-integral-para-la-conservacion-ambiental-el-bienestar-comunitario-y-el-desarrollo-sostenible-de-la-bahia-de-ohuira/)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -2378,9 +2378,9 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3986,15 +3986,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ingeniería completada (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año) / construcción prevista H1 2026; EXIM Bank gestiona ahora más de US$1,000 millones en financiamiento, como parte del paquete federal de US$3,000 millones en minerales críticos anunciado 7-8-ago-2026</t>
+          <t>Construcción (PFS define mina subterránea de 20,000 t/d y planta de cátodos de 72,000 t/año; EXIM Bank gestiona más de US$1,000 millones en financiamiento, como parte del paquete federal de US$3,000 millones en minerales críticos anunciado 7-8-ago-2026; Ivanhoe completó el pago final de adquisición de terreno —US$39.3 millones— satisfaciendo el acuerdo de compraventa, y cerró una línea de crédito bancario de US$200 millones para financiar el inicio de actividades mayores de construcción en 2026; primera producción de cobre prevista 2028)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); [MINING.COM](https://www.mining.com/web/trump-says-us-is-announcing-a-series-of-mining-projects-worth-3-billion/)</t>
+          <t>[Mining Weekly](https://www.miningweekly.com/article/ivanhoe-electric-pencils-in-2026-construction-start-at-arizona-copper-mine-2025-06-25); [Ivanhoe Electric](https://ivanhoeelectric.com/news/ivanhoe-electric-makes-final-land-acquisition-payment-at-the-santa-cruz-copper-project-in-arizona/)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -5390,17 +5390,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; nuevo Feasibility Study NI 43-101 —publicado 11/15-ago-2026— amplía el proyecto a 8 productos, incluyendo óxidos de disprosio y terbio, VPN8% antes de impuestos US$4,100 millones, vida de mina de 40 años, capex inicial US$1,850 millones a 35 meses; MOU firmado con Lockheed Martin para venta de ~16.5 ton/año de escandio; avanzando a ingeniería detallada, procura y contratación EPC; proyecto de niobio/escandio/titanio/tierras raras con planta de superficie que requerirá tubería de proceso)</t>
+          <t>Construcción (portal de mina de doble rampa, ~US$44.6 millones, iniciado feb/mar-2026; nuevo Feasibility Study NI 43-101 —publicado 11/15-ago-2026— amplía el proyecto a 8 productos, incluyendo óxidos de disprosio y terbio, VPN8% antes de impuestos US$4,100 millones, vida de mina de 40 años, capex inicial US$1,850 millones a 35 meses; MOU firmado con Lockheed Martin para venta de ~16.5 ton/año de escandio; Departamento de Defensa (programa DPA Title III) otorgó hasta US$10 millones a la subsidiaria Elk Creek Resources Corp. para desarrollo de producción de escandio, ago-2026; avanzando a ingeniería detallada, procura y contratación EPC; proyecto de niobio/escandio/titanio/tierras raras con planta de superficie que requerirá tubería de proceso)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); [Mining.com](https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/); [Daily Political](https://www.dailypolitical.com/2026/08/15/niocorps-elk-creek-study-sees-4-1b-npv-40-year-critical-minerals-mine.html)</t>
+          <t>[NioCorp](https://niocorp.com/niocorp-launches-construction-of-elk-creek-critical-minerals-project-mine-portal/); [Mining.com](https://www.mining.com/updated-feasibility-study-gives-niocorps-elk-creek-critical-minerals-project-a-4b-valuation/); [NioCorp DoD](https://www.niocorp.com/u-s-department-of-defense-awards-up-to-10-million-to-niocorps-subsidiary-elk-creek-resources-corp/)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -7103,6 +7103,191 @@
       <c r="G84" t="inlineStr">
         <is>
           <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Distrito Copper Creek / San Manuel</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Condado de Pinal, Arizona, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Faraday Copper Corp. (adquiriendo la propiedad San Manuel de BHP; BHP recibirá ~30% de acciones de Faraday)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Exploración/definición de recursos (Faraday firmó acuerdo definitivo para comprar la antigua mina San Manuel de BHP —subterránea y de tajo/ISL, operada 1955-1999— y combinarla con su proyecto adyacente Copper Creek, creando un distrito de &gt;18,000 millones de libras de cobre; asamblea de accionistas 25-ago-2026 para aprobar la transacción, cierre esperado 3T2026; plan de 23,000+ metros de perforación de confirmación desde 4T2026, recurso combinado a mediados de 2027)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>[MINING.COM](https://www.mining.com/faraday-targets-18b-lb-arizona-copper-district/)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IMA Mine</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Condado de Lemhi, Idaho, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>American Tungsten Corp.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>No especificado (geotécnica de presas de jales: NewFields MTDs)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Reactivación/pruebas metalúrgicas (mina histórica de tungsteno, produjo WO3 1945-1957; Fase I: reprocesamiento de jales superficiales; Fase II: rehabilitación de mina subterránea; pruebas metalúrgicas iniciadas jul-2026; definición de recursos, permisos y pruebas previstas concluir 4T2026, construcción fin de 2026/1T2027, primera venta de concentrado prevista inicios de 2027)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>[MINING.COM](https://www.mining.com/american-tungsten-kinks-off-construction-at-ima-project-in-idaho/)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Railroad Valley Minerals / Super-Brine Complex</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Railroad Valley, Nevada, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3 Proton Lithium (3PL Operating Inc.)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Exploración avanzada (depósito multi-mineral confirmado: litio, potasa, boro y lo que la empresa describe como el mayor depósito de tungsteno de EE.UU. —~1.78 millones de toneladas, valorado en ~US$152,000 millones in-situ—; ~17 millas cuadradas del área están retiradas de minería desde 2023 por solicitud de la NASA para calibración de satélites, lo que representa un obstáculo regulatorio; sin decisión de construcción)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>[MINING.COM](https://www.mining.com/largest-us-tungsten-discovery-hits-nasa-roadblock/)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>New Amalga Gold Project</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>~25 km al norte de Juneau, Alaska, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Grande Portage Resources Ltd.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Permitting temprano (recurso Indicado de 1.44 millones oz Au a 9.47 g/t e Inferido de 515,700 oz Au; obtuvo estatus de "Covered Project" bajo FAST-41 el 30-jul-2026, acelerando la revisión federal coordinada; quinta mina en Alaska con cobertura FAST-41, junto con Arctic, Johnson Tract, Donlin Gold y Graphite Creek)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>[Mining News North](https://www.miningnewsnorth.com/story/2026/08/07/news/new-amalga-gold-project-enters-fast-41/9803.html)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ElementUSA Gramercy — Planta de Tierras Raras/Minerales Críticos</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gramercy, St. John the Baptist Parish, Luisiana, EE.UU.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ElementUSA Inc. (en colaboración con Colorado School of Mines)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ingeniería/financiamiento asegurado (proyecto de US$850 millones para procesar "lodo rojo"/bauxite residue del antiguo refinerio de alúmina Atalco —~34 millones de toneladas almacenadas— y extraer galio, escandio, disprosio, gadolinio, iterbio, germanio e itrio; recibió US$67 millones del DOE y US$29.9 millones del DoD; construcción de planta de demostración prevista a iniciar mediados de 2027, producción inicial 3T2028)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>[Biz New Orleans](https://bizneworleans.com/elementusa-plans-850m-critical-minerals-refining-facility/); [Colorado School of Mines](https://www.minesnewsroom.com/news/colorado-school-mines-and-elementusa-awarded-67m-doe-construction-rare-earth-processing-plant)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -7117,15 +7302,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -8595,17 +8780,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; nuevo acuerdo con Hillcore Energy Capital para "Hillcore Power Center" de ~2.6GW —2.5GW gas natural + 100MW solar/batería—, primer bloque de ~350MW inicia construcción al firmarse acuerdos definitivos, duplicando la generación en sitio a 4.8GW en ~30 meses; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW)</t>
+          <t>Construcción (movimiento de tierra del campus inicial completo; 4.6 millas de gasoducto de 450 MMcf/d instaladas y conectadas al sistema interestatal de Energy Transfer, suficiente para los primeros 2GW; tubería de agua de 20"/7.2 millas completa; turbinas en sitio/tránsito: 3x GE Frame 6B, 3x Siemens SGT6-5000F, 6x Siemens SGT-800; nuevo acuerdo con Hillcore Energy Capital para "Hillcore Power Center" de ~2.6GW —2.5GW gas natural + 100MW solar/batería—, primer bloque de ~350MW inicia construcción al firmarse acuerdos definitivos, duplicando la generación en sitio a 4.8GW en ~30 meses; Fermi planea solicitar permiso TCEQ adicional por 5GW más, meta total 17GW; primer contrato de arrendamiento vinculante anunciado 10-ago-2026 con TensorWave —~US$6,500 millones a 15 años, instalación de 222MW con derechos de expansión hasta &gt;650MW combinados—; nombramiento 13-ago-2026 de Lee McIntire —ex-Bechtel/TerraPower— como nuevo CEO para liderar transición de desarrollo a construcción, meta de ~200MW de primera energía comercial en 6 meses; ~6GW de los 17GW planeados ya permitidos, &gt;US$1,500 millones invertidos a la fecha)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html); [DCD](https://www.datacenterdynamics.com/en/news/fermi-taps-hillcore-to-construct-26gw-gas-plant-for-up-to-11gw-project-matador-in-amarillo-texas/)</t>
+          <t>[StockTitan](https://www.stocktitan.net/news/FRMI/fermi-america-tells-texas-lawmakers-project-matador-will-push-the-z7wbkjm2tsxy.html); [DCD](https://www.datacenterdynamics.com/en/news/fermi-taps-hillcore-to-construct-26gw-gas-plant-for-up-to-11gw-project-matador-in-amarillo-texas/); [NewsChannel 10](https://www.newschannel10.com/2026/08/10/fermi-america-announces-65-billion-contract-with-tensorwave/); [247wallst](https://247wallst.com/investing/2026/08/13/fermi-lands-its-first-anchor-customer-and-names-a-ceo-as-project-matador-moves-to-construction/)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -10234,6 +10419,43 @@
       <c r="G84" t="inlineStr">
         <is>
           <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Crusoe / Blue Energy — Port of Victoria Campus</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Victoria, Texas, EE.UU. (Puerto de Victoria, campus de ~1,600 acres)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Crusoe (desarrollador/operador del centro de datos de IA); suministro de energía: Blue Energy</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>GE Vernova Hitachi Nuclear Energy (GVH, reactores modulares SMR BWRX-300); GE Vernova (turbinas de gas 7HA.02)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ingeniería/licenciamiento (Blue Energy y GE Vernova Hitachi firmaron acuerdo 13-ago-2026 para lanzar la siguiente fase —ingeniería de diseño, licenciamiento y análisis de seguridad— de una planta híbrida gas+nuclear de 2.5GW; dos turbinas de gas GE Vernova 7HA.02 suministrarían ~1GW como "puente de gas" desde 2030, seguido de hasta 1.5GW adicionales de hasta cinco SMR BWRX-300 desde 2032, para alimentar un campus de centro de datos de Crusoe de hasta 1.5GW; FID prevista 2027)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>[GE Vernova](https://www.gevernova.com/news/press-releases/blue-energy-ge-vernova-hitachi-launch-next-phase-gas-plus-nuclear-project); [DCD](https://www.datacenterdynamics.com/en/news/blue-energy-ge-vernova-hitachi-advance-25gw-gas-plus-nuclear-plant-in-texas-to-power-up-to-15gw-data-center/)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -67,7 +67,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -442,10 +442,10 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2389,10 +2389,10 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3122,17 +3122,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Pre-FID/Retraso legislativo persistente (tras el fracaso del HB 381, la coalición mayoritaria de la Cámara de Alaska anunció 13/14-ago-2026 que el nuevo proyecto de ley HB 4001 —exenciones fiscales necesarias para el gasoducto de 20 Mtpa— tampoco tiene los votos para pasar, por diferencias sobre alivio de impuesto predial; gobernador Dunleavy llamó a reconvocar sesión el 20-ago-2026; pese al estancamiento legislativo, avances comerciales recientes incluyen acuerdo de suministro de acero con POSCO vía Glenfarne y acuerdos preliminares de compra con JERA y Tokyo Gas por 2 Mtpa; Glenfarne aún no alcanza el umbral de contratos vinculantes por el 80% de la capacidad)</t>
+          <t>Pre-FID/Sesión especial legislativa terminó SIN acción (tras el fracaso del HB 381 y luego del HB 4001, el liderazgo del Senado de Alaska decidió no reconvocar la cámara para votar el proyecto de ley de exenciones fiscales de Dunleavy; el propio gobernador señaló 18/19-ago-2026 que ya no hay razón para continuar la tercera sesión especial y que la Legislatura no retomará la legislación fiscal este año, dando por terminado el esfuerzo; Glenfarne declaró que el fracaso del recorte fiscal causará retraso de cronograma y aumento de costos, y que evalúa "rutas alternativas" mientras continúa el trabajo comercial, de ingeniería y financiero para el proyecto completo —incluida la terminal de exportación de LNG—, valuado en hasta US$55,000 millones, con Glenfarne dueño de 75% y Alaska Gasline Development Corp del 25% restante; avances comerciales previos incluyen acuerdo de suministro de acero con POSCO y acuerdos preliminares de compra con JERA y Tokyo Gas por 2 Mtpa)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>[Alaska Beacon](https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/); [Alaska's News Source](https://www.alaskasnewssource.com/2026/08/13/alaska-lng-pipeline-bill-collapses-house-majority-says-it-lacks-votes/)</t>
+          <t>[Alaska Beacon](https://alaskabeacon.com/2026/07/17/hilcorp-killed-alaska-lng-bill-some-legislators-say-but-governor-calls-the-claim-bullst/); [Anchorage Daily News](https://www.adn.com/business-economy/energy/2026/08/19/alaska-lng-developer-looks-for-alternative-paths-after-effort-to-secure-multibillion-dollar-tax-cut-fails/)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -4040,10 +4040,10 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -7393,10 +7393,10 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>

--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -31,25 +31,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -66,8 +60,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -440,16 +434,16 @@
   <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -990,7 +984,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Construcción parcial/PAUSA parcial (unidad de amoniaco ~95% completa según Presidencia, ago-2026, aunque reportes locales citan avance de solo ~60% con obra detenida por bloqueo; movimiento indígena yoreme-mayo "¡Aquí No!" mantiene plantón bloqueando el acceso de personal a la obra desde el 7-jun-2026; GPO ofreció (8/10-ago-2026) pausar formalmente las fases de urea, metanol y terminal marina como condición para levantar el bloqueo; Secretaría de Economía sostuvo reuniones con comunidades de Ohuira, Paredones, Lázaro Cárdenas y Topolobampo presentando el "Plan Integral", pero las comunidades respondieron con desconfianza y mantienen el plantón indefinido)</t>
+          <t>Construcción parcial/PAUSA parcial (unidad de amoniaco ~95% completa según Presidencia, ago-2026 —prensa local cita 88% de avance—, aunque reportes locales previos citaban solo ~60% con obra detenida por bloqueo; movimiento indígena yoreme-mayo "¡Aquí No!" mantiene plantón bloqueando el acceso de personal a la obra desde el 7-jun-2026; GPO ofreció (8/10-ago-2026) pausar formalmente las fases de urea, metanol y terminal marina como condición para levantar el bloqueo; Secretaría de Economía sostuvo reuniones con comunidades de Ohuira, Paredones, Lázaro Cárdenas y Topolobampo presentando el "Plan Integral", pero las comunidades respondieron con desconfianza y mantienen el plantón indefinido)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1000,7 +994,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2322,17 +2316,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Anuncio/Planeación (anunciado 17-ago-2026; tres nuevas plantas criogénicas con capacidad combinada ~825 MMcf/d, más nuevo gasoducto de ~70 millas "Bull Run II" hacia el hub de Waha; entrada en servicio prevista 1S2028)</t>
+          <t>Anuncio/Planeación (anunciado 17-ago-2026; tres nuevas plantas criogénicas con capacidad combinada ~825 MMcf/d, más nuevo gasoducto de ~70 millas "Bull Run II" hacia el hub de Waha; entrada en servicio prevista 1S2028; Targa evalúa además hasta 5 plantas adicionales en Permian Delaware a más largo plazo)</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>[EnergyNow](https://energynow.com/2026/08/targa-to-build-three-permian-gas-processing-plants-new-pipeline/)</t>
+          <t>[EnergyNow](https://energynow.com/2026/08/targa-to-build-three-permian-gas-processing-plants-new-pipeline/); [Targa Resources](https://www.targaresources.com/news-releases/news-release-details/targa-resources-corp-announces-20-year-agreements-exxonmobil-and)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2387,16 +2381,16 @@
   <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -2456,17 +2450,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Construcción (FERC aprobó inicio de construcción de Trenes 4 y 5 en mar-2026; gasoducto de alimentación Rio Bravo Pipeline —138 millas, JV Whitewater/MPLX/Enbridge— en camino a entrar en servicio 2S2026); Train 6 avanza a permitting formal (FERC inició scoping del EIS, solicitud presentada 26-may-2026, sesión de scoping virtual 19-ago-2026, FID prevista 2027; ~6.03 mtpa adicionales, llevando el sitio a 48 mtpa con Trenes 7-8)</t>
+          <t>Construcción (FERC aprobó inicio de construcción de Trenes 4 y 5 en mar-2026; gasoducto de alimentación Rio Bravo Pipeline —138 millas, JV Whitewater/MPLX/Enbridge— en camino a entrar en servicio 2S2026); Train 6 avanza a permitting formal (FERC inició scoping del EIS, solicitud presentada 26-may-2026, sesión de scoping virtual 19-ago-2026, FID prevista 2027; ~6.03 mtpa adicionales, llevando el sitio a 48 mtpa con Trenes 7-8); adicionalmente FERC publicó 19-ago-2026 el calendario de preparación de una Environmental Assessment para la "Rio Grande LNG Capacity Amendment", que alinearía la capacidad aprobada de Trenes 4-5 de 5.4 a ~6.03 mtpa por tren (27.0→~30.15 mtpa); EA programada 25-ago-2026, decisión final 23-nov-2026</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); [Natural Gas Intel](https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/); [Federal Register](https://www.federalregister.gov/documents/2026/08/03/2026-15695/rio-grande-lng-train-6-llc-notice-of-intent-to-prepare-an-environmental-impact-statement-for-the); [LNG Prime](https://lngprime.com/americas/nextdecade-seeks-ferc-ok-for-sixth-rio-grande-lng-train/187820/)</t>
+          <t>[Bechtel](https://www.bechtel.com/press-releases/nextdecade-executes-epc-contract-with-bechtel-for-train-4-at-the-rio-grande-lng-facility/); [Natural Gas Intel](https://naturalgasintel.com/news/nextdecade-targets-more-than-36-mty-with-rio-grande-lng-upscale-sixth-train-expansion/); [Federal Register - Capacity Amendment](https://www.federalregister.gov/documents/2026/08/19/2026-16922); [LNG Prime](https://lngprime.com/americas/nextdecade-seeks-ferc-ok-for-sixth-rio-grande-lng-train/187820/)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2678,17 +2672,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026, y autorizó introducción de gas natural al Train 7, 28-jul-2026; FERC aprobó formalmente la introducción de gas natural al Train 7 —séptimo y último tren de la expansión midscale— el 4-ago-2026; primera producción de LNG esperada ago-2026, servicio comercial sep-2026; Trenes 5 y 6 completados mar/jun-2026; expansión completa de 7 trenes 85.4% de avance, prevista para fin de 2026)</t>
+          <t>Construcción (FERC autorizó introducción de gas combustible en Train 7, 17-jul-2026, y autorizó introducción de gas natural al Train 7, 28-jul-2026; FERC aprobó formalmente la introducción de gas natural al Train 7 —séptimo y último tren de la expansión midscale— el 4-ago-2026; Cheniere completó dos trenes adicionales de licuefacción en Stage 3 a mediados de ago-2026, elevando el avance del proyecto a ~98% completo; Train 7 en fase final de comisionamiento; finalización del build-out de 7 trenes prevista para fin de 2026)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>[PGJ](https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); [LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-expansion-project-85-4-percent-complete/155448/); [energiesmedia](https://energiesmedia.com/ferc-approves-cheniere-train-7-energies/)</t>
+          <t>[PGJ](https://pgjonline.com/news/2026/july/cheniere-gets-approval-to-introduce-gas-into-final-corpus-christi-lng-train); [OGJ](https://www.ogj.com/pipelines-transportation/lng/news/55340460/cheniere-completes-two-more-corpus-christi-stage-3-trains); [LNG Prime](https://lngprime.com/americas/chenieres-corpus-christi-stage-3-project-98-percent-complete/190871/)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4035,19 +4029,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="16"